--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="160">
   <si>
     <t xml:space="preserve">Nagroda Konstela - budżet edycji pierwszej, dwóch sponsorów</t>
   </si>
@@ -31,6 +31,9 @@
     <t xml:space="preserve">Edytuj wyłącznie żółte komórki. Blok A to fundator puli i gali, blok B to partner wydawniczy.</t>
   </si>
   <si>
+    <t xml:space="preserve">Konwencja: wszystkie kwoty są NETTO, chyba że etykieta mówi inaczej. Nagrody podane są BRUTTO, czyli przed potrąceniem 10% podatku.</t>
+  </si>
+  <si>
     <t xml:space="preserve">DŹWIGNIE</t>
   </si>
   <si>
@@ -40,19 +43,19 @@
     <t xml:space="preserve">Wpływa na ocenę formalną i korespondencję. Reszta pracy jest kosztem stałym.</t>
   </si>
   <si>
-    <t xml:space="preserve">Stawka godzinowa organizatora (netto, zł)</t>
+    <t xml:space="preserve">Stawka godzinowa organizatora (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Twoja stawka rynkowa; podstawa wyceny pracy w obu blokach.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nagroda główna (zł)</t>
+    <t xml:space="preserve">Nagroda główna (brutto, przed podatkiem 10%)</t>
   </si>
   <si>
     <t xml:space="preserve">Nike 1997 = 100 tys.; wg indeksu cen ok. 315 tys. w 2026 (Eurostat/FRED).</t>
   </si>
   <si>
-    <t xml:space="preserve">Nagroda dla pozostałych finalistów (zł)</t>
+    <t xml:space="preserve">Nagroda dla pozostałych finalistów (brutto)</t>
   </si>
   <si>
     <t xml:space="preserve">Dziewięć osób z dziesiątki antologii.</t>
@@ -91,12 +94,27 @@
     <t xml:space="preserve">Art. 30 ust. 1 pkt 2 ustawy o PIT; potrącany przy wypłacie.</t>
   </si>
   <si>
+    <t xml:space="preserve">Stawka VAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dotyczy faktur wystawianych sponsorom. Jeśli nie jesteś czynnym podatnikiem VAT, wpisz 0%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeżeli nie jesteś czynnym podatnikiem VAT, koszty twarde wpisuj w kwotach brutto,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bo nie odliczysz od nich podatku, a wtedy są dla Ciebie kosztem w pełnej wysokości.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nakład pracy organizatora z przypisaniem do bloku</t>
   </si>
   <si>
     <t xml:space="preserve">Blok A = nagroda i gala (fundator puli). Blok B = antologia i archiwum (partner wydawniczy).</t>
   </si>
   <si>
+    <t xml:space="preserve">Wycena godzin liczona jest po stawce netto z arkusza Założenia.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pozycja</t>
   </si>
   <si>
@@ -223,13 +241,16 @@
     <t xml:space="preserve">Wydatki pieniężne, poza pracą organizatora.</t>
   </si>
   <si>
-    <t xml:space="preserve">Jednostkowo</t>
+    <t xml:space="preserve">Kwoty netto. Pozycje bez VAT (np. opłaty urzędowe) wpisuj tak samo - różnicę zobaczysz w arkuszu Wnioski.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jednostkowo (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Ilość</t>
   </si>
   <si>
-    <t xml:space="preserve">Razem</t>
+    <t xml:space="preserve">Razem (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Gala: sala, obsługa, poczęstunek</t>
@@ -310,10 +331,13 @@
     <t xml:space="preserve">GitHub Pages i Cloudflare w planach darmowych</t>
   </si>
   <si>
-    <t xml:space="preserve">Koszty twarde blok A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koszty twarde blok B</t>
+    <t xml:space="preserve">Koszty twarde blok A (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koszty twarde blok B (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAZEM (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Pozycje najłatwiejsze do ścięcia w negocjacjach: gala, fotograf, przejazdy - celowo w bloku A,</t>
@@ -331,31 +355,31 @@
     <t xml:space="preserve">BLOK A - FUNDATOR NAGRODY I GALI (np. bank)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pula nagród</t>
+    <t xml:space="preserve">Pula nagród (brutto dla laureatów, bez VAT)</t>
   </si>
   <si>
     <t xml:space="preserve">Nagroda główna plus dziewięć wyróżnień.</t>
   </si>
   <si>
-    <t xml:space="preserve">Oprawa: gala, medal, dyplomy, przejazdy, obsługa prawna</t>
+    <t xml:space="preserve">Oprawa: gala, medal, dyplomy, przejazdy, obsługa prawna (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Koszty twarde przypisane do bloku A.</t>
   </si>
   <si>
-    <t xml:space="preserve">Prowadzenie konkursu: praca organizatora</t>
+    <t xml:space="preserve">Prowadzenie konkursu: praca organizatora (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Godziny bloku A razy stawka.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rezerwa</t>
+    <t xml:space="preserve">Rezerwa (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Narzut na nieprzewidziane, liczony od oprawy i pracy.</t>
   </si>
   <si>
-    <t xml:space="preserve">WNIOSEK A (netto)</t>
+    <t xml:space="preserve">WNIOSEK A - RAZEM NETTO</t>
   </si>
   <si>
     <t xml:space="preserve">Kwota netto; przy banku VAT jest ich realnym kosztem.</t>
@@ -367,61 +391,73 @@
     <t xml:space="preserve">Poniżej 30% rozmowa nie schodzi na wskaźniki.</t>
   </si>
   <si>
-    <t xml:space="preserve">Wniosek A brutto z VAT 23%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banki odliczają VAT w ograniczonym zakresie.</t>
+    <t xml:space="preserve">Wniosek A - VAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przy banku VAT jest w dużej części ich realnym kosztem, bo odliczają go w ograniczonym zakresie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WNIOSEK A - DO ZAPŁATY BRUTTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To jest liczba, którą sponsor widzi na fakturze.</t>
   </si>
   <si>
     <t xml:space="preserve">BLOK B - PARTNER WYDAWNICZY (fundacja korporacyjna, firma technologiczna)</t>
   </si>
   <si>
-    <t xml:space="preserve">Produkcja antologii i archiwum: koszty twarde</t>
+    <t xml:space="preserve">Produkcja antologii i archiwum: koszty twarde (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Koordynator, korekta, skład, druk, ISBN.</t>
   </si>
   <si>
-    <t xml:space="preserve">Redakcja, skład i publikacja: praca organizatora</t>
+    <t xml:space="preserve">Redakcja, skład i publikacja: praca organizatora (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Godziny bloku B razy stawka.</t>
   </si>
   <si>
-    <t xml:space="preserve">Marża</t>
+    <t xml:space="preserve">Marża (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Narzut zgodnie z założeniem w polu B11.</t>
   </si>
   <si>
-    <t xml:space="preserve">WNIOSEK B (netto)</t>
+    <t xml:space="preserve">WNIOSEK B - RAZEM NETTO</t>
   </si>
   <si>
     <t xml:space="preserve">Finansuje nazwany przedmiot: bezpłatną antologię.</t>
   </si>
   <si>
-    <t xml:space="preserve">Wniosek B brutto z VAT 23%</t>
+    <t xml:space="preserve">Wniosek B - VAT</t>
   </si>
   <si>
     <t xml:space="preserve">Zależy od statusu podatkowego partnera.</t>
   </si>
   <si>
+    <t xml:space="preserve">WNIOSEK B - DO ZAPŁATY BRUTTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To jest liczba, którą partner widzi na fakturze.</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAZEM I CO ZOSTAJE ORGANIZATOROWI</t>
   </si>
   <si>
-    <t xml:space="preserve">Oba wnioski netto</t>
+    <t xml:space="preserve">Oba wnioski - razem netto</t>
   </si>
   <si>
     <t xml:space="preserve">Suma obu bloków.</t>
   </si>
   <si>
-    <t xml:space="preserve">Przychód organizatora (bez puli nagród)</t>
+    <t xml:space="preserve">Przychód organizatora netto (bez puli nagród)</t>
   </si>
   <si>
     <t xml:space="preserve">Wszystko poza kwotami wypłacanymi laureatom.</t>
   </si>
   <si>
-    <t xml:space="preserve">minus koszty twarde</t>
+    <t xml:space="preserve">minus koszty twarde (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Wydatki rzeczywiste, w tym koordynator.</t>
@@ -436,7 +472,7 @@
     <t xml:space="preserve">Podatek liniowy i składka zdrowotna</t>
   </si>
   <si>
-    <t xml:space="preserve">ZOSTAJE NETTO</t>
+    <t xml:space="preserve">ZOSTAJE NA RĘKĘ (po podatku i składce)</t>
   </si>
   <si>
     <t xml:space="preserve">Wynagrodzenie za cały nakład pracy przy edycji.</t>
@@ -448,13 +484,13 @@
     <t xml:space="preserve">Z arkusza Praca.</t>
   </si>
   <si>
-    <t xml:space="preserve">STAWKA RZECZYWISTA ZA GODZINĘ</t>
+    <t xml:space="preserve">STAWKA RZECZYWISTA ZA GODZINĘ (na rękę)</t>
   </si>
   <si>
     <t xml:space="preserve">Porównaj ze stawką z pola B6 arkusza Założenia.</t>
   </si>
   <si>
-    <t xml:space="preserve">Podatek od nagród potrącany laureatom</t>
+    <t xml:space="preserve">Podatek od nagród potrącany laureatom (10% z kwot brutto)</t>
   </si>
   <si>
     <t xml:space="preserve">Płatnik odprowadza; nie jest Twoim kosztem.</t>
@@ -622,7 +658,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -639,6 +675,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -664,6 +704,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -728,6 +776,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -995,7 +1055,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50"/>
@@ -1013,121 +1073,147 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7" t="n">
+      <c r="A5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="n">
         <v>150</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>4</v>
+      <c r="C5" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="n">
+      <c r="A6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="10" t="n">
         <v>220</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>6</v>
+      <c r="C6" s="9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="9" t="n">
+      <c r="A7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="10" t="n">
         <v>300000</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>8</v>
+      <c r="C7" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B8" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>12</v>
+      <c r="C9" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="10" t="n">
+      <c r="A10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="11" t="n">
         <v>0.12</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>14</v>
+      <c r="C10" s="9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="10" t="n">
+      <c r="A11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>16</v>
+      <c r="C11" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="10" t="n">
+      <c r="A12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="11" t="n">
         <v>0.19</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>18</v>
+      <c r="C12" s="9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="10" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="10" t="n">
+      <c r="A14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>21</v>
+      <c r="C14" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1157,364 +1243,369 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>28</v>
+      <c r="A4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="7" t="n">
+      <c r="A5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="16" t="n">
         <f aca="false">C5+D5*Założenia!$B$5/60</f>
         <v>60</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="7" t="n">
+      <c r="A6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="16" t="n">
         <f aca="false">C6+D6*Założenia!$B$5/60</f>
         <v>24</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="7" t="n">
+      <c r="A7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="16" t="n">
         <f aca="false">C7+D7*Założenia!$B$5/60</f>
         <v>50</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="16" t="n">
         <f aca="false">C8+D8*Założenia!$B$5/60</f>
         <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="7" t="n">
+      <c r="A9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="16" t="n">
         <f aca="false">C9+D9*Założenia!$B$5/60</f>
         <v>20</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="7" t="n">
+      <c r="A10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="16" t="n">
         <f aca="false">C10+D10*Założenia!$B$5/60</f>
         <v>20</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="7" t="n">
+      <c r="A11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="16" t="n">
         <f aca="false">C11+D11*Założenia!$B$5/60</f>
         <v>40</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="7" t="n">
+      <c r="A12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="16" t="n">
         <f aca="false">C12+D12*Założenia!$B$5/60</f>
         <v>25</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="8" t="n">
         <v>45</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="16" t="n">
         <f aca="false">C13+D13*Założenia!$B$5/60</f>
         <v>45</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="7" t="n">
+      <c r="A14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="16" t="n">
         <f aca="false">C14+D14*Założenia!$B$5/60</f>
         <v>25</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="7" t="n">
+      <c r="A15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="16" t="n">
         <f aca="false">C15+D15*Założenia!$B$5/60</f>
         <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="7" t="n">
+      <c r="A16" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="16" t="n">
         <f aca="false">C16+D16*Założenia!$B$5/60</f>
         <v>45</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="7" t="n">
+      <c r="A17" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="16" t="n">
         <f aca="false">C17+D17*Założenia!$B$5/60</f>
         <v>40</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="7" t="n">
+      <c r="A18" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="16" t="n">
         <f aca="false">C18+D18*Założenia!$B$5/60</f>
         <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="15" t="n">
+      <c r="A20" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="18" t="n">
         <f aca="false">SUMIF($B$5:$B$18,"A",$E$5:$E$18)</f>
         <v>372</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="15" t="n">
+      <c r="A21" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="18" t="n">
         <f aca="false">SUMIF($B$5:$B$18,"B",$E$5:$E$18)</f>
         <v>115</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E22" s="16" t="n">
+      <c r="A22" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="19" t="n">
         <f aca="false">E20+E21</f>
         <v>487</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="E23" s="20" t="n">
         <f aca="false">E22/52</f>
         <v>9.36538461538462</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1545,339 +1636,344 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>68</v>
+      <c r="A4" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="9" t="n">
+      <c r="A5" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>8000</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="21" t="n">
         <f aca="false">C5*D5</f>
         <v>8000</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="9" t="n">
+      <c r="A6" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="10" t="n">
         <v>1500</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="21" t="n">
         <f aca="false">C6*D6</f>
         <v>1500</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="9" t="n">
+      <c r="A7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="10" t="n">
         <v>1200</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="21" t="n">
         <f aca="false">C7*D7</f>
         <v>1200</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="9" t="n">
+      <c r="A8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="10" t="n">
         <v>4000</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="21" t="n">
         <f aca="false">C8*D8</f>
         <v>4000</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="9" t="n">
+      <c r="A9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>6000</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="21" t="n">
         <f aca="false">C9*D9</f>
         <v>6000</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="9" t="n">
+      <c r="A10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="10" t="n">
         <v>1500</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="21" t="n">
         <f aca="false">C10*D10</f>
         <v>1500</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="9" t="n">
+      <c r="A11" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>250</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="21" t="n">
         <f aca="false">C11*D11</f>
         <v>250</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="9" t="n">
+      <c r="A12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="10" t="n">
         <v>18000</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="21" t="n">
         <f aca="false">C12*D12</f>
         <v>18000</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="9" t="n">
+      <c r="A13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="10" t="n">
         <v>4000</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="21" t="n">
         <f aca="false">C13*D13</f>
         <v>4000</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="9" t="n">
+      <c r="A14" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="21" t="n">
         <f aca="false">C14*D14</f>
         <v>3000</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="9" t="n">
+      <c r="A15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="10" t="n">
         <v>1200</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="21" t="n">
         <f aca="false">C15*D15</f>
         <v>1200</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="9" t="n">
+      <c r="A16" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="21" t="n">
         <f aca="false">C16*D16</f>
         <v>0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="9" t="n">
+      <c r="A17" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="21" t="n">
         <f aca="false">C17*D17</f>
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="19" t="n">
+      <c r="A19" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="22" t="n">
         <f aca="false">SUMIF($B$5:$B$17,"A",$E$5:$E$17)</f>
         <v>22450</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" s="19" t="n">
+      <c r="A20" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="22" t="n">
         <f aca="false">SUMIF($B$5:$B$17,"B",$E$5:$E$17)</f>
         <v>26200</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="20" t="n">
+      <c r="A21" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="23" t="n">
         <f aca="false">E19+E20</f>
         <v>48650</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1906,300 +2002,324 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
+      <c r="A4" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" s="23" t="n">
+      <c r="A5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="26" t="n">
         <f aca="false">Założenia!$B$7+Założenia!$B$8*Założenia!$B$9</f>
         <v>390000</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>103</v>
+      <c r="C5" s="9" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" s="23" t="n">
+      <c r="A6" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="26" t="n">
         <f aca="false">Koszty!$E$19</f>
         <v>22450</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>105</v>
+      <c r="C6" s="9" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="23" t="n">
+      <c r="A7" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="26" t="n">
         <f aca="false">Praca!$E$20*Założenia!$B$6</f>
         <v>81840</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>107</v>
+      <c r="C7" s="9" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="23" t="n">
+      <c r="A8" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="26" t="n">
         <f aca="false">(B6+B7)*Założenia!$B$10</f>
         <v>12514.8</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>109</v>
+      <c r="C8" s="9" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="25" t="n">
+      <c r="A9" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="28" t="n">
         <f aca="false">SUM(B5:B8)</f>
         <v>506804.8</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>111</v>
+      <c r="C9" s="9" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="26" t="n">
+      <c r="A10" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="29" t="n">
         <f aca="false">(B9-B5)/B9</f>
         <v>0.230472955267985</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>113</v>
+      <c r="C10" s="9" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="23" t="n">
-        <f aca="false">B9*1.23</f>
+      <c r="A11" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="26" t="n">
+        <f aca="false">B9*Założenia!$B$15</f>
+        <v>116565.104</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="31" t="n">
+        <f aca="false">B9+B11</f>
         <v>623369.904</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>115</v>
+      <c r="C12" s="32" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
+      <c r="A13" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B14" s="23" t="n">
+      <c r="A14" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="26" t="n">
         <f aca="false">Koszty!$E$20</f>
         <v>26200</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>118</v>
+      <c r="C14" s="9" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="23" t="n">
+      <c r="A15" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="26" t="n">
         <f aca="false">Praca!$E$21*Założenia!$B$6</f>
         <v>25300</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>120</v>
+      <c r="C15" s="9" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B16" s="23" t="n">
+      <c r="A16" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="26" t="n">
         <f aca="false">(B14+B15)*Założenia!$B$11</f>
         <v>15450</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>122</v>
+      <c r="C16" s="9" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17" s="25" t="n">
+      <c r="A17" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="28" t="n">
         <f aca="false">SUM(B14:B16)</f>
         <v>66950</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>124</v>
+      <c r="C17" s="9" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B18" s="23" t="n">
-        <f aca="false">B17*1.23</f>
+      <c r="A18" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="26" t="n">
+        <f aca="false">B17*Założenia!$B$15</f>
+        <v>15398.5</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19" s="31" t="n">
+        <f aca="false">B17+B18</f>
         <v>82348.5</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>126</v>
+      <c r="C19" s="32" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
+      <c r="A20" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="B21" s="25" t="n">
+      <c r="A21" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="28" t="n">
         <f aca="false">Wnioski!$B$9+Wnioski!$B$17</f>
         <v>573754.8</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>129</v>
+      <c r="C21" s="9" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B22" s="23" t="n">
+      <c r="A22" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" s="26" t="n">
         <f aca="false">Wnioski!$B$9-B5+Wnioski!$B$17</f>
         <v>183754.8</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>131</v>
+      <c r="C22" s="9" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B23" s="23" t="n">
+      <c r="A23" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="26" t="n">
         <f aca="false">-(Koszty!$E$19+Koszty!$E$20)</f>
         <v>-48650</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>133</v>
+      <c r="C23" s="9" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B24" s="23" t="n">
+      <c r="A24" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="26" t="n">
         <f aca="false">B22+B23</f>
         <v>135104.8</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>135</v>
+      <c r="C24" s="9" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B25" s="23" t="n">
+      <c r="A25" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="26" t="n">
         <f aca="false">-B24*(Założenia!$B$12+Założenia!$B$13)</f>
         <v>-32290.0472</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>18</v>
+      <c r="C25" s="9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="B26" s="25" t="n">
+      <c r="A26" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="28" t="n">
         <f aca="false">B24+B25</f>
         <v>102814.7528</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>138</v>
+      <c r="C26" s="9" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B27" s="29" t="n">
+      <c r="A27" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="35" t="n">
         <f aca="false">Praca!$E$22</f>
         <v>487</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>140</v>
+      <c r="C27" s="9" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="B28" s="25" t="n">
+      <c r="A28" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" s="28" t="n">
         <f aca="false">IFERROR(B26/B27,0)</f>
         <v>211.118588911704</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>142</v>
+      <c r="C28" s="9" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B29" s="23" t="n">
+      <c r="A29" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" s="26" t="n">
         <f aca="false">B5*Założenia!$B$14</f>
         <v>39000</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>144</v>
+      <c r="C29" s="9" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="162">
   <si>
     <t xml:space="preserve">Nagroda Konstela - budżet edycji pierwszej, dwóch sponsorów</t>
   </si>
@@ -313,10 +313,10 @@
     <t xml:space="preserve">szablon plus obsługa wydania</t>
   </si>
   <si>
-    <t xml:space="preserve">Druk 30 egz. dla Akademii, Kapituły, finalistów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z ekslibrisami podpisanymi na gali</t>
+    <t xml:space="preserve">Druk pierwszego nakładu antologii (100 egz.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">egzemplarze dla Kapituły, czytelników, finalistów i partnerów</t>
   </si>
   <si>
     <t xml:space="preserve">ISBN i egzemplarz obowiązkowy</t>
@@ -328,7 +328,13 @@
     <t xml:space="preserve">Hosting, poczta, narzędzia</t>
   </si>
   <si>
-    <t xml:space="preserve">GitHub Pages i Cloudflare w planach darmowych</t>
+    <t xml:space="preserve">domeny, poczta, narzędzia publikacyjne i archiwizujące</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powołanie fundacji-organizatora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notariusz, statut, wpis do KRS, fundusz założycielski</t>
   </si>
   <si>
     <t xml:space="preserve">Koszty twarde blok A (netto)</t>
@@ -409,7 +415,7 @@
     <t xml:space="preserve">Produkcja antologii i archiwum: koszty twarde (netto)</t>
   </si>
   <si>
-    <t xml:space="preserve">Koordynator, korekta, skład, druk, ISBN.</t>
+    <t xml:space="preserve">Koordynator, korekta, skład, druk, hosting, powołanie fundacji.</t>
   </si>
   <si>
     <t xml:space="preserve">Redakcja, skład i publikacja: praca organizatora (netto)</t>
@@ -658,7 +664,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -675,10 +681,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -707,11 +709,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -776,18 +778,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1073,146 +1063,146 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="9" t="n">
         <v>220</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="9" t="n">
         <v>300000</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="10" t="n">
         <v>0.19</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="10" t="n">
         <v>0.049</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="12" t="n">
         <v>0.23</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1251,42 +1241,42 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="15" t="n">
         <f aca="false">C5+D5*Założenia!$B$5/60</f>
         <v>60</v>
       </c>
@@ -1295,19 +1285,19 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="15" t="n">
         <f aca="false">C6+D6*Założenia!$B$5/60</f>
         <v>24</v>
       </c>
@@ -1316,19 +1306,19 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="15" t="n">
         <f aca="false">C7+D7*Założenia!$B$5/60</f>
         <v>50</v>
       </c>
@@ -1337,19 +1327,19 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="15" t="n">
         <f aca="false">C8+D8*Założenia!$B$5/60</f>
         <v>23</v>
       </c>
@@ -1358,19 +1348,19 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="15" t="n">
         <f aca="false">C9+D9*Założenia!$B$5/60</f>
         <v>20</v>
       </c>
@@ -1379,19 +1369,19 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="15" t="n">
         <f aca="false">C10+D10*Założenia!$B$5/60</f>
         <v>20</v>
       </c>
@@ -1400,19 +1390,19 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="15" t="n">
         <f aca="false">C11+D11*Założenia!$B$5/60</f>
         <v>40</v>
       </c>
@@ -1421,19 +1411,19 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="15" t="n">
         <f aca="false">C12+D12*Założenia!$B$5/60</f>
         <v>25</v>
       </c>
@@ -1442,19 +1432,19 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="15" t="n">
         <f aca="false">C13+D13*Założenia!$B$5/60</f>
         <v>45</v>
       </c>
@@ -1463,19 +1453,19 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="15" t="n">
         <f aca="false">C14+D14*Założenia!$B$5/60</f>
         <v>25</v>
       </c>
@@ -1484,19 +1474,19 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="15" t="n">
         <f aca="false">C15+D15*Założenia!$B$5/60</f>
         <v>40</v>
       </c>
@@ -1505,19 +1495,19 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="15" t="n">
         <f aca="false">C16+D16*Założenia!$B$5/60</f>
         <v>45</v>
       </c>
@@ -1526,19 +1516,19 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="15" t="n">
         <f aca="false">C17+D17*Założenia!$B$5/60</f>
         <v>40</v>
       </c>
@@ -1547,19 +1537,19 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="15" t="n">
         <f aca="false">C18+D18*Założenia!$B$5/60</f>
         <v>30</v>
       </c>
@@ -1568,28 +1558,28 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="17" t="n">
         <f aca="false">SUMIF($B$5:$B$18,"A",$E$5:$E$18)</f>
         <v>372</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="17" t="n">
         <f aca="false">SUMIF($B$5:$B$18,"B",$E$5:$E$18)</f>
         <v>115</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="18" t="n">
         <f aca="false">E20+E21</f>
         <v>487</v>
       </c>
@@ -1598,7 +1588,7 @@
       <c r="A23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="19" t="n">
         <f aca="false">E22/52</f>
         <v>9.36538461538462</v>
       </c>
@@ -1644,42 +1634,42 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="9" t="n">
         <v>8000</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="20" t="n">
         <f aca="false">C5*D5</f>
         <v>8000</v>
       </c>
@@ -1688,19 +1678,19 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>1500</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="20" t="n">
         <f aca="false">C6*D6</f>
         <v>1500</v>
       </c>
@@ -1709,19 +1699,19 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="9" t="n">
         <v>1200</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="20" t="n">
         <f aca="false">C7*D7</f>
         <v>1200</v>
       </c>
@@ -1730,19 +1720,19 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="20" t="n">
         <f aca="false">C8*D8</f>
         <v>4000</v>
       </c>
@@ -1751,19 +1741,19 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <v>6000</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="20" t="n">
         <f aca="false">C9*D9</f>
         <v>6000</v>
       </c>
@@ -1772,19 +1762,19 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>1500</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="20" t="n">
         <f aca="false">C10*D10</f>
         <v>1500</v>
       </c>
@@ -1793,19 +1783,19 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="20" t="n">
         <f aca="false">C11*D11</f>
         <v>250</v>
       </c>
@@ -1814,19 +1804,19 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <v>18000</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="20" t="n">
         <f aca="false">C12*D12</f>
         <v>18000</v>
       </c>
@@ -1835,19 +1825,19 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="20" t="n">
         <f aca="false">C13*D13</f>
         <v>4000</v>
       </c>
@@ -1856,19 +1846,19 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="20" t="n">
         <f aca="false">C14*D14</f>
         <v>3000</v>
       </c>
@@ -1877,40 +1867,40 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="10" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D15" s="8" t="n">
+      <c r="C15" s="9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="20" t="n">
         <f aca="false">C15*D15</f>
-        <v>1200</v>
+        <v>4000</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="21" t="n">
+      <c r="E16" s="20" t="n">
         <f aca="false">C16*D16</f>
         <v>0</v>
       </c>
@@ -1919,61 +1909,82 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="8" t="n">
+      <c r="C17" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D17" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="21" t="n">
+      <c r="E17" s="20" t="n">
         <f aca="false">C17*D17</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>101</v>
       </c>
     </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="20" t="n">
+        <f aca="false">C18*D18</f>
+        <v>3000</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="22" t="n">
-        <f aca="false">SUMIF($B$5:$B$17,"A",$E$5:$E$17)</f>
+      <c r="A19" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <f aca="false">SUMIF($B$5:$B$18,"A",$E$5:$E$18)</f>
         <v>22450</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" s="22" t="n">
-        <f aca="false">SUMIF($B$5:$B$17,"B",$E$5:$E$17)</f>
-        <v>26200</v>
+      <c r="A20" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" s="21" t="n">
+        <f aca="false">SUMIF($B$5:$B$18,"B",$E$5:$E$18)</f>
+        <v>33500</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="23" t="n">
+      <c r="A21" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="22" t="n">
         <f aca="false">E19+E20</f>
-        <v>48650</v>
+        <v>55950</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2002,324 +2013,324 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
+      <c r="A4" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="26" t="n">
+      <c r="A5" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="25" t="n">
         <f aca="false">Założenia!$B$7+Założenia!$B$8*Założenia!$B$9</f>
         <v>390000</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>111</v>
+      <c r="C5" s="8" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="26" t="n">
+      <c r="A6" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="25" t="n">
         <f aca="false">Koszty!$E$19</f>
         <v>22450</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>113</v>
+      <c r="C6" s="8" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" s="26" t="n">
+      <c r="A7" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="25" t="n">
         <f aca="false">Praca!$E$20*Założenia!$B$6</f>
         <v>81840</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>115</v>
+      <c r="C7" s="8" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="26" t="n">
+      <c r="A8" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <f aca="false">(B6+B7)*Założenia!$B$10</f>
         <v>12514.8</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>117</v>
+      <c r="C8" s="8" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="28" t="n">
+      <c r="A9" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="27" t="n">
         <f aca="false">SUM(B5:B8)</f>
         <v>506804.8</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>119</v>
+      <c r="C9" s="8" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="29" t="n">
+      <c r="A10" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="28" t="n">
         <f aca="false">(B9-B5)/B9</f>
         <v>0.230472955267985</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>121</v>
+      <c r="C10" s="8" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="26" t="n">
+      <c r="A11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="25" t="n">
         <f aca="false">B9*Założenia!$B$15</f>
         <v>116565.104</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12" s="31" t="n">
+      <c r="C11" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="27" t="n">
         <f aca="false">B9+B11</f>
         <v>623369.904</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>125</v>
+      <c r="C12" s="8" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
+      <c r="A13" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B14" s="26" t="n">
+      <c r="A14" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="25" t="n">
         <f aca="false">Koszty!$E$20</f>
-        <v>26200</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>128</v>
+        <v>33500</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="26" t="n">
+      <c r="A15" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="25" t="n">
         <f aca="false">Praca!$E$21*Założenia!$B$6</f>
         <v>25300</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>130</v>
+      <c r="C15" s="8" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="26" t="n">
+      <c r="A16" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="25" t="n">
         <f aca="false">(B14+B15)*Założenia!$B$11</f>
-        <v>15450</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>132</v>
+        <v>17640</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="B17" s="28" t="n">
+      <c r="A17" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" s="27" t="n">
         <f aca="false">SUM(B14:B16)</f>
-        <v>66950</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>134</v>
+        <v>76440</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B18" s="26" t="n">
+      <c r="A18" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B18" s="25" t="n">
         <f aca="false">B17*Założenia!$B$15</f>
-        <v>15398.5</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="B19" s="31" t="n">
+        <v>17581.2</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" s="27" t="n">
         <f aca="false">B17+B18</f>
-        <v>82348.5</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>138</v>
+        <v>94021.2</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="A20" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="B21" s="28" t="n">
+      <c r="A21" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="27" t="n">
         <f aca="false">Wnioski!$B$9+Wnioski!$B$17</f>
-        <v>573754.8</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>141</v>
+        <v>583244.8</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B22" s="26" t="n">
+      <c r="A22" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" s="25" t="n">
         <f aca="false">Wnioski!$B$9-B5+Wnioski!$B$17</f>
-        <v>183754.8</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>143</v>
+        <v>193244.8</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" s="26" t="n">
+      <c r="A23" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="25" t="n">
         <f aca="false">-(Koszty!$E$19+Koszty!$E$20)</f>
-        <v>-48650</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>145</v>
+        <v>-55950</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B24" s="26" t="n">
+      <c r="A24" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="25" t="n">
         <f aca="false">B22+B23</f>
-        <v>135104.8</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>147</v>
+        <v>137294.8</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B25" s="26" t="n">
+      <c r="A25" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="25" t="n">
         <f aca="false">-B24*(Założenia!$B$12+Założenia!$B$13)</f>
-        <v>-32290.0472</v>
-      </c>
-      <c r="C25" s="9" t="s">
+        <v>-32813.4572</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="B26" s="28" t="n">
+      <c r="A26" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26" s="27" t="n">
         <f aca="false">B24+B25</f>
-        <v>102814.7528</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>150</v>
+        <v>104481.3428</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B27" s="35" t="n">
+      <c r="A27" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" s="31" t="n">
         <f aca="false">Praca!$E$22</f>
         <v>487</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>152</v>
+      <c r="C27" s="8" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" s="28" t="n">
+      <c r="A28" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="27" t="n">
         <f aca="false">IFERROR(B26/B27,0)</f>
-        <v>211.118588911704</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>154</v>
+        <v>214.540744969199</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B29" s="26" t="n">
+      <c r="A29" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" s="25" t="n">
         <f aca="false">B5*Założenia!$B$14</f>
         <v>39000</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>156</v>
+      <c r="C29" s="8" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="172">
   <si>
     <t xml:space="preserve">Nagroda Konstela - budżet edycji pierwszej, dwóch sponsorów</t>
   </si>
@@ -220,6 +220,30 @@
     <t xml:space="preserve">jedna rozmowa na dwa tygodnie</t>
   </si>
   <si>
+    <t xml:space="preserve">Skraper i kopia archiwalna zgłoszenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playwright: PDF, pełny HTML, zrzut, znacznik czasu, suma kontrolna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narzędzie do oceny formalnej</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liczenie słów i wypowiedzi, wykluczanie kodu, język, ciągłość wątku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel oceny dla Akademii i Kapituły</t>
+  </si>
+  <si>
+    <t xml:space="preserve">konta, przydziały, karta oceny, rozbieżności, trzeci odczyt, ślad audytowy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publiczne archiwum rozmów na stronie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generowanie stron z kopii, nawigacja, tryb redakcji fragmentów</t>
+  </si>
+  <si>
     <t xml:space="preserve">Godziny blok A</t>
   </si>
   <si>
@@ -277,12 +301,6 @@
     <t xml:space="preserve">zwrot kosztów</t>
   </si>
   <si>
-    <t xml:space="preserve">Konsultacja prawna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cztery obszary; obowiązkowa przed naborem</t>
-  </si>
-  <si>
     <t xml:space="preserve">Obsługa księgowa projektu</t>
   </si>
   <si>
@@ -295,19 +313,37 @@
     <t xml:space="preserve">opłacone</t>
   </si>
   <si>
-    <t xml:space="preserve">Koordynator na I-III 2028 (zlecenie)</t>
+    <t xml:space="preserve">Powołanie fundacji-organizatora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notariusz, statut, wpis do KRS, fundusz założycielski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsultacja prawna przed otwarciem naboru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sześć obszarów, w tym licencja i archiwum; obowiązkowa przed naborem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domeny, poczta, hosting, narzędzia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infrastruktura publikacyjna i archiwizująca przez cały rok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koordynator wydania I-III 2028 (zlecenie)</t>
   </si>
   <si>
     <t xml:space="preserve">zdejmuje 80-100 h ze szczytu; plan sukcesji</t>
   </si>
   <si>
-    <t xml:space="preserve">Korekta zewnętrzna antologii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">korekta językowa dziesięciu rozmów i not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skład DTP zewnętrzny</t>
+    <t xml:space="preserve">Korekta językowa antologii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">korekta dziesięciu rozmów i not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skład i przygotowanie do druku (DTP)</t>
   </si>
   <si>
     <t xml:space="preserve">szablon plus obsługa wydania</t>
@@ -316,25 +352,19 @@
     <t xml:space="preserve">Druk pierwszego nakładu antologii (100 egz.)</t>
   </si>
   <si>
-    <t xml:space="preserve">egzemplarze dla Kapituły, czytelników, finalistów i partnerów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISBN i egzemplarz obowiązkowy</t>
+    <t xml:space="preserve">z ekslibrisami podpisanymi na gali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadanie ISBN i egzemplarz obowiązkowy</t>
   </si>
   <si>
     <t xml:space="preserve">nadanie bezpłatne</t>
   </si>
   <si>
-    <t xml:space="preserve">Hosting, poczta, narzędzia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">domeny, poczta, narzędzia publikacyjne i archiwizujące</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Powołanie fundacji-organizatora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notariusz, statut, wpis do KRS, fundusz założycielski</t>
+    <t xml:space="preserve">Przebudowa strony: UI/UX i teksty (agencja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projekt i wdrożenie strony Nagrody wraz z copywritingiem</t>
   </si>
   <si>
     <t xml:space="preserve">Koszty twarde blok A (netto)</t>
@@ -421,7 +451,7 @@
     <t xml:space="preserve">Redakcja, skład i publikacja: praca organizatora (netto)</t>
   </si>
   <si>
-    <t xml:space="preserve">Godziny bloku B razy stawka.</t>
+    <t xml:space="preserve">Godziny bloku B razy stawka, w tym 285 h prac programistycznych.</t>
   </si>
   <si>
     <t xml:space="preserve">Marża (netto)</t>
@@ -664,7 +694,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -729,23 +759,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1222,7 +1244,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
@@ -1557,45 +1579,133 @@
         <v>64</v>
       </c>
     </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <f aca="false">C19+D19*Założenia!$B$5/60</f>
+        <v>50</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <f aca="false">SUMIF($B$5:$B$18,"A",$E$5:$E$18)</f>
+      <c r="A20" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <f aca="false">C20+D20*Założenia!$B$5/60</f>
+        <v>25</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <f aca="false">C21+D21*Założenia!$B$5/60</f>
+        <v>160</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <f aca="false">C22+D22*Założenia!$B$5/60</f>
+        <v>50</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3"/>
+      <c r="E23" s="16"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <f aca="false">SUMIF($B$5:$B$22,"A",$E$5:$E$22)</f>
         <v>372</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <f aca="false">SUMIF($B$5:$B$18,"B",$E$5:$E$18)</f>
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <f aca="false">E20+E21</f>
-        <v>487</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="19" t="n">
-        <f aca="false">E22/52</f>
-        <v>9.36538461538462</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>69</v>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <f aca="false">SUMIF($B$5:$B$22,"B",$E$5:$E$22)</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <f aca="false">E25+E26</f>
+        <v>772</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <f aca="false">E27/52</f>
+        <v>14.8461538461538</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1614,7 +1724,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
@@ -1626,17 +1736,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1647,18 +1757,18 @@
         <v>31</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>36</v>
@@ -1669,17 +1779,17 @@
       <c r="D5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="17" t="n">
         <f aca="false">C5*D5</f>
         <v>8000</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>36</v>
@@ -1690,17 +1800,17 @@
       <c r="D6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="17" t="n">
         <f aca="false">C6*D6</f>
         <v>1500</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>36</v>
@@ -1711,17 +1821,17 @@
       <c r="D7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="17" t="n">
         <f aca="false">C7*D7</f>
         <v>1200</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>36</v>
@@ -1732,143 +1842,143 @@
       <c r="D8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="17" t="n">
         <f aca="false">C8*D8</f>
         <v>4000</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="17" t="n">
         <f aca="false">C9*D9</f>
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="17" t="n">
         <f aca="false">C10*D10</f>
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="17" t="n">
         <f aca="false">C11*D11</f>
-        <v>250</v>
+        <v>3000</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="17" t="n">
         <f aca="false">C12*D12</f>
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="17" t="n">
         <f aca="false">C13*D13</f>
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>3000</v>
+        <v>18000</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="17" t="n">
         <f aca="false">C14*D14</f>
-        <v>3000</v>
+        <v>18000</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>59</v>
@@ -1879,112 +1989,134 @@
       <c r="D15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="17" t="n">
         <f aca="false">C15*D15</f>
         <v>4000</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="17" t="n">
         <f aca="false">C16*D16</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E17" s="17" t="n">
         <f aca="false">C17*D17</f>
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="20" t="n">
+      <c r="E18" s="17" t="n">
         <f aca="false">C18*D18</f>
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" s="21" t="n">
-        <f aca="false">SUMIF($B$5:$B$18,"A",$E$5:$E$18)</f>
-        <v>22450</v>
+      <c r="A19" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <f aca="false">C19*D19</f>
+        <v>15000</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="21" t="n">
-        <f aca="false">SUMIF($B$5:$B$18,"B",$E$5:$E$18)</f>
-        <v>33500</v>
+      <c r="A20" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <f aca="false">SUMIF($B$5:$B$19,"A",$E$5:$E$19)</f>
+        <v>16450</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" s="22" t="n">
-        <f aca="false">E19+E20</f>
-        <v>55950</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
+      <c r="A21" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <f aca="false">SUMIF($B$5:$B$19,"B",$E$5:$E$19)</f>
+        <v>54500</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <f aca="false">E20+E21</f>
+        <v>70950</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2013,324 +2145,324 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
+      <c r="A4" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B5" s="25" t="n">
+        <v>122</v>
+      </c>
+      <c r="B5" s="23" t="n">
         <f aca="false">Założenia!$B$7+Założenia!$B$8*Założenia!$B$9</f>
         <v>390000</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="25" t="n">
-        <f aca="false">Koszty!$E$19</f>
-        <v>22450</v>
+        <v>124</v>
+      </c>
+      <c r="B6" s="23" t="n">
+        <f aca="false">Koszty!$E$20</f>
+        <v>16450</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7" s="25" t="n">
-        <f aca="false">Praca!$E$20*Założenia!$B$6</f>
+        <v>126</v>
+      </c>
+      <c r="B7" s="23" t="n">
+        <f aca="false">Praca!$E$25*Założenia!$B$6</f>
         <v>81840</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B8" s="25" t="n">
+        <v>128</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <f aca="false">(B6+B7)*Założenia!$B$10</f>
-        <v>12514.8</v>
+        <v>11794.8</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="27" t="n">
+      <c r="A9" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="25" t="n">
         <f aca="false">SUM(B5:B8)</f>
-        <v>506804.8</v>
+        <v>500084.8</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B10" s="28" t="n">
+        <v>132</v>
+      </c>
+      <c r="B10" s="26" t="n">
         <f aca="false">(B9-B5)/B9</f>
-        <v>0.230472955267985</v>
+        <v>0.22013226556776</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B11" s="25" t="n">
+        <v>134</v>
+      </c>
+      <c r="B11" s="23" t="n">
         <f aca="false">B9*Założenia!$B$15</f>
-        <v>116565.104</v>
+        <v>115019.504</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="27" t="n">
+      <c r="A12" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="25" t="n">
         <f aca="false">B9+B11</f>
-        <v>623369.904</v>
+        <v>615104.304</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
+      <c r="A13" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="25" t="n">
-        <f aca="false">Koszty!$E$20</f>
-        <v>33500</v>
+        <v>139</v>
+      </c>
+      <c r="B14" s="23" t="n">
+        <f aca="false">Koszty!$E$21</f>
+        <v>54500</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B15" s="25" t="n">
-        <f aca="false">Praca!$E$21*Założenia!$B$6</f>
-        <v>25300</v>
+        <v>141</v>
+      </c>
+      <c r="B15" s="23" t="n">
+        <f aca="false">Praca!$E$26*Założenia!$B$6</f>
+        <v>88000</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B16" s="25" t="n">
+        <v>143</v>
+      </c>
+      <c r="B16" s="23" t="n">
         <f aca="false">(B14+B15)*Założenia!$B$11</f>
-        <v>17640</v>
+        <v>42750</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="B17" s="27" t="n">
+      <c r="A17" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="25" t="n">
         <f aca="false">SUM(B14:B16)</f>
-        <v>76440</v>
+        <v>185250</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B18" s="25" t="n">
+        <v>147</v>
+      </c>
+      <c r="B18" s="23" t="n">
         <f aca="false">B17*Założenia!$B$15</f>
-        <v>17581.2</v>
+        <v>42607.5</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="B19" s="27" t="n">
+      <c r="A19" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B19" s="25" t="n">
         <f aca="false">B17+B18</f>
-        <v>94021.2</v>
+        <v>227857.5</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="B21" s="27" t="n">
+      <c r="A21" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="25" t="n">
         <f aca="false">Wnioski!$B$9+Wnioski!$B$17</f>
-        <v>583244.8</v>
+        <v>685334.8</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" s="25" t="n">
+        <v>154</v>
+      </c>
+      <c r="B22" s="23" t="n">
         <f aca="false">Wnioski!$B$9-B5+Wnioski!$B$17</f>
-        <v>193244.8</v>
+        <v>295334.8</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="B23" s="25" t="n">
-        <f aca="false">-(Koszty!$E$19+Koszty!$E$20)</f>
-        <v>-55950</v>
+        <v>156</v>
+      </c>
+      <c r="B23" s="23" t="n">
+        <f aca="false">-(Koszty!$E$20+Koszty!$E$21)</f>
+        <v>-70950</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="25" t="n">
+        <v>158</v>
+      </c>
+      <c r="B24" s="23" t="n">
         <f aca="false">B22+B23</f>
-        <v>137294.8</v>
+        <v>224384.8</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B25" s="25" t="n">
+        <v>160</v>
+      </c>
+      <c r="B25" s="23" t="n">
         <f aca="false">-B24*(Założenia!$B$12+Założenia!$B$13)</f>
-        <v>-32813.4572</v>
+        <v>-53627.9672</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B26" s="27" t="n">
+      <c r="A26" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="25" t="n">
         <f aca="false">B24+B25</f>
-        <v>104481.3428</v>
+        <v>170756.8328</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B27" s="31" t="n">
-        <f aca="false">Praca!$E$22</f>
-        <v>487</v>
+        <v>163</v>
+      </c>
+      <c r="B27" s="29" t="n">
+        <f aca="false">Praca!$E$27</f>
+        <v>772</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="B28" s="27" t="n">
+      <c r="A28" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" s="25" t="n">
         <f aca="false">IFERROR(B26/B27,0)</f>
-        <v>214.540744969199</v>
+        <v>221.187607253886</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="B29" s="25" t="n">
+        <v>167</v>
+      </c>
+      <c r="B29" s="23" t="n">
         <f aca="false">B5*Założenia!$B$14</f>
         <v>39000</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Wyjaśnienia" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Budżet N" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Budżet A" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Budżet P" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Budżet Nagrody" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Budżet Antologii" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Budżet Plebiscytu" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Budżet Akademii" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,12 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="226">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
   <si>
-    <t xml:space="preserve">Trzy osobne budżety, bo każdy sponsor finansuje nazwaną rzecz i dostaje osobną fakturę.</t>
+    <t xml:space="preserve">Cztery osobne budżety, bo każdy sponsor finansuje nazwany zakres, a nie udział w całości.</t>
   </si>
   <si>
     <t xml:space="preserve">ILE I OD KOGO</t>
@@ -43,24 +44,30 @@
     <t xml:space="preserve">Kwota netto</t>
   </si>
   <si>
-    <t xml:space="preserve">Budżet N - Nagroda i gala</t>
+    <t xml:space="preserve">Budżet Nagrody - nagroda i gala</t>
   </si>
   <si>
     <t xml:space="preserve">Fundator puli nagród</t>
   </si>
   <si>
-    <t xml:space="preserve">Budżet A - Antologia i archiwum</t>
+    <t xml:space="preserve">Budżet Antologii - antologia i archiwum</t>
   </si>
   <si>
     <t xml:space="preserve">Partner wydawniczy / sponsor organizacyjny</t>
   </si>
   <si>
-    <t xml:space="preserve">Budżet P - Plebiscyt na piosenkę</t>
+    <t xml:space="preserve">Budżet Plebiscytu - plebiscyt na piosenkę</t>
   </si>
   <si>
     <t xml:space="preserve">Sponsor plebiscytu</t>
   </si>
   <si>
+    <t xml:space="preserve">Budżet Akademii - pierwsza runda oceny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sponsor Akademii (np. sieć handlowa - vouchery)</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAZEM</t>
   </si>
   <si>
@@ -142,19 +149,19 @@
     <t xml:space="preserve">Propozycja, do potwierdzenia.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rezerwa w budżecie N</t>
+    <t xml:space="preserve">Rezerwa w Budżecie Nagrody</t>
   </si>
   <si>
     <t xml:space="preserve">Narzut na nieprzewidziane.</t>
   </si>
   <si>
-    <t xml:space="preserve">Marża w budżecie A</t>
+    <t xml:space="preserve">Marża w Budżecie Antologii</t>
   </si>
   <si>
     <t xml:space="preserve">Narzut partnera wydawniczego.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rezerwa w budżecie P</t>
+    <t xml:space="preserve">Rezerwa w Budżecie Plebiscytu</t>
   </si>
   <si>
     <t xml:space="preserve">Stawka VAT</t>
@@ -181,21 +188,51 @@
     <t xml:space="preserve">Realizacja części artystycznej gali</t>
   </si>
   <si>
-    <t xml:space="preserve">stoi na zerze - zależy od miejsca gali, które nie jest wybrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Po wpisaniu obu kwota budżetu P wzrośnie.</t>
+    <t xml:space="preserve">Po wpisaniu obu kwota Budżetu Plebiscytu wzrośnie.</t>
   </si>
   <si>
     <t xml:space="preserve">JAK CZYTAĆ BUDŻETY</t>
   </si>
   <si>
-    <t xml:space="preserve">Każda z trzech zakładek ma ten sam układ: praca organizatora, koszty twarde, podsumowanie.</t>
+    <t xml:space="preserve">Każda z zakładek budżetowych ma ten sam układ: praca organizatora, koszty twarde, podsumowanie.</t>
   </si>
   <si>
     <t xml:space="preserve">W podsumowaniu jest kwota netto, VAT i kwota brutto, którą sponsor widzi na fakturze.</t>
   </si>
   <si>
+    <t xml:space="preserve">AKADEMIA - PARAMETRY SKALOWANIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odczytów na jedno zgłoszenie w rundzie pierwszej</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulamin § 8: co najmniej dwóch czytelników przy 21-60 zgłoszeniach; powyżej 200 przesiew jednoosobowy z drugim odczytem poniżej progu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voucher za każde 100 ocenionych rozmów (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Świadczenie rzeczowe sponsora Akademii. Do ustalenia ze sponsorem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarium podstawowe czytelnika (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przeniesione z Budżetu Nagrody. Voucher jest dodatkiem, nie zamiennikiem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liczba czytelników w pierwszej edycji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maksymalnie 20 zgłoszeń na czytelnika (regulamin § 8).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maksimum zgłoszeń na czytelnika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z regulaminu. Wyznacza, ilu ludzi trzeba przy danym wolumenie.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Finansuje: Fundator puli nagród. Kwoty netto, chyba że napisano inaczej.</t>
   </si>
   <si>
@@ -337,12 +374,15 @@
     <t xml:space="preserve">opłacone</t>
   </si>
   <si>
-    <t xml:space="preserve">Honoraria Akademii i Kapituły</t>
+    <t xml:space="preserve">Honoraria Kapituły</t>
   </si>
   <si>
     <t xml:space="preserve">15 czytelników po 2 500 zł, 4 jurorów po 8 000 zł</t>
   </si>
   <si>
+    <t xml:space="preserve">4 jurorów po 8 000 zł; honoraria Akademii przeniesione do Budżetu Akademii</t>
+  </si>
+  <si>
     <t xml:space="preserve">Promocja naboru</t>
   </si>
   <si>
@@ -572,6 +612,96 @@
   </si>
   <si>
     <t xml:space="preserve">Koszty twarde bez nagród</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finansuje: Sponsor Akademii. Kwoty netto. Vouchery są świadczeniem rzeczowym i rosną wprost z liczbą ocenionych rozmów.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na żółto pola do edycji w zakładce Wyjaśnienia. Praca organizatora przy prowadzeniu Akademii została w Budżecie Nagrody, żeby nie liczyć jej dwa razy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILE ROZMÓW TRZEBA PRZECZYTAĆ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liczba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zgłoszenia do Nagrody</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parametr wspólny dla wszystkich budżetów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odczytów na zgłoszenie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulamin § 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razem odczytów w rundzie pierwszej</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to jest praca, którą finansuje sponsor Akademii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WYNAGRODZENIE CZYTELNIKÓW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stawka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarium podstawowe czytelników</t>
+  </si>
+  <si>
+    <t xml:space="preserve">przeniesione z Budżetu Nagrody</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vouchery za oceniane rozmowy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jeden voucher za każde rozpoczęte 100 odczytów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razem dla czytelników</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa i rozliczenie voucherów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ewidencja, PIT-11 dla czytelników, korespondencja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiały kalibracyjne i szkolenie czytelników</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trzy rozmowy kotwiczne, instrukcja, spotkanie wprowadzające</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wynagrodzenie czytelników</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezerwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAK TO SIĘ SKALUJE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vouchery rosną wprost z liczbą rozmów, więc sponsor płaci za wykonaną pracę, a nie za prognozę. Ludzi trzeba jednak znaleźć osobno: ostatnia kolumna pokazuje, ilu czytelników wymaga dany wolumen przy limicie z regulaminu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zgłoszeń w edycji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odczytów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voucherów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koszt voucherów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potrzebnych czytelników</t>
   </si>
 </sst>
 </file>
@@ -585,7 +715,7 @@
     <numFmt numFmtId="167" formatCode="0%"/>
     <numFmt numFmtId="168" formatCode="0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -645,8 +775,30 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF8A6A23"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Consolas"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -706,7 +858,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -739,8 +891,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -755,19 +919,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -775,11 +959,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1113,8 +1317,8 @@
         <v>7</v>
       </c>
       <c r="C6" s="7" t="n">
-        <f aca="false">'Budżet N'!$D$39</f>
-        <v>603684.8</v>
+        <f aca="false">'Budżet Nagrody'!$D$39</f>
+        <v>561684.8</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -1130,7 +1334,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="7" t="n">
-        <f aca="false">'Budżet A'!$D$35</f>
+        <f aca="false">'Budżet Antologii'!$D$35</f>
         <v>271700</v>
       </c>
       <c r="D7" s="3"/>
@@ -1147,7 +1351,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="7" t="n">
-        <f aca="false">'Budżet P'!$D$30</f>
+        <f aca="false">'Budżet Plebiscytu'!$D$30</f>
         <v>256616</v>
       </c>
       <c r="D8" s="3"/>
@@ -1157,24 +1361,26 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="C9" s="8" t="n">
-        <f aca="false">'Budżet N'!$D$39+'Budżet A'!$D$35+'Budżet P'!$D$30</f>
-        <v>1132000.8</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+        <f aca="false">'Budżet Akademii'!$D$27</f>
+        <v>49280</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
+      <c r="A10" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="C10" s="9" t="n">
+        <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$35+'Budżet Plebiscytu'!$D$30+'Budżet Akademii'!$D$27</f>
+        <v>1139280.8</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1182,11 +1388,9 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1194,11 +1398,11 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="A12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1206,13 +1410,7 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>220</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="3"/>
@@ -1225,10 +1423,10 @@
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>150</v>
-      </c>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="3"/>
@@ -1241,10 +1439,10 @@
       <c r="A15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="9" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="B15" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="3"/>
@@ -1257,10 +1455,10 @@
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="12" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="3"/>
@@ -1273,10 +1471,10 @@
       <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B17" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="3"/>
@@ -1289,10 +1487,10 @@
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="9" t="n">
-        <v>150</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="B18" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="3"/>
@@ -1305,10 +1503,10 @@
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="9" t="n">
-        <v>35000</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="B19" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="3"/>
@@ -1321,10 +1519,10 @@
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="B20" s="12" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="3"/>
@@ -1337,10 +1535,10 @@
       <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="9" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="B21" s="12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="3"/>
@@ -1353,10 +1551,10 @@
       <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="B22" s="12" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="3"/>
@@ -1369,10 +1567,10 @@
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="B23" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="3"/>
@@ -1385,10 +1583,10 @@
       <c r="A24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="B24" s="12" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>38</v>
       </c>
       <c r="D24" s="3"/>
@@ -1401,10 +1599,10 @@
       <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="B25" s="12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>40</v>
       </c>
       <c r="D25" s="3"/>
@@ -1417,10 +1615,10 @@
       <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C26" s="10" t="s">
+      <c r="B26" s="14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>42</v>
       </c>
       <c r="D26" s="3"/>
@@ -1433,11 +1631,11 @@
       <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>40</v>
+      <c r="B27" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1447,13 +1645,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="11" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="C28" s="10" t="s">
         <v>45</v>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1465,10 +1663,10 @@
       <c r="A29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B29" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C29" s="10" t="s">
+      <c r="B29" s="14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>47</v>
       </c>
       <c r="D29" s="3"/>
@@ -1478,9 +1676,15 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
+      <c r="A30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>49</v>
+      </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -1488,11 +1692,9 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -1500,13 +1702,9 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="A32" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -1528,11 +1726,11 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -1540,9 +1738,9 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
+      <c r="A35" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -1550,11 +1748,9 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -1562,11 +1758,11 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -1585,14 +1781,77 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+    </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" s="19" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1705,7 +1964,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1717,7 +1976,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1739,7 +1998,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1751,301 +2010,301 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="13" t="n">
+      <c r="A7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="14" t="n">
-        <f aca="false">B7+C7*Wyjaśnienia!$B$14/60</f>
+      <c r="D7" s="22" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>60</v>
       </c>
-      <c r="E7" s="15" t="n">
-        <f aca="false">D7*Wyjaśnienia!$B$13</f>
+      <c r="E7" s="23" t="n">
+        <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>13200</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>67</v>
+      <c r="F7" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="13" t="n">
+      <c r="A8" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="14" t="n">
-        <f aca="false">B8+C8*Wyjaśnienia!$B$14/60</f>
+      <c r="D8" s="22" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>24</v>
       </c>
-      <c r="E8" s="15" t="n">
-        <f aca="false">D8*Wyjaśnienia!$B$13</f>
+      <c r="E8" s="23" t="n">
+        <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>5280</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>69</v>
+      <c r="F8" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="13" t="n">
+      <c r="A9" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="14" t="n">
-        <f aca="false">B9+C9*Wyjaśnienia!$B$14/60</f>
+      <c r="D9" s="22" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E9" s="15" t="n">
-        <f aca="false">D9*Wyjaśnienia!$B$13</f>
+      <c r="E9" s="23" t="n">
+        <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>71</v>
+      <c r="F9" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="13" t="n">
+      <c r="A10" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="14" t="n">
-        <f aca="false">B10+C10*Wyjaśnienia!$B$14/60</f>
+      <c r="D10" s="22" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>23</v>
       </c>
-      <c r="E10" s="15" t="n">
-        <f aca="false">D10*Wyjaśnienia!$B$13</f>
+      <c r="E10" s="23" t="n">
+        <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>5060</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>73</v>
+      <c r="F10" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="13" t="n">
+      <c r="A11" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="14" t="n">
-        <f aca="false">B11+C11*Wyjaśnienia!$B$14/60</f>
+      <c r="D11" s="22" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E11" s="15" t="n">
-        <f aca="false">D11*Wyjaśnienia!$B$13</f>
+      <c r="E11" s="23" t="n">
+        <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>75</v>
+      <c r="F11" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="13" t="n">
+      <c r="A12" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="14" t="n">
-        <f aca="false">B12+C12*Wyjaśnienia!$B$14/60</f>
+      <c r="D12" s="22" t="n">
+        <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E12" s="15" t="n">
-        <f aca="false">D12*Wyjaśnienia!$B$13</f>
+      <c r="E12" s="23" t="n">
+        <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>77</v>
+      <c r="F12" s="13" t="s">
+        <v>89</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="13" t="n">
+      <c r="A13" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="14" t="n">
-        <f aca="false">B13+C13*Wyjaśnienia!$B$14/60</f>
+      <c r="D13" s="22" t="n">
+        <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E13" s="15" t="n">
-        <f aca="false">D13*Wyjaśnienia!$B$13</f>
+      <c r="E13" s="23" t="n">
+        <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>79</v>
+      <c r="F13" s="13" t="s">
+        <v>91</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="13" t="n">
+      <c r="A14" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="14" t="n">
-        <f aca="false">B14+C14*Wyjaśnienia!$B$14/60</f>
+      <c r="D14" s="22" t="n">
+        <f aca="false">B14+C14*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E14" s="15" t="n">
-        <f aca="false">D14*Wyjaśnienia!$B$13</f>
+      <c r="E14" s="23" t="n">
+        <f aca="false">D14*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>81</v>
+      <c r="F14" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="13" t="n">
+      <c r="A15" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="21" t="n">
         <v>45</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="14" t="n">
-        <f aca="false">B15+C15*Wyjaśnienia!$B$14/60</f>
+      <c r="D15" s="22" t="n">
+        <f aca="false">B15+C15*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E15" s="15" t="n">
-        <f aca="false">D15*Wyjaśnienia!$B$13</f>
+      <c r="E15" s="23" t="n">
+        <f aca="false">D15*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>83</v>
+      <c r="F15" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="13" t="n">
+      <c r="A16" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="14" t="n">
-        <f aca="false">B16+C16*Wyjaśnienia!$B$14/60</f>
+      <c r="D16" s="22" t="n">
+        <f aca="false">B16+C16*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E16" s="15" t="n">
-        <f aca="false">D16*Wyjaśnienia!$B$13</f>
+      <c r="E16" s="23" t="n">
+        <f aca="false">D16*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>85</v>
+      <c r="F16" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="13" t="n">
+      <c r="A17" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="14" t="n">
-        <f aca="false">B17+C17*Wyjaśnienia!$B$14/60</f>
+      <c r="D17" s="22" t="n">
+        <f aca="false">B17+C17*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E17" s="15" t="n">
-        <f aca="false">D17*Wyjaśnienia!$B$13</f>
+      <c r="E17" s="23" t="n">
+        <f aca="false">D17*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>87</v>
+      <c r="F17" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="24" t="n">
         <f aca="false">SUM(D7:D17)</f>
         <v>372</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="9" t="n">
         <f aca="false">SUM(E7:E17)</f>
         <v>81840</v>
       </c>
@@ -2065,7 +2324,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2077,229 +2336,231 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="17" t="n">
+      <c r="A22" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="25" t="n">
         <v>8000</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="23" t="n">
         <f aca="false">B22*C22</f>
         <v>8000</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>93</v>
+      <c r="E22" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="17" t="n">
+      <c r="A23" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="25" t="n">
         <v>1500</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="23" t="n">
         <f aca="false">B23*C23</f>
         <v>1500</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>95</v>
+      <c r="E23" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="17" t="n">
+      <c r="A24" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="25" t="n">
         <v>1200</v>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C24" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="23" t="n">
         <f aca="false">B24*C24</f>
         <v>1200</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>97</v>
+      <c r="E24" s="13" t="s">
+        <v>109</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25" s="17" t="n">
+      <c r="A25" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="25" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="23" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>99</v>
+      <c r="E25" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B26" s="17" t="n">
+      <c r="A26" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="25" t="n">
         <v>1500</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="23" t="n">
         <f aca="false">B26*C26</f>
         <v>1500</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>101</v>
+      <c r="E26" s="13" t="s">
+        <v>113</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B27" s="17" t="n">
+      <c r="A27" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="25" t="n">
         <v>250</v>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="23" t="n">
         <f aca="false">B27*C27</f>
         <v>250</v>
       </c>
-      <c r="E27" s="10" t="s">
-        <v>103</v>
+      <c r="E27" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B28" s="17" t="n">
-        <v>69500</v>
-      </c>
-      <c r="C28" s="13" t="n">
+      <c r="A28" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B28" s="25" t="n">
+        <v>32000</v>
+      </c>
+      <c r="C28" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="23" t="n">
         <f aca="false">B28*C28</f>
-        <v>69500</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>32000</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B29" s="17" t="n">
+      <c r="A29" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" s="25" t="n">
         <v>15000</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="23" t="n">
         <f aca="false">B29*C29</f>
         <v>15000</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>107</v>
+      <c r="E29" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" s="17" t="n">
+      <c r="A30" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" s="25" t="n">
         <v>8000</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C30" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="23" t="n">
         <f aca="false">B30*C30</f>
         <v>8000</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>109</v>
+      <c r="E30" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B31" s="17" t="n">
+      <c r="A31" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="13" t="n">
+      <c r="C31" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D31" s="23" t="n">
         <f aca="false">B31*C31</f>
         <v>0</v>
       </c>
-      <c r="E31" s="10" t="s">
-        <v>111</v>
+      <c r="E31" s="13" t="s">
+        <v>124</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -2307,13 +2568,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="9" t="n">
         <f aca="false">SUM(D22:D31)</f>
-        <v>108950</v>
+        <v>71450</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -2332,7 +2593,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2343,13 +2604,13 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="s">
-        <v>114</v>
+      <c r="A35" s="20" t="s">
+        <v>127</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="15" t="n">
-        <f aca="false">Wyjaśnienia!$B$15+Wyjaśnienia!$B$16*Wyjaśnienia!$B$17</f>
+      <c r="D35" s="23" t="n">
+        <f aca="false">Wyjaśnienia!$B$16+Wyjaśnienia!$B$17*Wyjaśnienia!$B$18</f>
         <v>390000</v>
       </c>
       <c r="E35" s="3"/>
@@ -2358,8 +2619,8 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12" t="s">
-        <v>115</v>
+      <c r="A36" s="20" t="s">
+        <v>128</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2373,14 +2634,14 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
-        <v>116</v>
+      <c r="A37" s="20" t="s">
+        <v>129</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="7" t="n">
         <f aca="false">D32</f>
-        <v>108950</v>
+        <v>71450</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -2388,14 +2649,14 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="s">
-        <v>117</v>
+      <c r="A38" s="20" t="s">
+        <v>130</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="7" t="n">
-        <f aca="false">(D36+D37)*Wyjaśnienia!$B$25</f>
-        <v>22894.8</v>
+        <f aca="false">(D36+D37)*Wyjaśnienia!$B$26</f>
+        <v>18394.8</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2404,13 +2665,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="9" t="n">
         <f aca="false">SUM(D35:D38)</f>
-        <v>603684.8</v>
+        <v>561684.8</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2418,14 +2679,14 @@
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12" t="s">
-        <v>119</v>
+      <c r="A40" s="20" t="s">
+        <v>132</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="7" t="n">
-        <f aca="false">D39*Wyjaśnienia!$B$28</f>
-        <v>138847.504</v>
+        <f aca="false">D39*Wyjaśnienia!$B$29</f>
+        <v>129187.504</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -2434,13 +2695,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="18" t="n">
+      <c r="D41" s="26" t="n">
         <f aca="false">D39+D40</f>
-        <v>742532.304</v>
+        <v>690872.304</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -2560,7 +2821,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2572,7 +2833,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2594,7 +2855,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2606,205 +2867,205 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="13" t="n">
+      <c r="A7" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="21" t="n">
         <v>45</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="14" t="n">
-        <f aca="false">B7+C7*Wyjaśnienia!$B$14/60</f>
+      <c r="D7" s="22" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E7" s="15" t="n">
-        <f aca="false">D7*Wyjaśnienia!$B$13</f>
+      <c r="E7" s="23" t="n">
+        <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>123</v>
+      <c r="F7" s="13" t="s">
+        <v>136</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="13" t="n">
+      <c r="A8" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="14" t="n">
-        <f aca="false">B8+C8*Wyjaśnienia!$B$14/60</f>
+      <c r="D8" s="22" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="15" t="n">
-        <f aca="false">D8*Wyjaśnienia!$B$13</f>
+      <c r="E8" s="23" t="n">
+        <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>125</v>
+      <c r="F8" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="13" t="n">
+      <c r="A9" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="14" t="n">
-        <f aca="false">B9+C9*Wyjaśnienia!$B$14/60</f>
+      <c r="D9" s="22" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="15" t="n">
-        <f aca="false">D9*Wyjaśnienia!$B$13</f>
+      <c r="E9" s="23" t="n">
+        <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>127</v>
+      <c r="F9" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B10" s="13" t="n">
+      <c r="A10" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="14" t="n">
-        <f aca="false">B10+C10*Wyjaśnienia!$B$14/60</f>
+      <c r="D10" s="22" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E10" s="15" t="n">
-        <f aca="false">D10*Wyjaśnienia!$B$13</f>
+      <c r="E10" s="23" t="n">
+        <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>129</v>
+      <c r="F10" s="13" t="s">
+        <v>142</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" s="13" t="n">
+      <c r="A11" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="14" t="n">
-        <f aca="false">B11+C11*Wyjaśnienia!$B$14/60</f>
+      <c r="D11" s="22" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E11" s="15" t="n">
-        <f aca="false">D11*Wyjaśnienia!$B$13</f>
+      <c r="E11" s="23" t="n">
+        <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>131</v>
+      <c r="F11" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="13" t="n">
+      <c r="A12" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="21" t="n">
         <v>160</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="14" t="n">
-        <f aca="false">B12+C12*Wyjaśnienia!$B$14/60</f>
+      <c r="D12" s="22" t="n">
+        <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>160</v>
       </c>
-      <c r="E12" s="15" t="n">
-        <f aca="false">D12*Wyjaśnienia!$B$13</f>
+      <c r="E12" s="23" t="n">
+        <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>35200</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>133</v>
+      <c r="F12" s="13" t="s">
+        <v>146</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="B13" s="13" t="n">
+      <c r="A13" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="14" t="n">
-        <f aca="false">B13+C13*Wyjaśnienia!$B$14/60</f>
+      <c r="D13" s="22" t="n">
+        <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E13" s="15" t="n">
-        <f aca="false">D13*Wyjaśnienia!$B$13</f>
+      <c r="E13" s="23" t="n">
+        <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>135</v>
+      <c r="F13" s="13" t="s">
+        <v>148</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="24" t="n">
         <f aca="false">SUM(D7:D13)</f>
         <v>400</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="9" t="n">
         <f aca="false">SUM(E7:E13)</f>
         <v>88000</v>
       </c>
@@ -2824,7 +3085,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -2836,250 +3097,250 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="B18" s="17" t="n">
+      <c r="A18" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18" s="25" t="n">
         <v>3000</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="23" t="n">
         <f aca="false">B18*C18</f>
         <v>3000</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>137</v>
+      <c r="E18" s="13" t="s">
+        <v>150</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B19" s="17" t="n">
+      <c r="A19" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19" s="25" t="n">
         <v>6000</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="23" t="n">
         <f aca="false">B19*C19</f>
         <v>6000</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>139</v>
+      <c r="E19" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="B20" s="17" t="n">
+      <c r="A20" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="25" t="n">
         <v>10000</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="23" t="n">
         <f aca="false">B20*C20</f>
         <v>10000</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>141</v>
+      <c r="E20" s="13" t="s">
+        <v>154</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="B21" s="17" t="n">
+      <c r="A21" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B21" s="25" t="n">
         <v>40000</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="23" t="n">
         <f aca="false">B21*C21</f>
         <v>40000</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>143</v>
+      <c r="E21" s="13" t="s">
+        <v>156</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" s="17" t="n">
+      <c r="A22" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="25" t="n">
         <v>4000</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="23" t="n">
         <f aca="false">B22*C22</f>
         <v>4000</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>145</v>
+      <c r="E22" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="B23" s="17" t="n">
+      <c r="A23" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="25" t="n">
         <v>3000</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="23" t="n">
         <f aca="false">B23*C23</f>
         <v>3000</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>147</v>
+      <c r="E23" s="13" t="s">
+        <v>160</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="17" t="n">
+      <c r="A24" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="25" t="n">
         <v>4000</v>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C24" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="23" t="n">
         <f aca="false">B24*C24</f>
         <v>4000</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>149</v>
+      <c r="E24" s="13" t="s">
+        <v>162</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B25" s="17" t="n">
+      <c r="A25" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="23" t="n">
         <f aca="false">B25*C25</f>
         <v>0</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>151</v>
+      <c r="E25" s="13" t="s">
+        <v>164</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B26" s="17" t="n">
+      <c r="A26" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="25" t="n">
         <v>15000</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="23" t="n">
         <f aca="false">B26*C26</f>
         <v>15000</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>153</v>
+      <c r="E26" s="13" t="s">
+        <v>166</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="B27" s="17" t="n">
+      <c r="A27" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="B27" s="25" t="n">
         <v>6000</v>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="23" t="n">
         <f aca="false">B27*C27</f>
         <v>6000</v>
       </c>
-      <c r="E27" s="10" t="s">
-        <v>155</v>
+      <c r="E27" s="13" t="s">
+        <v>168</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B28" s="17" t="n">
+      <c r="A28" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="B28" s="25" t="n">
         <v>30000</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C28" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="23" t="n">
         <f aca="false">B28*C28</f>
         <v>30000</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>157</v>
+      <c r="E28" s="13" t="s">
+        <v>170</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -3087,11 +3348,11 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="9" t="n">
         <f aca="false">SUM(D18:D28)</f>
         <v>121000</v>
       </c>
@@ -3112,7 +3373,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -3123,8 +3384,8 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="s">
-        <v>115</v>
+      <c r="A32" s="20" t="s">
+        <v>128</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -3138,8 +3399,8 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12" t="s">
-        <v>116</v>
+      <c r="A33" s="20" t="s">
+        <v>129</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -3153,13 +3414,13 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="s">
-        <v>158</v>
+      <c r="A34" s="20" t="s">
+        <v>171</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="7" t="n">
-        <f aca="false">(D32+D33)*Wyjaśnienia!$B$26</f>
+        <f aca="false">(D32+D33)*Wyjaśnienia!$B$27</f>
         <v>62700</v>
       </c>
       <c r="E34" s="3"/>
@@ -3169,11 +3430,11 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="9" t="n">
         <f aca="false">SUM(D32:D34)</f>
         <v>271700</v>
       </c>
@@ -3183,13 +3444,13 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12" t="s">
-        <v>119</v>
+      <c r="A36" s="20" t="s">
+        <v>132</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="7" t="n">
-        <f aca="false">D35*Wyjaśnienia!$B$28</f>
+        <f aca="false">D35*Wyjaśnienia!$B$29</f>
         <v>62491</v>
       </c>
       <c r="E36" s="3"/>
@@ -3199,11 +3460,11 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="18" t="n">
+      <c r="D37" s="26" t="n">
         <f aca="false">D35+D36</f>
         <v>334191</v>
       </c>
@@ -3329,7 +3590,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3341,7 +3602,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3363,7 +3624,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -3375,157 +3636,157 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="B7" s="13" t="n">
+      <c r="A7" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="14" t="n">
-        <f aca="false">B7+C7*Wyjaśnienia!$B$18/60</f>
+      <c r="D7" s="22" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$19/60</f>
         <v>25</v>
       </c>
-      <c r="E7" s="15" t="n">
-        <f aca="false">D7*Wyjaśnienia!$B$13</f>
+      <c r="E7" s="23" t="n">
+        <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>161</v>
+      <c r="F7" s="13" t="s">
+        <v>174</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B8" s="13" t="n">
+      <c r="A8" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="14" t="n">
-        <f aca="false">B8+C8*Wyjaśnienia!$B$18/60</f>
+      <c r="D8" s="22" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$19/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="15" t="n">
-        <f aca="false">D8*Wyjaśnienia!$B$13</f>
+      <c r="E8" s="23" t="n">
+        <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>163</v>
+      <c r="F8" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="13" t="n">
+      <c r="A9" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="14" t="n">
-        <f aca="false">B9+C9*Wyjaśnienia!$B$18/60</f>
+      <c r="D9" s="22" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$19/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="15" t="n">
-        <f aca="false">D9*Wyjaśnienia!$B$13</f>
+      <c r="E9" s="23" t="n">
+        <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>165</v>
+      <c r="F9" s="13" t="s">
+        <v>178</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" s="13" t="n">
+      <c r="A10" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="14" t="n">
-        <f aca="false">B10+C10*Wyjaśnienia!$B$18/60</f>
+      <c r="D10" s="22" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$19/60</f>
         <v>20</v>
       </c>
-      <c r="E10" s="15" t="n">
-        <f aca="false">D10*Wyjaśnienia!$B$13</f>
+      <c r="E10" s="23" t="n">
+        <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>167</v>
+      <c r="F10" s="13" t="s">
+        <v>180</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="B11" s="13" t="n">
+      <c r="A11" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="14" t="n">
-        <f aca="false">B11+C11*Wyjaśnienia!$B$18/60</f>
+      <c r="D11" s="22" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$19/60</f>
         <v>50</v>
       </c>
-      <c r="E11" s="15" t="n">
-        <f aca="false">D11*Wyjaśnienia!$B$13</f>
+      <c r="E11" s="23" t="n">
+        <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>169</v>
+      <c r="F11" s="13" t="s">
+        <v>182</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="24" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>165</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="9" t="n">
         <f aca="false">SUM(E7:E11)</f>
         <v>36300</v>
       </c>
@@ -3545,7 +3806,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -3557,172 +3818,172 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="B16" s="15" t="n">
-        <f aca="false">Wyjaśnienia!$B$19</f>
+      <c r="A16" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" s="23" t="n">
+        <f aca="false">Wyjaśnienia!$B$20</f>
         <v>35000</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="23" t="n">
         <f aca="false">B16*C16</f>
         <v>35000</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>171</v>
+      <c r="E16" s="13" t="s">
+        <v>184</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B17" s="15" t="n">
-        <f aca="false">Wyjaśnienia!$B$20</f>
+      <c r="A17" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="B17" s="23" t="n">
+        <f aca="false">Wyjaśnienia!$B$21</f>
         <v>4000</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="23" t="n">
         <f aca="false">B17*C17</f>
         <v>4000</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>173</v>
+      <c r="E17" s="13" t="s">
+        <v>186</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B18" s="15" t="n">
-        <f aca="false">Wyjaśnienia!$B$21</f>
+      <c r="A18" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="23" t="n">
+        <f aca="false">Wyjaśnienia!$B$22</f>
         <v>7500</v>
       </c>
-      <c r="C18" s="14" t="n">
-        <f aca="false">Wyjaśnienia!$B$22</f>
+      <c r="C18" s="22" t="n">
+        <f aca="false">Wyjaśnienia!$B$23</f>
         <v>10</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="23" t="n">
         <f aca="false">B18*C18</f>
         <v>75000</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>175</v>
+      <c r="E18" s="13" t="s">
+        <v>188</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="15" t="n">
-        <f aca="false">Wyjaśnienia!$B$23</f>
+      <c r="A19" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="23" t="n">
+        <f aca="false">Wyjaśnienia!$B$24</f>
         <v>80000</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="23" t="n">
         <f aca="false">B19*C19</f>
         <v>80000</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>176</v>
+      <c r="E19" s="13" t="s">
+        <v>189</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="15" t="n">
-        <f aca="false">Wyjaśnienia!$B$24</f>
+      <c r="A20" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="23" t="n">
+        <f aca="false">Wyjaśnienia!$B$25</f>
         <v>3000</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="23" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>177</v>
+      <c r="E20" s="13" t="s">
+        <v>190</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="B21" s="17" t="n">
+      <c r="A21" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="23" t="n">
         <f aca="false">B21*C21</f>
         <v>0</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>179</v>
+      <c r="E21" s="13" t="s">
+        <v>192</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="B22" s="17" t="n">
+      <c r="A22" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="23" t="n">
         <f aca="false">B22*C22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>181</v>
+      <c r="E22" s="13" t="s">
+        <v>194</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -3730,11 +3991,11 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="9" t="n">
         <f aca="false">SUM(D16:D22)</f>
         <v>197000</v>
       </c>
@@ -3755,7 +4016,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -3766,13 +4027,13 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
-        <v>114</v>
+      <c r="A26" s="20" t="s">
+        <v>127</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="15" t="n">
-        <f aca="false">Wyjaśnienia!$B$19+Wyjaśnienia!$B$20</f>
+      <c r="D26" s="23" t="n">
+        <f aca="false">Wyjaśnienia!$B$20+Wyjaśnienia!$B$21</f>
         <v>39000</v>
       </c>
       <c r="E26" s="3"/>
@@ -3781,8 +4042,8 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
-        <v>115</v>
+      <c r="A27" s="20" t="s">
+        <v>128</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -3796,8 +4057,8 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
-        <v>182</v>
+      <c r="A28" s="20" t="s">
+        <v>195</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -3811,13 +4072,13 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
-        <v>117</v>
+      <c r="A29" s="20" t="s">
+        <v>130</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="7" t="n">
-        <f aca="false">(D27+D28)*Wyjaśnienia!$B$27</f>
+        <f aca="false">(D27+D28)*Wyjaśnienia!$B$28</f>
         <v>23316</v>
       </c>
       <c r="E29" s="3"/>
@@ -3827,11 +4088,11 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="9" t="n">
         <f aca="false">SUM(D26:D29)</f>
         <v>256616</v>
       </c>
@@ -3841,13 +4102,13 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
-        <v>119</v>
+      <c r="A31" s="20" t="s">
+        <v>132</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="7" t="n">
-        <f aca="false">D30*Wyjaśnienia!$B$28</f>
+        <f aca="false">D30*Wyjaśnienia!$B$29</f>
         <v>59021.68</v>
       </c>
       <c r="E31" s="3"/>
@@ -3857,11 +4118,11 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="18" t="n">
+      <c r="D32" s="26" t="n">
         <f aca="false">D30+D31</f>
         <v>315637.68</v>
       </c>
@@ -3960,4 +4221,427 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="62"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" s="29" t="n">
+        <f aca="false">Wyjaśnienia!$B$15</f>
+        <v>150</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" s="29" t="n">
+        <f aca="false">Wyjaśnienia!$B$42</f>
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="30" t="n">
+        <f aca="false">B7*B8</f>
+        <v>300</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" s="8" t="n">
+        <f aca="false">Wyjaśnienia!$B$44</f>
+        <v>2500</v>
+      </c>
+      <c r="C13" s="29" t="n">
+        <f aca="false">Wyjaśnienia!$B$45</f>
+        <v>15</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <f aca="false">B13*C13</f>
+        <v>37500</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <f aca="false">Wyjaśnienia!$B$43</f>
+        <v>500</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <f aca="false">ROUNDUP(B9/100,0)</f>
+        <v>3</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <f aca="false">B14*C14</f>
+        <v>1500</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <f aca="false">SUM(D13:D14)</f>
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <f aca="false">B19*C19</f>
+        <v>2000</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <f aca="false">B20*C20</f>
+        <v>3000</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="31" t="n">
+        <f aca="false">SUM(D19:D20)</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <f aca="false">D15</f>
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <f aca="false">D21</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <f aca="false">(D24+D25)*Wyjaśnienia!$B$26</f>
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="31" t="n">
+        <f aca="false">SUM(D24:D26)</f>
+        <v>49280</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <f aca="false">D27*Wyjaśnienia!$B$29</f>
+        <v>11334.4</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="31" t="n">
+        <f aca="false">D27+D28</f>
+        <v>60614.4</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="29" t="n">
+        <v>150</v>
+      </c>
+      <c r="B34" s="29" t="n">
+        <f aca="false">A34*Wyjaśnienia!$B$42</f>
+        <v>300</v>
+      </c>
+      <c r="C34" s="29" t="n">
+        <f aca="false">ROUNDUP(B34/100,0)</f>
+        <v>3</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <f aca="false">C34*Wyjaśnienia!$B$43</f>
+        <v>1500</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <f aca="false">ROUNDUP(A34/Wyjaśnienia!$B$46,0)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B35" s="29" t="n">
+        <f aca="false">A35*Wyjaśnienia!$B$42</f>
+        <v>2000</v>
+      </c>
+      <c r="C35" s="29" t="n">
+        <f aca="false">ROUNDUP(B35/100,0)</f>
+        <v>20</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <f aca="false">C35*Wyjaśnienia!$B$43</f>
+        <v>10000</v>
+      </c>
+      <c r="E35" s="29" t="n">
+        <f aca="false">ROUNDUP(A35/Wyjaśnienia!$B$46,0)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B36" s="29" t="n">
+        <f aca="false">A36*Wyjaśnienia!$B$42</f>
+        <v>20000</v>
+      </c>
+      <c r="C36" s="29" t="n">
+        <f aca="false">ROUNDUP(B36/100,0)</f>
+        <v>200</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <f aca="false">C36*Wyjaśnienia!$B$43</f>
+        <v>100000</v>
+      </c>
+      <c r="E36" s="29" t="n">
+        <f aca="false">ROUNDUP(A36/Wyjaśnienia!$B$46,0)</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="29" t="n">
+        <v>100000</v>
+      </c>
+      <c r="B37" s="29" t="n">
+        <f aca="false">A37*Wyjaśnienia!$B$42</f>
+        <v>200000</v>
+      </c>
+      <c r="C37" s="29" t="n">
+        <f aca="false">ROUNDUP(B37/100,0)</f>
+        <v>2000</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <f aca="false">C37*Wyjaśnienia!$B$43</f>
+        <v>1000000</v>
+      </c>
+      <c r="E37" s="29" t="n">
+        <f aca="false">ROUNDUP(A37/Wyjaśnienia!$B$46,0)</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="29" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="B38" s="29" t="n">
+        <f aca="false">A38*Wyjaśnienia!$B$42</f>
+        <v>2000000</v>
+      </c>
+      <c r="C38" s="29" t="n">
+        <f aca="false">ROUNDUP(B38/100,0)</f>
+        <v>20000</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <f aca="false">C38*Wyjaśnienia!$B$43</f>
+        <v>10000000</v>
+      </c>
+      <c r="E38" s="29" t="n">
+        <f aca="false">ROUNDUP(A38/Wyjaśnienia!$B$46,0)</f>
+        <v>50000</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -858,7 +858,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -891,20 +891,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -919,23 +907,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -967,24 +943,40 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1367,7 +1359,7 @@
       <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="7" t="n">
         <f aca="false">'Budżet Akademii'!$D$27</f>
         <v>49280</v>
       </c>
@@ -1377,7 +1369,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="8" t="n">
         <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$35+'Budżet Plebiscytu'!$D$30+'Budżet Akademii'!$D$27</f>
         <v>1139280.8</v>
       </c>
@@ -1388,9 +1380,7 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
+      <c r="A11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1410,9 +1400,11 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1423,10 +1415,10 @@
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="9" t="n">
         <v>220</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="3"/>
@@ -1439,10 +1431,10 @@
       <c r="A15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="3"/>
@@ -1455,10 +1447,10 @@
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="9" t="n">
         <v>300000</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="3"/>
@@ -1471,10 +1463,10 @@
       <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="10" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="3"/>
@@ -1487,10 +1479,10 @@
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="3"/>
@@ -1503,10 +1495,10 @@
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="3"/>
@@ -1519,10 +1511,10 @@
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="9" t="n">
         <v>35000</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="3"/>
@@ -1535,10 +1527,10 @@
       <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="3"/>
@@ -1551,10 +1543,10 @@
       <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="9" t="n">
         <v>7500</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="3"/>
@@ -1567,10 +1559,10 @@
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="10" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="3"/>
@@ -1583,10 +1575,10 @@
       <c r="A24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="9" t="n">
         <v>80000</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D24" s="3"/>
@@ -1599,10 +1591,10 @@
       <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D25" s="3"/>
@@ -1615,10 +1607,10 @@
       <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B26" s="11" t="n">
         <v>0.12</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D26" s="3"/>
@@ -1631,10 +1623,10 @@
       <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="10" t="s">
         <v>44</v>
       </c>
       <c r="D27" s="3"/>
@@ -1647,10 +1639,10 @@
       <c r="A28" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="11" t="n">
         <v>0.12</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="3"/>
@@ -1663,10 +1655,10 @@
       <c r="A29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="11" t="n">
         <v>0.23</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D29" s="3"/>
@@ -1679,10 +1671,10 @@
       <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D30" s="3"/>
@@ -1692,9 +1684,7 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
+      <c r="A31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -1702,9 +1692,11 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="5" t="s">
         <v>50</v>
       </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -1726,11 +1718,9 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -1738,9 +1728,11 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="4" t="s">
         <v>54</v>
       </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -1748,9 +1740,7 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
+      <c r="A36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -1782,9 +1772,11 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="4" t="s">
         <v>57</v>
       </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -1793,15 +1785,17 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="12" t="s">
         <v>58</v>
       </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="18" t="n">
+      <c r="B42" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="3" t="s">
@@ -1812,7 +1806,7 @@
       <c r="A43" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="19" t="n">
+      <c r="B43" s="13" t="n">
         <v>500</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -1823,7 +1817,7 @@
       <c r="A44" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="19" t="n">
+      <c r="B44" s="13" t="n">
         <v>2500</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -1834,7 +1828,7 @@
       <c r="A45" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="18" t="n">
+      <c r="B45" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -1845,7 +1839,7 @@
       <c r="A46" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="18" t="n">
+      <c r="B46" s="9" t="n">
         <v>20</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -1912,17 +1906,18 @@
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A41:C41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2031,264 +2026,264 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="16" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>60</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="17" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>13200</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="10" t="s">
         <v>79</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="16" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>24</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="17" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>5280</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="10" t="s">
         <v>81</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="16" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="17" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="10" t="s">
         <v>83</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="21" t="n">
+      <c r="B10" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="16" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>23</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="17" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>5060</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="10" t="s">
         <v>85</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="21" t="n">
+      <c r="B11" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="16" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="17" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="10" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="16" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="17" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="10" t="s">
         <v>89</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="21" t="n">
+      <c r="B13" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="16" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="17" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="10" t="s">
         <v>91</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="21" t="n">
+      <c r="B14" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="16" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="17" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="10" t="s">
         <v>93</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="16" t="n">
         <f aca="false">B15+C15*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="17" t="n">
         <f aca="false">D15*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="10" t="s">
         <v>95</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="21" t="n">
+      <c r="B16" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="16" t="n">
         <f aca="false">B16+C16*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="17" t="n">
         <f aca="false">D16*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="10" t="s">
         <v>97</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="21" t="n">
+      <c r="B17" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="16" t="n">
         <f aca="false">B17+C17*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="17" t="n">
         <f aca="false">D17*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="10" t="s">
         <v>99</v>
       </c>
       <c r="G17" s="3"/>
@@ -2300,11 +2295,11 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="18" t="n">
         <f aca="false">SUM(D7:D17)</f>
         <v>372</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <f aca="false">SUM(E7:E17)</f>
         <v>81840</v>
       </c>
@@ -2355,20 +2350,20 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="19" t="n">
         <v>8000</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="17" t="n">
         <f aca="false">B22*C22</f>
         <v>8000</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="10" t="s">
         <v>105</v>
       </c>
       <c r="F22" s="3"/>
@@ -2376,20 +2371,20 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="19" t="n">
         <v>1500</v>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="17" t="n">
         <f aca="false">B23*C23</f>
         <v>1500</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F23" s="3"/>
@@ -2397,20 +2392,20 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="25" t="n">
+      <c r="B24" s="19" t="n">
         <v>1200</v>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="17" t="n">
         <f aca="false">B24*C24</f>
         <v>1200</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="10" t="s">
         <v>109</v>
       </c>
       <c r="F24" s="3"/>
@@ -2418,20 +2413,20 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="25" t="n">
+      <c r="B25" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="17" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="10" t="s">
         <v>111</v>
       </c>
       <c r="F25" s="3"/>
@@ -2439,20 +2434,20 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="25" t="n">
+      <c r="B26" s="19" t="n">
         <v>1500</v>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="23" t="n">
+      <c r="D26" s="17" t="n">
         <f aca="false">B26*C26</f>
         <v>1500</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="10" t="s">
         <v>113</v>
       </c>
       <c r="F26" s="3"/>
@@ -2460,20 +2455,20 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="25" t="n">
+      <c r="B27" s="19" t="n">
         <v>250</v>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="23" t="n">
+      <c r="D27" s="17" t="n">
         <f aca="false">B27*C27</f>
         <v>250</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="10" t="s">
         <v>115</v>
       </c>
       <c r="F27" s="3"/>
@@ -2481,20 +2476,20 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="C28" s="21" t="n">
+      <c r="C28" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="17" t="n">
         <f aca="false">B28*C28</f>
         <v>32000</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="10" t="s">
         <v>117</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -2504,20 +2499,20 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="19" t="n">
         <v>15000</v>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="23" t="n">
+      <c r="D29" s="17" t="n">
         <f aca="false">B29*C29</f>
         <v>15000</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="10" t="s">
         <v>120</v>
       </c>
       <c r="F29" s="3"/>
@@ -2525,20 +2520,20 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="19" t="n">
         <v>8000</v>
       </c>
-      <c r="C30" s="21" t="n">
+      <c r="C30" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="17" t="n">
         <f aca="false">B30*C30</f>
         <v>8000</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="10" t="s">
         <v>122</v>
       </c>
       <c r="F30" s="3"/>
@@ -2546,20 +2541,20 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="21" t="n">
+      <c r="C31" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D31" s="17" t="n">
         <f aca="false">B31*C31</f>
         <v>0</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="10" t="s">
         <v>124</v>
       </c>
       <c r="F31" s="3"/>
@@ -2572,7 +2567,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <f aca="false">SUM(D22:D31)</f>
         <v>71450</v>
       </c>
@@ -2604,12 +2599,12 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="14" t="s">
         <v>127</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="23" t="n">
+      <c r="D35" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$16+Wyjaśnienia!$B$17*Wyjaśnienia!$B$18</f>
         <v>390000</v>
       </c>
@@ -2619,7 +2614,7 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="14" t="s">
         <v>128</v>
       </c>
       <c r="B36" s="3"/>
@@ -2634,7 +2629,7 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="14" t="s">
         <v>129</v>
       </c>
       <c r="B37" s="3"/>
@@ -2649,7 +2644,7 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="14" t="s">
         <v>130</v>
       </c>
       <c r="B38" s="3"/>
@@ -2669,7 +2664,7 @@
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="9" t="n">
+      <c r="D39" s="8" t="n">
         <f aca="false">SUM(D35:D38)</f>
         <v>561684.8</v>
       </c>
@@ -2679,7 +2674,7 @@
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="20" t="s">
+      <c r="A40" s="14" t="s">
         <v>132</v>
       </c>
       <c r="B40" s="3"/>
@@ -2699,7 +2694,7 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="26" t="n">
+      <c r="D41" s="20" t="n">
         <f aca="false">D39+D40</f>
         <v>690872.304</v>
       </c>
@@ -2888,168 +2883,168 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="16" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="17" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="10" t="s">
         <v>136</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="16" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="17" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="10" t="s">
         <v>138</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="16" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="17" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="10" t="s">
         <v>140</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="21" t="n">
+      <c r="B10" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="16" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="17" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="10" t="s">
         <v>142</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="21" t="n">
+      <c r="B11" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="16" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="17" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="10" t="s">
         <v>144</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="16" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>160</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="17" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>35200</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="10" t="s">
         <v>146</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="21" t="n">
+      <c r="B13" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="16" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="17" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="10" t="s">
         <v>148</v>
       </c>
       <c r="G13" s="3"/>
@@ -3061,11 +3056,11 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="18" t="n">
         <f aca="false">SUM(D7:D13)</f>
         <v>400</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <f aca="false">SUM(E7:E13)</f>
         <v>88000</v>
       </c>
@@ -3116,20 +3111,20 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B18" s="25" t="n">
+      <c r="B18" s="19" t="n">
         <v>3000</v>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="17" t="n">
         <f aca="false">B18*C18</f>
         <v>3000</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="10" t="s">
         <v>150</v>
       </c>
       <c r="F18" s="3"/>
@@ -3137,20 +3132,20 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="19" t="n">
         <v>6000</v>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="17" t="n">
         <f aca="false">B19*C19</f>
         <v>6000</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="10" t="s">
         <v>152</v>
       </c>
       <c r="F19" s="3"/>
@@ -3158,20 +3153,20 @@
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="19" t="n">
         <v>10000</v>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="17" t="n">
         <f aca="false">B20*C20</f>
         <v>10000</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="10" t="s">
         <v>154</v>
       </c>
       <c r="F20" s="3"/>
@@ -3179,20 +3174,20 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="B21" s="25" t="n">
+      <c r="B21" s="19" t="n">
         <v>40000</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="17" t="n">
         <f aca="false">B21*C21</f>
         <v>40000</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="10" t="s">
         <v>156</v>
       </c>
       <c r="F21" s="3"/>
@@ -3200,20 +3195,20 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="17" t="n">
         <f aca="false">B22*C22</f>
         <v>4000</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="10" t="s">
         <v>158</v>
       </c>
       <c r="F22" s="3"/>
@@ -3221,20 +3216,20 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="19" t="n">
         <v>3000</v>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="17" t="n">
         <f aca="false">B23*C23</f>
         <v>3000</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="10" t="s">
         <v>160</v>
       </c>
       <c r="F23" s="3"/>
@@ -3242,20 +3237,20 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="25" t="n">
+      <c r="B24" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="17" t="n">
         <f aca="false">B24*C24</f>
         <v>4000</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="10" t="s">
         <v>162</v>
       </c>
       <c r="F24" s="3"/>
@@ -3263,20 +3258,20 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="B25" s="25" t="n">
+      <c r="B25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="17" t="n">
         <f aca="false">B25*C25</f>
         <v>0</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="10" t="s">
         <v>164</v>
       </c>
       <c r="F25" s="3"/>
@@ -3284,20 +3279,20 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="25" t="n">
+      <c r="B26" s="19" t="n">
         <v>15000</v>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="23" t="n">
+      <c r="D26" s="17" t="n">
         <f aca="false">B26*C26</f>
         <v>15000</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="10" t="s">
         <v>166</v>
       </c>
       <c r="F26" s="3"/>
@@ -3305,20 +3300,20 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="25" t="n">
+      <c r="B27" s="19" t="n">
         <v>6000</v>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="23" t="n">
+      <c r="D27" s="17" t="n">
         <f aca="false">B27*C27</f>
         <v>6000</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="10" t="s">
         <v>168</v>
       </c>
       <c r="F27" s="3"/>
@@ -3326,20 +3321,20 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="19" t="n">
         <v>30000</v>
       </c>
-      <c r="C28" s="21" t="n">
+      <c r="C28" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="17" t="n">
         <f aca="false">B28*C28</f>
         <v>30000</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="10" t="s">
         <v>170</v>
       </c>
       <c r="F28" s="3"/>
@@ -3352,7 +3347,7 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <f aca="false">SUM(D18:D28)</f>
         <v>121000</v>
       </c>
@@ -3384,7 +3379,7 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="14" t="s">
         <v>128</v>
       </c>
       <c r="B32" s="3"/>
@@ -3399,7 +3394,7 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="14" t="s">
         <v>129</v>
       </c>
       <c r="B33" s="3"/>
@@ -3414,7 +3409,7 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="14" t="s">
         <v>171</v>
       </c>
       <c r="B34" s="3"/>
@@ -3434,7 +3429,7 @@
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <f aca="false">SUM(D32:D34)</f>
         <v>271700</v>
       </c>
@@ -3444,7 +3439,7 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="14" t="s">
         <v>132</v>
       </c>
       <c r="B36" s="3"/>
@@ -3464,7 +3459,7 @@
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="26" t="n">
+      <c r="D37" s="20" t="n">
         <f aca="false">D35+D36</f>
         <v>334191</v>
       </c>
@@ -3657,120 +3652,120 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="16" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$19/60</f>
         <v>25</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="17" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="10" t="s">
         <v>174</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="16" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$19/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="17" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="10" t="s">
         <v>176</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="16" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$19/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="17" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="10" t="s">
         <v>178</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B10" s="21" t="n">
+      <c r="B10" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="16" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$19/60</f>
         <v>20</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="17" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="10" t="s">
         <v>180</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B11" s="21" t="n">
+      <c r="B11" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="16" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$19/60</f>
         <v>50</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="17" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="10" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="3"/>
@@ -3782,11 +3777,11 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="18" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>165</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <f aca="false">SUM(E7:E11)</f>
         <v>36300</v>
       </c>
@@ -3837,21 +3832,21 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$20</f>
         <v>35000</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="17" t="n">
         <f aca="false">B16*C16</f>
         <v>35000</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="10" t="s">
         <v>184</v>
       </c>
       <c r="F16" s="3"/>
@@ -3859,21 +3854,21 @@
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="23" t="n">
+      <c r="B17" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$21</f>
         <v>4000</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="17" t="n">
         <f aca="false">B17*C17</f>
         <v>4000</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="10" t="s">
         <v>186</v>
       </c>
       <c r="F17" s="3"/>
@@ -3881,22 +3876,22 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="B18" s="23" t="n">
+      <c r="B18" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$22</f>
         <v>7500</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="16" t="n">
         <f aca="false">Wyjaśnienia!$B$23</f>
         <v>10</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="17" t="n">
         <f aca="false">B18*C18</f>
         <v>75000</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="10" t="s">
         <v>188</v>
       </c>
       <c r="F18" s="3"/>
@@ -3904,21 +3899,21 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="23" t="n">
+      <c r="B19" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$24</f>
         <v>80000</v>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="17" t="n">
         <f aca="false">B19*C19</f>
         <v>80000</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="10" t="s">
         <v>189</v>
       </c>
       <c r="F19" s="3"/>
@@ -3926,21 +3921,21 @@
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="23" t="n">
+      <c r="B20" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$25</f>
         <v>3000</v>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="17" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="10" t="s">
         <v>190</v>
       </c>
       <c r="F20" s="3"/>
@@ -3948,20 +3943,20 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B21" s="25" t="n">
+      <c r="B21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="17" t="n">
         <f aca="false">B21*C21</f>
         <v>0</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="10" t="s">
         <v>192</v>
       </c>
       <c r="F21" s="3"/>
@@ -3969,20 +3964,20 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="17" t="n">
         <f aca="false">B22*C22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="10" t="s">
         <v>194</v>
       </c>
       <c r="F22" s="3"/>
@@ -3995,7 +3990,7 @@
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <f aca="false">SUM(D16:D22)</f>
         <v>197000</v>
       </c>
@@ -4027,12 +4022,12 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="14" t="s">
         <v>127</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="23" t="n">
+      <c r="D26" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$20+Wyjaśnienia!$B$21</f>
         <v>39000</v>
       </c>
@@ -4042,7 +4037,7 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="14" t="s">
         <v>128</v>
       </c>
       <c r="B27" s="3"/>
@@ -4057,7 +4052,7 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="14" t="s">
         <v>195</v>
       </c>
       <c r="B28" s="3"/>
@@ -4072,7 +4067,7 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="14" t="s">
         <v>130</v>
       </c>
       <c r="B29" s="3"/>
@@ -4092,7 +4087,7 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="8" t="n">
         <f aca="false">SUM(D26:D29)</f>
         <v>256616</v>
       </c>
@@ -4102,7 +4097,7 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="14" t="s">
         <v>132</v>
       </c>
       <c r="B31" s="3"/>
@@ -4122,7 +4117,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="26" t="n">
+      <c r="D32" s="20" t="n">
         <f aca="false">D30+D31</f>
         <v>315637.68</v>
       </c>
@@ -4231,411 +4226,555 @@
   <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="21" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="22" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="22" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="23" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$15</f>
         <v>150</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$42</f>
         <v>2</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="26" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="E12" s="24"/>
+      <c r="F12" s="23" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="27" t="n">
         <f aca="false">Wyjaśnienia!$B$44</f>
         <v>2500</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$45</f>
         <v>15</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="27" t="n">
         <f aca="false">B13*C13</f>
         <v>37500</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="E13" s="24"/>
+      <c r="F13" s="24" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="27" t="n">
         <f aca="false">Wyjaśnienia!$B$43</f>
         <v>500</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <f aca="false">ROUNDUP(B9/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="27" t="n">
         <f aca="false">B14*C14</f>
         <v>1500</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="24"/>
+      <c r="F14" s="24" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="D15" s="31" t="n">
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="28" t="n">
         <f aca="false">SUM(D13:D14)</f>
         <v>39000</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="s">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="E18" s="24"/>
+      <c r="F18" s="23" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="B19" s="19" t="n">
+      <c r="B19" s="29" t="n">
         <v>2000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="27" t="n">
         <f aca="false">B19*C19</f>
         <v>2000</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="E19" s="24"/>
+      <c r="F19" s="24" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="27" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="E20" s="24"/>
+      <c r="F20" s="24" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="D21" s="31" t="n">
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="28" t="n">
         <f aca="false">SUM(D19:D20)</f>
         <v>5000</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="27" t="n">
         <f aca="false">D15</f>
         <v>39000</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="27" t="n">
         <f aca="false">D21</f>
         <v>5000</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="27" t="n">
         <f aca="false">(D24+D25)*Wyjaśnienia!$B$26</f>
         <v>5280</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28" t="s">
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="D27" s="31" t="n">
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="28" t="n">
         <f aca="false">SUM(D24:D26)</f>
         <v>49280</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="27" t="n">
         <f aca="false">D27*Wyjaśnienia!$B$29</f>
         <v>11334.4</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="28" t="s">
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="D29" s="31" t="n">
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="28" t="n">
         <f aca="false">D27+D28</f>
         <v>60614.4</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="28" t="s">
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="23" t="s">
         <v>224</v>
       </c>
-      <c r="E33" s="28" t="s">
+      <c r="E33" s="23" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="29" t="n">
+      <c r="F33" s="24"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="25" t="n">
         <f aca="false">A34*Wyjaśnienia!$B$42</f>
         <v>300</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <f aca="false">ROUNDUP(B34/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="27" t="n">
         <f aca="false">C34*Wyjaśnienia!$B$43</f>
         <v>1500</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <f aca="false">ROUNDUP(A34/Wyjaśnienia!$B$46,0)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29" t="n">
+      <c r="F34" s="24"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="25" t="n">
         <v>1000</v>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="25" t="n">
         <f aca="false">A35*Wyjaśnienia!$B$42</f>
         <v>2000</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <f aca="false">ROUNDUP(B35/100,0)</f>
         <v>20</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="27" t="n">
         <f aca="false">C35*Wyjaśnienia!$B$43</f>
         <v>10000</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <f aca="false">ROUNDUP(A35/Wyjaśnienia!$B$46,0)</f>
         <v>50</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="29" t="n">
+      <c r="F35" s="24"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="25" t="n">
         <v>10000</v>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="25" t="n">
         <f aca="false">A36*Wyjaśnienia!$B$42</f>
         <v>20000</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <f aca="false">ROUNDUP(B36/100,0)</f>
         <v>200</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="27" t="n">
         <f aca="false">C36*Wyjaśnienia!$B$43</f>
         <v>100000</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <f aca="false">ROUNDUP(A36/Wyjaśnienia!$B$46,0)</f>
         <v>500</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="29" t="n">
+      <c r="F36" s="24"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="25" t="n">
         <v>100000</v>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="25" t="n">
         <f aca="false">A37*Wyjaśnienia!$B$42</f>
         <v>200000</v>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <f aca="false">ROUNDUP(B37/100,0)</f>
         <v>2000</v>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D37" s="27" t="n">
         <f aca="false">C37*Wyjaśnienia!$B$43</f>
         <v>1000000</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <f aca="false">ROUNDUP(A37/Wyjaśnienia!$B$46,0)</f>
         <v>5000</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="29" t="n">
+      <c r="F37" s="24"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="25" t="n">
         <v>1000000</v>
       </c>
-      <c r="B38" s="29" t="n">
+      <c r="B38" s="25" t="n">
         <f aca="false">A38*Wyjaśnienia!$B$42</f>
         <v>2000000</v>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <f aca="false">ROUNDUP(B38/100,0)</f>
         <v>20000</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="27" t="n">
         <f aca="false">C38*Wyjaśnienia!$B$43</f>
         <v>10000000</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <f aca="false">ROUNDUP(A38/Wyjaśnienia!$B$46,0)</f>
         <v>50000</v>
       </c>
+      <c r="F38" s="24"/>
     </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:F32"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -858,7 +858,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -885,6 +885,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -953,6 +957,10 @@
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1292,7 +1300,7 @@
       <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="3"/>
@@ -1308,7 +1316,7 @@
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <f aca="false">'Budżet Nagrody'!$D$39</f>
         <v>561684.8</v>
       </c>
@@ -1325,7 +1333,7 @@
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <f aca="false">'Budżet Antologii'!$D$35</f>
         <v>271700</v>
       </c>
@@ -1342,7 +1350,7 @@
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <f aca="false">'Budżet Plebiscytu'!$D$30</f>
         <v>256616</v>
       </c>
@@ -1359,7 +1367,7 @@
       <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <f aca="false">'Budżet Akademii'!$D$27</f>
         <v>49280</v>
       </c>
@@ -1369,7 +1377,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="9" t="n">
         <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$35+'Budżet Plebiscytu'!$D$30+'Budżet Akademii'!$D$27</f>
         <v>1139280.8</v>
       </c>
@@ -1415,10 +1423,10 @@
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="10" t="n">
         <v>220</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="3"/>
@@ -1431,10 +1439,10 @@
       <c r="A15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="3"/>
@@ -1447,10 +1455,10 @@
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="10" t="n">
         <v>300000</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="3"/>
@@ -1463,10 +1471,10 @@
       <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="3"/>
@@ -1479,10 +1487,10 @@
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="3"/>
@@ -1495,10 +1503,10 @@
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="3"/>
@@ -1511,10 +1519,10 @@
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="10" t="n">
         <v>35000</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="3"/>
@@ -1527,10 +1535,10 @@
       <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="10" t="n">
         <v>4000</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="3"/>
@@ -1543,10 +1551,10 @@
       <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="10" t="n">
         <v>7500</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="3"/>
@@ -1559,10 +1567,10 @@
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="11" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="3"/>
@@ -1575,10 +1583,10 @@
       <c r="A24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="10" t="n">
         <v>80000</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="11" t="s">
         <v>38</v>
       </c>
       <c r="D24" s="3"/>
@@ -1591,10 +1599,10 @@
       <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="11" t="s">
         <v>40</v>
       </c>
       <c r="D25" s="3"/>
@@ -1607,10 +1615,10 @@
       <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="11" t="s">
         <v>42</v>
       </c>
       <c r="D26" s="3"/>
@@ -1623,10 +1631,10 @@
       <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>44</v>
       </c>
       <c r="D27" s="3"/>
@@ -1639,10 +1647,10 @@
       <c r="A28" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="11" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="3"/>
@@ -1655,10 +1663,10 @@
       <c r="A29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" s="12" t="n">
         <v>0.23</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="11" t="s">
         <v>47</v>
       </c>
       <c r="D29" s="3"/>
@@ -1671,10 +1679,10 @@
       <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="11" t="s">
         <v>49</v>
       </c>
       <c r="D30" s="3"/>
@@ -1785,17 +1793,17 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="9" t="n">
+      <c r="B42" s="10" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="3" t="s">
@@ -1806,7 +1814,7 @@
       <c r="A43" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="14" t="n">
         <v>500</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -1817,7 +1825,7 @@
       <c r="A44" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="13" t="n">
+      <c r="B44" s="14" t="n">
         <v>2500</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -1828,7 +1836,7 @@
       <c r="A45" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="9" t="n">
+      <c r="B45" s="10" t="n">
         <v>15</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -1839,7 +1847,7 @@
       <c r="A46" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="9" t="n">
+      <c r="B46" s="10" t="n">
         <v>20</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -2007,16 +2015,16 @@
       <c r="A6" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -2026,264 +2034,264 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>60</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>13200</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>79</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>24</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>5280</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>81</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>83</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>23</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>5060</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>85</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>89</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="11" t="s">
         <v>91</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="11" t="s">
         <v>93</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <f aca="false">B15+C15*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <f aca="false">D15*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="11" t="s">
         <v>95</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <f aca="false">B16+C16*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <f aca="false">D16*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="11" t="s">
         <v>97</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <f aca="false">B17+C17*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <f aca="false">D17*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="11" t="s">
         <v>99</v>
       </c>
       <c r="G17" s="3"/>
@@ -2295,11 +2303,11 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="19" t="n">
         <f aca="false">SUM(D7:D17)</f>
         <v>372</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="9" t="n">
         <f aca="false">SUM(E7:E17)</f>
         <v>81840</v>
       </c>
@@ -2333,13 +2341,13 @@
       <c r="A21" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="6" t="s">
@@ -2350,20 +2358,20 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="20" t="n">
         <v>8000</v>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="18" t="n">
         <f aca="false">B22*C22</f>
         <v>8000</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="11" t="s">
         <v>105</v>
       </c>
       <c r="F22" s="3"/>
@@ -2371,20 +2379,20 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B23" s="20" t="n">
         <v>1500</v>
       </c>
-      <c r="C23" s="15" t="n">
+      <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="18" t="n">
         <f aca="false">B23*C23</f>
         <v>1500</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="11" t="s">
         <v>107</v>
       </c>
       <c r="F23" s="3"/>
@@ -2392,20 +2400,20 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B24" s="20" t="n">
         <v>1200</v>
       </c>
-      <c r="C24" s="15" t="n">
+      <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="18" t="n">
         <f aca="false">B24*C24</f>
         <v>1200</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="11" t="s">
         <v>109</v>
       </c>
       <c r="F24" s="3"/>
@@ -2413,20 +2421,20 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B25" s="20" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="15" t="n">
+      <c r="C25" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="18" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="11" t="s">
         <v>111</v>
       </c>
       <c r="F25" s="3"/>
@@ -2434,20 +2442,20 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B26" s="20" t="n">
         <v>1500</v>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C26" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <f aca="false">B26*C26</f>
         <v>1500</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="11" t="s">
         <v>113</v>
       </c>
       <c r="F26" s="3"/>
@@ -2455,20 +2463,20 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="19" t="n">
+      <c r="B27" s="20" t="n">
         <v>250</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <f aca="false">B27*C27</f>
         <v>250</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="11" t="s">
         <v>115</v>
       </c>
       <c r="F27" s="3"/>
@@ -2476,20 +2484,20 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="19" t="n">
+      <c r="B28" s="20" t="n">
         <v>32000</v>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <f aca="false">B28*C28</f>
         <v>32000</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="11" t="s">
         <v>117</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -2499,20 +2507,20 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B29" s="19" t="n">
+      <c r="B29" s="20" t="n">
         <v>15000</v>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="18" t="n">
         <f aca="false">B29*C29</f>
         <v>15000</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="11" t="s">
         <v>120</v>
       </c>
       <c r="F29" s="3"/>
@@ -2520,20 +2528,20 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B30" s="19" t="n">
+      <c r="B30" s="20" t="n">
         <v>8000</v>
       </c>
-      <c r="C30" s="15" t="n">
+      <c r="C30" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="18" t="n">
         <f aca="false">B30*C30</f>
         <v>8000</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="11" t="s">
         <v>122</v>
       </c>
       <c r="F30" s="3"/>
@@ -2541,20 +2549,20 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="15" t="n">
+      <c r="C31" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="18" t="n">
         <f aca="false">B31*C31</f>
         <v>0</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F31" s="3"/>
@@ -2567,7 +2575,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="9" t="n">
         <f aca="false">SUM(D22:D31)</f>
         <v>71450</v>
       </c>
@@ -2599,12 +2607,12 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="15" t="s">
         <v>127</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$16+Wyjaśnienia!$B$17*Wyjaśnienia!$B$18</f>
         <v>390000</v>
       </c>
@@ -2614,12 +2622,12 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="15" t="s">
         <v>128</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="8" t="n">
         <f aca="false">E18</f>
         <v>81840</v>
       </c>
@@ -2629,12 +2637,12 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="15" t="s">
         <v>129</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="7" t="n">
+      <c r="D37" s="8" t="n">
         <f aca="false">D32</f>
         <v>71450</v>
       </c>
@@ -2644,12 +2652,12 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="15" t="s">
         <v>130</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="8" t="n">
         <f aca="false">(D36+D37)*Wyjaśnienia!$B$26</f>
         <v>18394.8</v>
       </c>
@@ -2664,7 +2672,7 @@
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="9" t="n">
         <f aca="false">SUM(D35:D38)</f>
         <v>561684.8</v>
       </c>
@@ -2674,12 +2682,12 @@
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="15" t="s">
         <v>132</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="8" t="n">
         <f aca="false">D39*Wyjaśnienia!$B$29</f>
         <v>129187.504</v>
       </c>
@@ -2694,7 +2702,7 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="20" t="n">
+      <c r="D41" s="21" t="n">
         <f aca="false">D39+D40</f>
         <v>690872.304</v>
       </c>
@@ -2864,16 +2872,16 @@
       <c r="A6" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -2883,168 +2891,168 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>136</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>138</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>140</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>142</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>144</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="16" t="n">
         <v>160</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>160</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>35200</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>146</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="11" t="s">
         <v>148</v>
       </c>
       <c r="G13" s="3"/>
@@ -3056,11 +3064,11 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <f aca="false">SUM(D7:D13)</f>
         <v>400</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="9" t="n">
         <f aca="false">SUM(E7:E13)</f>
         <v>88000</v>
       </c>
@@ -3094,13 +3102,13 @@
       <c r="A17" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>76</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -3111,20 +3119,20 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B18" s="19" t="n">
+      <c r="B18" s="20" t="n">
         <v>3000</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <f aca="false">B18*C18</f>
         <v>3000</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="11" t="s">
         <v>150</v>
       </c>
       <c r="F18" s="3"/>
@@ -3132,20 +3140,20 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="B19" s="19" t="n">
+      <c r="B19" s="20" t="n">
         <v>6000</v>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <f aca="false">B19*C19</f>
         <v>6000</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="11" t="s">
         <v>152</v>
       </c>
       <c r="F19" s="3"/>
@@ -3153,20 +3161,20 @@
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="20" t="n">
         <v>10000</v>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <f aca="false">B20*C20</f>
         <v>10000</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F20" s="3"/>
@@ -3174,20 +3182,20 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="20" t="n">
         <v>40000</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">B21*C21</f>
         <v>40000</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="11" t="s">
         <v>156</v>
       </c>
       <c r="F21" s="3"/>
@@ -3195,20 +3203,20 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="20" t="n">
         <v>4000</v>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="18" t="n">
         <f aca="false">B22*C22</f>
         <v>4000</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="11" t="s">
         <v>158</v>
       </c>
       <c r="F22" s="3"/>
@@ -3216,20 +3224,20 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B23" s="20" t="n">
         <v>3000</v>
       </c>
-      <c r="C23" s="15" t="n">
+      <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="18" t="n">
         <f aca="false">B23*C23</f>
         <v>3000</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="11" t="s">
         <v>160</v>
       </c>
       <c r="F23" s="3"/>
@@ -3237,20 +3245,20 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B24" s="20" t="n">
         <v>4000</v>
       </c>
-      <c r="C24" s="15" t="n">
+      <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="18" t="n">
         <f aca="false">B24*C24</f>
         <v>4000</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="11" t="s">
         <v>162</v>
       </c>
       <c r="F24" s="3"/>
@@ -3258,20 +3266,20 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B25" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="15" t="n">
+      <c r="C25" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="18" t="n">
         <f aca="false">B25*C25</f>
         <v>0</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="11" t="s">
         <v>164</v>
       </c>
       <c r="F25" s="3"/>
@@ -3279,20 +3287,20 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B26" s="20" t="n">
         <v>15000</v>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C26" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <f aca="false">B26*C26</f>
         <v>15000</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="11" t="s">
         <v>166</v>
       </c>
       <c r="F26" s="3"/>
@@ -3300,20 +3308,20 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="19" t="n">
+      <c r="B27" s="20" t="n">
         <v>6000</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <f aca="false">B27*C27</f>
         <v>6000</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="11" t="s">
         <v>168</v>
       </c>
       <c r="F27" s="3"/>
@@ -3321,20 +3329,20 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B28" s="19" t="n">
+      <c r="B28" s="20" t="n">
         <v>30000</v>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <f aca="false">B28*C28</f>
         <v>30000</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="11" t="s">
         <v>170</v>
       </c>
       <c r="F28" s="3"/>
@@ -3347,7 +3355,7 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="9" t="n">
         <f aca="false">SUM(D18:D28)</f>
         <v>121000</v>
       </c>
@@ -3379,12 +3387,12 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="15" t="s">
         <v>128</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="8" t="n">
         <f aca="false">E14</f>
         <v>88000</v>
       </c>
@@ -3394,12 +3402,12 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="15" t="s">
         <v>129</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="7" t="n">
+      <c r="D33" s="8" t="n">
         <f aca="false">D29</f>
         <v>121000</v>
       </c>
@@ -3409,12 +3417,12 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="15" t="s">
         <v>171</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="7" t="n">
+      <c r="D34" s="8" t="n">
         <f aca="false">(D32+D33)*Wyjaśnienia!$B$27</f>
         <v>62700</v>
       </c>
@@ -3429,7 +3437,7 @@
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="9" t="n">
         <f aca="false">SUM(D32:D34)</f>
         <v>271700</v>
       </c>
@@ -3439,12 +3447,12 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="15" t="s">
         <v>132</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="8" t="n">
         <f aca="false">D35*Wyjaśnienia!$B$29</f>
         <v>62491</v>
       </c>
@@ -3459,7 +3467,7 @@
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="20" t="n">
+      <c r="D37" s="21" t="n">
         <f aca="false">D35+D36</f>
         <v>334191</v>
       </c>
@@ -3633,16 +3641,16 @@
       <c r="A6" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -3652,120 +3660,120 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$19/60</f>
         <v>25</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>174</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$19/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>176</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$19/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>178</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$19/60</f>
         <v>20</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>180</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$19/60</f>
         <v>50</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="3"/>
@@ -3777,11 +3785,11 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>165</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="9" t="n">
         <f aca="false">SUM(E7:E11)</f>
         <v>36300</v>
       </c>
@@ -3815,13 +3823,13 @@
       <c r="A15" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>76</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -3832,21 +3840,21 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$20</f>
         <v>35000</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <f aca="false">B16*C16</f>
         <v>35000</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="11" t="s">
         <v>184</v>
       </c>
       <c r="F16" s="3"/>
@@ -3854,21 +3862,21 @@
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$21</f>
         <v>4000</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <f aca="false">B17*C17</f>
         <v>4000</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="11" t="s">
         <v>186</v>
       </c>
       <c r="F17" s="3"/>
@@ -3876,22 +3884,22 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$22</f>
         <v>7500</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$23</f>
         <v>10</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <f aca="false">B18*C18</f>
         <v>75000</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="11" t="s">
         <v>188</v>
       </c>
       <c r="F18" s="3"/>
@@ -3899,21 +3907,21 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$24</f>
         <v>80000</v>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <f aca="false">B19*C19</f>
         <v>80000</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="11" t="s">
         <v>189</v>
       </c>
       <c r="F19" s="3"/>
@@ -3921,21 +3929,21 @@
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$25</f>
         <v>3000</v>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="11" t="s">
         <v>190</v>
       </c>
       <c r="F20" s="3"/>
@@ -3943,20 +3951,20 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">B21*C21</f>
         <v>0</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="11" t="s">
         <v>192</v>
       </c>
       <c r="F21" s="3"/>
@@ -3964,20 +3972,20 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="18" t="n">
         <f aca="false">B22*C22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="11" t="s">
         <v>194</v>
       </c>
       <c r="F22" s="3"/>
@@ -3990,7 +3998,7 @@
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="9" t="n">
         <f aca="false">SUM(D16:D22)</f>
         <v>197000</v>
       </c>
@@ -4022,12 +4030,12 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="15" t="s">
         <v>127</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$20+Wyjaśnienia!$B$21</f>
         <v>39000</v>
       </c>
@@ -4037,12 +4045,12 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="15" t="s">
         <v>128</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="8" t="n">
         <f aca="false">E12</f>
         <v>36300</v>
       </c>
@@ -4052,12 +4060,12 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="15" t="s">
         <v>195</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="8" t="n">
         <f aca="false">D23-D26</f>
         <v>158000</v>
       </c>
@@ -4067,12 +4075,12 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="15" t="s">
         <v>130</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="7" t="n">
+      <c r="D29" s="8" t="n">
         <f aca="false">(D27+D28)*Wyjaśnienia!$B$28</f>
         <v>23316</v>
       </c>
@@ -4087,7 +4095,7 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="9" t="n">
         <f aca="false">SUM(D26:D29)</f>
         <v>256616</v>
       </c>
@@ -4097,12 +4105,12 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="15" t="s">
         <v>132</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="8" t="n">
         <f aca="false">D30*Wyjaśnienia!$B$29</f>
         <v>59021.68</v>
       </c>
@@ -4117,7 +4125,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="20" t="n">
+      <c r="D32" s="21" t="n">
         <f aca="false">D30+D31</f>
         <v>315637.68</v>
       </c>
@@ -4235,533 +4243,533 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="23" t="s">
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="24" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="27" t="n">
         <f aca="false">Wyjaśnienia!$B$15</f>
         <v>150</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24" t="s">
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="27" t="n">
         <f aca="false">Wyjaśnienia!$B$42</f>
         <v>2</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24" t="s">
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="28" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24" t="s">
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="24"/>
-      <c r="F12" s="23" t="s">
+      <c r="E12" s="26"/>
+      <c r="F12" s="24" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="29" t="n">
         <f aca="false">Wyjaśnienia!$B$44</f>
         <v>2500</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="27" t="n">
         <f aca="false">Wyjaśnienia!$B$45</f>
         <v>15</v>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="29" t="n">
         <f aca="false">B13*C13</f>
         <v>37500</v>
       </c>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24" t="s">
+      <c r="E13" s="26"/>
+      <c r="F13" s="26" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="29" t="n">
         <f aca="false">Wyjaśnienia!$B$43</f>
         <v>500</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="27" t="n">
         <f aca="false">ROUNDUP(B9/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="29" t="n">
         <f aca="false">B14*C14</f>
         <v>1500</v>
       </c>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24" t="s">
+      <c r="E14" s="26"/>
+      <c r="F14" s="26" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="28" t="n">
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="30" t="n">
         <f aca="false">SUM(D13:D14)</f>
         <v>39000</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="24"/>
-      <c r="F18" s="23" t="s">
+      <c r="E18" s="26"/>
+      <c r="F18" s="24" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="31" t="n">
         <v>2000</v>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C19" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D19" s="29" t="n">
         <f aca="false">B19*C19</f>
         <v>2000</v>
       </c>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24" t="s">
+      <c r="E19" s="26"/>
+      <c r="F19" s="26" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="31" t="n">
         <v>3000</v>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C20" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="29" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24" t="s">
+      <c r="E20" s="26"/>
+      <c r="F20" s="26" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="28" t="n">
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="30" t="n">
         <f aca="false">SUM(D19:D20)</f>
         <v>5000</v>
       </c>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="27" t="n">
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="29" t="n">
         <f aca="false">D15</f>
         <v>39000</v>
       </c>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="27" t="n">
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="29" t="n">
         <f aca="false">D21</f>
         <v>5000</v>
       </c>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="27" t="n">
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="29" t="n">
         <f aca="false">(D24+D25)*Wyjaśnienia!$B$26</f>
         <v>5280</v>
       </c>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="28" t="n">
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="30" t="n">
         <f aca="false">SUM(D24:D26)</f>
         <v>49280</v>
       </c>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="27" t="n">
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="29" t="n">
         <f aca="false">D27*Wyjaśnienia!$B$29</f>
         <v>11334.4</v>
       </c>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="28" t="n">
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="30" t="n">
         <f aca="false">D27+D28</f>
         <v>60614.4</v>
       </c>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="E33" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="F33" s="24"/>
+      <c r="F33" s="26"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="25" t="n">
+      <c r="A34" s="27" t="n">
         <v>150</v>
       </c>
-      <c r="B34" s="25" t="n">
+      <c r="B34" s="27" t="n">
         <f aca="false">A34*Wyjaśnienia!$B$42</f>
         <v>300</v>
       </c>
-      <c r="C34" s="25" t="n">
+      <c r="C34" s="27" t="n">
         <f aca="false">ROUNDUP(B34/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D34" s="27" t="n">
+      <c r="D34" s="29" t="n">
         <f aca="false">C34*Wyjaśnienia!$B$43</f>
         <v>1500</v>
       </c>
-      <c r="E34" s="25" t="n">
+      <c r="E34" s="27" t="n">
         <f aca="false">ROUNDUP(A34/Wyjaśnienia!$B$46,0)</f>
         <v>8</v>
       </c>
-      <c r="F34" s="24"/>
+      <c r="F34" s="26"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="25" t="n">
+      <c r="A35" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="B35" s="25" t="n">
+      <c r="B35" s="27" t="n">
         <f aca="false">A35*Wyjaśnienia!$B$42</f>
         <v>2000</v>
       </c>
-      <c r="C35" s="25" t="n">
+      <c r="C35" s="27" t="n">
         <f aca="false">ROUNDUP(B35/100,0)</f>
         <v>20</v>
       </c>
-      <c r="D35" s="27" t="n">
+      <c r="D35" s="29" t="n">
         <f aca="false">C35*Wyjaśnienia!$B$43</f>
         <v>10000</v>
       </c>
-      <c r="E35" s="25" t="n">
+      <c r="E35" s="27" t="n">
         <f aca="false">ROUNDUP(A35/Wyjaśnienia!$B$46,0)</f>
         <v>50</v>
       </c>
-      <c r="F35" s="24"/>
+      <c r="F35" s="26"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="25" t="n">
+      <c r="A36" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="B36" s="25" t="n">
+      <c r="B36" s="27" t="n">
         <f aca="false">A36*Wyjaśnienia!$B$42</f>
         <v>20000</v>
       </c>
-      <c r="C36" s="25" t="n">
+      <c r="C36" s="27" t="n">
         <f aca="false">ROUNDUP(B36/100,0)</f>
         <v>200</v>
       </c>
-      <c r="D36" s="27" t="n">
+      <c r="D36" s="29" t="n">
         <f aca="false">C36*Wyjaśnienia!$B$43</f>
         <v>100000</v>
       </c>
-      <c r="E36" s="25" t="n">
+      <c r="E36" s="27" t="n">
         <f aca="false">ROUNDUP(A36/Wyjaśnienia!$B$46,0)</f>
         <v>500</v>
       </c>
-      <c r="F36" s="24"/>
+      <c r="F36" s="26"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="25" t="n">
+      <c r="A37" s="27" t="n">
         <v>100000</v>
       </c>
-      <c r="B37" s="25" t="n">
+      <c r="B37" s="27" t="n">
         <f aca="false">A37*Wyjaśnienia!$B$42</f>
         <v>200000</v>
       </c>
-      <c r="C37" s="25" t="n">
+      <c r="C37" s="27" t="n">
         <f aca="false">ROUNDUP(B37/100,0)</f>
         <v>2000</v>
       </c>
-      <c r="D37" s="27" t="n">
+      <c r="D37" s="29" t="n">
         <f aca="false">C37*Wyjaśnienia!$B$43</f>
         <v>1000000</v>
       </c>
-      <c r="E37" s="25" t="n">
+      <c r="E37" s="27" t="n">
         <f aca="false">ROUNDUP(A37/Wyjaśnienia!$B$46,0)</f>
         <v>5000</v>
       </c>
-      <c r="F37" s="24"/>
+      <c r="F37" s="26"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="25" t="n">
+      <c r="A38" s="27" t="n">
         <v>1000000</v>
       </c>
-      <c r="B38" s="25" t="n">
+      <c r="B38" s="27" t="n">
         <f aca="false">A38*Wyjaśnienia!$B$42</f>
         <v>2000000</v>
       </c>
-      <c r="C38" s="25" t="n">
+      <c r="C38" s="27" t="n">
         <f aca="false">ROUNDUP(B38/100,0)</f>
         <v>20000</v>
       </c>
-      <c r="D38" s="27" t="n">
+      <c r="D38" s="29" t="n">
         <f aca="false">C38*Wyjaśnienia!$B$43</f>
         <v>10000000</v>
       </c>
-      <c r="E38" s="25" t="n">
+      <c r="E38" s="27" t="n">
         <f aca="false">ROUNDUP(A38/Wyjaśnienia!$B$46,0)</f>
         <v>50000</v>
       </c>
-      <c r="F38" s="24"/>
+      <c r="F38" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="231">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -485,6 +485,9 @@
     <t xml:space="preserve">sześć obszarów, w tym licencja i archiwum; obowiązkowa przed naborem</t>
   </si>
   <si>
+    <t xml:space="preserve">sześć obszarów, w tym licencja i archiwum; kwota z zapasem wobec ofert kancelarii</t>
+  </si>
+  <si>
     <t xml:space="preserve">Domeny, poczta, hosting, magazyn kopii archiwalnych</t>
   </si>
   <si>
@@ -539,6 +542,12 @@
     <t xml:space="preserve">Dostęp do narzędzi AI, bez których 937 godzin pracy organizatora nie jest wykonalne; rzędu 2,5 tys. zł miesięcznie</t>
   </si>
   <si>
+    <t xml:space="preserve">Rejestracja znaku towarowego Konstela w EUIPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jedna klasa, ochrona w całej Unii; opłaty urzędowe około 850 euro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marża (od pracy i kosztów, bez nagród)</t>
   </si>
   <si>
@@ -609,6 +618,12 @@
   </si>
   <si>
     <t xml:space="preserve">DO WYCENY - zależy od miejsca gali, które nie jest wybrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa prawna plebiscytu (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">odrębne zlecenie na pytania plebiscytowe; kwota z zapasem wobec ofert kancelarii</t>
   </si>
   <si>
     <t xml:space="preserve">Koszty twarde bez nagród</t>
@@ -858,7 +873,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -947,6 +962,34 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -961,10 +1004,6 @@
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1334,8 +1373,8 @@
         <v>9</v>
       </c>
       <c r="C7" s="8" t="n">
-        <f aca="false">'Budżet Antologii'!$D$35</f>
-        <v>271700</v>
+        <f aca="false">'Budżet Antologii'!$D$36</f>
+        <v>277550</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -1351,8 +1390,8 @@
         <v>11</v>
       </c>
       <c r="C8" s="8" t="n">
-        <f aca="false">'Budżet Plebiscytu'!$D$30</f>
-        <v>256616</v>
+        <f aca="false">'Budżet Plebiscytu'!$D$31</f>
+        <v>261656</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -1378,8 +1417,8 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="9" t="n">
-        <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$35+'Budżet Plebiscytu'!$D$30+'Budżet Akademii'!$D$27</f>
-        <v>1139280.8</v>
+        <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$36+'Budżet Plebiscytu'!$D$31+'Budżet Akademii'!$D$27</f>
+        <v>1150170.8</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -3156,13 +3195,15 @@
       <c r="E19" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B20" s="20" t="n">
         <v>10000</v>
@@ -3175,7 +3216,7 @@
         <v>10000</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -3183,7 +3224,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>40000</v>
@@ -3196,7 +3237,7 @@
         <v>40000</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -3204,7 +3245,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B22" s="20" t="n">
         <v>4000</v>
@@ -3217,7 +3258,7 @@
         <v>4000</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -3225,7 +3266,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B23" s="20" t="n">
         <v>3000</v>
@@ -3238,7 +3279,7 @@
         <v>3000</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -3246,7 +3287,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B24" s="20" t="n">
         <v>4000</v>
@@ -3259,7 +3300,7 @@
         <v>4000</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -3267,7 +3308,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B25" s="20" t="n">
         <v>0</v>
@@ -3280,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -3288,7 +3329,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B26" s="20" t="n">
         <v>15000</v>
@@ -3301,7 +3342,7 @@
         <v>15000</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -3309,7 +3350,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B27" s="20" t="n">
         <v>6000</v>
@@ -3322,7 +3363,7 @@
         <v>6000</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -3330,7 +3371,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B28" s="20" t="n">
         <v>30000</v>
@@ -3343,73 +3384,71 @@
         <v>30000</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" s="23" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C29" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="25" t="n">
+        <f aca="false">B29*C29</f>
+        <v>4500</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="9" t="n">
-        <f aca="false">SUM(D18:D28)</f>
-        <v>121000</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="D30" s="9" t="n">
+        <f aca="false">SUM(D18:D29)</f>
+        <v>125500</v>
+      </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="8" t="n">
-        <f aca="false">E14</f>
-        <v>88000</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+      <c r="A32" s="27" t="s">
+        <v>126</v>
+      </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="8" t="n">
-        <f aca="false">D29</f>
-        <v>121000</v>
+        <f aca="false">E14</f>
+        <v>88000</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -3418,13 +3457,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="8" t="n">
-        <f aca="false">(D32+D33)*Wyjaśnienia!$B$27</f>
-        <v>62700</v>
+        <f aca="false">D30</f>
+        <v>125500</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -3432,14 +3471,14 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>131</v>
+      <c r="A35" s="15" t="s">
+        <v>174</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="9" t="n">
-        <f aca="false">SUM(D32:D34)</f>
-        <v>271700</v>
+      <c r="D35" s="8" t="n">
+        <f aca="false">(D33+D34)*Wyjaśnienia!$B$27</f>
+        <v>64050</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -3447,14 +3486,14 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>132</v>
+      <c r="A36" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="8" t="n">
-        <f aca="false">D35*Wyjaśnienia!$B$29</f>
-        <v>62491</v>
+      <c r="D36" s="9" t="n">
+        <f aca="false">SUM(D33:D35)</f>
+        <v>277550</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -3462,21 +3501,35 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
-        <v>133</v>
+      <c r="A37" s="15" t="s">
+        <v>132</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="21" t="n">
-        <f aca="false">D35+D36</f>
-        <v>334191</v>
+      <c r="D37" s="8" t="n">
+        <f aca="false">D36*Wyjaśnienia!$B$29</f>
+        <v>63836.5</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="21" t="n">
+        <f aca="false">D36+D37</f>
+        <v>341386.5</v>
+      </c>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+    </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3593,7 +3646,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3661,7 +3714,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B7" s="16" t="n">
         <v>0</v>
@@ -3678,14 +3731,14 @@
         <v>5500</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>40</v>
@@ -3702,14 +3755,14 @@
         <v>8800</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>30</v>
@@ -3726,14 +3779,14 @@
         <v>6600</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>20</v>
@@ -3750,14 +3803,14 @@
         <v>4400</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>50</v>
@@ -3774,7 +3827,7 @@
         <v>11000</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -3841,7 +3894,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B16" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$20</f>
@@ -3855,7 +3908,7 @@
         <v>35000</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -3863,7 +3916,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B17" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$21</f>
@@ -3877,7 +3930,7 @@
         <v>4000</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -3885,7 +3938,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$22</f>
@@ -3900,7 +3953,7 @@
         <v>75000</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -3922,7 +3975,7 @@
         <v>80000</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -3944,7 +3997,7 @@
         <v>3000</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -3952,7 +4005,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B21" s="20" t="n">
         <v>0</v>
@@ -3965,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -3973,7 +4026,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B22" s="20" t="n">
         <v>0</v>
@@ -3986,73 +4039,71 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <f aca="false">B23*C23</f>
+        <v>4500</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="9" t="n">
-        <f aca="false">SUM(D16:D22)</f>
-        <v>197000</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="D24" s="9" t="n">
+        <f aca="false">SUM(D16:D23)</f>
+        <v>201500</v>
+      </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="18" t="n">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$20+Wyjaśnienia!$B$21</f>
         <v>39000</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="8" t="n">
-        <f aca="false">E12</f>
-        <v>36300</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -4061,13 +4112,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="8" t="n">
-        <f aca="false">D23-D26</f>
-        <v>158000</v>
+        <f aca="false">E12</f>
+        <v>36300</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -4076,13 +4127,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="8" t="n">
-        <f aca="false">(D27+D28)*Wyjaśnienia!$B$28</f>
-        <v>23316</v>
+        <f aca="false">D24-D27</f>
+        <v>162500</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -4090,14 +4141,14 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>131</v>
+      <c r="A30" s="15" t="s">
+        <v>130</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="9" t="n">
-        <f aca="false">SUM(D26:D29)</f>
-        <v>256616</v>
+      <c r="D30" s="8" t="n">
+        <f aca="false">(D28+D29)*Wyjaśnienia!$B$28</f>
+        <v>23856</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -4105,14 +4156,14 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
-        <v>132</v>
+      <c r="A31" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="8" t="n">
-        <f aca="false">D30*Wyjaśnienia!$B$29</f>
-        <v>59021.68</v>
+      <c r="D31" s="9" t="n">
+        <f aca="false">SUM(D27:D30)</f>
+        <v>261656</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -4120,21 +4171,35 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>133</v>
+      <c r="A32" s="15" t="s">
+        <v>132</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="21" t="n">
-        <f aca="false">D30+D31</f>
-        <v>315637.68</v>
+      <c r="D32" s="8" t="n">
+        <f aca="false">D31*Wyjaśnienia!$B$29</f>
+        <v>60180.88</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="21" t="n">
+        <f aca="false">D31+D32</f>
+        <v>321836.88</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+    </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4243,38 +4308,38 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="A2" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
+      <c r="A3" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -4283,75 +4348,75 @@
       <c r="F5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="24" t="s">
+      <c r="B6" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="31" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="27" t="n">
+      <c r="A7" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="33" t="n">
         <f aca="false">Wyjaśnienia!$B$15</f>
         <v>150</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26" t="s">
-        <v>201</v>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="27" t="n">
+      <c r="A8" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="33" t="n">
         <f aca="false">Wyjaśnienia!$B$42</f>
         <v>2</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26" t="s">
-        <v>203</v>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" s="28" t="n">
+      <c r="A9" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" s="34" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26" t="s">
-        <v>205</v>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4360,85 +4425,85 @@
       <c r="F11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="C12" s="25" t="s">
+      <c r="B12" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="26"/>
-      <c r="F12" s="24" t="s">
+      <c r="E12" s="22"/>
+      <c r="F12" s="31" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="29" t="n">
+      <c r="A13" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="B13" s="35" t="n">
         <f aca="false">Wyjaśnienia!$B$44</f>
         <v>2500</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="33" t="n">
         <f aca="false">Wyjaśnienia!$B$45</f>
         <v>15</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="35" t="n">
         <f aca="false">B13*C13</f>
         <v>37500</v>
       </c>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26" t="s">
-        <v>209</v>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="B14" s="29" t="n">
+      <c r="A14" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" s="35" t="n">
         <f aca="false">Wyjaśnienia!$B$43</f>
         <v>500</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="33" t="n">
         <f aca="false">ROUNDUP(B9/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="35" t="n">
         <f aca="false">B14*C14</f>
         <v>1500</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26" t="s">
-        <v>211</v>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="30" t="n">
+      <c r="A15" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="36" t="n">
         <f aca="false">SUM(D13:D14)</f>
         <v>39000</v>
       </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
@@ -4451,81 +4516,81 @@
       <c r="F17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="24" t="s">
+      <c r="E18" s="22"/>
+      <c r="F18" s="31" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B19" s="31" t="n">
+      <c r="A19" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="B19" s="37" t="n">
         <v>2000</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="35" t="n">
         <f aca="false">B19*C19</f>
         <v>2000</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26" t="s">
-        <v>214</v>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="B20" s="31" t="n">
+      <c r="A20" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="B20" s="37" t="n">
         <v>3000</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="35" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26" t="s">
-        <v>216</v>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="30" t="n">
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="36" t="n">
         <f aca="false">SUM(D19:D20)</f>
         <v>5000</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
@@ -4538,94 +4603,94 @@
       <c r="F23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="29" t="n">
+      <c r="A24" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="35" t="n">
         <f aca="false">D15</f>
         <v>39000</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="29" t="n">
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="35" t="n">
         <f aca="false">D21</f>
         <v>5000</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="29" t="n">
+      <c r="A26" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="35" t="n">
         <f aca="false">(D24+D25)*Wyjaśnienia!$B$26</f>
         <v>5280</v>
       </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="30" t="n">
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="36" t="n">
         <f aca="false">SUM(D24:D26)</f>
         <v>49280</v>
       </c>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="29" t="n">
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="35" t="n">
         <f aca="false">D27*Wyjaśnienia!$B$29</f>
         <v>11334.4</v>
       </c>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="30" t="n">
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="36" t="n">
         <f aca="false">D27+D28</f>
         <v>60614.4</v>
       </c>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="26"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -4634,142 +4699,142 @@
       <c r="F31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
+      <c r="A32" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="F33" s="26"/>
+      <c r="A33" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="F33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="27" t="n">
+      <c r="A34" s="33" t="n">
         <v>150</v>
       </c>
-      <c r="B34" s="27" t="n">
+      <c r="B34" s="33" t="n">
         <f aca="false">A34*Wyjaśnienia!$B$42</f>
         <v>300</v>
       </c>
-      <c r="C34" s="27" t="n">
+      <c r="C34" s="33" t="n">
         <f aca="false">ROUNDUP(B34/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="35" t="n">
         <f aca="false">C34*Wyjaśnienia!$B$43</f>
         <v>1500</v>
       </c>
-      <c r="E34" s="27" t="n">
+      <c r="E34" s="33" t="n">
         <f aca="false">ROUNDUP(A34/Wyjaśnienia!$B$46,0)</f>
         <v>8</v>
       </c>
-      <c r="F34" s="26"/>
+      <c r="F34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="27" t="n">
+      <c r="A35" s="33" t="n">
         <v>1000</v>
       </c>
-      <c r="B35" s="27" t="n">
+      <c r="B35" s="33" t="n">
         <f aca="false">A35*Wyjaśnienia!$B$42</f>
         <v>2000</v>
       </c>
-      <c r="C35" s="27" t="n">
+      <c r="C35" s="33" t="n">
         <f aca="false">ROUNDUP(B35/100,0)</f>
         <v>20</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="35" t="n">
         <f aca="false">C35*Wyjaśnienia!$B$43</f>
         <v>10000</v>
       </c>
-      <c r="E35" s="27" t="n">
+      <c r="E35" s="33" t="n">
         <f aca="false">ROUNDUP(A35/Wyjaśnienia!$B$46,0)</f>
         <v>50</v>
       </c>
-      <c r="F35" s="26"/>
+      <c r="F35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="27" t="n">
+      <c r="A36" s="33" t="n">
         <v>10000</v>
       </c>
-      <c r="B36" s="27" t="n">
+      <c r="B36" s="33" t="n">
         <f aca="false">A36*Wyjaśnienia!$B$42</f>
         <v>20000</v>
       </c>
-      <c r="C36" s="27" t="n">
+      <c r="C36" s="33" t="n">
         <f aca="false">ROUNDUP(B36/100,0)</f>
         <v>200</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="35" t="n">
         <f aca="false">C36*Wyjaśnienia!$B$43</f>
         <v>100000</v>
       </c>
-      <c r="E36" s="27" t="n">
+      <c r="E36" s="33" t="n">
         <f aca="false">ROUNDUP(A36/Wyjaśnienia!$B$46,0)</f>
         <v>500</v>
       </c>
-      <c r="F36" s="26"/>
+      <c r="F36" s="22"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="27" t="n">
+      <c r="A37" s="33" t="n">
         <v>100000</v>
       </c>
-      <c r="B37" s="27" t="n">
+      <c r="B37" s="33" t="n">
         <f aca="false">A37*Wyjaśnienia!$B$42</f>
         <v>200000</v>
       </c>
-      <c r="C37" s="27" t="n">
+      <c r="C37" s="33" t="n">
         <f aca="false">ROUNDUP(B37/100,0)</f>
         <v>2000</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="35" t="n">
         <f aca="false">C37*Wyjaśnienia!$B$43</f>
         <v>1000000</v>
       </c>
-      <c r="E37" s="27" t="n">
+      <c r="E37" s="33" t="n">
         <f aca="false">ROUNDUP(A37/Wyjaśnienia!$B$46,0)</f>
         <v>5000</v>
       </c>
-      <c r="F37" s="26"/>
+      <c r="F37" s="22"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="27" t="n">
+      <c r="A38" s="33" t="n">
         <v>1000000</v>
       </c>
-      <c r="B38" s="27" t="n">
+      <c r="B38" s="33" t="n">
         <f aca="false">A38*Wyjaśnienia!$B$42</f>
         <v>2000000</v>
       </c>
-      <c r="C38" s="27" t="n">
+      <c r="C38" s="33" t="n">
         <f aca="false">ROUNDUP(B38/100,0)</f>
         <v>20000</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="35" t="n">
         <f aca="false">C38*Wyjaśnienia!$B$43</f>
         <v>10000000</v>
       </c>
-      <c r="E38" s="27" t="n">
+      <c r="E38" s="33" t="n">
         <f aca="false">ROUNDUP(A38/Wyjaśnienia!$B$46,0)</f>
         <v>50000</v>
       </c>
-      <c r="F38" s="26"/>
+      <c r="F38" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="226">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -485,9 +485,6 @@
     <t xml:space="preserve">sześć obszarów, w tym licencja i archiwum; obowiązkowa przed naborem</t>
   </si>
   <si>
-    <t xml:space="preserve">sześć obszarów, w tym licencja i archiwum; kwota z zapasem wobec ofert kancelarii</t>
-  </si>
-  <si>
     <t xml:space="preserve">Domeny, poczta, hosting, magazyn kopii archiwalnych</t>
   </si>
   <si>
@@ -542,12 +539,6 @@
     <t xml:space="preserve">Dostęp do narzędzi AI, bez których 937 godzin pracy organizatora nie jest wykonalne; rzędu 2,5 tys. zł miesięcznie</t>
   </si>
   <si>
-    <t xml:space="preserve">Rejestracja znaku towarowego Konstela w EUIPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jedna klasa, ochrona w całej Unii; opłaty urzędowe około 850 euro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Marża (od pracy i kosztów, bez nagród)</t>
   </si>
   <si>
@@ -618,12 +609,6 @@
   </si>
   <si>
     <t xml:space="preserve">DO WYCENY - zależy od miejsca gali, które nie jest wybrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsługa prawna plebiscytu (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">odrębne zlecenie na pytania plebiscytowe; kwota z zapasem wobec ofert kancelarii</t>
   </si>
   <si>
     <t xml:space="preserve">Koszty twarde bez nagród</t>
@@ -873,7 +858,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -900,10 +885,6 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -962,34 +943,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1002,8 +955,8 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1339,7 +1292,7 @@
       <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="3"/>
@@ -1355,7 +1308,7 @@
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="7" t="n">
         <f aca="false">'Budżet Nagrody'!$D$39</f>
         <v>561684.8</v>
       </c>
@@ -1372,9 +1325,9 @@
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="8" t="n">
-        <f aca="false">'Budżet Antologii'!$D$36</f>
-        <v>277550</v>
+      <c r="C7" s="7" t="n">
+        <f aca="false">'Budżet Antologii'!$D$35</f>
+        <v>271700</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -1389,9 +1342,9 @@
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="8" t="n">
-        <f aca="false">'Budżet Plebiscytu'!$D$31</f>
-        <v>261656</v>
+      <c r="C8" s="7" t="n">
+        <f aca="false">'Budżet Plebiscytu'!$D$30</f>
+        <v>256616</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -1406,7 +1359,7 @@
       <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="7" t="n">
         <f aca="false">'Budżet Akademii'!$D$27</f>
         <v>49280</v>
       </c>
@@ -1416,9 +1369,9 @@
         <v>14</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="9" t="n">
-        <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$36+'Budżet Plebiscytu'!$D$31+'Budżet Akademii'!$D$27</f>
-        <v>1150170.8</v>
+      <c r="C10" s="8" t="n">
+        <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$35+'Budżet Plebiscytu'!$D$30+'Budżet Akademii'!$D$27</f>
+        <v>1139280.8</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1462,10 +1415,10 @@
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="9" t="n">
         <v>220</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="3"/>
@@ -1478,10 +1431,10 @@
       <c r="A15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="3"/>
@@ -1494,10 +1447,10 @@
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="9" t="n">
         <v>300000</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="3"/>
@@ -1510,10 +1463,10 @@
       <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="3"/>
@@ -1526,10 +1479,10 @@
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="3"/>
@@ -1542,10 +1495,10 @@
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="3"/>
@@ -1558,10 +1511,10 @@
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="9" t="n">
         <v>35000</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="3"/>
@@ -1574,10 +1527,10 @@
       <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="3"/>
@@ -1590,10 +1543,10 @@
       <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="9" t="n">
         <v>7500</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="3"/>
@@ -1606,10 +1559,10 @@
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="3"/>
@@ -1622,10 +1575,10 @@
       <c r="A24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="9" t="n">
         <v>80000</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>38</v>
       </c>
       <c r="D24" s="3"/>
@@ -1638,10 +1591,10 @@
       <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B25" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>40</v>
       </c>
       <c r="D25" s="3"/>
@@ -1654,10 +1607,10 @@
       <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="11" t="n">
         <v>0.12</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D26" s="3"/>
@@ -1670,10 +1623,10 @@
       <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="11" t="n">
         <v>0.3</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>44</v>
       </c>
       <c r="D27" s="3"/>
@@ -1686,10 +1639,10 @@
       <c r="A28" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="11" t="n">
         <v>0.12</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="3"/>
@@ -1702,10 +1655,10 @@
       <c r="A29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="11" t="n">
         <v>0.23</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>47</v>
       </c>
       <c r="D29" s="3"/>
@@ -1718,10 +1671,10 @@
       <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>49</v>
       </c>
       <c r="D30" s="3"/>
@@ -1832,17 +1785,17 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="10" t="n">
+      <c r="B42" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="3" t="s">
@@ -1853,7 +1806,7 @@
       <c r="A43" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="13" t="n">
         <v>500</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -1864,7 +1817,7 @@
       <c r="A44" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="14" t="n">
+      <c r="B44" s="13" t="n">
         <v>2500</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -1875,7 +1828,7 @@
       <c r="A45" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="10" t="n">
+      <c r="B45" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -1886,7 +1839,7 @@
       <c r="A46" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="10" t="n">
+      <c r="B46" s="9" t="n">
         <v>20</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -2054,16 +2007,16 @@
       <c r="A6" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -2073,264 +2026,264 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="16" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>60</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="17" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>13200</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>79</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="16" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>24</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="17" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>5280</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>81</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="16" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="17" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>83</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="16" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>23</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="17" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>5060</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>85</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="16" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="17" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="10" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="16" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="17" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>89</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="16" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="17" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>91</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="16" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="17" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>93</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="16" t="n">
         <f aca="false">B15+C15*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="17" t="n">
         <f aca="false">D15*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>95</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="16" t="n">
         <f aca="false">B16+C16*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="17" t="n">
         <f aca="false">D16*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>97</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="16" t="n">
         <f aca="false">B17+C17*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="17" t="n">
         <f aca="false">D17*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>99</v>
       </c>
       <c r="G17" s="3"/>
@@ -2342,11 +2295,11 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="18" t="n">
         <f aca="false">SUM(D7:D17)</f>
         <v>372</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <f aca="false">SUM(E7:E17)</f>
         <v>81840</v>
       </c>
@@ -2380,13 +2333,13 @@
       <c r="A21" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="6" t="s">
@@ -2397,20 +2350,20 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B22" s="19" t="n">
         <v>8000</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="17" t="n">
         <f aca="false">B22*C22</f>
         <v>8000</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="10" t="s">
         <v>105</v>
       </c>
       <c r="F22" s="3"/>
@@ -2418,20 +2371,20 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="20" t="n">
+      <c r="B23" s="19" t="n">
         <v>1500</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="17" t="n">
         <f aca="false">B23*C23</f>
         <v>1500</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="10" t="s">
         <v>107</v>
       </c>
       <c r="F23" s="3"/>
@@ -2439,20 +2392,20 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="20" t="n">
+      <c r="B24" s="19" t="n">
         <v>1200</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="17" t="n">
         <f aca="false">B24*C24</f>
         <v>1200</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="10" t="s">
         <v>109</v>
       </c>
       <c r="F24" s="3"/>
@@ -2460,20 +2413,20 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="20" t="n">
+      <c r="B25" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="17" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="10" t="s">
         <v>111</v>
       </c>
       <c r="F25" s="3"/>
@@ -2481,20 +2434,20 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="19" t="n">
         <v>1500</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="17" t="n">
         <f aca="false">B26*C26</f>
         <v>1500</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="10" t="s">
         <v>113</v>
       </c>
       <c r="F26" s="3"/>
@@ -2502,20 +2455,20 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="20" t="n">
+      <c r="B27" s="19" t="n">
         <v>250</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="17" t="n">
         <f aca="false">B27*C27</f>
         <v>250</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="10" t="s">
         <v>115</v>
       </c>
       <c r="F27" s="3"/>
@@ -2523,20 +2476,20 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="20" t="n">
+      <c r="B28" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="17" t="n">
         <f aca="false">B28*C28</f>
         <v>32000</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="10" t="s">
         <v>117</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -2546,20 +2499,20 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="19" t="n">
         <v>15000</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="D29" s="17" t="n">
         <f aca="false">B29*C29</f>
         <v>15000</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="10" t="s">
         <v>120</v>
       </c>
       <c r="F29" s="3"/>
@@ -2567,20 +2520,20 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="19" t="n">
         <v>8000</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="18" t="n">
+      <c r="D30" s="17" t="n">
         <f aca="false">B30*C30</f>
         <v>8000</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="10" t="s">
         <v>122</v>
       </c>
       <c r="F30" s="3"/>
@@ -2588,20 +2541,20 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="20" t="n">
+      <c r="B31" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C31" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="18" t="n">
+      <c r="D31" s="17" t="n">
         <f aca="false">B31*C31</f>
         <v>0</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="10" t="s">
         <v>124</v>
       </c>
       <c r="F31" s="3"/>
@@ -2614,7 +2567,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <f aca="false">SUM(D22:D31)</f>
         <v>71450</v>
       </c>
@@ -2646,12 +2599,12 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="14" t="s">
         <v>127</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="18" t="n">
+      <c r="D35" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$16+Wyjaśnienia!$B$17*Wyjaśnienia!$B$18</f>
         <v>390000</v>
       </c>
@@ -2661,12 +2614,12 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="14" t="s">
         <v>128</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="7" t="n">
         <f aca="false">E18</f>
         <v>81840</v>
       </c>
@@ -2676,12 +2629,12 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="14" t="s">
         <v>129</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="8" t="n">
+      <c r="D37" s="7" t="n">
         <f aca="false">D32</f>
         <v>71450</v>
       </c>
@@ -2691,12 +2644,12 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="14" t="s">
         <v>130</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="7" t="n">
         <f aca="false">(D36+D37)*Wyjaśnienia!$B$26</f>
         <v>18394.8</v>
       </c>
@@ -2711,7 +2664,7 @@
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="9" t="n">
+      <c r="D39" s="8" t="n">
         <f aca="false">SUM(D35:D38)</f>
         <v>561684.8</v>
       </c>
@@ -2721,12 +2674,12 @@
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="14" t="s">
         <v>132</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="8" t="n">
+      <c r="D40" s="7" t="n">
         <f aca="false">D39*Wyjaśnienia!$B$29</f>
         <v>129187.504</v>
       </c>
@@ -2741,7 +2694,7 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="21" t="n">
+      <c r="D41" s="20" t="n">
         <f aca="false">D39+D40</f>
         <v>690872.304</v>
       </c>
@@ -2911,16 +2864,16 @@
       <c r="A6" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -2930,168 +2883,168 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="16" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="17" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>136</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="16" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="17" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>138</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="16" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="17" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>140</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="16" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="17" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>142</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="16" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="17" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="10" t="s">
         <v>144</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="16" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>160</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="17" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>35200</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>146</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="16" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="17" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>148</v>
       </c>
       <c r="G13" s="3"/>
@@ -3103,11 +3056,11 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="18" t="n">
         <f aca="false">SUM(D7:D13)</f>
         <v>400</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <f aca="false">SUM(E7:E13)</f>
         <v>88000</v>
       </c>
@@ -3141,13 +3094,13 @@
       <c r="A17" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>76</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -3158,20 +3111,20 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B18" s="19" t="n">
         <v>3000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="17" t="n">
         <f aca="false">B18*C18</f>
         <v>3000</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="10" t="s">
         <v>150</v>
       </c>
       <c r="F18" s="3"/>
@@ -3179,276 +3132,276 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="B19" s="20" t="n">
+      <c r="B19" s="19" t="n">
         <v>6000</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="17" t="n">
         <f aca="false">B19*C19</f>
         <v>6000</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>153</v>
-      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B20" s="20" t="n">
+      <c r="A20" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="19" t="n">
         <v>10000</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="17" t="n">
         <f aca="false">B20*C20</f>
         <v>10000</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>155</v>
+      <c r="E20" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="B21" s="20" t="n">
+      <c r="A21" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B21" s="19" t="n">
         <v>40000</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="17" t="n">
         <f aca="false">B21*C21</f>
         <v>40000</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>157</v>
+      <c r="E21" s="10" t="s">
+        <v>156</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="B22" s="20" t="n">
+      <c r="A22" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="17" t="n">
         <f aca="false">B22*C22</f>
         <v>4000</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>159</v>
+      <c r="E22" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="B23" s="20" t="n">
+      <c r="A23" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="19" t="n">
         <v>3000</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="17" t="n">
         <f aca="false">B23*C23</f>
         <v>3000</v>
       </c>
-      <c r="E23" s="11" t="s">
-        <v>161</v>
+      <c r="E23" s="10" t="s">
+        <v>160</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="B24" s="20" t="n">
+      <c r="A24" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="17" t="n">
         <f aca="false">B24*C24</f>
         <v>4000</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>163</v>
+      <c r="E24" s="10" t="s">
+        <v>162</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="B25" s="20" t="n">
+      <c r="A25" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="17" t="n">
         <f aca="false">B25*C25</f>
         <v>0</v>
       </c>
-      <c r="E25" s="11" t="s">
-        <v>165</v>
+      <c r="E25" s="10" t="s">
+        <v>164</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="B26" s="20" t="n">
+      <c r="A26" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="19" t="n">
         <v>15000</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="17" t="n">
         <f aca="false">B26*C26</f>
         <v>15000</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>167</v>
+      <c r="E26" s="10" t="s">
+        <v>166</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="B27" s="20" t="n">
+      <c r="A27" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B27" s="19" t="n">
         <v>6000</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="17" t="n">
         <f aca="false">B27*C27</f>
         <v>6000</v>
       </c>
-      <c r="E27" s="11" t="s">
-        <v>169</v>
+      <c r="E27" s="10" t="s">
+        <v>168</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="B28" s="20" t="n">
+      <c r="A28" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="B28" s="19" t="n">
         <v>30000</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="17" t="n">
         <f aca="false">B28*C28</f>
         <v>30000</v>
       </c>
-      <c r="E28" s="11" t="s">
-        <v>171</v>
+      <c r="E28" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="B29" s="23" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C29" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="25" t="n">
-        <f aca="false">B29*C29</f>
-        <v>4500</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>173</v>
-      </c>
+      <c r="A29" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="8" t="n">
+        <f aca="false">SUM(D18:D28)</f>
+        <v>121000</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>125</v>
-      </c>
+      <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="9" t="n">
-        <f aca="false">SUM(D18:D29)</f>
-        <v>125500</v>
-      </c>
+      <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="26"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
+      <c r="A31" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="27" t="s">
-        <v>126</v>
-      </c>
+      <c r="A32" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="7" t="n">
+        <f aca="false">E14</f>
+        <v>88000</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
-        <v>128</v>
+      <c r="A33" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="8" t="n">
-        <f aca="false">E14</f>
-        <v>88000</v>
+      <c r="D33" s="7" t="n">
+        <f aca="false">D29</f>
+        <v>121000</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -3456,14 +3409,14 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
-        <v>129</v>
+      <c r="A34" s="14" t="s">
+        <v>171</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="8" t="n">
-        <f aca="false">D30</f>
-        <v>125500</v>
+      <c r="D34" s="7" t="n">
+        <f aca="false">(D32+D33)*Wyjaśnienia!$B$27</f>
+        <v>62700</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -3471,14 +3424,14 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
-        <v>174</v>
+      <c r="A35" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="8" t="n">
-        <f aca="false">(D33+D34)*Wyjaśnienia!$B$27</f>
-        <v>64050</v>
+        <f aca="false">SUM(D32:D34)</f>
+        <v>271700</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -3486,14 +3439,14 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>131</v>
+      <c r="A36" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="9" t="n">
-        <f aca="false">SUM(D33:D35)</f>
-        <v>277550</v>
+      <c r="D36" s="7" t="n">
+        <f aca="false">D35*Wyjaśnienia!$B$29</f>
+        <v>62491</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -3501,35 +3454,21 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
-        <v>132</v>
+      <c r="A37" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="8" t="n">
-        <f aca="false">D36*Wyjaśnienia!$B$29</f>
-        <v>63836.5</v>
+      <c r="D37" s="20" t="n">
+        <f aca="false">D35+D36</f>
+        <v>334191</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="21" t="n">
-        <f aca="false">D36+D37</f>
-        <v>341386.5</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3646,7 +3585,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3694,16 +3633,16 @@
       <c r="A6" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -3713,121 +3652,121 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="A7" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="16" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$19/60</f>
         <v>25</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="17" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>177</v>
+      <c r="F7" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B8" s="16" t="n">
+      <c r="A8" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="16" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$19/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="17" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>179</v>
+      <c r="F8" s="10" t="s">
+        <v>176</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="16" t="n">
+      <c r="A9" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="16" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$19/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="17" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>181</v>
+      <c r="F9" s="10" t="s">
+        <v>178</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="16" t="n">
+      <c r="A10" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="16" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$19/60</f>
         <v>20</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="17" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>183</v>
+      <c r="F10" s="10" t="s">
+        <v>180</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="B11" s="16" t="n">
+      <c r="A11" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="16" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$19/60</f>
         <v>50</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="17" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>185</v>
+      <c r="F11" s="10" t="s">
+        <v>182</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -3838,11 +3777,11 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="18" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>165</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <f aca="false">SUM(E7:E11)</f>
         <v>36300</v>
       </c>
@@ -3876,13 +3815,13 @@
       <c r="A15" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>76</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -3893,217 +3832,219 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B16" s="18" t="n">
+      <c r="A16" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$20</f>
         <v>35000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="17" t="n">
         <f aca="false">B16*C16</f>
         <v>35000</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>187</v>
+      <c r="E16" s="10" t="s">
+        <v>184</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="B17" s="18" t="n">
+      <c r="A17" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B17" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$21</f>
         <v>4000</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="17" t="n">
         <f aca="false">B17*C17</f>
         <v>4000</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>189</v>
+      <c r="E17" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="B18" s="18" t="n">
+      <c r="A18" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$22</f>
         <v>7500</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="16" t="n">
         <f aca="false">Wyjaśnienia!$B$23</f>
         <v>10</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="17" t="n">
         <f aca="false">B18*C18</f>
         <v>75000</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>191</v>
+      <c r="E18" s="10" t="s">
+        <v>188</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$24</f>
         <v>80000</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="17" t="n">
         <f aca="false">B19*C19</f>
         <v>80000</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>192</v>
+      <c r="E19" s="10" t="s">
+        <v>189</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$25</f>
         <v>3000</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="17" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>193</v>
+      <c r="E20" s="10" t="s">
+        <v>190</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="B21" s="20" t="n">
+      <c r="A21" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="17" t="n">
         <f aca="false">B21*C21</f>
         <v>0</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>195</v>
+      <c r="E21" s="10" t="s">
+        <v>192</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="B22" s="20" t="n">
+      <c r="A22" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="17" t="n">
         <f aca="false">B22*C22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>197</v>
+      <c r="E22" s="10" t="s">
+        <v>194</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="B23" s="14" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C23" s="28" t="n">
-        <v>1</v>
-      </c>
+      <c r="A23" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="8" t="n">
-        <f aca="false">B23*C23</f>
-        <v>4500</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>199</v>
-      </c>
+        <f aca="false">SUM(D16:D22)</f>
+        <v>197000</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>125</v>
-      </c>
+      <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="9" t="n">
-        <f aca="false">SUM(D16:D23)</f>
-        <v>201500</v>
-      </c>
+      <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
+      <c r="A25" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="27" t="s">
-        <v>126</v>
-      </c>
+      <c r="A26" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="17" t="n">
+        <f aca="false">Wyjaśnienia!$B$20+Wyjaśnienia!$B$21</f>
+        <v>39000</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>127</v>
+      <c r="A27" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="18" t="n">
-        <f aca="false">Wyjaśnienia!$B$20+Wyjaśnienia!$B$21</f>
-        <v>39000</v>
+      <c r="D27" s="7" t="n">
+        <f aca="false">E12</f>
+        <v>36300</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -4111,14 +4052,14 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>128</v>
+      <c r="A28" s="14" t="s">
+        <v>195</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="8" t="n">
-        <f aca="false">E12</f>
-        <v>36300</v>
+      <c r="D28" s="7" t="n">
+        <f aca="false">D23-D26</f>
+        <v>158000</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -4126,14 +4067,14 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>200</v>
+      <c r="A29" s="14" t="s">
+        <v>130</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="8" t="n">
-        <f aca="false">D24-D27</f>
-        <v>162500</v>
+      <c r="D29" s="7" t="n">
+        <f aca="false">(D27+D28)*Wyjaśnienia!$B$28</f>
+        <v>23316</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -4141,14 +4082,14 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>130</v>
+      <c r="A30" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="8" t="n">
-        <f aca="false">(D28+D29)*Wyjaśnienia!$B$28</f>
-        <v>23856</v>
+        <f aca="false">SUM(D26:D29)</f>
+        <v>256616</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -4156,14 +4097,14 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>131</v>
+      <c r="A31" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="9" t="n">
-        <f aca="false">SUM(D27:D30)</f>
-        <v>261656</v>
+      <c r="D31" s="7" t="n">
+        <f aca="false">D30*Wyjaśnienia!$B$29</f>
+        <v>59021.68</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -4171,35 +4112,21 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
-        <v>132</v>
+      <c r="A32" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="8" t="n">
-        <f aca="false">D31*Wyjaśnienia!$B$29</f>
-        <v>60180.88</v>
+      <c r="D32" s="20" t="n">
+        <f aca="false">D30+D31</f>
+        <v>315637.68</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="21" t="n">
-        <f aca="false">D31+D32</f>
-        <v>321836.88</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4308,533 +4235,533 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="A2" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
+      <c r="A3" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="A5" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="31" t="s">
+      <c r="B6" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="33" t="n">
+      <c r="A7" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$15</f>
         <v>150</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22" t="s">
-        <v>206</v>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="B8" s="33" t="n">
+      <c r="A8" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$42</f>
         <v>2</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22" t="s">
-        <v>208</v>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="B9" s="34" t="n">
+      <c r="A9" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="26" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="A11" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="C12" s="32" t="s">
+      <c r="B12" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="C12" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="31" t="s">
+      <c r="E12" s="24"/>
+      <c r="F12" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B13" s="35" t="n">
+      <c r="A13" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" s="27" t="n">
         <f aca="false">Wyjaśnienia!$B$44</f>
         <v>2500</v>
       </c>
-      <c r="C13" s="33" t="n">
+      <c r="C13" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$45</f>
         <v>15</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="27" t="n">
         <f aca="false">B13*C13</f>
         <v>37500</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22" t="s">
-        <v>214</v>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="B14" s="35" t="n">
+      <c r="A14" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="27" t="n">
         <f aca="false">Wyjaśnienia!$B$43</f>
         <v>500</v>
       </c>
-      <c r="C14" s="33" t="n">
+      <c r="C14" s="25" t="n">
         <f aca="false">ROUNDUP(B9/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="27" t="n">
         <f aca="false">B14*C14</f>
         <v>1500</v>
       </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22" t="s">
-        <v>216</v>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="36" t="n">
+      <c r="A15" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="28" t="n">
         <f aca="false">SUM(D13:D14)</f>
         <v>39000</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="31" t="s">
+      <c r="E18" s="24"/>
+      <c r="F18" s="23" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="B19" s="37" t="n">
+      <c r="A19" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" s="29" t="n">
         <v>2000</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="27" t="n">
         <f aca="false">B19*C19</f>
         <v>2000</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22" t="s">
-        <v>219</v>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="B20" s="37" t="n">
+      <c r="A20" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="27" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22" t="s">
-        <v>221</v>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="36" t="n">
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="28" t="n">
         <f aca="false">SUM(D19:D20)</f>
         <v>5000</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="35" t="n">
+      <c r="A24" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="27" t="n">
         <f aca="false">D15</f>
         <v>39000</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="35" t="n">
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="27" t="n">
         <f aca="false">D21</f>
         <v>5000</v>
       </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="35" t="n">
+      <c r="A26" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="27" t="n">
         <f aca="false">(D24+D25)*Wyjaśnienia!$B$26</f>
         <v>5280</v>
       </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="36" t="n">
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="28" t="n">
         <f aca="false">SUM(D24:D26)</f>
         <v>49280</v>
       </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="35" t="n">
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="27" t="n">
         <f aca="false">D27*Wyjaśnienia!$B$29</f>
         <v>11334.4</v>
       </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="36" t="n">
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="28" t="n">
         <f aca="false">D27+D28</f>
         <v>60614.4</v>
       </c>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="D33" s="23" t="s">
         <v>224</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30" t="s">
+      <c r="E33" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="B33" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="D33" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="E33" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="F33" s="22"/>
+      <c r="F33" s="24"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="33" t="n">
+      <c r="A34" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="B34" s="33" t="n">
+      <c r="B34" s="25" t="n">
         <f aca="false">A34*Wyjaśnienia!$B$42</f>
         <v>300</v>
       </c>
-      <c r="C34" s="33" t="n">
+      <c r="C34" s="25" t="n">
         <f aca="false">ROUNDUP(B34/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D34" s="35" t="n">
+      <c r="D34" s="27" t="n">
         <f aca="false">C34*Wyjaśnienia!$B$43</f>
         <v>1500</v>
       </c>
-      <c r="E34" s="33" t="n">
+      <c r="E34" s="25" t="n">
         <f aca="false">ROUNDUP(A34/Wyjaśnienia!$B$46,0)</f>
         <v>8</v>
       </c>
-      <c r="F34" s="22"/>
+      <c r="F34" s="24"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="33" t="n">
+      <c r="A35" s="25" t="n">
         <v>1000</v>
       </c>
-      <c r="B35" s="33" t="n">
+      <c r="B35" s="25" t="n">
         <f aca="false">A35*Wyjaśnienia!$B$42</f>
         <v>2000</v>
       </c>
-      <c r="C35" s="33" t="n">
+      <c r="C35" s="25" t="n">
         <f aca="false">ROUNDUP(B35/100,0)</f>
         <v>20</v>
       </c>
-      <c r="D35" s="35" t="n">
+      <c r="D35" s="27" t="n">
         <f aca="false">C35*Wyjaśnienia!$B$43</f>
         <v>10000</v>
       </c>
-      <c r="E35" s="33" t="n">
+      <c r="E35" s="25" t="n">
         <f aca="false">ROUNDUP(A35/Wyjaśnienia!$B$46,0)</f>
         <v>50</v>
       </c>
-      <c r="F35" s="22"/>
+      <c r="F35" s="24"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="33" t="n">
+      <c r="A36" s="25" t="n">
         <v>10000</v>
       </c>
-      <c r="B36" s="33" t="n">
+      <c r="B36" s="25" t="n">
         <f aca="false">A36*Wyjaśnienia!$B$42</f>
         <v>20000</v>
       </c>
-      <c r="C36" s="33" t="n">
+      <c r="C36" s="25" t="n">
         <f aca="false">ROUNDUP(B36/100,0)</f>
         <v>200</v>
       </c>
-      <c r="D36" s="35" t="n">
+      <c r="D36" s="27" t="n">
         <f aca="false">C36*Wyjaśnienia!$B$43</f>
         <v>100000</v>
       </c>
-      <c r="E36" s="33" t="n">
+      <c r="E36" s="25" t="n">
         <f aca="false">ROUNDUP(A36/Wyjaśnienia!$B$46,0)</f>
         <v>500</v>
       </c>
-      <c r="F36" s="22"/>
+      <c r="F36" s="24"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="33" t="n">
+      <c r="A37" s="25" t="n">
         <v>100000</v>
       </c>
-      <c r="B37" s="33" t="n">
+      <c r="B37" s="25" t="n">
         <f aca="false">A37*Wyjaśnienia!$B$42</f>
         <v>200000</v>
       </c>
-      <c r="C37" s="33" t="n">
+      <c r="C37" s="25" t="n">
         <f aca="false">ROUNDUP(B37/100,0)</f>
         <v>2000</v>
       </c>
-      <c r="D37" s="35" t="n">
+      <c r="D37" s="27" t="n">
         <f aca="false">C37*Wyjaśnienia!$B$43</f>
         <v>1000000</v>
       </c>
-      <c r="E37" s="33" t="n">
+      <c r="E37" s="25" t="n">
         <f aca="false">ROUNDUP(A37/Wyjaśnienia!$B$46,0)</f>
         <v>5000</v>
       </c>
-      <c r="F37" s="22"/>
+      <c r="F37" s="24"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="33" t="n">
+      <c r="A38" s="25" t="n">
         <v>1000000</v>
       </c>
-      <c r="B38" s="33" t="n">
+      <c r="B38" s="25" t="n">
         <f aca="false">A38*Wyjaśnienia!$B$42</f>
         <v>2000000</v>
       </c>
-      <c r="C38" s="33" t="n">
+      <c r="C38" s="25" t="n">
         <f aca="false">ROUNDUP(B38/100,0)</f>
         <v>20000</v>
       </c>
-      <c r="D38" s="35" t="n">
+      <c r="D38" s="27" t="n">
         <f aca="false">C38*Wyjaśnienia!$B$43</f>
         <v>10000000</v>
       </c>
-      <c r="E38" s="33" t="n">
+      <c r="E38" s="25" t="n">
         <f aca="false">ROUNDUP(A38/Wyjaśnienia!$B$46,0)</f>
         <v>50000</v>
       </c>
-      <c r="F38" s="22"/>
+      <c r="F38" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="237">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -473,6 +473,9 @@
     <t xml:space="preserve">generowanie stron z kopii, nawigacja, tryb redakcji fragmentów</t>
   </si>
   <si>
+    <t xml:space="preserve">Koordynacja podcastu: goście, terminy, publikacja</t>
+  </si>
+  <si>
     <t xml:space="preserve">Powołanie fundacji-organizatora</t>
   </si>
   <si>
@@ -485,6 +488,9 @@
     <t xml:space="preserve">sześć obszarów, w tym licencja i archiwum; obowiązkowa przed naborem</t>
   </si>
   <si>
+    <t xml:space="preserve">sześć obszarów, w tym licencja i archiwum; kwota z zapasem wobec ofert kancelarii</t>
+  </si>
+  <si>
     <t xml:space="preserve">Domeny, poczta, hosting, magazyn kopii archiwalnych</t>
   </si>
   <si>
@@ -539,6 +545,18 @@
     <t xml:space="preserve">Dostęp do narzędzi AI, bez których 937 godzin pracy organizatora nie jest wykonalne; rzędu 2,5 tys. zł miesięcznie</t>
   </si>
   <si>
+    <t xml:space="preserve">Rejestracja znaku towarowego Konstela w EUIPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jedna klasa, ochrona w całej Unii; opłaty urzędowe około 850 euro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkcja podcastu wraz z honorarium prowadzącego (24 odcinki)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - nagranie, montaż, dźwięk, wersja wideo i dystrybucja; honorarium prowadzącego nieustalone</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marża (od pracy i kosztów, bez nagród)</t>
   </si>
   <si>
@@ -609,6 +627,21 @@
   </si>
   <si>
     <t xml:space="preserve">DO WYCENY - zależy od miejsca gali, które nie jest wybrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa prawna plebiscytu (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - zakres plebiscytowy nie był objęty wyceną z 22.10.2026; osobne zlecenie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">odrębne zlecenie na pytania plebiscytowe; kwota z zapasem wobec ofert kancelarii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dojazd i nocleg dziesięciu finalistów na galę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - udział czołowej trójki obowiązkowy (§ 14 regulaminu plebiscytu), pokrycie dla całej dziesiątki</t>
   </si>
   <si>
     <t xml:space="preserve">Koszty twarde bez nagród</t>
@@ -858,7 +891,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -885,6 +918,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -943,6 +980,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -955,8 +1004,8 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1292,7 +1341,7 @@
       <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="3"/>
@@ -1308,7 +1357,7 @@
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <f aca="false">'Budżet Nagrody'!$D$39</f>
         <v>561684.8</v>
       </c>
@@ -1325,9 +1374,9 @@
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="7" t="n">
-        <f aca="false">'Budżet Antologii'!$D$35</f>
-        <v>271700</v>
+      <c r="C7" s="8" t="n">
+        <f aca="false">'Budżet Antologii'!$D$38</f>
+        <v>298142</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -1342,8 +1391,8 @@
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <f aca="false">'Budżet Plebiscytu'!$D$30</f>
+      <c r="C8" s="8" t="n">
+        <f aca="false">'Budżet Plebiscytu'!$D$32</f>
         <v>256616</v>
       </c>
       <c r="D8" s="3"/>
@@ -1359,7 +1408,7 @@
       <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <f aca="false">'Budżet Akademii'!$D$27</f>
         <v>49280</v>
       </c>
@@ -1369,9 +1418,9 @@
         <v>14</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="8" t="n">
-        <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$35+'Budżet Plebiscytu'!$D$30+'Budżet Akademii'!$D$27</f>
-        <v>1139280.8</v>
+      <c r="C10" s="9" t="n">
+        <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Akademii'!$D$27</f>
+        <v>1165722.8</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1415,10 +1464,10 @@
       <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="10" t="n">
         <v>220</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="3"/>
@@ -1431,10 +1480,10 @@
       <c r="A15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="3"/>
@@ -1447,10 +1496,10 @@
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="10" t="n">
         <v>300000</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="3"/>
@@ -1463,10 +1512,10 @@
       <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="3"/>
@@ -1479,10 +1528,10 @@
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>26</v>
       </c>
       <c r="D18" s="3"/>
@@ -1495,10 +1544,10 @@
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="10" t="n">
         <v>150</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D19" s="3"/>
@@ -1511,10 +1560,10 @@
       <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="10" t="n">
         <v>35000</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="3"/>
@@ -1527,10 +1576,10 @@
       <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="10" t="n">
         <v>4000</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="3"/>
@@ -1543,10 +1592,10 @@
       <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="10" t="n">
         <v>7500</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="11" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="3"/>
@@ -1559,10 +1608,10 @@
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="11" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="3"/>
@@ -1575,10 +1624,10 @@
       <c r="A24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="10" t="n">
         <v>80000</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="11" t="s">
         <v>38</v>
       </c>
       <c r="D24" s="3"/>
@@ -1591,10 +1640,10 @@
       <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="10" t="n">
         <v>3000</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="11" t="s">
         <v>40</v>
       </c>
       <c r="D25" s="3"/>
@@ -1607,10 +1656,10 @@
       <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="11" t="s">
         <v>42</v>
       </c>
       <c r="D26" s="3"/>
@@ -1623,10 +1672,10 @@
       <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B27" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>44</v>
       </c>
       <c r="D27" s="3"/>
@@ -1639,10 +1688,10 @@
       <c r="A28" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="11" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="3"/>
@@ -1655,10 +1704,10 @@
       <c r="A29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B29" s="11" t="n">
+      <c r="B29" s="12" t="n">
         <v>0.23</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="11" t="s">
         <v>47</v>
       </c>
       <c r="D29" s="3"/>
@@ -1671,10 +1720,10 @@
       <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="11" t="s">
         <v>49</v>
       </c>
       <c r="D30" s="3"/>
@@ -1785,17 +1834,17 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B42" s="9" t="n">
+      <c r="B42" s="10" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="3" t="s">
@@ -1806,7 +1855,7 @@
       <c r="A43" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="14" t="n">
         <v>500</v>
       </c>
       <c r="C43" s="3" t="s">
@@ -1817,7 +1866,7 @@
       <c r="A44" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="13" t="n">
+      <c r="B44" s="14" t="n">
         <v>2500</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -1828,7 +1877,7 @@
       <c r="A45" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="9" t="n">
+      <c r="B45" s="10" t="n">
         <v>15</v>
       </c>
       <c r="C45" s="3" t="s">
@@ -1839,7 +1888,7 @@
       <c r="A46" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B46" s="9" t="n">
+      <c r="B46" s="10" t="n">
         <v>20</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -2007,16 +2056,16 @@
       <c r="A6" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -2026,264 +2075,264 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="16" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>60</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>13200</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>79</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>24</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>5280</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>81</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>83</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>23</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>5060</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>85</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>87</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>89</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="11" t="s">
         <v>91</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="11" t="s">
         <v>93</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <f aca="false">B15+C15*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <f aca="false">D15*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="11" t="s">
         <v>95</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <f aca="false">B16+C16*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <f aca="false">D16*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="11" t="s">
         <v>97</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <f aca="false">B17+C17*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <f aca="false">D17*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="11" t="s">
         <v>99</v>
       </c>
       <c r="G17" s="3"/>
@@ -2295,11 +2344,11 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="19" t="n">
         <f aca="false">SUM(D7:D17)</f>
         <v>372</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="9" t="n">
         <f aca="false">SUM(E7:E17)</f>
         <v>81840</v>
       </c>
@@ -2333,13 +2382,13 @@
       <c r="A21" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>76</v>
       </c>
       <c r="E21" s="6" t="s">
@@ -2350,20 +2399,20 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="20" t="n">
         <v>8000</v>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="18" t="n">
         <f aca="false">B22*C22</f>
         <v>8000</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="11" t="s">
         <v>105</v>
       </c>
       <c r="F22" s="3"/>
@@ -2371,20 +2420,20 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B23" s="20" t="n">
         <v>1500</v>
       </c>
-      <c r="C23" s="15" t="n">
+      <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="18" t="n">
         <f aca="false">B23*C23</f>
         <v>1500</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="11" t="s">
         <v>107</v>
       </c>
       <c r="F23" s="3"/>
@@ -2392,20 +2441,20 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B24" s="20" t="n">
         <v>1200</v>
       </c>
-      <c r="C24" s="15" t="n">
+      <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="18" t="n">
         <f aca="false">B24*C24</f>
         <v>1200</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="11" t="s">
         <v>109</v>
       </c>
       <c r="F24" s="3"/>
@@ -2413,20 +2462,20 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B25" s="20" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="15" t="n">
+      <c r="C25" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="18" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="11" t="s">
         <v>111</v>
       </c>
       <c r="F25" s="3"/>
@@ -2434,20 +2483,20 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B26" s="20" t="n">
         <v>1500</v>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C26" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <f aca="false">B26*C26</f>
         <v>1500</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="11" t="s">
         <v>113</v>
       </c>
       <c r="F26" s="3"/>
@@ -2455,20 +2504,20 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="19" t="n">
+      <c r="B27" s="20" t="n">
         <v>250</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <f aca="false">B27*C27</f>
         <v>250</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="11" t="s">
         <v>115</v>
       </c>
       <c r="F27" s="3"/>
@@ -2476,20 +2525,20 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="19" t="n">
+      <c r="B28" s="20" t="n">
         <v>32000</v>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <f aca="false">B28*C28</f>
         <v>32000</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="11" t="s">
         <v>117</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -2499,20 +2548,20 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B29" s="19" t="n">
+      <c r="B29" s="20" t="n">
         <v>15000</v>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="18" t="n">
         <f aca="false">B29*C29</f>
         <v>15000</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="11" t="s">
         <v>120</v>
       </c>
       <c r="F29" s="3"/>
@@ -2520,20 +2569,20 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B30" s="19" t="n">
+      <c r="B30" s="20" t="n">
         <v>8000</v>
       </c>
-      <c r="C30" s="15" t="n">
+      <c r="C30" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="18" t="n">
         <f aca="false">B30*C30</f>
         <v>8000</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="11" t="s">
         <v>122</v>
       </c>
       <c r="F30" s="3"/>
@@ -2541,20 +2590,20 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="15" t="n">
+      <c r="C31" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="18" t="n">
         <f aca="false">B31*C31</f>
         <v>0</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="11" t="s">
         <v>124</v>
       </c>
       <c r="F31" s="3"/>
@@ -2567,7 +2616,7 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="9" t="n">
         <f aca="false">SUM(D22:D31)</f>
         <v>71450</v>
       </c>
@@ -2599,12 +2648,12 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="15" t="s">
         <v>127</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="17" t="n">
+      <c r="D35" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$16+Wyjaśnienia!$B$17*Wyjaśnienia!$B$18</f>
         <v>390000</v>
       </c>
@@ -2614,12 +2663,12 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="15" t="s">
         <v>128</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="7" t="n">
+      <c r="D36" s="8" t="n">
         <f aca="false">E18</f>
         <v>81840</v>
       </c>
@@ -2629,12 +2678,12 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="15" t="s">
         <v>129</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="7" t="n">
+      <c r="D37" s="8" t="n">
         <f aca="false">D32</f>
         <v>71450</v>
       </c>
@@ -2644,12 +2693,12 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="15" t="s">
         <v>130</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="7" t="n">
+      <c r="D38" s="8" t="n">
         <f aca="false">(D36+D37)*Wyjaśnienia!$B$26</f>
         <v>18394.8</v>
       </c>
@@ -2664,7 +2713,7 @@
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="9" t="n">
         <f aca="false">SUM(D35:D38)</f>
         <v>561684.8</v>
       </c>
@@ -2674,12 +2723,12 @@
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="15" t="s">
         <v>132</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="8" t="n">
         <f aca="false">D39*Wyjaśnienia!$B$29</f>
         <v>129187.504</v>
       </c>
@@ -2694,7 +2743,7 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="20" t="n">
+      <c r="D41" s="21" t="n">
         <f aca="false">D39+D40</f>
         <v>690872.304</v>
       </c>
@@ -2864,16 +2913,16 @@
       <c r="A6" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -2883,311 +2932,312 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>136</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>138</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>140</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>142</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>144</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="16" t="n">
         <v>160</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>160</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>35200</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>146</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="11" t="s">
         <v>148</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <f aca="false">B14+C14*Wyjaśnienia!$B$15/60</f>
+        <v>72</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <f aca="false">D14*Wyjaśnienia!$B$14</f>
+        <v>15840</v>
+      </c>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="18" t="n">
-        <f aca="false">SUM(D7:D13)</f>
-        <v>400</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <f aca="false">SUM(E7:E13)</f>
-        <v>88000</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+      <c r="D15" s="19" t="n">
+        <f aca="false">SUM(D7:D14)</f>
+        <v>472</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <f aca="false">SUM(E7:E14)</f>
+        <v>103840</v>
+      </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F17" s="3"/>
+      <c r="A17" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="B18" s="19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="17" t="n">
-        <f aca="false">B18*C18</f>
-        <v>3000</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>150</v>
+      <c r="A18" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <f aca="false">B19*C19</f>
+        <v>3000</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="B19" s="19" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C19" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="17" t="n">
-        <f aca="false">B19*C19</f>
-        <v>6000</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>152</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="20" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <f aca="false">B20*C20</f>
+        <v>6000</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="19" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="17" t="n">
-        <f aca="false">B20*C20</f>
-        <v>10000</v>
-      </c>
-      <c r="E20" s="10" t="s">
+      <c r="F20" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B21" s="19" t="n">
-        <v>40000</v>
-      </c>
-      <c r="C21" s="15" t="n">
+      <c r="B21" s="20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">B21*C21</f>
-        <v>40000</v>
-      </c>
-      <c r="E21" s="10" t="s">
+        <v>10000</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>156</v>
       </c>
       <c r="F21" s="3"/>
@@ -3195,20 +3245,20 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B22" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C22" s="15" t="n">
+      <c r="B22" s="20" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="18" t="n">
         <f aca="false">B22*C22</f>
-        <v>4000</v>
-      </c>
-      <c r="E22" s="10" t="s">
+        <v>40000</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>158</v>
       </c>
       <c r="F22" s="3"/>
@@ -3216,20 +3266,20 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C23" s="15" t="n">
+      <c r="B23" s="20" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="18" t="n">
         <f aca="false">B23*C23</f>
-        <v>3000</v>
-      </c>
-      <c r="E23" s="10" t="s">
+        <v>4000</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>160</v>
       </c>
       <c r="F23" s="3"/>
@@ -3237,20 +3287,20 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C24" s="15" t="n">
+      <c r="B24" s="20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="18" t="n">
         <f aca="false">B24*C24</f>
-        <v>4000</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>162</v>
       </c>
       <c r="F24" s="3"/>
@@ -3258,20 +3308,20 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="B25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="15" t="n">
+      <c r="B25" s="20" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C25" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="18" t="n">
         <f aca="false">B25*C25</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="10" t="s">
+        <v>4000</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>164</v>
       </c>
       <c r="F25" s="3"/>
@@ -3279,20 +3329,20 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="19" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C26" s="15" t="n">
+      <c r="B26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <f aca="false">B26*C26</f>
-        <v>15000</v>
-      </c>
-      <c r="E26" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" s="11" t="s">
         <v>166</v>
       </c>
       <c r="F26" s="3"/>
@@ -3300,20 +3350,20 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="19" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C27" s="15" t="n">
+      <c r="B27" s="20" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C27" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <f aca="false">B27*C27</f>
-        <v>6000</v>
-      </c>
-      <c r="E27" s="10" t="s">
+        <v>15000</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>168</v>
       </c>
       <c r="F27" s="3"/>
@@ -3321,20 +3371,20 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B28" s="19" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C28" s="15" t="n">
+      <c r="B28" s="20" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C28" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <f aca="false">B28*C28</f>
-        <v>30000</v>
-      </c>
-      <c r="E28" s="10" t="s">
+        <v>6000</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>170</v>
       </c>
       <c r="F28" s="3"/>
@@ -3342,51 +3392,72 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="8" t="n">
-        <f aca="false">SUM(D18:D28)</f>
-        <v>121000</v>
-      </c>
-      <c r="E29" s="3"/>
+      <c r="A29" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <f aca="false">B29*C29</f>
+        <v>30000</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>172</v>
+      </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
+      <c r="A30" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <f aca="false">B30*C30</f>
+        <v>4500</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="A31" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <f aca="false">B31*C31</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
-        <v>128</v>
+      <c r="A32" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="7" t="n">
-        <f aca="false">E14</f>
-        <v>88000</v>
+      <c r="D32" s="9" t="n">
+        <f aca="false">SUM(D19:D31)</f>
+        <v>125500</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -3394,44 +3465,36 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="7" t="n">
-        <f aca="false">D29</f>
-        <v>121000</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="7" t="n">
-        <f aca="false">(D32+D33)*Wyjaśnienia!$B$27</f>
-        <v>62700</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
+      <c r="A34" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>131</v>
+      <c r="A35" s="15" t="s">
+        <v>128</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="8" t="n">
-        <f aca="false">SUM(D32:D34)</f>
-        <v>271700</v>
+        <f aca="false">E15</f>
+        <v>103840</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -3439,14 +3502,14 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
-        <v>132</v>
+      <c r="A36" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="7" t="n">
-        <f aca="false">D35*Wyjaśnienia!$B$29</f>
-        <v>62491</v>
+      <c r="D36" s="8" t="n">
+        <f aca="false">D32</f>
+        <v>125500</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -3454,23 +3517,65 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
-        <v>133</v>
+      <c r="A37" s="15" t="s">
+        <v>177</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="20" t="n">
-        <f aca="false">D35+D36</f>
-        <v>334191</v>
+      <c r="D37" s="8" t="n">
+        <f aca="false">(D35+D36)*Wyjaśnienia!$B$27</f>
+        <v>68802</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="9" t="n">
+        <f aca="false">SUM(D35:D37)</f>
+        <v>298142</v>
+      </c>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="8" t="n">
+        <f aca="false">D38*Wyjaśnienia!$B$29</f>
+        <v>68572.66</v>
+      </c>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="21" t="n">
+        <f aca="false">D38+D39</f>
+        <v>366714.66</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+    </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3537,13 +3642,14 @@
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:F34"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3585,7 +3691,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3633,16 +3739,16 @@
       <c r="A6" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>76</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -3652,121 +3758,121 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" s="15" t="n">
+      <c r="A7" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$19/60</f>
         <v>25</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>174</v>
+      <c r="F7" s="11" t="s">
+        <v>180</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" s="15" t="n">
+      <c r="A8" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$19/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>176</v>
+      <c r="F8" s="11" t="s">
+        <v>182</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9" s="15" t="n">
+      <c r="A9" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$19/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>178</v>
+      <c r="F9" s="11" t="s">
+        <v>184</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="B10" s="15" t="n">
+      <c r="A10" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$19/60</f>
         <v>20</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>180</v>
+      <c r="F10" s="11" t="s">
+        <v>186</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="15" t="n">
+      <c r="A11" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$19/60</f>
         <v>50</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>182</v>
+      <c r="F11" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -3777,11 +3883,11 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>165</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="9" t="n">
         <f aca="false">SUM(E7:E11)</f>
         <v>36300</v>
       </c>
@@ -3815,13 +3921,13 @@
       <c r="A15" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>76</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -3832,234 +3938,244 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="17" t="n">
+      <c r="A16" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$20</f>
         <v>35000</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <f aca="false">B16*C16</f>
         <v>35000</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>184</v>
+      <c r="E16" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="B17" s="17" t="n">
+      <c r="A17" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B17" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$21</f>
         <v>4000</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <f aca="false">B17*C17</f>
         <v>4000</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>186</v>
+      <c r="E17" s="11" t="s">
+        <v>192</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="17" t="n">
+      <c r="A18" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$22</f>
         <v>7500</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <f aca="false">Wyjaśnienia!$B$23</f>
         <v>10</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <f aca="false">B18*C18</f>
         <v>75000</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>188</v>
+      <c r="E18" s="11" t="s">
+        <v>194</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$24</f>
         <v>80000</v>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <f aca="false">B19*C19</f>
         <v>80000</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>189</v>
+      <c r="E19" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$25</f>
         <v>3000</v>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>190</v>
+      <c r="E20" s="11" t="s">
+        <v>196</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="B21" s="19" t="n">
+      <c r="A21" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="B21" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">B21*C21</f>
         <v>0</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>192</v>
+      <c r="E21" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="19" t="n">
+      <c r="A22" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="B22" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="18" t="n">
         <f aca="false">B22*C22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>194</v>
+      <c r="E22" s="11" t="s">
+        <v>200</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <f aca="false">B23*C23</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <f aca="false">B24*C24</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F24" s="22"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="8" t="n">
-        <f aca="false">SUM(D16:D22)</f>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="19" t="n">
+        <f aca="false">SUM(D16:D24)</f>
         <v>197000</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="17" t="n">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="18" t="n">
         <f aca="false">Wyjaśnienia!$B$20+Wyjaśnienia!$B$21</f>
         <v>39000</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="7" t="n">
-        <f aca="false">E12</f>
-        <v>36300</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="7" t="n">
-        <f aca="false">D23-D26</f>
-        <v>158000</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -4067,14 +4183,14 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="s">
-        <v>130</v>
+      <c r="A29" s="15" t="s">
+        <v>128</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="7" t="n">
-        <f aca="false">(D27+D28)*Wyjaśnienia!$B$28</f>
-        <v>23316</v>
+      <c r="D29" s="8" t="n">
+        <f aca="false">E12</f>
+        <v>36300</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -4082,14 +4198,14 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>131</v>
+      <c r="A30" s="15" t="s">
+        <v>206</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="8" t="n">
-        <f aca="false">SUM(D26:D29)</f>
-        <v>256616</v>
+        <f aca="false">D25-D28</f>
+        <v>158000</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -4097,14 +4213,14 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
-        <v>132</v>
+      <c r="A31" s="15" t="s">
+        <v>130</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="7" t="n">
-        <f aca="false">D30*Wyjaśnienia!$B$29</f>
-        <v>59021.68</v>
+      <c r="D31" s="8" t="n">
+        <f aca="false">(D29+D30)*Wyjaśnienia!$B$28</f>
+        <v>23316</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -4113,21 +4229,49 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="20" t="n">
-        <f aca="false">D30+D31</f>
-        <v>315637.68</v>
+      <c r="D32" s="9" t="n">
+        <f aca="false">SUM(D28:D31)</f>
+        <v>256616</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="8" t="n">
+        <f aca="false">D32*Wyjaśnienia!$B$29</f>
+        <v>59021.68</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="21" t="n">
+        <f aca="false">D32+D33</f>
+        <v>315637.68</v>
+      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+    </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4200,13 +4344,14 @@
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4235,533 +4380,533 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="A2" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
+      <c r="A3" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
+      <c r="A5" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="23" t="s">
+      <c r="B6" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="25" t="n">
+      <c r="A7" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="B7" s="29" t="n">
         <f aca="false">Wyjaśnienia!$B$15</f>
         <v>150</v>
       </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24" t="s">
-        <v>201</v>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="25" t="n">
+      <c r="A8" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="B8" s="29" t="n">
         <f aca="false">Wyjaśnienia!$B$42</f>
         <v>2</v>
       </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24" t="s">
-        <v>203</v>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" s="26" t="n">
+      <c r="A9" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="30" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="A11" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="24"/>
-      <c r="F12" s="23" t="s">
+      <c r="E12" s="22"/>
+      <c r="F12" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="27" t="n">
+      <c r="A13" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="31" t="n">
         <f aca="false">Wyjaśnienia!$B$44</f>
         <v>2500</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="29" t="n">
         <f aca="false">Wyjaśnienia!$B$45</f>
         <v>15</v>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="31" t="n">
         <f aca="false">B13*C13</f>
         <v>37500</v>
       </c>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24" t="s">
-        <v>209</v>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="B14" s="27" t="n">
+      <c r="A14" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="B14" s="31" t="n">
         <f aca="false">Wyjaśnienia!$B$43</f>
         <v>500</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="29" t="n">
         <f aca="false">ROUNDUP(B9/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="31" t="n">
         <f aca="false">B14*C14</f>
         <v>1500</v>
       </c>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24" t="s">
-        <v>211</v>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="28" t="n">
+      <c r="A15" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="32" t="n">
         <f aca="false">SUM(D13:D14)</f>
         <v>39000</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="24"/>
-      <c r="F18" s="23" t="s">
+      <c r="E18" s="22"/>
+      <c r="F18" s="27" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="B19" s="29" t="n">
+      <c r="A19" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="B19" s="33" t="n">
         <v>2000</v>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D19" s="31" t="n">
         <f aca="false">B19*C19</f>
         <v>2000</v>
       </c>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24" t="s">
-        <v>214</v>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="B20" s="29" t="n">
+      <c r="A20" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" s="33" t="n">
         <v>3000</v>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C20" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="31" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24" t="s">
-        <v>216</v>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="28" t="n">
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="32" t="n">
         <f aca="false">SUM(D19:D20)</f>
         <v>5000</v>
       </c>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="27" t="n">
+      <c r="A24" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="31" t="n">
         <f aca="false">D15</f>
         <v>39000</v>
       </c>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="27" t="n">
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="31" t="n">
         <f aca="false">D21</f>
         <v>5000</v>
       </c>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="27" t="n">
+      <c r="A26" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="31" t="n">
         <f aca="false">(D24+D25)*Wyjaśnienia!$B$26</f>
         <v>5280</v>
       </c>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="28" t="n">
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="32" t="n">
         <f aca="false">SUM(D24:D26)</f>
         <v>49280</v>
       </c>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="27" t="n">
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="31" t="n">
         <f aca="false">D27*Wyjaśnienia!$B$29</f>
         <v>11334.4</v>
       </c>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="28" t="n">
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="32" t="n">
         <f aca="false">D27+D28</f>
         <v>60614.4</v>
       </c>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
+      <c r="A31" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
+      <c r="A32" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="F33" s="24"/>
+      <c r="A33" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="F33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="25" t="n">
+      <c r="A34" s="29" t="n">
         <v>150</v>
       </c>
-      <c r="B34" s="25" t="n">
+      <c r="B34" s="29" t="n">
         <f aca="false">A34*Wyjaśnienia!$B$42</f>
         <v>300</v>
       </c>
-      <c r="C34" s="25" t="n">
+      <c r="C34" s="29" t="n">
         <f aca="false">ROUNDUP(B34/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D34" s="27" t="n">
+      <c r="D34" s="31" t="n">
         <f aca="false">C34*Wyjaśnienia!$B$43</f>
         <v>1500</v>
       </c>
-      <c r="E34" s="25" t="n">
+      <c r="E34" s="29" t="n">
         <f aca="false">ROUNDUP(A34/Wyjaśnienia!$B$46,0)</f>
         <v>8</v>
       </c>
-      <c r="F34" s="24"/>
+      <c r="F34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="25" t="n">
+      <c r="A35" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="B35" s="25" t="n">
+      <c r="B35" s="29" t="n">
         <f aca="false">A35*Wyjaśnienia!$B$42</f>
         <v>2000</v>
       </c>
-      <c r="C35" s="25" t="n">
+      <c r="C35" s="29" t="n">
         <f aca="false">ROUNDUP(B35/100,0)</f>
         <v>20</v>
       </c>
-      <c r="D35" s="27" t="n">
+      <c r="D35" s="31" t="n">
         <f aca="false">C35*Wyjaśnienia!$B$43</f>
         <v>10000</v>
       </c>
-      <c r="E35" s="25" t="n">
+      <c r="E35" s="29" t="n">
         <f aca="false">ROUNDUP(A35/Wyjaśnienia!$B$46,0)</f>
         <v>50</v>
       </c>
-      <c r="F35" s="24"/>
+      <c r="F35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="25" t="n">
+      <c r="A36" s="29" t="n">
         <v>10000</v>
       </c>
-      <c r="B36" s="25" t="n">
+      <c r="B36" s="29" t="n">
         <f aca="false">A36*Wyjaśnienia!$B$42</f>
         <v>20000</v>
       </c>
-      <c r="C36" s="25" t="n">
+      <c r="C36" s="29" t="n">
         <f aca="false">ROUNDUP(B36/100,0)</f>
         <v>200</v>
       </c>
-      <c r="D36" s="27" t="n">
+      <c r="D36" s="31" t="n">
         <f aca="false">C36*Wyjaśnienia!$B$43</f>
         <v>100000</v>
       </c>
-      <c r="E36" s="25" t="n">
+      <c r="E36" s="29" t="n">
         <f aca="false">ROUNDUP(A36/Wyjaśnienia!$B$46,0)</f>
         <v>500</v>
       </c>
-      <c r="F36" s="24"/>
+      <c r="F36" s="22"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="25" t="n">
+      <c r="A37" s="29" t="n">
         <v>100000</v>
       </c>
-      <c r="B37" s="25" t="n">
+      <c r="B37" s="29" t="n">
         <f aca="false">A37*Wyjaśnienia!$B$42</f>
         <v>200000</v>
       </c>
-      <c r="C37" s="25" t="n">
+      <c r="C37" s="29" t="n">
         <f aca="false">ROUNDUP(B37/100,0)</f>
         <v>2000</v>
       </c>
-      <c r="D37" s="27" t="n">
+      <c r="D37" s="31" t="n">
         <f aca="false">C37*Wyjaśnienia!$B$43</f>
         <v>1000000</v>
       </c>
-      <c r="E37" s="25" t="n">
+      <c r="E37" s="29" t="n">
         <f aca="false">ROUNDUP(A37/Wyjaśnienia!$B$46,0)</f>
         <v>5000</v>
       </c>
-      <c r="F37" s="24"/>
+      <c r="F37" s="22"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="25" t="n">
+      <c r="A38" s="29" t="n">
         <v>1000000</v>
       </c>
-      <c r="B38" s="25" t="n">
+      <c r="B38" s="29" t="n">
         <f aca="false">A38*Wyjaśnienia!$B$42</f>
         <v>2000000</v>
       </c>
-      <c r="C38" s="25" t="n">
+      <c r="C38" s="29" t="n">
         <f aca="false">ROUNDUP(B38/100,0)</f>
         <v>20000</v>
       </c>
-      <c r="D38" s="27" t="n">
+      <c r="D38" s="31" t="n">
         <f aca="false">C38*Wyjaśnienia!$B$43</f>
         <v>10000000</v>
       </c>
-      <c r="E38" s="25" t="n">
+      <c r="E38" s="29" t="n">
         <f aca="false">ROUNDUP(A38/Wyjaśnienia!$B$46,0)</f>
         <v>50000</v>
       </c>
-      <c r="F38" s="24"/>
+      <c r="F38" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Budżet Nagrody" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Budżet Antologii" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Budżet Plebiscytu" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Budżet Akademii" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Budżet Plakatu" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Budżet Akademii" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="292">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
   <si>
-    <t xml:space="preserve">Cztery osobne budżety, bo każdy sponsor finansuje nazwany zakres, a nie udział w całości.</t>
+    <t xml:space="preserve">Pięć osobnych budżetów, bo każdy sponsor finansuje nazwany zakres, a nie udział w całości.</t>
   </si>
   <si>
     <t xml:space="preserve">ILE I OD KOGO</t>
@@ -68,6 +69,12 @@
     <t xml:space="preserve">Sponsor Akademii (np. sieć handlowa - vouchery)</t>
   </si>
   <si>
+    <t xml:space="preserve">Budżet Plakatu - plebiscyt na plakat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecenas konkursu plakatu</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAZEM</t>
   </si>
   <si>
@@ -188,7 +195,7 @@
     <t xml:space="preserve">Realizacja części artystycznej gali</t>
   </si>
   <si>
-    <t xml:space="preserve">Po wpisaniu obu kwota Budżetu Plebiscytu wzrośnie.</t>
+    <t xml:space="preserve">Po wpisaniu tych kwot rosną Budżet Plebiscytu i Budżet Plakatu. W Budżecie Plakatu czekają na wycenę trzy pozycje: wystawa, obsługa prawna i dojazdy finalistów.</t>
   </si>
   <si>
     <t xml:space="preserve">JAK CZYTAĆ BUDŻETY</t>
@@ -233,6 +240,75 @@
     <t xml:space="preserve">Z regulaminu. Wyznacza, ilu ludzi trzeba przy danym wolumenie.</t>
   </si>
   <si>
+    <t xml:space="preserve">PLAKAT - PARAMETRY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liczba zgłoszeń plakatów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wpływa na koszt kontroli formalnej.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagrody plakatu łącznie (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 tys. + 25 tys. + 15 tys. dla czołowej trójki.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagroda publiczności plakatu (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jedna nagroda, bez nagrody za uzasadnienie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statuetki i dyplomy plakatu (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jak przy plebiscycie piosenki.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liczba jurorów plakatu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Składu jeszcze nie ma. Przy trzech pozycja spada do 8,7 tys., przy siedmiu rośnie do 20,3 tys.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Godzin oceny na jurora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oglądanie reprodukcji jest szybsze niż odsłuch utworów; przy Kapitule przyjęto 15 h.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stawka jury plakatu za godzinę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stawka przyjęta dla Kapituły oceniającej rozmowy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liczba prac finałowych</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dziesiątka, której oryginały jadą na wystawę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport jednej pracy w jedną stronę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szacunek, nie oferta. Format do 150 cm przekracza limity standardowych przesyłek.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ubezpieczenie prac na czas wystawy (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szacunek przy sumie deklarowanej rzędu 100 tys. zł dla całej dziesiątki.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezerwa w Budżecie Plakatu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narzut na nieprzewidziane, jak w pozostałych budżetach.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Finansuje: Fundator puli nagród. Kwoty netto, chyba że napisano inaczej.</t>
   </si>
   <si>
@@ -645,6 +721,96 @@
   </si>
   <si>
     <t xml:space="preserve">Koszty twarde bez nagród</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finansuje: Mecenas konkursu plakatu. Kwoty netto, chyba że napisano inaczej.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrola formalna zgłoszeń plakatów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">format, proporcje, rozdzielczość, oświadczenia; 8 minut na zgłoszenie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa jury plakatu: przydziały, preselekcja, obrady, werdykt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">werdykt zapada przed galą, bo okładka antologii idzie do druku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ukryte liczniki, ogłoszenie na gali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przyjęcie, ewidencja i zwrot oryginałów finalistów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protokoły odbioru, stan prac, ubezpieczenie, wysyłka powrotna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uzgodnienie okładki antologii ze zwycięzcą</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zgoda w 7 dni po werdykcie, typografia, kadrowanie, redakcja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dotarcie do szkół artystycznych i środowiska ilustratorów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASP, licea plastyczne, grupy ilustratorów, konkursy plakatowe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa licytacji: warunki, zgody, rozliczenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propozycja po zamknięciu ocen, podział 50/50, rozliczenie na piśmie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagrody plakatu (brutto dla laureatów)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">czołowa trójka: 50, 25 i 15 tys.; podatek 10% jak przy Nagrodzie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagroda publiczności (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jedna nagroda, dla pracy z największą liczbą głosów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jak przy plebiscycie piosenki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honoraria jury plakatu za ocenę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stawka Kapituły, 10 h na jurora, skład pięcioosobowy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport oryginałów w obie strony (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">szacunek, nie oferta; organizator pokrywa obie strony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">szacunek przy sumie deklarowanej rzędu 100 tys. zł</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizacja wystawy przy gali (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - zawieszenie, oświetlenie, opisy prac; zależy od miejsca gali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa prawna regulaminu plakatu (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - odrębne zlecenie kancelarii, nie złożone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dojazd i nocleg finalistów na galę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - jak przy plebiscycie piosenki</t>
   </si>
   <si>
     <t xml:space="preserve">Finansuje: Sponsor Akademii. Kwoty netto. Vouchery są świadczeniem rzeczowym i rosną wprost z liczbą ocenionych rozmów.</t>
@@ -810,6 +976,13 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color rgb="FF8A6A23"/>
       <name val="Cambria"/>
       <family val="0"/>
@@ -824,13 +997,6 @@
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -891,7 +1057,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -932,6 +1098,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -944,7 +1118,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -952,19 +1126,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -972,7 +1162,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -992,7 +1182,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1000,11 +1214,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1012,7 +1226,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1020,7 +1234,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1417,10 +1631,12 @@
       <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Akademii'!$D$27</f>
-        <v>1165722.8</v>
+        <f aca="false">'Budżet Plakatu'!$D$34</f>
+        <v>171736</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1429,7 +1645,13 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
+      <c r="A11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$27</f>
+        <v>1337458.8</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1438,7 +1660,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1450,7 +1672,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1462,13 +1684,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B14" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>18</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1478,13 +1700,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B15" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>20</v>
+      <c r="C15" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1494,13 +1716,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B16" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>22</v>
+      <c r="C16" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1510,13 +1732,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B17" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>24</v>
+      <c r="C17" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1526,13 +1748,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B18" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>26</v>
+      <c r="C18" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1542,13 +1764,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B19" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>28</v>
+      <c r="C19" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -1558,13 +1780,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B20" s="12" t="n">
         <v>35000</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>30</v>
+      <c r="C20" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1574,13 +1796,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B21" s="12" t="n">
         <v>4000</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>32</v>
+      <c r="C21" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1590,13 +1812,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B22" s="12" t="n">
         <v>7500</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>34</v>
+      <c r="C22" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1606,13 +1828,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B23" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>36</v>
+      <c r="C23" s="13" t="s">
+        <v>38</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -1622,13 +1844,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B24" s="12" t="n">
         <v>80000</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>38</v>
+      <c r="C24" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1638,13 +1860,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="B25" s="12" t="n">
         <v>3000</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>40</v>
+      <c r="C25" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1654,13 +1876,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="B26" s="14" t="n">
         <v>0.12</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>42</v>
+      <c r="C26" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1670,13 +1892,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="B27" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>44</v>
+      <c r="C27" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1686,13 +1908,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="B28" s="14" t="n">
         <v>0.12</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>42</v>
+      <c r="C28" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1702,13 +1924,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="B29" s="14" t="n">
         <v>0.23</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>47</v>
+      <c r="C29" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -1718,13 +1940,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="B30" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>49</v>
+      <c r="C30" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1742,7 +1964,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -1754,10 +1976,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -1768,7 +1990,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -1778,7 +2000,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1798,7 +2020,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -1810,7 +2032,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1822,7 +2044,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1834,80 +2056,196 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
+      <c r="A41" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="B42" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B43" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="B43" s="16" t="n">
         <v>500</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B44" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="B44" s="16" t="n">
         <v>2500</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B45" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="B45" s="12" t="n">
         <v>15</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B46" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="B46" s="12" t="n">
         <v>20</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="19" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" s="19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B52" s="19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="19" t="n">
+        <v>290</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B56" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B59" s="20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1955,7 +2293,7 @@
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
@@ -1967,6 +2305,7 @@
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A48:C48"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2008,7 +2347,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2020,7 +2359,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2042,7 +2381,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2054,297 +2393,297 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="A7" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>60</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="24" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>13200</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>79</v>
+      <c r="F7" s="13" t="s">
+        <v>104</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="16" t="n">
+      <c r="A8" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="23" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>24</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="24" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>5280</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>81</v>
+      <c r="F8" s="13" t="s">
+        <v>106</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="16" t="n">
+      <c r="A9" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="23" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="24" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>83</v>
+      <c r="F9" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="16" t="n">
+      <c r="A10" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="23" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>23</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="24" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>5060</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>85</v>
+      <c r="F10" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="16" t="n">
+      <c r="A11" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="23" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="24" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>87</v>
+      <c r="F11" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="16" t="n">
+      <c r="A12" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="23" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="24" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>89</v>
+      <c r="F12" s="13" t="s">
+        <v>114</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="16" t="n">
+      <c r="A13" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="23" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="24" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>91</v>
+      <c r="F13" s="13" t="s">
+        <v>116</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="16" t="n">
+      <c r="A14" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="23" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="24" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>93</v>
+      <c r="F14" s="13" t="s">
+        <v>118</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="16" t="n">
+      <c r="A15" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="22" t="n">
         <v>45</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="23" t="n">
         <f aca="false">B15+C15*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="24" t="n">
         <f aca="false">D15*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>95</v>
+      <c r="F15" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="16" t="n">
+      <c r="A16" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="23" t="n">
         <f aca="false">B16+C16*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="24" t="n">
         <f aca="false">D16*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>97</v>
+      <c r="F16" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="16" t="n">
+      <c r="A17" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="23" t="n">
         <f aca="false">B17+C17*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="24" t="n">
         <f aca="false">D17*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>99</v>
+      <c r="F17" s="13" t="s">
+        <v>124</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="25" t="n">
         <f aca="false">SUM(D7:D17)</f>
         <v>372</v>
       </c>
@@ -2368,7 +2707,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2380,231 +2719,231 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" s="20" t="n">
+      <c r="A22" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="26" t="n">
         <v>8000</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="24" t="n">
         <f aca="false">B22*C22</f>
         <v>8000</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>105</v>
+      <c r="E22" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B23" s="20" t="n">
+      <c r="A23" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="26" t="n">
         <v>1500</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="24" t="n">
         <f aca="false">B23*C23</f>
         <v>1500</v>
       </c>
-      <c r="E23" s="11" t="s">
-        <v>107</v>
+      <c r="E23" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="20" t="n">
+      <c r="A24" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" s="26" t="n">
         <v>1200</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="24" t="n">
         <f aca="false">B24*C24</f>
         <v>1200</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>109</v>
+      <c r="E24" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B25" s="20" t="n">
+      <c r="A25" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="26" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="24" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
-      <c r="E25" s="11" t="s">
-        <v>111</v>
+      <c r="E25" s="13" t="s">
+        <v>136</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" s="20" t="n">
+      <c r="A26" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="26" t="n">
         <v>1500</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="24" t="n">
         <f aca="false">B26*C26</f>
         <v>1500</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>113</v>
+      <c r="E26" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" s="20" t="n">
+      <c r="A27" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="26" t="n">
         <v>250</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="24" t="n">
         <f aca="false">B27*C27</f>
         <v>250</v>
       </c>
-      <c r="E27" s="11" t="s">
-        <v>115</v>
+      <c r="E27" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="B28" s="20" t="n">
+      <c r="A28" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" s="26" t="n">
         <v>32000</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="24" t="n">
         <f aca="false">B28*C28</f>
         <v>32000</v>
       </c>
-      <c r="E28" s="11" t="s">
-        <v>117</v>
+      <c r="E28" s="13" t="s">
+        <v>142</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="B29" s="20" t="n">
+      <c r="A29" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="26" t="n">
         <v>15000</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="D29" s="24" t="n">
         <f aca="false">B29*C29</f>
         <v>15000</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>120</v>
+      <c r="E29" s="13" t="s">
+        <v>145</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="B30" s="20" t="n">
+      <c r="A30" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B30" s="26" t="n">
         <v>8000</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="18" t="n">
+      <c r="D30" s="24" t="n">
         <f aca="false">B30*C30</f>
         <v>8000</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>122</v>
+      <c r="E30" s="13" t="s">
+        <v>147</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="20" t="n">
+      <c r="A31" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C31" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="18" t="n">
+      <c r="D31" s="24" t="n">
         <f aca="false">B31*C31</f>
         <v>0</v>
       </c>
-      <c r="E31" s="11" t="s">
-        <v>124</v>
+      <c r="E31" s="13" t="s">
+        <v>149</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -2612,7 +2951,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2637,7 +2976,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2648,12 +2987,12 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
-        <v>127</v>
+      <c r="A35" s="21" t="s">
+        <v>152</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="18" t="n">
+      <c r="D35" s="24" t="n">
         <f aca="false">Wyjaśnienia!$B$16+Wyjaśnienia!$B$17*Wyjaśnienia!$B$18</f>
         <v>390000</v>
       </c>
@@ -2663,8 +3002,8 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>128</v>
+      <c r="A36" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2678,8 +3017,8 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
-        <v>129</v>
+      <c r="A37" s="21" t="s">
+        <v>154</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2693,8 +3032,8 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="s">
-        <v>130</v>
+      <c r="A38" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2709,7 +3048,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2723,8 +3062,8 @@
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
-        <v>132</v>
+      <c r="A40" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2739,11 +3078,11 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="21" t="n">
+      <c r="D41" s="27" t="n">
         <f aca="false">D39+D40</f>
         <v>690872.304</v>
       </c>
@@ -2865,7 +3204,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2877,7 +3216,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2899,7 +3238,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2911,221 +3250,221 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="A7" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <v>45</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="24" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>136</v>
+      <c r="F7" s="13" t="s">
+        <v>161</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="B8" s="16" t="n">
+      <c r="A8" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="23" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="24" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>138</v>
+      <c r="F8" s="13" t="s">
+        <v>163</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" s="16" t="n">
+      <c r="A9" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="23" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="24" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>140</v>
+      <c r="F9" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="16" t="n">
+      <c r="A10" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="23" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="24" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>142</v>
+      <c r="F10" s="13" t="s">
+        <v>167</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" s="16" t="n">
+      <c r="A11" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="23" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="24" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>144</v>
+      <c r="F11" s="13" t="s">
+        <v>169</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B12" s="16" t="n">
+      <c r="A12" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="22" t="n">
         <v>160</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="23" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>160</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="24" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>35200</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>146</v>
+      <c r="F12" s="13" t="s">
+        <v>171</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="16" t="n">
+      <c r="A13" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="23" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="24" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>148</v>
+      <c r="F13" s="13" t="s">
+        <v>173</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="16" t="n">
+      <c r="A14" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="22" t="n">
         <v>72</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="23" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$15/60</f>
         <v>72</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="24" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$14</f>
         <v>15840</v>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="25" t="n">
         <f aca="false">SUM(D7:D14)</f>
         <v>472</v>
       </c>
@@ -3149,7 +3488,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -3161,283 +3500,283 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="B19" s="20" t="n">
+      <c r="A19" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B19" s="26" t="n">
         <v>3000</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="24" t="n">
         <f aca="false">B19*C19</f>
         <v>3000</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>151</v>
+      <c r="E19" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="B20" s="20" t="n">
+      <c r="A20" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="B20" s="26" t="n">
         <v>6000</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="24" t="n">
         <f aca="false">B20*C20</f>
         <v>6000</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>153</v>
+      <c r="E20" s="13" t="s">
+        <v>178</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B21" s="20" t="n">
+      <c r="A21" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B21" s="26" t="n">
         <v>10000</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="24" t="n">
         <f aca="false">B21*C21</f>
         <v>10000</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>156</v>
+      <c r="E21" s="13" t="s">
+        <v>181</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B22" s="20" t="n">
+      <c r="A22" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B22" s="26" t="n">
         <v>40000</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="24" t="n">
         <f aca="false">B22*C22</f>
         <v>40000</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>158</v>
+      <c r="E22" s="13" t="s">
+        <v>183</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="B23" s="20" t="n">
+      <c r="A23" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B23" s="26" t="n">
         <v>4000</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="24" t="n">
         <f aca="false">B23*C23</f>
         <v>4000</v>
       </c>
-      <c r="E23" s="11" t="s">
-        <v>160</v>
+      <c r="E23" s="13" t="s">
+        <v>185</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B24" s="20" t="n">
+      <c r="A24" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B24" s="26" t="n">
         <v>3000</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="24" t="n">
         <f aca="false">B24*C24</f>
         <v>3000</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>162</v>
+      <c r="E24" s="13" t="s">
+        <v>187</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B25" s="20" t="n">
+      <c r="A25" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B25" s="26" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="24" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
-      <c r="E25" s="11" t="s">
-        <v>164</v>
+      <c r="E25" s="13" t="s">
+        <v>189</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="B26" s="20" t="n">
+      <c r="A26" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B26" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="24" t="n">
         <f aca="false">B26*C26</f>
         <v>0</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>166</v>
+      <c r="E26" s="13" t="s">
+        <v>191</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B27" s="20" t="n">
+      <c r="A27" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B27" s="26" t="n">
         <v>15000</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="24" t="n">
         <f aca="false">B27*C27</f>
         <v>15000</v>
       </c>
-      <c r="E27" s="11" t="s">
-        <v>168</v>
+      <c r="E27" s="13" t="s">
+        <v>193</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B28" s="20" t="n">
+      <c r="A28" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="B28" s="26" t="n">
         <v>6000</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="24" t="n">
         <f aca="false">B28*C28</f>
         <v>6000</v>
       </c>
-      <c r="E28" s="11" t="s">
-        <v>170</v>
+      <c r="E28" s="13" t="s">
+        <v>195</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B29" s="20" t="n">
+      <c r="A29" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B29" s="26" t="n">
         <v>30000</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="D29" s="24" t="n">
         <f aca="false">B29*C29</f>
         <v>30000</v>
       </c>
-      <c r="E29" s="11" t="s">
-        <v>172</v>
+      <c r="E29" s="13" t="s">
+        <v>197</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="B30" s="14" t="n">
+      <c r="A30" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="B30" s="16" t="n">
         <v>4500</v>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C30" s="29" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">B30*C30</f>
         <v>4500</v>
       </c>
-      <c r="F30" s="22" t="s">
-        <v>174</v>
+      <c r="F30" s="28" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="B31" s="14" t="n">
+      <c r="A31" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="B31" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C31" s="29" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="8" t="n">
@@ -3445,13 +3784,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F31" s="22"/>
+        <v>201</v>
+      </c>
+      <c r="F31" s="28"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -3465,18 +3804,18 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -3487,8 +3826,8 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
-        <v>128</v>
+      <c r="A35" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -3502,8 +3841,8 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>129</v>
+      <c r="A36" s="21" t="s">
+        <v>154</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -3517,8 +3856,8 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
-        <v>177</v>
+      <c r="A37" s="21" t="s">
+        <v>202</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -3533,7 +3872,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -3547,8 +3886,8 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15" t="s">
-        <v>132</v>
+      <c r="A39" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -3563,11 +3902,11 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="21" t="n">
+      <c r="D40" s="27" t="n">
         <f aca="false">D38+D39</f>
         <v>366714.66</v>
       </c>
@@ -3691,7 +4030,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3703,7 +4042,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3725,7 +4064,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -3737,153 +4076,153 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="A7" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$19/60</f>
         <v>25</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="24" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>180</v>
+      <c r="F7" s="13" t="s">
+        <v>205</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="B8" s="16" t="n">
+      <c r="A8" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="23" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$19/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="24" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>182</v>
+      <c r="F8" s="13" t="s">
+        <v>207</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="B9" s="16" t="n">
+      <c r="A9" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="23" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$19/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="24" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>184</v>
+      <c r="F9" s="13" t="s">
+        <v>209</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="16" t="n">
+      <c r="A10" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="23" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$19/60</f>
         <v>20</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="24" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>186</v>
+      <c r="F10" s="13" t="s">
+        <v>211</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="B11" s="16" t="n">
+      <c r="A11" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="23" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$19/60</f>
         <v>50</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="24" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>188</v>
+      <c r="F11" s="13" t="s">
+        <v>213</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="25" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>165</v>
       </c>
@@ -3907,7 +4246,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -3919,185 +4258,185 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="B16" s="18" t="n">
+      <c r="A16" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" s="24" t="n">
         <f aca="false">Wyjaśnienia!$B$20</f>
         <v>35000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="24" t="n">
         <f aca="false">B16*C16</f>
         <v>35000</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>190</v>
+      <c r="E16" s="13" t="s">
+        <v>215</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="B17" s="18" t="n">
+      <c r="A17" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B17" s="24" t="n">
         <f aca="false">Wyjaśnienia!$B$21</f>
         <v>4000</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="24" t="n">
         <f aca="false">B17*C17</f>
         <v>4000</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>192</v>
+      <c r="E17" s="13" t="s">
+        <v>217</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="B18" s="18" t="n">
+      <c r="A18" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B18" s="24" t="n">
         <f aca="false">Wyjaśnienia!$B$22</f>
         <v>7500</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="23" t="n">
         <f aca="false">Wyjaśnienia!$B$23</f>
         <v>10</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="24" t="n">
         <f aca="false">B18*C18</f>
         <v>75000</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>194</v>
+      <c r="E18" s="13" t="s">
+        <v>219</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="18" t="n">
+      <c r="A19" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="24" t="n">
         <f aca="false">Wyjaśnienia!$B$24</f>
         <v>80000</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="24" t="n">
         <f aca="false">B19*C19</f>
         <v>80000</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>195</v>
+      <c r="E19" s="13" t="s">
+        <v>220</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="18" t="n">
+      <c r="A20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="24" t="n">
         <f aca="false">Wyjaśnienia!$B$25</f>
         <v>3000</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="24" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>196</v>
+      <c r="E20" s="13" t="s">
+        <v>221</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B21" s="20" t="n">
+      <c r="A21" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B21" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="24" t="n">
         <f aca="false">B21*C21</f>
         <v>0</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>198</v>
+      <c r="E21" s="13" t="s">
+        <v>223</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="B22" s="20" t="n">
+      <c r="A22" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="24" t="n">
         <f aca="false">B22*C22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>200</v>
+      <c r="E22" s="13" t="s">
+        <v>225</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="B23" s="14" t="n">
+      <c r="A23" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="B23" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="29" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -4105,20 +4444,20 @@
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>203</v>
+        <v>227</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="B24" s="14" t="n">
+      <c r="A24" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="B24" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C24" s="29" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -4126,17 +4465,17 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F24" s="22"/>
+        <v>230</v>
+      </c>
+      <c r="F24" s="28"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="25" t="n">
         <f aca="false">SUM(D16:D24)</f>
         <v>197000</v>
       </c>
@@ -4146,18 +4485,18 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -4168,12 +4507,12 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
-        <v>127</v>
+      <c r="A28" s="21" t="s">
+        <v>152</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="24" t="n">
         <f aca="false">Wyjaśnienia!$B$20+Wyjaśnienia!$B$21</f>
         <v>39000</v>
       </c>
@@ -4183,8 +4522,8 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>128</v>
+      <c r="A29" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -4198,8 +4537,8 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>206</v>
+      <c r="A30" s="21" t="s">
+        <v>231</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -4213,8 +4552,8 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
-        <v>130</v>
+      <c r="A31" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -4229,7 +4568,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -4243,8 +4582,8 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
-        <v>132</v>
+      <c r="A33" s="21" t="s">
+        <v>157</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -4259,11 +4598,11 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="21" t="n">
+      <c r="D34" s="27" t="n">
         <f aca="false">D32+D33</f>
         <v>315637.68</v>
       </c>
@@ -4368,6 +4707,547 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="62"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$49/60</f>
+        <v>20</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <f aca="false">D7*Wyjaśnienia!$B$14</f>
+        <v>4400</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$49/60</f>
+        <v>30</v>
+      </c>
+      <c r="E8" s="35" t="n">
+        <f aca="false">D8*Wyjaśnienia!$B$14</f>
+        <v>6600</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$49/60</f>
+        <v>20</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <f aca="false">D9*Wyjaśnienia!$B$14</f>
+        <v>4400</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$49/60</f>
+        <v>35</v>
+      </c>
+      <c r="E10" s="35" t="n">
+        <f aca="false">D10*Wyjaśnienia!$B$14</f>
+        <v>7700</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$49/60</f>
+        <v>15</v>
+      </c>
+      <c r="E11" s="35" t="n">
+        <f aca="false">D11*Wyjaśnienia!$B$14</f>
+        <v>3300</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <f aca="false">B12+C12*Wyjaśnienia!$B$49/60</f>
+        <v>50</v>
+      </c>
+      <c r="E12" s="35" t="n">
+        <f aca="false">D12*Wyjaśnienia!$B$14</f>
+        <v>11000</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="B13" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <f aca="false">B13+C13*Wyjaśnienia!$B$49/60</f>
+        <v>20</v>
+      </c>
+      <c r="E13" s="35" t="n">
+        <f aca="false">D13*Wyjaśnienia!$B$14</f>
+        <v>4400</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="36" t="n">
+        <f aca="false">SUM(D7:D13)</f>
+        <v>190</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <f aca="false">SUM(E7:E13)</f>
+        <v>41800</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="B18" s="35" t="n">
+        <f aca="false">Wyjaśnienia!$B$50</f>
+        <v>90000</v>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="35" t="n">
+        <f aca="false">B18*C18</f>
+        <v>90000</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="B19" s="35" t="n">
+        <f aca="false">Wyjaśnienia!$B$51</f>
+        <v>3000</v>
+      </c>
+      <c r="C19" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="35" t="n">
+        <f aca="false">B19*C19</f>
+        <v>3000</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="35" t="n">
+        <f aca="false">Wyjaśnienia!$B$52</f>
+        <v>3000</v>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="35" t="n">
+        <f aca="false">B20*C20</f>
+        <v>3000</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="B21" s="35" t="n">
+        <f aca="false">Wyjaśnienia!$B$55*Wyjaśnienia!$B$54</f>
+        <v>2900</v>
+      </c>
+      <c r="C21" s="34" t="n">
+        <f aca="false">Wyjaśnienia!$B$53</f>
+        <v>5</v>
+      </c>
+      <c r="D21" s="35" t="n">
+        <f aca="false">B21*C21</f>
+        <v>14500</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>253</v>
+      </c>
+      <c r="B22" s="35" t="n">
+        <f aca="false">Wyjaśnienia!$B$57*2</f>
+        <v>800</v>
+      </c>
+      <c r="C22" s="34" t="n">
+        <f aca="false">Wyjaśnienia!$B$56</f>
+        <v>10</v>
+      </c>
+      <c r="D22" s="35" t="n">
+        <f aca="false">B22*C22</f>
+        <v>8000</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="35" t="n">
+        <f aca="false">Wyjaśnienia!$B$58</f>
+        <v>3000</v>
+      </c>
+      <c r="C23" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="35" t="n">
+        <f aca="false">B23*C23</f>
+        <v>3000</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="35" t="n">
+        <f aca="false">B24*C24</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="35" t="n">
+        <f aca="false">B25*C25</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="35" t="n">
+        <f aca="false">B26*C26</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <f aca="false">SUM(D18:D26)</f>
+        <v>121500</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" s="35" t="n">
+        <f aca="false">Wyjaśnienia!$B$50+Wyjaśnienia!$B$51</f>
+        <v>93000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="35" t="n">
+        <f aca="false">E14</f>
+        <v>41800</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="D32" s="35" t="n">
+        <f aca="false">D27-D30</f>
+        <v>28500</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" s="35" t="n">
+        <f aca="false">(D31+D32)*Wyjaśnienia!$B$59</f>
+        <v>8436</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <f aca="false">SUM(D30:D33)</f>
+        <v>171736</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" s="35" t="n">
+        <f aca="false">D34*Wyjaśnienia!$B$29</f>
+        <v>39499.28</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <f aca="false">D34+D35</f>
+        <v>211235.28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F38"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4380,533 +5260,533 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="A2" s="38" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="A3" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="A5" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="27" t="s">
-        <v>77</v>
+      <c r="A6" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="39" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="B7" s="29" t="n">
+      <c r="A7" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="41" t="n">
         <f aca="false">Wyjaśnienia!$B$15</f>
         <v>150</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22" t="s">
-        <v>212</v>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B8" s="29" t="n">
+      <c r="A8" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" s="41" t="n">
         <f aca="false">Wyjaśnienia!$B$42</f>
         <v>2</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22" t="s">
-        <v>214</v>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="B9" s="30" t="n">
+      <c r="A9" s="39" t="s">
+        <v>270</v>
+      </c>
+      <c r="B9" s="42" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22" t="s">
-        <v>216</v>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="A11" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="27" t="s">
-        <v>77</v>
+      <c r="A12" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="28"/>
+      <c r="F12" s="39" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="B13" s="31" t="n">
+      <c r="A13" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="B13" s="43" t="n">
         <f aca="false">Wyjaśnienia!$B$44</f>
         <v>2500</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="41" t="n">
         <f aca="false">Wyjaśnienia!$B$45</f>
         <v>15</v>
       </c>
-      <c r="D13" s="31" t="n">
+      <c r="D13" s="43" t="n">
         <f aca="false">B13*C13</f>
         <v>37500</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22" t="s">
-        <v>220</v>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="B14" s="31" t="n">
+      <c r="A14" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="B14" s="43" t="n">
         <f aca="false">Wyjaśnienia!$B$43</f>
         <v>500</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="41" t="n">
         <f aca="false">ROUNDUP(B9/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="43" t="n">
         <f aca="false">B14*C14</f>
         <v>1500</v>
       </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22" t="s">
-        <v>222</v>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="32" t="n">
+      <c r="A15" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="44" t="n">
         <f aca="false">SUM(D13:D14)</f>
         <v>39000</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="28" t="s">
+      <c r="E18" s="28"/>
+      <c r="F18" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="27" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="B19" s="33" t="n">
+      <c r="A19" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="B19" s="45" t="n">
         <v>2000</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="31" t="n">
+      <c r="D19" s="43" t="n">
         <f aca="false">B19*C19</f>
         <v>2000</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22" t="s">
-        <v>225</v>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="B20" s="33" t="n">
+      <c r="A20" s="28" t="s">
+        <v>281</v>
+      </c>
+      <c r="B20" s="45" t="n">
         <v>3000</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="31" t="n">
+      <c r="D20" s="43" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22" t="s">
-        <v>227</v>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="32" t="n">
+      <c r="A21" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="44" t="n">
         <f aca="false">SUM(D19:D20)</f>
         <v>5000</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="A23" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="31" t="n">
+      <c r="A24" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="43" t="n">
         <f aca="false">D15</f>
         <v>39000</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="31" t="n">
+      <c r="A25" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="43" t="n">
         <f aca="false">D21</f>
         <v>5000</v>
       </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="31" t="n">
+      <c r="A26" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="43" t="n">
         <f aca="false">(D24+D25)*Wyjaśnienia!$B$26</f>
         <v>5280</v>
       </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="32" t="n">
+      <c r="A27" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="44" t="n">
         <f aca="false">SUM(D24:D26)</f>
         <v>49280</v>
       </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="31" t="n">
+      <c r="A28" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="43" t="n">
         <f aca="false">D27*Wyjaśnienia!$B$29</f>
         <v>11334.4</v>
       </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="32" t="n">
+      <c r="A29" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="44" t="n">
         <f aca="false">D27+D28</f>
         <v>60614.4</v>
       </c>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
+      <c r="A30" s="28"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
+      <c r="A31" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
+      <c r="A32" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="E33" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="F33" s="22"/>
+      <c r="A33" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="B33" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="F33" s="28"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="29" t="n">
+      <c r="A34" s="41" t="n">
         <v>150</v>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="41" t="n">
         <f aca="false">A34*Wyjaśnienia!$B$42</f>
         <v>300</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="41" t="n">
         <f aca="false">ROUNDUP(B34/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D34" s="31" t="n">
+      <c r="D34" s="43" t="n">
         <f aca="false">C34*Wyjaśnienia!$B$43</f>
         <v>1500</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="41" t="n">
         <f aca="false">ROUNDUP(A34/Wyjaśnienia!$B$46,0)</f>
         <v>8</v>
       </c>
-      <c r="F34" s="22"/>
+      <c r="F34" s="28"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29" t="n">
+      <c r="A35" s="41" t="n">
         <v>1000</v>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="41" t="n">
         <f aca="false">A35*Wyjaśnienia!$B$42</f>
         <v>2000</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="41" t="n">
         <f aca="false">ROUNDUP(B35/100,0)</f>
         <v>20</v>
       </c>
-      <c r="D35" s="31" t="n">
+      <c r="D35" s="43" t="n">
         <f aca="false">C35*Wyjaśnienia!$B$43</f>
         <v>10000</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="41" t="n">
         <f aca="false">ROUNDUP(A35/Wyjaśnienia!$B$46,0)</f>
         <v>50</v>
       </c>
-      <c r="F35" s="22"/>
+      <c r="F35" s="28"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="29" t="n">
+      <c r="A36" s="41" t="n">
         <v>10000</v>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="41" t="n">
         <f aca="false">A36*Wyjaśnienia!$B$42</f>
         <v>20000</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="41" t="n">
         <f aca="false">ROUNDUP(B36/100,0)</f>
         <v>200</v>
       </c>
-      <c r="D36" s="31" t="n">
+      <c r="D36" s="43" t="n">
         <f aca="false">C36*Wyjaśnienia!$B$43</f>
         <v>100000</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="41" t="n">
         <f aca="false">ROUNDUP(A36/Wyjaśnienia!$B$46,0)</f>
         <v>500</v>
       </c>
-      <c r="F36" s="22"/>
+      <c r="F36" s="28"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="29" t="n">
+      <c r="A37" s="41" t="n">
         <v>100000</v>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="41" t="n">
         <f aca="false">A37*Wyjaśnienia!$B$42</f>
         <v>200000</v>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="41" t="n">
         <f aca="false">ROUNDUP(B37/100,0)</f>
         <v>2000</v>
       </c>
-      <c r="D37" s="31" t="n">
+      <c r="D37" s="43" t="n">
         <f aca="false">C37*Wyjaśnienia!$B$43</f>
         <v>1000000</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="41" t="n">
         <f aca="false">ROUNDUP(A37/Wyjaśnienia!$B$46,0)</f>
         <v>5000</v>
       </c>
-      <c r="F37" s="22"/>
+      <c r="F37" s="28"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="41" t="n">
         <v>1000000</v>
       </c>
-      <c r="B38" s="29" t="n">
+      <c r="B38" s="41" t="n">
         <f aca="false">A38*Wyjaśnienia!$B$42</f>
         <v>2000000</v>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="41" t="n">
         <f aca="false">ROUNDUP(B38/100,0)</f>
         <v>20000</v>
       </c>
-      <c r="D38" s="31" t="n">
+      <c r="D38" s="43" t="n">
         <f aca="false">C38*Wyjaśnienia!$B$43</f>
         <v>10000000</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="41" t="n">
         <f aca="false">ROUNDUP(A38/Wyjaśnienia!$B$46,0)</f>
         <v>50000</v>
       </c>
-      <c r="F38" s="22"/>
+      <c r="F38" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="293">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -667,6 +667,9 @@
   </si>
   <si>
     <t xml:space="preserve">grupy muzyków, szkoły muzyczne, scena coverowa, radia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powyżej progu zgłoszeń pierwsze przejście oceny przechodzi na Akademię, tak jak w konkursie rozmów - dlatego te godziny nie rosną z naborem. Minuty na zgłoszenie dotyczą wyłącznie kontroli formalnej.</t>
   </si>
   <si>
     <t xml:space="preserve">Nagrody plebiscytu (brutto dla laureatów)</t>
@@ -1057,7 +1060,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1102,7 +1105,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1126,19 +1129,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1182,27 +1177,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2140,7 +2123,7 @@
       <c r="A50" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B50" s="19" t="n">
+      <c r="B50" s="16" t="n">
         <v>90000</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -2151,7 +2134,7 @@
       <c r="A51" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B51" s="19" t="n">
+      <c r="B51" s="16" t="n">
         <v>3000</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -2162,7 +2145,7 @@
       <c r="A52" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B52" s="19" t="n">
+      <c r="B52" s="16" t="n">
         <v>3000</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -2195,7 +2178,7 @@
       <c r="A55" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B55" s="19" t="n">
+      <c r="B55" s="16" t="n">
         <v>290</v>
       </c>
       <c r="C55" s="1" t="s">
@@ -2217,7 +2200,7 @@
       <c r="A57" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B57" s="19" t="n">
+      <c r="B57" s="16" t="n">
         <v>400</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -2228,7 +2211,7 @@
       <c r="A58" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B58" s="19" t="n">
+      <c r="B58" s="16" t="n">
         <v>3000</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -2239,7 +2222,7 @@
       <c r="A59" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B59" s="20" t="n">
+      <c r="B59" s="14" t="n">
         <v>0.12</v>
       </c>
       <c r="C59" s="1" t="s">
@@ -2414,20 +2397,20 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="21" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>60</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="22" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>13200</v>
       </c>
@@ -2438,20 +2421,20 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="21" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>24</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="22" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>5280</v>
       </c>
@@ -2462,20 +2445,20 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="21" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="22" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
@@ -2486,20 +2469,20 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="21" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>23</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="22" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>5060</v>
       </c>
@@ -2510,20 +2493,20 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="21" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="22" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
@@ -2534,20 +2517,20 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="21" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>20</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="22" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
@@ -2558,20 +2541,20 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="21" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="22" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
@@ -2582,20 +2565,20 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="21" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="22" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
@@ -2606,20 +2589,20 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="21" t="n">
         <f aca="false">B15+C15*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="22" t="n">
         <f aca="false">D15*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
@@ -2630,20 +2613,20 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="21" t="n">
         <f aca="false">B16+C16*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="E16" s="22" t="n">
         <f aca="false">D16*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
@@ -2654,20 +2637,20 @@
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="21" t="n">
         <f aca="false">B17+C17*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="22" t="n">
         <f aca="false">D17*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
@@ -2683,7 +2666,7 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="23" t="n">
         <f aca="false">SUM(D7:D17)</f>
         <v>372</v>
       </c>
@@ -2738,16 +2721,16 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="24" t="n">
         <v>8000</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D22" s="22" t="n">
         <f aca="false">B22*C22</f>
         <v>8000</v>
       </c>
@@ -2759,16 +2742,16 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="24" t="n">
         <v>1500</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D23" s="22" t="n">
         <f aca="false">B23*C23</f>
         <v>1500</v>
       </c>
@@ -2780,16 +2763,16 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="24" t="n">
         <v>1200</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="24" t="n">
+      <c r="D24" s="22" t="n">
         <f aca="false">B24*C24</f>
         <v>1200</v>
       </c>
@@ -2801,16 +2784,16 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="24" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="22" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
@@ -2822,16 +2805,16 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="24" t="n">
         <v>1500</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="24" t="n">
+      <c r="D26" s="22" t="n">
         <f aca="false">B26*C26</f>
         <v>1500</v>
       </c>
@@ -2843,16 +2826,16 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="24" t="n">
         <v>250</v>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C27" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="24" t="n">
+      <c r="D27" s="22" t="n">
         <f aca="false">B27*C27</f>
         <v>250</v>
       </c>
@@ -2864,16 +2847,16 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="24" t="n">
         <v>32000</v>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="24" t="n">
+      <c r="D28" s="22" t="n">
         <f aca="false">B28*C28</f>
         <v>32000</v>
       </c>
@@ -2887,16 +2870,16 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="24" t="n">
         <v>15000</v>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="24" t="n">
+      <c r="D29" s="22" t="n">
         <f aca="false">B29*C29</f>
         <v>15000</v>
       </c>
@@ -2908,16 +2891,16 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="24" t="n">
         <v>8000</v>
       </c>
-      <c r="C30" s="22" t="n">
+      <c r="C30" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="24" t="n">
+      <c r="D30" s="22" t="n">
         <f aca="false">B30*C30</f>
         <v>8000</v>
       </c>
@@ -2929,16 +2912,16 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="22" t="n">
+      <c r="C31" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="24" t="n">
+      <c r="D31" s="22" t="n">
         <f aca="false">B31*C31</f>
         <v>0</v>
       </c>
@@ -2987,12 +2970,12 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="19" t="s">
         <v>152</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="24" t="n">
+      <c r="D35" s="22" t="n">
         <f aca="false">Wyjaśnienia!$B$16+Wyjaśnienia!$B$17*Wyjaśnienia!$B$18</f>
         <v>390000</v>
       </c>
@@ -3002,7 +2985,7 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="19" t="s">
         <v>153</v>
       </c>
       <c r="B36" s="3"/>
@@ -3017,7 +3000,7 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="19" t="s">
         <v>154</v>
       </c>
       <c r="B37" s="3"/>
@@ -3032,7 +3015,7 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="19" t="s">
         <v>155</v>
       </c>
       <c r="B38" s="3"/>
@@ -3062,7 +3045,7 @@
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="19" t="s">
         <v>157</v>
       </c>
       <c r="B40" s="3"/>
@@ -3082,7 +3065,7 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="27" t="n">
+      <c r="D41" s="25" t="n">
         <f aca="false">D39+D40</f>
         <v>690872.304</v>
       </c>
@@ -3271,20 +3254,20 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="21" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$15/60</f>
         <v>45</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="22" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>9900</v>
       </c>
@@ -3295,20 +3278,20 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="21" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$15/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="22" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
@@ -3319,20 +3302,20 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="21" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="22" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
@@ -3343,20 +3326,20 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="21" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="22" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
@@ -3367,20 +3350,20 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="21" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$15/60</f>
         <v>25</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="22" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
@@ -3391,20 +3374,20 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="21" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$15/60</f>
         <v>160</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="22" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>35200</v>
       </c>
@@ -3415,20 +3398,20 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="21" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$15/60</f>
         <v>50</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="22" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
@@ -3439,20 +3422,20 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="20" t="n">
         <v>72</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="21" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$15/60</f>
         <v>72</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="22" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$14</f>
         <v>15840</v>
       </c>
@@ -3464,7 +3447,7 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="23" t="n">
         <f aca="false">SUM(D7:D14)</f>
         <v>472</v>
       </c>
@@ -3519,16 +3502,16 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="24" t="n">
         <v>3000</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="22" t="n">
         <f aca="false">B19*C19</f>
         <v>3000</v>
       </c>
@@ -3540,16 +3523,16 @@
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="24" t="n">
         <v>6000</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="22" t="n">
         <f aca="false">B20*C20</f>
         <v>6000</v>
       </c>
@@ -3563,16 +3546,16 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="24" t="n">
         <v>10000</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="22" t="n">
         <f aca="false">B21*C21</f>
         <v>10000</v>
       </c>
@@ -3584,16 +3567,16 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="24" t="n">
         <v>40000</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D22" s="22" t="n">
         <f aca="false">B22*C22</f>
         <v>40000</v>
       </c>
@@ -3605,16 +3588,16 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="24" t="n">
         <v>4000</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D23" s="22" t="n">
         <f aca="false">B23*C23</f>
         <v>4000</v>
       </c>
@@ -3626,16 +3609,16 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="24" t="n">
         <v>3000</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="24" t="n">
+      <c r="D24" s="22" t="n">
         <f aca="false">B24*C24</f>
         <v>3000</v>
       </c>
@@ -3647,16 +3630,16 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="24" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="22" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
@@ -3668,16 +3651,16 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="24" t="n">
+      <c r="D26" s="22" t="n">
         <f aca="false">B26*C26</f>
         <v>0</v>
       </c>
@@ -3689,16 +3672,16 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="24" t="n">
         <v>15000</v>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C27" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="24" t="n">
+      <c r="D27" s="22" t="n">
         <f aca="false">B27*C27</f>
         <v>15000</v>
       </c>
@@ -3710,16 +3693,16 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="24" t="n">
         <v>6000</v>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="24" t="n">
+      <c r="D28" s="22" t="n">
         <f aca="false">B28*C28</f>
         <v>6000</v>
       </c>
@@ -3731,16 +3714,16 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="24" t="n">
         <v>30000</v>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="24" t="n">
+      <c r="D29" s="22" t="n">
         <f aca="false">B29*C29</f>
         <v>30000</v>
       </c>
@@ -3752,31 +3735,31 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="26" t="s">
         <v>198</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>4500</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="27" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">B30*C30</f>
         <v>4500</v>
       </c>
-      <c r="F30" s="28" t="s">
+      <c r="F30" s="26" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="26" t="s">
         <v>200</v>
       </c>
       <c r="B31" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="27" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="8" t="n">
@@ -3786,7 +3769,7 @@
       <c r="E31" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F31" s="28"/>
+      <c r="F31" s="26"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
@@ -3804,12 +3787,12 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
@@ -3826,7 +3809,7 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="19" t="s">
         <v>153</v>
       </c>
       <c r="B35" s="3"/>
@@ -3841,7 +3824,7 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="19" t="s">
         <v>154</v>
       </c>
       <c r="B36" s="3"/>
@@ -3856,7 +3839,7 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="19" t="s">
         <v>202</v>
       </c>
       <c r="B37" s="3"/>
@@ -3886,7 +3869,7 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="19" t="s">
         <v>157</v>
       </c>
       <c r="B39" s="3"/>
@@ -3906,7 +3889,7 @@
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="27" t="n">
+      <c r="D40" s="25" t="n">
         <f aca="false">D38+D39</f>
         <v>366714.66</v>
       </c>
@@ -4097,20 +4080,20 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="21" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$19/60</f>
         <v>25</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="22" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>5500</v>
       </c>
@@ -4121,20 +4104,18 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="23" t="n">
+      <c r="C8" s="21"/>
+      <c r="D8" s="21" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$19/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="22" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>8800</v>
       </c>
@@ -4145,20 +4126,18 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="23" t="n">
+      <c r="C9" s="21"/>
+      <c r="D9" s="21" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$19/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="22" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
@@ -4169,20 +4148,18 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="23" t="n">
+      <c r="C10" s="21"/>
+      <c r="D10" s="21" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$19/60</f>
         <v>20</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="22" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
@@ -4193,20 +4170,18 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="23" t="n">
+      <c r="C11" s="21"/>
+      <c r="D11" s="21" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$19/60</f>
         <v>50</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="22" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
@@ -4222,7 +4197,7 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="23" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>165</v>
       </c>
@@ -4230,7 +4205,9 @@
         <f aca="false">SUM(E7:E11)</f>
         <v>36300</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
@@ -4277,166 +4254,166 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="B16" s="24" t="n">
+      <c r="A16" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B16" s="22" t="n">
         <f aca="false">Wyjaśnienia!$B$20</f>
         <v>35000</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="22" t="n">
         <f aca="false">B16*C16</f>
         <v>35000</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="B17" s="24" t="n">
+      <c r="A17" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B17" s="22" t="n">
         <f aca="false">Wyjaśnienia!$B$21</f>
         <v>4000</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="22" t="n">
         <f aca="false">B17*C17</f>
         <v>4000</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="B18" s="24" t="n">
+      <c r="A18" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="22" t="n">
         <f aca="false">Wyjaśnienia!$B$22</f>
         <v>7500</v>
       </c>
-      <c r="C18" s="23" t="n">
+      <c r="C18" s="21" t="n">
         <f aca="false">Wyjaśnienia!$B$23</f>
         <v>10</v>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="22" t="n">
         <f aca="false">B18*C18</f>
         <v>75000</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="22" t="n">
         <f aca="false">Wyjaśnienia!$B$24</f>
         <v>80000</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="22" t="n">
         <f aca="false">B19*C19</f>
         <v>80000</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="22" t="n">
         <f aca="false">Wyjaśnienia!$B$25</f>
         <v>3000</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="22" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="B21" s="26" t="n">
+      <c r="A21" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B21" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="22" t="n">
         <f aca="false">B21*C21</f>
         <v>0</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="B22" s="26" t="n">
+      <c r="A22" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B22" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D22" s="22" t="n">
         <f aca="false">B22*C22</f>
         <v>0</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="s">
-        <v>226</v>
+      <c r="A23" s="26" t="s">
+        <v>227</v>
       </c>
       <c r="B23" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="27" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -4444,20 +4421,20 @@
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F23" s="28" t="s">
         <v>228</v>
       </c>
+      <c r="F23" s="26" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
-        <v>229</v>
+      <c r="A24" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="B24" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="27" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -4465,9 +4442,9 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="F24" s="28"/>
+        <v>231</v>
+      </c>
+      <c r="F24" s="26"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
@@ -4475,7 +4452,7 @@
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="25" t="n">
+      <c r="D25" s="23" t="n">
         <f aca="false">SUM(D16:D24)</f>
         <v>197000</v>
       </c>
@@ -4485,12 +4462,12 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
@@ -4507,12 +4484,12 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="19" t="s">
         <v>152</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="24" t="n">
+      <c r="D28" s="22" t="n">
         <f aca="false">Wyjaśnienia!$B$20+Wyjaśnienia!$B$21</f>
         <v>39000</v>
       </c>
@@ -4522,7 +4499,7 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="19" t="s">
         <v>153</v>
       </c>
       <c r="B29" s="3"/>
@@ -4537,8 +4514,8 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21" t="s">
-        <v>231</v>
+      <c r="A30" s="19" t="s">
+        <v>232</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -4552,7 +4529,7 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="19" t="s">
         <v>155</v>
       </c>
       <c r="B31" s="3"/>
@@ -4582,7 +4559,7 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="19" t="s">
         <v>157</v>
       </c>
       <c r="B33" s="3"/>
@@ -4602,7 +4579,7 @@
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="27" t="n">
+      <c r="D34" s="25" t="n">
         <f aca="false">D32+D33</f>
         <v>315637.68</v>
       </c>
@@ -4710,77 +4687,77 @@
   <dimension ref="A1:F36"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="31" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="32" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>233</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>0</v>
@@ -4788,155 +4765,143 @@
       <c r="C7" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D7" s="30" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$49/60</f>
         <v>20</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="8" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F7" s="0" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="F7" s="3" t="s">
         <v>235</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="B8" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="34" t="n">
+      <c r="C8" s="30"/>
+      <c r="D8" s="30" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$49/60</f>
         <v>30</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="8" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$14</f>
         <v>6600</v>
       </c>
-      <c r="F8" s="0" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="F8" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>210</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="C9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="34" t="n">
+      <c r="C9" s="30"/>
+      <c r="D9" s="30" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$49/60</f>
         <v>20</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="8" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F9" s="0" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="F9" s="3" t="s">
         <v>238</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>239</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="C10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="34" t="n">
+      <c r="C10" s="30"/>
+      <c r="D10" s="30" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$49/60</f>
         <v>35</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="8" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$14</f>
         <v>7700</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="F10" s="3" t="s">
         <v>240</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="B11" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="34" t="n">
+      <c r="C11" s="30"/>
+      <c r="D11" s="30" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$49/60</f>
         <v>15</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="8" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$14</f>
         <v>3300</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="F11" s="3" t="s">
         <v>242</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>243</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="C12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="34" t="n">
+      <c r="C12" s="30"/>
+      <c r="D12" s="30" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$49/60</f>
         <v>50</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="8" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$14</f>
         <v>11000</v>
       </c>
-      <c r="F12" s="0" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="F12" s="3" t="s">
         <v>244</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>245</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="34" t="n">
+      <c r="C13" s="30"/>
+      <c r="D13" s="30" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$49/60</f>
         <v>20</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="8" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$14</f>
         <v>4400</v>
       </c>
-      <c r="F13" s="0" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="s">
+      <c r="F13" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="36" t="n">
+      <c r="D14" s="31" t="n">
         <f aca="false">SUM(D7:D13)</f>
         <v>190</v>
       </c>
@@ -4944,206 +4909,209 @@
         <f aca="false">SUM(E7:E13)</f>
         <v>41800</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="s">
+      <c r="F14" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="33" t="s">
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>246</v>
-      </c>
-      <c r="B18" s="35" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B18" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$50</f>
         <v>90000</v>
       </c>
-      <c r="C18" s="34" t="n">
+      <c r="C18" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="8" t="n">
         <f aca="false">B18*C18</f>
         <v>90000</v>
       </c>
-      <c r="E18" s="0" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="E18" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B19" s="35" t="n">
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B19" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$51</f>
         <v>3000</v>
       </c>
-      <c r="C19" s="34" t="n">
+      <c r="C19" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="8" t="n">
         <f aca="false">B19*C19</f>
         <v>3000</v>
       </c>
-      <c r="E19" s="0" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="E19" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="35" t="n">
+      <c r="B20" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$52</f>
         <v>3000</v>
       </c>
-      <c r="C20" s="34" t="n">
+      <c r="C20" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="8" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="0" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="E20" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B21" s="35" t="n">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B21" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$55*Wyjaśnienia!$B$54</f>
         <v>2900</v>
       </c>
-      <c r="C21" s="34" t="n">
+      <c r="C21" s="30" t="n">
         <f aca="false">Wyjaśnienia!$B$53</f>
         <v>5</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="8" t="n">
         <f aca="false">B21*C21</f>
         <v>14500</v>
       </c>
-      <c r="E21" s="0" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="E21" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B22" s="35" t="n">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B22" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$57*2</f>
         <v>800</v>
       </c>
-      <c r="C22" s="34" t="n">
+      <c r="C22" s="30" t="n">
         <f aca="false">Wyjaśnienia!$B$56</f>
         <v>10</v>
       </c>
-      <c r="D22" s="35" t="n">
+      <c r="D22" s="8" t="n">
         <f aca="false">B22*C22</f>
         <v>8000</v>
       </c>
-      <c r="E22" s="0" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="E22" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="35" t="n">
+      <c r="B23" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$58</f>
         <v>3000</v>
       </c>
-      <c r="C23" s="34" t="n">
+      <c r="C23" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="35" t="n">
+      <c r="D23" s="8" t="n">
         <f aca="false">B23*C23</f>
         <v>3000</v>
       </c>
-      <c r="E23" s="0" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="E23" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="19" t="n">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B24" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="34" t="n">
+      <c r="C24" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="35" t="n">
+      <c r="D24" s="8" t="n">
         <f aca="false">B24*C24</f>
         <v>0</v>
       </c>
-      <c r="E24" s="0" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="E24" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B25" s="19" t="n">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B25" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="34" t="n">
+      <c r="C25" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="35" t="n">
+      <c r="D25" s="8" t="n">
         <f aca="false">B25*C25</f>
         <v>0</v>
       </c>
-      <c r="E25" s="0" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="E25" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B26" s="19" t="n">
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B26" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="34" t="n">
+      <c r="C26" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="35" t="n">
+      <c r="D26" s="8" t="n">
         <f aca="false">B26*C26</f>
         <v>0</v>
       </c>
-      <c r="E26" s="0" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="33" t="s">
+      <c r="E26" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
         <v>150</v>
       </c>
       <c r="D27" s="11" t="n">
@@ -5151,54 +5119,54 @@
         <v>121500</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="31" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="35" t="n">
+      <c r="D30" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$50+Wyjaśnienia!$B$51</f>
         <v>93000</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D31" s="35" t="n">
+      <c r="D31" s="8" t="n">
         <f aca="false">E14</f>
         <v>41800</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>231</v>
-      </c>
-      <c r="D32" s="35" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D32" s="8" t="n">
         <f aca="false">D27-D30</f>
         <v>28500</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D33" s="35" t="n">
+      <c r="D33" s="8" t="n">
         <f aca="false">(D31+D32)*Wyjaśnienia!$B$59</f>
         <v>8436</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="33" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10" t="s">
         <v>156</v>
       </c>
       <c r="D34" s="11" t="n">
@@ -5206,17 +5174,17 @@
         <v>171736</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D35" s="35" t="n">
+      <c r="D35" s="8" t="n">
         <f aca="false">D34*Wyjaśnienia!$B$29</f>
         <v>39499.28</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="33" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10" t="s">
         <v>158</v>
       </c>
       <c r="D36" s="11" t="n">
@@ -5260,38 +5228,38 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
-        <v>262</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="A2" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
+      <c r="A3" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
@@ -5300,75 +5268,75 @@
       <c r="F5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="40" t="s">
-        <v>265</v>
-      </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="39" t="s">
+      <c r="B6" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="34" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="41" t="n">
+      <c r="A7" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="36" t="n">
         <f aca="false">Wyjaśnienia!$B$15</f>
         <v>150</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28" t="s">
-        <v>267</v>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="41" t="n">
+      <c r="A8" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="36" t="n">
         <f aca="false">Wyjaśnienia!$B$42</f>
         <v>2</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28" t="s">
-        <v>269</v>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="s">
-        <v>270</v>
-      </c>
-      <c r="B9" s="42" t="n">
+      <c r="A9" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="37" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28" t="s">
-        <v>271</v>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -5377,85 +5345,85 @@
       <c r="F11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="40" t="s">
-        <v>273</v>
-      </c>
-      <c r="C12" s="40" t="s">
+      <c r="B12" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="C12" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="39" t="s">
+      <c r="E12" s="26"/>
+      <c r="F12" s="34" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="s">
-        <v>274</v>
-      </c>
-      <c r="B13" s="43" t="n">
+      <c r="A13" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="B13" s="38" t="n">
         <f aca="false">Wyjaśnienia!$B$44</f>
         <v>2500</v>
       </c>
-      <c r="C13" s="41" t="n">
+      <c r="C13" s="36" t="n">
         <f aca="false">Wyjaśnienia!$B$45</f>
         <v>15</v>
       </c>
-      <c r="D13" s="43" t="n">
+      <c r="D13" s="38" t="n">
         <f aca="false">B13*C13</f>
         <v>37500</v>
       </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28" t="s">
-        <v>275</v>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="B14" s="43" t="n">
+      <c r="A14" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B14" s="38" t="n">
         <f aca="false">Wyjaśnienia!$B$43</f>
         <v>500</v>
       </c>
-      <c r="C14" s="41" t="n">
+      <c r="C14" s="36" t="n">
         <f aca="false">ROUNDUP(B9/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D14" s="43" t="n">
+      <c r="D14" s="38" t="n">
         <f aca="false">B14*C14</f>
         <v>1500</v>
       </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28" t="s">
-        <v>277</v>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39" t="s">
-        <v>278</v>
-      </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="44" t="n">
+      <c r="A15" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="39" t="n">
         <f aca="false">SUM(D13:D14)</f>
         <v>39000</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
@@ -5468,81 +5436,81 @@
       <c r="F17" s="15"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="39" t="s">
+      <c r="E18" s="26"/>
+      <c r="F18" s="34" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="B19" s="45" t="n">
+      <c r="A19" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="B19" s="40" t="n">
         <v>2000</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="43" t="n">
+      <c r="D19" s="38" t="n">
         <f aca="false">B19*C19</f>
         <v>2000</v>
       </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28" t="s">
-        <v>280</v>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="B20" s="45" t="n">
+      <c r="A20" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B20" s="40" t="n">
         <v>3000</v>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C20" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="43" t="n">
+      <c r="D20" s="38" t="n">
         <f aca="false">B20*C20</f>
         <v>3000</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28" t="s">
-        <v>282</v>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="44" t="n">
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="39" t="n">
         <f aca="false">SUM(D19:D20)</f>
         <v>5000</v>
       </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
@@ -5555,94 +5523,94 @@
       <c r="F23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
-        <v>283</v>
-      </c>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="43" t="n">
+      <c r="A24" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="38" t="n">
         <f aca="false">D15</f>
         <v>39000</v>
       </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="43" t="n">
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="38" t="n">
         <f aca="false">D21</f>
         <v>5000</v>
       </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="s">
-        <v>284</v>
-      </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="43" t="n">
+      <c r="A26" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="38" t="n">
         <f aca="false">(D24+D25)*Wyjaśnienia!$B$26</f>
         <v>5280</v>
       </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="44" t="n">
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="39" t="n">
         <f aca="false">SUM(D24:D26)</f>
         <v>49280</v>
       </c>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="43" t="n">
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="38" t="n">
         <f aca="false">D27*Wyjaśnienia!$B$29</f>
         <v>11334.4</v>
       </c>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="44" t="n">
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="39" t="n">
         <f aca="false">D27+D28</f>
         <v>60614.4</v>
       </c>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -5651,142 +5619,142 @@
       <c r="F31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="B32" s="38"/>
-      <c r="C32" s="38"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
+      <c r="A32" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="40" t="s">
-        <v>287</v>
-      </c>
-      <c r="B33" s="40" t="s">
+      <c r="A33" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="B33" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="D33" s="40" t="s">
+      <c r="C33" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="E33" s="40" t="s">
+      <c r="D33" s="35" t="s">
         <v>291</v>
       </c>
-      <c r="F33" s="28"/>
+      <c r="E33" s="35" t="s">
+        <v>292</v>
+      </c>
+      <c r="F33" s="26"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="41" t="n">
+      <c r="A34" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="B34" s="41" t="n">
+      <c r="B34" s="36" t="n">
         <f aca="false">A34*Wyjaśnienia!$B$42</f>
         <v>300</v>
       </c>
-      <c r="C34" s="41" t="n">
+      <c r="C34" s="36" t="n">
         <f aca="false">ROUNDUP(B34/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D34" s="43" t="n">
+      <c r="D34" s="38" t="n">
         <f aca="false">C34*Wyjaśnienia!$B$43</f>
         <v>1500</v>
       </c>
-      <c r="E34" s="41" t="n">
+      <c r="E34" s="36" t="n">
         <f aca="false">ROUNDUP(A34/Wyjaśnienia!$B$46,0)</f>
         <v>8</v>
       </c>
-      <c r="F34" s="28"/>
+      <c r="F34" s="26"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="41" t="n">
+      <c r="A35" s="36" t="n">
         <v>1000</v>
       </c>
-      <c r="B35" s="41" t="n">
+      <c r="B35" s="36" t="n">
         <f aca="false">A35*Wyjaśnienia!$B$42</f>
         <v>2000</v>
       </c>
-      <c r="C35" s="41" t="n">
+      <c r="C35" s="36" t="n">
         <f aca="false">ROUNDUP(B35/100,0)</f>
         <v>20</v>
       </c>
-      <c r="D35" s="43" t="n">
+      <c r="D35" s="38" t="n">
         <f aca="false">C35*Wyjaśnienia!$B$43</f>
         <v>10000</v>
       </c>
-      <c r="E35" s="41" t="n">
+      <c r="E35" s="36" t="n">
         <f aca="false">ROUNDUP(A35/Wyjaśnienia!$B$46,0)</f>
         <v>50</v>
       </c>
-      <c r="F35" s="28"/>
+      <c r="F35" s="26"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="41" t="n">
+      <c r="A36" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="B36" s="41" t="n">
+      <c r="B36" s="36" t="n">
         <f aca="false">A36*Wyjaśnienia!$B$42</f>
         <v>20000</v>
       </c>
-      <c r="C36" s="41" t="n">
+      <c r="C36" s="36" t="n">
         <f aca="false">ROUNDUP(B36/100,0)</f>
         <v>200</v>
       </c>
-      <c r="D36" s="43" t="n">
+      <c r="D36" s="38" t="n">
         <f aca="false">C36*Wyjaśnienia!$B$43</f>
         <v>100000</v>
       </c>
-      <c r="E36" s="41" t="n">
+      <c r="E36" s="36" t="n">
         <f aca="false">ROUNDUP(A36/Wyjaśnienia!$B$46,0)</f>
         <v>500</v>
       </c>
-      <c r="F36" s="28"/>
+      <c r="F36" s="26"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="41" t="n">
+      <c r="A37" s="36" t="n">
         <v>100000</v>
       </c>
-      <c r="B37" s="41" t="n">
+      <c r="B37" s="36" t="n">
         <f aca="false">A37*Wyjaśnienia!$B$42</f>
         <v>200000</v>
       </c>
-      <c r="C37" s="41" t="n">
+      <c r="C37" s="36" t="n">
         <f aca="false">ROUNDUP(B37/100,0)</f>
         <v>2000</v>
       </c>
-      <c r="D37" s="43" t="n">
+      <c r="D37" s="38" t="n">
         <f aca="false">C37*Wyjaśnienia!$B$43</f>
         <v>1000000</v>
       </c>
-      <c r="E37" s="41" t="n">
+      <c r="E37" s="36" t="n">
         <f aca="false">ROUNDUP(A37/Wyjaśnienia!$B$46,0)</f>
         <v>5000</v>
       </c>
-      <c r="F37" s="28"/>
+      <c r="F37" s="26"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="41" t="n">
+      <c r="A38" s="36" t="n">
         <v>1000000</v>
       </c>
-      <c r="B38" s="41" t="n">
+      <c r="B38" s="36" t="n">
         <f aca="false">A38*Wyjaśnienia!$B$42</f>
         <v>2000000</v>
       </c>
-      <c r="C38" s="41" t="n">
+      <c r="C38" s="36" t="n">
         <f aca="false">ROUNDUP(B38/100,0)</f>
         <v>20000</v>
       </c>
-      <c r="D38" s="43" t="n">
+      <c r="D38" s="38" t="n">
         <f aca="false">C38*Wyjaśnienia!$B$43</f>
         <v>10000000</v>
       </c>
-      <c r="E38" s="41" t="n">
+      <c r="E38" s="36" t="n">
         <f aca="false">ROUNDUP(A38/Wyjaśnienia!$B$46,0)</f>
         <v>50000</v>
       </c>
-      <c r="F38" s="28"/>
+      <c r="F38" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -888,7 +888,7 @@
     <t xml:space="preserve">JAK TO SIĘ SKALUJE</t>
   </si>
   <si>
-    <t xml:space="preserve">Vouchery rosną wprost z liczbą rozmów, więc sponsor płaci za wykonaną pracę, a nie za prognozę. Ludzi trzeba jednak znaleźć osobno: ostatnia kolumna pokazuje, ilu czytelników wymaga dany wolumen przy limicie z regulaminu.</t>
+    <t xml:space="preserve">Vouchery rosną wprost z liczbą rozmów, więc sponsor płaci za wykonaną pracę, a nie za prognozę. Ludzi trzeba jednak znaleźć osobno: ostatnia kolumna liczy czytelników od liczby ODCZYTÓW, nie od liczby zgłoszeń - przy dwóch odczytach na zgłoszenie i limicie 20 zgłoszeń na czytelnika 150 zgłoszeń wymaga 15 osób, nie 8. Tabela przy większych wolumenach nie modeluje odrębnie trybu jednoosobowego, drugich odczytów poniżej progu ani audytu losowego - te trzy rzeczy trzeba policzyć osobno przed ogłoszeniem progu.</t>
   </si>
   <si>
     <t xml:space="preserve">Zgłoszeń w edycji</t>
@@ -5663,8 +5663,8 @@
         <v>1500</v>
       </c>
       <c r="E34" s="36" t="n">
-        <f aca="false">ROUNDUP(A34/Wyjaśnienia!$B$46,0)</f>
-        <v>8</v>
+        <f aca="false">ROUNDUP(B34/Wyjaśnienia!$B$46,0)</f>
+        <v>15</v>
       </c>
       <c r="F34" s="26"/>
     </row>
@@ -5685,8 +5685,8 @@
         <v>10000</v>
       </c>
       <c r="E35" s="36" t="n">
-        <f aca="false">ROUNDUP(A35/Wyjaśnienia!$B$46,0)</f>
-        <v>50</v>
+        <f aca="false">ROUNDUP(B35/Wyjaśnienia!$B$46,0)</f>
+        <v>100</v>
       </c>
       <c r="F35" s="26"/>
     </row>
@@ -5707,8 +5707,8 @@
         <v>100000</v>
       </c>
       <c r="E36" s="36" t="n">
-        <f aca="false">ROUNDUP(A36/Wyjaśnienia!$B$46,0)</f>
-        <v>500</v>
+        <f aca="false">ROUNDUP(B36/Wyjaśnienia!$B$46,0)</f>
+        <v>1000</v>
       </c>
       <c r="F36" s="26"/>
     </row>
@@ -5729,8 +5729,8 @@
         <v>1000000</v>
       </c>
       <c r="E37" s="36" t="n">
-        <f aca="false">ROUNDUP(A37/Wyjaśnienia!$B$46,0)</f>
-        <v>5000</v>
+        <f aca="false">ROUNDUP(B37/Wyjaśnienia!$B$46,0)</f>
+        <v>10000</v>
       </c>
       <c r="F37" s="26"/>
     </row>
@@ -5751,8 +5751,8 @@
         <v>10000000</v>
       </c>
       <c r="E38" s="36" t="n">
-        <f aca="false">ROUNDUP(A38/Wyjaśnienia!$B$46,0)</f>
-        <v>50000</v>
+        <f aca="false">ROUNDUP(B38/Wyjaśnienia!$B$46,0)</f>
+        <v>100000</v>
       </c>
       <c r="F38" s="26"/>
     </row>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -270,7 +270,7 @@
     <t xml:space="preserve">Liczba jurorów plakatu</t>
   </si>
   <si>
-    <t xml:space="preserve">Składu jeszcze nie ma. Przy trzech pozycja spada do 8,7 tys., przy siedmiu rośnie do 20,3 tys.</t>
+    <t xml:space="preserve">Kotwica, nie decyzja: pozycja honorariów w Budżecie Plakatu stoi na zerze jako DO USTALENIA, do rozmowy z przewodniczącym jury.</t>
   </si>
   <si>
     <t xml:space="preserve">Godzin oceny na jurora</t>
@@ -786,7 +786,7 @@
     <t xml:space="preserve">Honoraria jury plakatu za ocenę (netto)</t>
   </si>
   <si>
-    <t xml:space="preserve">stawka Kapituły, 10 h na jurora, skład pięcioosobowy</t>
+    <t xml:space="preserve">DO USTALENIA - stawka godzinowa jest przy nazwisku złym narzędziem; kotwica z Wyjaśnień (5 osób x 10 h x 290 zł) dałaby 14 500 zł</t>
   </si>
   <si>
     <t xml:space="preserve">Transport oryginałów w obie strony (netto)</t>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">'Budżet Plakatu'!$D$34</f>
-        <v>171736</v>
+        <v>155496</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$27</f>
-        <v>1337458.8</v>
+        <v>1321218.8</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5001,17 +5001,15 @@
       <c r="A21" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B21" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$55*Wyjaśnienia!$B$54</f>
-        <v>2900</v>
+      <c r="B21" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="30" t="n">
-        <f aca="false">Wyjaśnienia!$B$53</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D21" s="8" t="n">
         <f aca="false">B21*C21</f>
-        <v>14500</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>253</v>
@@ -5116,7 +5114,7 @@
       </c>
       <c r="D27" s="11" t="n">
         <f aca="false">SUM(D18:D26)</f>
-        <v>121500</v>
+        <v>107000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5153,7 +5151,7 @@
       </c>
       <c r="D32" s="8" t="n">
         <f aca="false">D27-D30</f>
-        <v>28500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5162,7 +5160,7 @@
       </c>
       <c r="D33" s="8" t="n">
         <f aca="false">(D31+D32)*Wyjaśnienia!$B$59</f>
-        <v>8436</v>
+        <v>6696</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5171,7 +5169,7 @@
       </c>
       <c r="D34" s="11" t="n">
         <f aca="false">SUM(D30:D33)</f>
-        <v>171736</v>
+        <v>155496</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5180,7 +5178,7 @@
       </c>
       <c r="D35" s="8" t="n">
         <f aca="false">D34*Wyjaśnienia!$B$29</f>
-        <v>39499.28</v>
+        <v>35764.08</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5189,7 +5187,7 @@
       </c>
       <c r="D36" s="11" t="n">
         <f aca="false">D34+D35</f>
-        <v>211235.28</v>
+        <v>191260.08</v>
       </c>
     </row>
   </sheetData>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -519,10 +519,10 @@
     <t xml:space="preserve">szablon przygotowany w styczniu</t>
   </si>
   <si>
-    <t xml:space="preserve">Archiwum: publikacja porcjami przez rok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jedna rozmowa na dwa tygodnie</t>
+    <t xml:space="preserve">Przegląd treści zgłoszeń przed publikacją w archiwum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 minut na zgłoszenie: dane osobowe osób trzecich i cudze materiały poza prawem cytatu (regulamin § 11 ust. 11 lit. e i j). Partią, między zamknięciem naboru a ogłoszeniem wyników. Zastąpiło publikację archiwum porcjami przez rok, z której zrezygnowano.</t>
   </si>
   <si>
     <t xml:space="preserve">Skraper i kopia archiwalna zgłoszenia</t>
@@ -573,7 +573,7 @@
     <t xml:space="preserve">magazyn obiektowy w UE z kopią zapasową, retencja min. 5 lat, PDF/HTML/zrzuty/EPUB; w tym skrzynka pocztowa w domenie wraz z aliasami (kontakt@, imienny) - rzędu 150-450 zł rocznie, aliasy bez dopłaty; przejście na własną skrzynkę przenosi MX i wyłącza Cloudflare Email Routing</t>
   </si>
   <si>
-    <t xml:space="preserve">Koordynator wydania i moderacji I-III 2028 (B2B)</t>
+    <t xml:space="preserve">Koordynator wydania i moderacji I-IV 2028 (B2B)</t>
   </si>
   <si>
     <t xml:space="preserve">pełne zaangażowanie I-III 2028, moderacja archiwum i obsługa zgłoszeń przy dużym napływie</t>
@@ -591,10 +591,10 @@
     <t xml:space="preserve">szablon plus obsługa wydania</t>
   </si>
   <si>
-    <t xml:space="preserve">Druk pierwszego nakładu antologii (100 egz.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z ekslibrisami podpisanymi na gali</t>
+    <t xml:space="preserve">Krótki nakład antologii na galę (100 egz.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gwarantowany przez organizatora, niezależny od partnera wydawniczego; nakład handlowy jest po stronie partnera</t>
   </si>
   <si>
     <t xml:space="preserve">Nadanie ISBN i egzemplarz obowiązkowy</t>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">'Budżet Antologii'!$D$38</f>
-        <v>298142</v>
+        <v>311012</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$27</f>
-        <v>1321218.8</v>
+        <v>1334088.8</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -3306,18 +3306,18 @@
         <v>164</v>
       </c>
       <c r="B9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20" t="n">
         <v>30</v>
-      </c>
-      <c r="C9" s="20" t="n">
-        <v>0</v>
       </c>
       <c r="D9" s="21" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E9" s="22" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
-        <v>6600</v>
+        <v>16500</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>165</v>
@@ -3449,11 +3449,11 @@
       <c r="C15" s="3"/>
       <c r="D15" s="23" t="n">
         <f aca="false">SUM(D7:D14)</f>
-        <v>472</v>
+        <v>517</v>
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">SUM(E7:E14)</f>
-        <v>103840</v>
+        <v>113740</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -3816,7 +3816,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="8" t="n">
         <f aca="false">E15</f>
-        <v>103840</v>
+        <v>113740</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -3846,7 +3846,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="8" t="n">
         <f aca="false">(D35+D36)*Wyjaśnienia!$B$27</f>
-        <v>68802</v>
+        <v>71772</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -3861,7 +3861,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="9" t="n">
         <f aca="false">SUM(D35:D37)</f>
-        <v>298142</v>
+        <v>311012</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -3876,7 +3876,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="8" t="n">
         <f aca="false">D38*Wyjaśnienia!$B$29</f>
-        <v>68572.66</v>
+        <v>71532.76</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -3891,7 +3891,7 @@
       <c r="C40" s="3"/>
       <c r="D40" s="25" t="n">
         <f aca="false">D38+D39</f>
-        <v>366714.66</v>
+        <v>382544.76</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -519,10 +519,10 @@
     <t xml:space="preserve">szablon przygotowany w styczniu</t>
   </si>
   <si>
-    <t xml:space="preserve">Przegląd treści zgłoszeń przed publikacją w archiwum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 minut na zgłoszenie: dane osobowe osób trzecich i cudze materiały poza prawem cytatu (regulamin § 11 ust. 11 lit. e i j). Partią, między zamknięciem naboru a ogłoszeniem wyników. Zastąpiło publikację archiwum porcjami przez rok, z której zrezygnowano.</t>
+    <t xml:space="preserve">Rozstrzyganie zgłoszeń oznaczonych przez oceniających</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oznaczanie zastrzeżeń prawnych robi Akademia przy czytaniu (regulamin § 8 ust. 3a), bo skaluje się razem z naborem. Organizator rozstrzyga tylko zgłoszenia oznaczone, wraz z zawiadomieniem uczestnika. Wpisane 4 minuty na zgłoszenie są uśrednieniem: przy części zgłoszeń nie ma nic do rozstrzygania, przy oznaczonych rozstrzygnięcie i korespondencja zajmują kilkadziesiąt minut.</t>
   </si>
   <si>
     <t xml:space="preserve">Skraper i kopia archiwalna zgłoszenia</t>
@@ -831,7 +831,7 @@
     <t xml:space="preserve">Zgłoszenia do Nagrody</t>
   </si>
   <si>
-    <t xml:space="preserve">parametr wspólny dla wszystkich budżetów</t>
+    <t xml:space="preserve">Honorarium obejmuje także oznaczanie zastrzeżeń prawnych przy czytaniu (regulamin § 8 ust. 3a): dane osób trzecich, całe cudze utwory krótkie, wgrane cudze materiały. Oznaczenie nie wpływa na punktację.</t>
   </si>
   <si>
     <t xml:space="preserve">Odczytów na zgłoszenie</t>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">'Budżet Antologii'!$D$38</f>
-        <v>311012</v>
+        <v>292422</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$27</f>
-        <v>1334088.8</v>
+        <v>1315498.8</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -3309,15 +3309,15 @@
         <v>0</v>
       </c>
       <c r="C9" s="20" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D9" s="21" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$15/60</f>
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="E9" s="22" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$14</f>
-        <v>16500</v>
+        <v>2200</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>165</v>
@@ -3449,11 +3449,11 @@
       <c r="C15" s="3"/>
       <c r="D15" s="23" t="n">
         <f aca="false">SUM(D7:D14)</f>
-        <v>517</v>
+        <v>452</v>
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">SUM(E7:E14)</f>
-        <v>113740</v>
+        <v>99440</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -3816,7 +3816,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="8" t="n">
         <f aca="false">E15</f>
-        <v>113740</v>
+        <v>99440</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -3846,7 +3846,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="8" t="n">
         <f aca="false">(D35+D36)*Wyjaśnienia!$B$27</f>
-        <v>71772</v>
+        <v>67482</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -3861,7 +3861,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="9" t="n">
         <f aca="false">SUM(D35:D37)</f>
-        <v>311012</v>
+        <v>292422</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -3876,7 +3876,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="8" t="n">
         <f aca="false">D38*Wyjaśnienia!$B$29</f>
-        <v>71532.76</v>
+        <v>67257.06</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -3891,7 +3891,7 @@
       <c r="C40" s="3"/>
       <c r="D40" s="25" t="n">
         <f aca="false">D38+D39</f>
-        <v>382544.76</v>
+        <v>359679.06</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -165,7 +165,7 @@
     <t xml:space="preserve">Marża w Budżecie Antologii</t>
   </si>
   <si>
-    <t xml:space="preserve">Narzut partnera wydawniczego.</t>
+    <t xml:space="preserve">Narzut wynagrodzenia podmiotu, który wykona tę część, liczony od pracy i kosztów twardych. Nie są to środki pozostające u Organizatora ani rezerwa. W kosztorysie dotacyjnym pozycja ta nie wystąpi.</t>
   </si>
   <si>
     <t xml:space="preserve">Rezerwa w Budżecie Plebiscytu</t>
@@ -522,7 +522,7 @@
     <t xml:space="preserve">Rozstrzyganie zgłoszeń oznaczonych przez oceniających</t>
   </si>
   <si>
-    <t xml:space="preserve">Oznaczanie zastrzeżeń prawnych robi Akademia przy czytaniu (regulamin § 8 ust. 3a), bo skaluje się razem z naborem. Organizator rozstrzyga tylko zgłoszenia oznaczone, wraz z zawiadomieniem uczestnika. Wpisane 4 minuty na zgłoszenie są uśrednieniem: przy części zgłoszeń nie ma nic do rozstrzygania, przy oznaczonych rozstrzygnięcie i korespondencja zajmują kilkadziesiąt minut.</t>
+    <t xml:space="preserve">Oznaczanie zastrzeżeń prawnych robi Akademia przy czytaniu (regulamin § 8 ust. 3a), bo skaluje się razem z naborem. Organizator rozstrzyga co do zgłoszeń oznaczonych oraz co do przypadków, w których otrzymał konkretny sygnał albo sam powziął wiadomość o problemie, wraz z zawiadomieniem uczestnika. Wpisane 4 minuty na zgłoszenie są uśrednieniem: przy części zgłoszeń nie ma nic do rozstrzygania, przy oznaczonych rozstrzygnięcie i korespondencja zajmują kilkadziesiąt minut.</t>
   </si>
   <si>
     <t xml:space="preserve">Skraper i kopia archiwalna zgłoszenia</t>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="292">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -150,10 +150,10 @@
     <t xml:space="preserve">Środek widełek 60-100 tys. Górny koniec przy szerszym składzie.</t>
   </si>
   <si>
-    <t xml:space="preserve">Statuetki i dyplomy plebiscytu (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propozycja, do potwierdzenia.</t>
+    <t xml:space="preserve">Medalion zwycięzcy i dyplomy piosenki (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten sam mosiężny medalion co w konkursie rozmów, cena jak w Budżecie Nagrody.</t>
   </si>
   <si>
     <t xml:space="preserve">Rezerwa w Budżecie Nagrody</t>
@@ -261,10 +261,7 @@
     <t xml:space="preserve">Jedna nagroda, bez nagrody za uzasadnienie.</t>
   </si>
   <si>
-    <t xml:space="preserve">Statuetki i dyplomy plakatu (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jak przy plebiscycie piosenki.</t>
+    <t xml:space="preserve">Medalion zwycięzcy i dyplomy plakatu (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Liczba jurorów plakatu</t>
@@ -693,7 +690,10 @@
     <t xml:space="preserve">nagranie i premiera na początku 2027, otwiera nabór</t>
   </si>
   <si>
-    <t xml:space="preserve">propozycja, do potwierdzenia</t>
+    <t xml:space="preserve">Medalion zwycięzcy i dyplomy finalistów (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ten sam medalion, który otrzymuje laureat konkursu rozmów; dyplomy dla całej dziesiątki</t>
   </si>
   <si>
     <t xml:space="preserve">Honoraria jury plebiscytu za ocenę (netto)</t>
@@ -778,9 +778,6 @@
   </si>
   <si>
     <t xml:space="preserve">jedna nagroda, dla pracy z największą liczbą głosów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jak przy plebiscycie piosenki</t>
   </si>
   <si>
     <t xml:space="preserve">Honoraria jury plakatu za ocenę (netto)</t>
@@ -1590,7 +1587,7 @@
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">'Budżet Plebiscytu'!$D$32</f>
-        <v>256616</v>
+        <v>254600</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -1619,7 +1616,7 @@
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">'Budżet Plakatu'!$D$34</f>
-        <v>155496</v>
+        <v>153480</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1633,7 +1630,7 @@
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">'Budżet Nagrody'!$D$39+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$27</f>
-        <v>1315498.8</v>
+        <v>1311466.8</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -1846,7 +1843,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="12" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>42</v>
@@ -2146,87 +2143,87 @@
         <v>78</v>
       </c>
       <c r="B52" s="16" t="n">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B53" s="18" t="n">
         <v>5</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B54" s="18" t="n">
         <v>10</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B55" s="16" t="n">
         <v>290</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B56" s="18" t="n">
         <v>10</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B57" s="16" t="n">
         <v>400</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B58" s="16" t="n">
         <v>3000</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B59" s="14" t="n">
         <v>0.12</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2330,7 +2327,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2342,7 +2339,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2364,7 +2361,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2376,29 +2373,29 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B7" s="20" t="n">
         <v>60</v>
@@ -2415,14 +2412,14 @@
         <v>13200</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" s="20" t="n">
         <v>24</v>
@@ -2439,14 +2436,14 @@
         <v>5280</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B9" s="20" t="n">
         <v>50</v>
@@ -2463,14 +2460,14 @@
         <v>11000</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" s="20" t="n">
         <v>8</v>
@@ -2487,14 +2484,14 @@
         <v>5060</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B11" s="20" t="n">
         <v>10</v>
@@ -2511,14 +2508,14 @@
         <v>4400</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B12" s="20" t="n">
         <v>20</v>
@@ -2535,14 +2532,14 @@
         <v>4400</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B13" s="20" t="n">
         <v>40</v>
@@ -2559,14 +2556,14 @@
         <v>8800</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B14" s="20" t="n">
         <v>25</v>
@@ -2583,14 +2580,14 @@
         <v>5500</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B15" s="20" t="n">
         <v>45</v>
@@ -2607,14 +2604,14 @@
         <v>9900</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B16" s="20" t="n">
         <v>25</v>
@@ -2631,14 +2628,14 @@
         <v>5500</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B17" s="20" t="n">
         <v>40</v>
@@ -2655,14 +2652,14 @@
         <v>8800</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2690,7 +2687,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2702,19 +2699,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>128</v>
-      </c>
       <c r="D21" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -2722,7 +2719,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" s="24" t="n">
         <v>8000</v>
@@ -2735,7 +2732,7 @@
         <v>8000</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -2743,7 +2740,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B23" s="24" t="n">
         <v>1500</v>
@@ -2756,7 +2753,7 @@
         <v>1500</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -2764,7 +2761,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B24" s="24" t="n">
         <v>1200</v>
@@ -2777,7 +2774,7 @@
         <v>1200</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -2785,7 +2782,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B25" s="24" t="n">
         <v>4000</v>
@@ -2798,7 +2795,7 @@
         <v>4000</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -2806,7 +2803,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B26" s="24" t="n">
         <v>1500</v>
@@ -2819,7 +2816,7 @@
         <v>1500</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -2827,7 +2824,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B27" s="24" t="n">
         <v>250</v>
@@ -2840,7 +2837,7 @@
         <v>250</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -2848,7 +2845,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B28" s="24" t="n">
         <v>32000</v>
@@ -2861,17 +2858,17 @@
         <v>32000</v>
       </c>
       <c r="E28" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B29" s="24" t="n">
         <v>15000</v>
@@ -2884,7 +2881,7 @@
         <v>15000</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -2892,7 +2889,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B30" s="24" t="n">
         <v>8000</v>
@@ -2905,7 +2902,7 @@
         <v>8000</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -2913,7 +2910,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B31" s="24" t="n">
         <v>0</v>
@@ -2926,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -2934,7 +2931,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2959,7 +2956,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2971,7 +2968,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2986,7 +2983,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -3001,7 +2998,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -3016,7 +3013,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -3031,7 +3028,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -3046,7 +3043,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -3061,7 +3058,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -3187,7 +3184,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3199,7 +3196,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3221,7 +3218,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -3233,29 +3230,29 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B7" s="20" t="n">
         <v>45</v>
@@ -3272,14 +3269,14 @@
         <v>9900</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B8" s="20" t="n">
         <v>40</v>
@@ -3296,14 +3293,14 @@
         <v>8800</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B9" s="20" t="n">
         <v>0</v>
@@ -3320,14 +3317,14 @@
         <v>2200</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B10" s="20" t="n">
         <v>50</v>
@@ -3344,14 +3341,14 @@
         <v>11000</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B11" s="20" t="n">
         <v>25</v>
@@ -3368,14 +3365,14 @@
         <v>5500</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B12" s="20" t="n">
         <v>160</v>
@@ -3392,14 +3389,14 @@
         <v>35200</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B13" s="20" t="n">
         <v>50</v>
@@ -3416,14 +3413,14 @@
         <v>11000</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B14" s="20" t="n">
         <v>72</v>
@@ -3443,7 +3440,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -3471,7 +3468,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -3483,19 +3480,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>128</v>
-      </c>
       <c r="D18" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -3503,7 +3500,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B19" s="24" t="n">
         <v>3000</v>
@@ -3516,7 +3513,7 @@
         <v>3000</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -3524,7 +3521,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B20" s="24" t="n">
         <v>6000</v>
@@ -3537,17 +3534,17 @@
         <v>6000</v>
       </c>
       <c r="E20" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B21" s="24" t="n">
         <v>10000</v>
@@ -3560,7 +3557,7 @@
         <v>10000</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -3568,7 +3565,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="24" t="n">
         <v>40000</v>
@@ -3581,7 +3578,7 @@
         <v>40000</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -3589,7 +3586,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B23" s="24" t="n">
         <v>4000</v>
@@ -3602,7 +3599,7 @@
         <v>4000</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -3610,7 +3607,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B24" s="24" t="n">
         <v>3000</v>
@@ -3623,7 +3620,7 @@
         <v>3000</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -3631,7 +3628,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B25" s="24" t="n">
         <v>4000</v>
@@ -3644,7 +3641,7 @@
         <v>4000</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -3652,7 +3649,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B26" s="24" t="n">
         <v>0</v>
@@ -3665,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -3673,7 +3670,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B27" s="24" t="n">
         <v>15000</v>
@@ -3686,7 +3683,7 @@
         <v>15000</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -3694,7 +3691,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B28" s="24" t="n">
         <v>6000</v>
@@ -3707,7 +3704,7 @@
         <v>6000</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -3715,7 +3712,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B29" s="24" t="n">
         <v>30000</v>
@@ -3728,7 +3725,7 @@
         <v>30000</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -3736,7 +3733,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>4500</v>
@@ -3749,12 +3746,12 @@
         <v>4500</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="26" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B31" s="16" t="n">
         <v>0</v>
@@ -3767,13 +3764,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F31" s="26"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -3798,7 +3795,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -3810,7 +3807,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -3825,7 +3822,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -3840,7 +3837,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -3855,7 +3852,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -3870,7 +3867,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -3885,7 +3882,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -4013,7 +4010,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4025,7 +4022,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -4047,7 +4044,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -4059,29 +4056,29 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B7" s="20" t="n">
         <v>0</v>
@@ -4098,14 +4095,14 @@
         <v>5500</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B8" s="20" t="n">
         <v>40</v>
@@ -4120,14 +4117,14 @@
         <v>8800</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B9" s="20" t="n">
         <v>30</v>
@@ -4142,14 +4139,14 @@
         <v>6600</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B10" s="20" t="n">
         <v>20</v>
@@ -4164,14 +4161,14 @@
         <v>4400</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B11" s="20" t="n">
         <v>50</v>
@@ -4186,14 +4183,14 @@
         <v>11000</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -4206,7 +4203,7 @@
         <v>36300</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -4223,7 +4220,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -4235,19 +4232,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>128</v>
-      </c>
       <c r="D15" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -4255,7 +4252,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B16" s="22" t="n">
         <f aca="false">Wyjaśnienia!$B$20</f>
@@ -4269,7 +4266,7 @@
         <v>35000</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -4277,7 +4274,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B17" s="22" t="n">
         <f aca="false">Wyjaśnienia!$B$21</f>
@@ -4291,7 +4288,7 @@
         <v>4000</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -4299,7 +4296,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" s="22" t="n">
         <f aca="false">Wyjaśnienia!$B$22</f>
@@ -4314,7 +4311,7 @@
         <v>75000</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -4336,7 +4333,7 @@
         <v>80000</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -4344,18 +4341,18 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>41</v>
+        <v>221</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">Wyjaśnienia!$B$25</f>
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="C20" s="20" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="22" t="n">
         <f aca="false">B20*C20</f>
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>222</v>
@@ -4448,13 +4445,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="23" t="n">
         <f aca="false">SUM(D16:D24)</f>
-        <v>197000</v>
+        <v>195200</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="3"/>
@@ -4473,7 +4470,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -4485,7 +4482,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -4500,7 +4497,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -4521,7 +4518,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="8" t="n">
         <f aca="false">D25-D28</f>
-        <v>158000</v>
+        <v>156200</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -4530,13 +4527,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="8" t="n">
         <f aca="false">(D29+D30)*Wyjaśnienia!$B$28</f>
-        <v>23316</v>
+        <v>23100</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -4545,13 +4542,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="9" t="n">
         <f aca="false">SUM(D28:D31)</f>
-        <v>256616</v>
+        <v>254600</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -4560,13 +4557,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="8" t="n">
         <f aca="false">D32*Wyjaśnienia!$B$29</f>
-        <v>59021.68</v>
+        <v>58558</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -4575,13 +4572,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="25" t="n">
         <f aca="false">D32+D33</f>
-        <v>315637.68</v>
+        <v>313158</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -4717,7 +4714,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -4727,7 +4724,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
@@ -4737,22 +4734,22 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="C6" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4799,7 +4796,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>20</v>
@@ -4899,7 +4896,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D14" s="31" t="n">
         <f aca="false">SUM(D7:D13)</f>
@@ -4910,12 +4907,12 @@
         <v>41800</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
@@ -4925,19 +4922,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B17" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>128</v>
-      </c>
       <c r="D17" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>101</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4980,26 +4977,26 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="B20" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$52</f>
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="C20" s="30" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="8" t="n">
         <f aca="false">B20*C20</f>
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B21" s="16" t="n">
         <v>0</v>
@@ -5012,12 +5009,12 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B22" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$57*2</f>
@@ -5032,12 +5029,12 @@
         <v>8000</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$58</f>
@@ -5051,12 +5048,12 @@
         <v>3000</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B24" s="16" t="n">
         <v>0</v>
@@ -5069,12 +5066,12 @@
         <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B25" s="16" t="n">
         <v>0</v>
@@ -5087,12 +5084,12 @@
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B26" s="16" t="n">
         <v>0</v>
@@ -5105,21 +5102,21 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D27" s="11" t="n">
         <f aca="false">SUM(D18:D26)</f>
-        <v>107000</v>
+        <v>105200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -5129,7 +5126,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$50+Wyjaśnienia!$B$51</f>
@@ -5138,7 +5135,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D31" s="8" t="n">
         <f aca="false">E14</f>
@@ -5151,43 +5148,43 @@
       </c>
       <c r="D32" s="8" t="n">
         <f aca="false">D27-D30</f>
-        <v>14000</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D33" s="8" t="n">
         <f aca="false">(D31+D32)*Wyjaśnienia!$B$59</f>
-        <v>6696</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D34" s="11" t="n">
         <f aca="false">SUM(D30:D33)</f>
-        <v>155496</v>
+        <v>153480</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D35" s="8" t="n">
         <f aca="false">D34*Wyjaśnienia!$B$29</f>
-        <v>35764.08</v>
+        <v>35300.4</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D36" s="11" t="n">
         <f aca="false">D34+D35</f>
-        <v>191260.08</v>
+        <v>188780.4</v>
       </c>
     </row>
   </sheetData>
@@ -5237,7 +5234,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="33" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
@@ -5247,7 +5244,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
@@ -5257,7 +5254,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
@@ -5267,21 +5264,21 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B7" s="36" t="n">
         <f aca="false">Wyjaśnienia!$B$15</f>
@@ -5291,12 +5288,12 @@
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
       <c r="F7" s="26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B8" s="36" t="n">
         <f aca="false">Wyjaśnienia!$B$42</f>
@@ -5306,12 +5303,12 @@
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
       <c r="F8" s="26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="34" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B9" s="37" t="n">
         <f aca="false">B7*B8</f>
@@ -5321,7 +5318,7 @@
       <c r="D9" s="26"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5334,7 +5331,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -5344,25 +5341,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E12" s="26"/>
       <c r="F12" s="34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B13" s="38" t="n">
         <f aca="false">Wyjaśnienia!$B$44</f>
@@ -5378,12 +5375,12 @@
       </c>
       <c r="E13" s="26"/>
       <c r="F13" s="26" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B14" s="38" t="n">
         <f aca="false">Wyjaśnienia!$B$43</f>
@@ -5399,12 +5396,12 @@
       </c>
       <c r="E14" s="26"/>
       <c r="F14" s="26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="34" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B15" s="26"/>
       <c r="C15" s="26"/>
@@ -5425,7 +5422,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -5435,25 +5432,25 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B18" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="35" t="s">
-        <v>128</v>
-      </c>
       <c r="D18" s="35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E18" s="26"/>
       <c r="F18" s="34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B19" s="40" t="n">
         <v>2000</v>
@@ -5467,12 +5464,12 @@
       </c>
       <c r="E19" s="26"/>
       <c r="F19" s="26" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B20" s="40" t="n">
         <v>3000</v>
@@ -5486,12 +5483,12 @@
       </c>
       <c r="E20" s="26"/>
       <c r="F20" s="26" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="26"/>
@@ -5512,7 +5509,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -5522,7 +5519,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="26"/>
@@ -5535,7 +5532,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="26"/>
@@ -5548,7 +5545,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="26"/>
@@ -5561,7 +5558,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -5574,7 +5571,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B28" s="26"/>
       <c r="C28" s="26"/>
@@ -5587,7 +5584,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
@@ -5608,7 +5605,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -5618,7 +5615,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="33"/>
@@ -5628,19 +5625,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="B33" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="B33" s="35" t="s">
+      <c r="C33" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="C33" s="35" t="s">
+      <c r="D33" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="D33" s="35" t="s">
+      <c r="E33" s="35" t="s">
         <v>291</v>
-      </c>
-      <c r="E33" s="35" t="s">
-        <v>292</v>
       </c>
       <c r="F33" s="26"/>
     </row>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -747,7 +747,7 @@
     <t xml:space="preserve">Przyjęcie, ewidencja i zwrot oryginałów finalistów</t>
   </si>
   <si>
-    <t xml:space="preserve">protokoły odbioru, stan prac, ubezpieczenie, wysyłka powrotna</t>
+    <t xml:space="preserve">Dwie lokalizacje: wystawa przy gali i wernisaż w galerii sztuki (regulamin § 10 ust. 3a), więc protokoły, przewóz między miejscami i ubezpieczenie na dłuższy okres - do 120 dni od dostarczenia pracy. Przy wycenie sprawdzić, czy 35 godzin wystarcza.</t>
   </si>
   <si>
     <t xml:space="preserve">Uzgodnienie okładki antologii ze zwycięzcą</t>
@@ -795,10 +795,10 @@
     <t xml:space="preserve">szacunek przy sumie deklarowanej rzędu 100 tys. zł</t>
   </si>
   <si>
-    <t xml:space="preserve">Realizacja wystawy przy gali (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - zawieszenie, oświetlenie, opisy prac; zależy od miejsca gali</t>
+    <t xml:space="preserve">Realizacja wystawy przy gali i wernisażu w galerii (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - zawieszenie, oświetlenie, opisy prac w dwóch miejscach, przewóz między nimi, obsługa wernisażu</t>
   </si>
   <si>
     <t xml:space="preserve">Obsługa prawna regulaminu plakatu (netto)</t>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="370">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -112,13 +112,25 @@
     <t xml:space="preserve">Wyróżnienie dla finalisty (brutto)</t>
   </si>
   <si>
-    <t xml:space="preserve">Dziewięć osób z dziesiątki antologii.</t>
+    <t xml:space="preserve">Siedem osób z dziesiątki antologii, poza podium.</t>
   </si>
   <si>
     <t xml:space="preserve">Liczba wyróżnień</t>
   </si>
   <si>
-    <t xml:space="preserve">Dziesiątka minus laureat.</t>
+    <t xml:space="preserve">Dziesiątka minus laureat, drugie i trzecie miejsce.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagroda za drugie miejsce (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Druga rozmowa z werdyktu jury.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagroda za trzecie miejsce (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trzecia rozmowa z werdyktu jury.</t>
   </si>
   <si>
     <t xml:space="preserve">Liczba zgłoszeń do plebiscytu</t>
@@ -157,10 +169,10 @@
     <t xml:space="preserve">Środek widełek 60-100 tys. Górny koniec przy szerszym składzie.</t>
   </si>
   <si>
-    <t xml:space="preserve">Medalion zwycięzcy i dyplomy piosenki (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten sam mosiężny medalion co w konkursie rozmów, cena jak w Budżecie Nagrody.</t>
+    <t xml:space="preserve">Medal zwycięzcy i dyplomy piosenki (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten sam mosiężny medal co w konkursie rozmów, cena jak w Budżecie Nagrody.</t>
   </si>
   <si>
     <t xml:space="preserve">Rezerwa w Budżecie Nagrody</t>
@@ -268,7 +280,7 @@
     <t xml:space="preserve">Jedna nagroda, bez nagrody za uzasadnienie.</t>
   </si>
   <si>
-    <t xml:space="preserve">Medalion zwycięzcy i dyplomy plakatu (netto)</t>
+    <t xml:space="preserve">Medal zwycięzcy i dyplomy plakatu (netto)</t>
   </si>
   <si>
     <t xml:space="preserve">Liczba jurorów plakatu</t>
@@ -280,13 +292,13 @@
     <t xml:space="preserve">Godzin oceny na jurora</t>
   </si>
   <si>
-    <t xml:space="preserve">Oglądanie reprodukcji jest szybsze niż odsłuch utworów; przy Kapitule przyjęto 15 h.</t>
+    <t xml:space="preserve">Oglądanie reprodukcji jest szybsze niż odsłuch utworów; przy jury przyjęto 15 h.</t>
   </si>
   <si>
     <t xml:space="preserve">Stawka jury plakatu za godzinę (netto)</t>
   </si>
   <si>
-    <t xml:space="preserve">Stawka przyjęta dla Kapituły oceniającej rozmowy.</t>
+    <t xml:space="preserve">Stawka przyjęta dla jury oceniającej rozmowy.</t>
   </si>
   <si>
     <t xml:space="preserve">Liczba prac finałowych</t>
@@ -334,10 +346,10 @@
     <t xml:space="preserve">Jedna nagroda, dla filmu z największą liczbą głosów.</t>
   </si>
   <si>
-    <t xml:space="preserve">Medalion zwycięzcy i dyplomy filmu (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten sam mosiężny medalion co w pozostałych plebiscytach; dyplomy dla pięciu finalistów.</t>
+    <t xml:space="preserve">Medal zwycięzcy i dyplomy filmu (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten sam mosiężny medal co w pozostałych plebiscytach; dyplomy dla pięciu finalistów.</t>
   </si>
   <si>
     <t xml:space="preserve">Liczba filmów finałowych</t>
@@ -409,7 +421,7 @@
     <t xml:space="preserve">Uwagi</t>
   </si>
   <si>
-    <t xml:space="preserve">Rekrutacja Kapituły i Akademii, korespondencja</t>
+    <t xml:space="preserve">Rekrutacja jury i Akademii, korespondencja</t>
   </si>
   <si>
     <t xml:space="preserve">15 czytelników, 3-5 jurorów, lista rezerwowa</t>
@@ -445,7 +457,7 @@
     <t xml:space="preserve">inscenizacja, treści trudne, odmowy publikacji</t>
   </si>
   <si>
-    <t xml:space="preserve">Koordynacja rundy drugiej z Kapitułą</t>
+    <t xml:space="preserve">Koordynacja rundy drugiej z jury</t>
   </si>
   <si>
     <t xml:space="preserve">spotkania, protokoły, rozbieżności</t>
@@ -505,7 +517,7 @@
     <t xml:space="preserve">mosiądz grawerowany, 10 dyplomów</t>
   </si>
   <si>
-    <t xml:space="preserve">Przejazdy i noclegi Kapituły</t>
+    <t xml:space="preserve">Przejazdy i noclegi jury</t>
   </si>
   <si>
     <t xml:space="preserve">zwrot kosztów</t>
@@ -523,7 +535,7 @@
     <t xml:space="preserve">opłacone</t>
   </si>
   <si>
-    <t xml:space="preserve">Honoraria Kapituły</t>
+    <t xml:space="preserve">Honoraria jury</t>
   </si>
   <si>
     <t xml:space="preserve">15 czytelników po 2 500 zł, 4 jurorów po 8 000 zł</t>
@@ -583,10 +595,10 @@
     <t xml:space="preserve">Finansuje: Partner wydawniczy / sponsor organizacyjny. Kwoty netto, chyba że napisano inaczej.</t>
   </si>
   <si>
-    <t xml:space="preserve">Antologia: redakcja not Kapituły i uzupełnienia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noty pisze Kapituła (§ 8 ust. 13a)</t>
+    <t xml:space="preserve">Antologia: redakcja not jury i uzupełnienia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noty pisze jury (§ 8 ust. 13a)</t>
   </si>
   <si>
     <t xml:space="preserve">Skład, korekta autorska, EPUB i PDF</t>
@@ -613,7 +625,7 @@
     <t xml:space="preserve">liczenie słów i wypowiedzi, wykluczanie kodu, język, ciągłość wątku</t>
   </si>
   <si>
-    <t xml:space="preserve">Panel oceny dla Akademii i Kapituły</t>
+    <t xml:space="preserve">Panel oceny dla Akademii i jury</t>
   </si>
   <si>
     <t xml:space="preserve">konta, przydziały, karta oceny, rozbieżności, trzeci odczyt, ślad audytowy</t>
@@ -778,7 +790,7 @@
     <t xml:space="preserve">Honoraria jury plebiscytu za ocenę (netto)</t>
   </si>
   <si>
-    <t xml:space="preserve">DO USTALENIA - kotwica: stawka Kapituły ok. 290 zł/h, ok. 15 h na jurora</t>
+    <t xml:space="preserve">DO USTALENIA - kotwica: stawka jury ok. 290 zł/h, ok. 15 h na jurora</t>
   </si>
   <si>
     <t xml:space="preserve">Realizacja części artystycznej gali (netto)</t>
@@ -1280,7 +1292,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1341,7 +1353,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1349,11 +1377,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1385,10 +1417,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1418,6 +1446,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1776,7 +1808,7 @@
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">'Budżet Nagrody'!$D$40</f>
-        <v>565044.8</v>
+        <v>570044.8</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -1865,7 +1897,7 @@
       </c>
       <c r="C12" s="11" t="n">
         <f aca="false">'Budżet Nagrody'!$D$40+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$34</f>
-        <v>1681506.8</v>
+        <v>1686506.8</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -1966,7 +1998,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>30</v>
@@ -1982,39 +2014,29 @@
         <v>31</v>
       </c>
       <c r="B20" s="12" t="n">
-        <v>150</v>
+        <v>20000</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="12" t="n">
-        <v>35000</v>
+        <v>5000</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="12" t="n">
-        <v>4000</v>
+        <v>150</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>36</v>
@@ -2030,7 +2052,7 @@
         <v>37</v>
       </c>
       <c r="B23" s="12" t="n">
-        <v>7500</v>
+        <v>35000</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>38</v>
@@ -2046,7 +2068,7 @@
         <v>39</v>
       </c>
       <c r="B24" s="12" t="n">
-        <v>10</v>
+        <v>4000</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>40</v>
@@ -2062,7 +2084,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="12" t="n">
-        <v>80000</v>
+        <v>7500</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>42</v>
@@ -2078,7 +2100,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="12" t="n">
-        <v>1200</v>
+        <v>10</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>44</v>
@@ -2093,8 +2115,8 @@
       <c r="A27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>0.12</v>
+      <c r="B27" s="12" t="n">
+        <v>80000</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>46</v>
@@ -2109,8 +2131,8 @@
       <c r="A28" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>0.3</v>
+      <c r="B28" s="12" t="n">
+        <v>1200</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>48</v>
@@ -2129,7 +2151,7 @@
         <v>0.12</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -2139,13 +2161,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" s="14" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -2155,13 +2177,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="14" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -2170,7 +2192,15 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3"/>
+      <c r="A32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>55</v>
+      </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -2178,11 +2208,15 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
+      <c r="A33" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>57</v>
+      </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2190,13 +2224,7 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="3"/>
+      <c r="A34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2204,8 +2232,8 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>57</v>
+      <c r="A35" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -2214,11 +2242,13 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
+      <c r="A36" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="17"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2226,7 +2256,9 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3"/>
+      <c r="A37" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -2234,11 +2266,11 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
+      <c r="A38" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2246,11 +2278,9 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2258,44 +2288,42 @@
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+      <c r="A40" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+    </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B43" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
+      <c r="A42" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>500</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="A44" s="19" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2303,8 +2331,8 @@
       <c r="A45" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B45" s="16" t="n">
-        <v>2500</v>
+      <c r="B45" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>68</v>
@@ -2314,8 +2342,8 @@
       <c r="A46" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B46" s="12" t="n">
-        <v>15</v>
+      <c r="B46" s="20" t="n">
+        <v>500</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>70</v>
@@ -2325,40 +2353,38 @@
       <c r="A47" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B47" s="12" t="n">
-        <v>20</v>
+      <c r="B47" s="20" t="n">
+        <v>2500</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B50" s="18" t="n">
-        <v>150</v>
-      </c>
-      <c r="C50" s="1" t="s">
+      <c r="A49" s="15" t="s">
         <v>75</v>
       </c>
-    </row>
+      <c r="B49" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B51" s="16" t="n">
-        <v>90000</v>
-      </c>
-      <c r="C51" s="1" t="s">
+      <c r="A51" s="21" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2366,8 +2392,8 @@
       <c r="A52" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B52" s="16" t="n">
-        <v>3000</v>
+      <c r="B52" s="22" t="n">
+        <v>150</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>79</v>
@@ -2377,41 +2403,41 @@
       <c r="A53" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B53" s="16" t="n">
-        <v>1200</v>
+      <c r="B53" s="20" t="n">
+        <v>90000</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B54" s="18" t="n">
-        <v>5</v>
+        <v>82</v>
+      </c>
+      <c r="B54" s="20" t="n">
+        <v>3000</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B55" s="18" t="n">
-        <v>10</v>
+        <v>84</v>
+      </c>
+      <c r="B55" s="20" t="n">
+        <v>1200</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B56" s="16" t="n">
-        <v>290</v>
+      <c r="B56" s="22" t="n">
+        <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>86</v>
@@ -2421,7 +2447,7 @@
       <c r="A57" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B57" s="18" t="n">
+      <c r="B57" s="22" t="n">
         <v>10</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -2432,8 +2458,8 @@
       <c r="A58" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B58" s="16" t="n">
-        <v>400</v>
+      <c r="B58" s="20" t="n">
+        <v>290</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>90</v>
@@ -2443,8 +2469,8 @@
       <c r="A59" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B59" s="16" t="n">
-        <v>3000</v>
+      <c r="B59" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>92</v>
@@ -2454,40 +2480,38 @@
       <c r="A60" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B60" s="14" t="n">
-        <v>0.12</v>
+      <c r="B60" s="20" t="n">
+        <v>400</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B61" s="20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B63" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="C63" s="1" t="s">
+      <c r="A62" s="23" t="s">
         <v>97</v>
       </c>
-    </row>
+      <c r="B62" s="23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B64" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="C64" s="1" t="s">
+      <c r="A64" s="21" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2496,7 +2520,7 @@
         <v>100</v>
       </c>
       <c r="B65" s="12" t="n">
-        <v>3000</v>
+        <v>150</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>101</v>
@@ -2507,7 +2531,7 @@
         <v>102</v>
       </c>
       <c r="B66" s="12" t="n">
-        <v>1200</v>
+        <v>180000</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>103</v>
@@ -2518,7 +2542,7 @@
         <v>104</v>
       </c>
       <c r="B67" s="12" t="n">
-        <v>5</v>
+        <v>3000</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>105</v>
@@ -2529,7 +2553,7 @@
         <v>106</v>
       </c>
       <c r="B68" s="12" t="n">
-        <v>5</v>
+        <v>1200</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>107</v>
@@ -2540,7 +2564,7 @@
         <v>108</v>
       </c>
       <c r="B69" s="12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>109</v>
@@ -2551,43 +2575,43 @@
         <v>110</v>
       </c>
       <c r="B70" s="12" t="n">
-        <v>290</v>
+        <v>5</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B71" s="12" t="n">
-        <v>0.12</v>
+        <v>25</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B72" s="12" t="n">
-        <v>2</v>
+        <v>290</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B73" s="12" t="n">
-        <v>300</v>
+        <v>0.12</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2595,14 +2619,34 @@
         <v>116</v>
       </c>
       <c r="B74" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B75" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B76" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2688,7 +2732,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2700,7 +2744,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2722,7 +2766,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2734,297 +2778,297 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="B7" s="20" t="n">
+      <c r="A7" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="26" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$16/60</f>
         <v>60</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="27" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$15</f>
         <v>13200</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="20" t="n">
+      <c r="A8" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="26" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$16/60</f>
         <v>24</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="27" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$15</f>
         <v>5280</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="B9" s="20" t="n">
+      <c r="A9" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$16/60</f>
         <v>50</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="27" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$15</f>
         <v>11000</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="20" t="n">
+      <c r="A10" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="26" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$16/60</f>
         <v>23</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="27" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$15</f>
         <v>5060</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="B11" s="20" t="n">
+      <c r="A11" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="26" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$16/60</f>
         <v>20</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="27" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$15</f>
         <v>4400</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="20" t="n">
+      <c r="A12" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="26" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$16/60</f>
         <v>20</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="27" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$15</f>
         <v>4400</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="B13" s="20" t="n">
+      <c r="A13" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="26" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$16/60</f>
         <v>40</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="27" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$15</f>
         <v>8800</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="20" t="n">
+      <c r="A14" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="26" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$16/60</f>
         <v>25</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="27" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$15</f>
         <v>5500</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="B15" s="20" t="n">
+      <c r="A15" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="25" t="n">
         <v>45</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="26" t="n">
         <f aca="false">B15+C15*Wyjaśnienia!$B$16/60</f>
         <v>45</v>
       </c>
-      <c r="E15" s="22" t="n">
+      <c r="E15" s="27" t="n">
         <f aca="false">D15*Wyjaśnienia!$B$15</f>
         <v>9900</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B16" s="20" t="n">
+      <c r="A16" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="26" t="n">
         <f aca="false">B16+C16*Wyjaśnienia!$B$16/60</f>
         <v>25</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="27" t="n">
         <f aca="false">D16*Wyjaśnienia!$B$15</f>
         <v>5500</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="B17" s="20" t="n">
+      <c r="A17" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="26" t="n">
         <f aca="false">B17+C17*Wyjaśnienia!$B$16/60</f>
         <v>40</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="27" t="n">
         <f aca="false">D17*Wyjaśnienia!$B$15</f>
         <v>8800</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="28" t="n">
         <f aca="false">SUM(D7:D17)</f>
         <v>372</v>
       </c>
@@ -3048,7 +3092,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -3060,226 +3104,226 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B22" s="24" t="n">
+      <c r="A22" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="29" t="n">
         <v>8000</v>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="27" t="n">
         <f aca="false">B22*C22</f>
         <v>8000</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="24" t="n">
+      <c r="A23" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="29" t="n">
         <v>1500</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="27" t="n">
         <f aca="false">B23*C23</f>
         <v>1500</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="B24" s="24" t="n">
+      <c r="A24" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="29" t="n">
         <v>1200</v>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="27" t="n">
         <f aca="false">B24*C24</f>
         <v>1200</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="B25" s="24" t="n">
+      <c r="A25" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" s="29" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="22" t="n">
+      <c r="D25" s="27" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="24" t="n">
+      <c r="A26" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="29" t="n">
         <v>1500</v>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="27" t="n">
         <f aca="false">B26*C26</f>
         <v>1500</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="B27" s="24" t="n">
+      <c r="A27" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="B27" s="29" t="n">
         <v>250</v>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="22" t="n">
+      <c r="D27" s="27" t="n">
         <f aca="false">B27*C27</f>
         <v>250</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="B28" s="24" t="n">
+      <c r="A28" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B28" s="29" t="n">
         <v>32000</v>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="27" t="n">
         <f aca="false">B28*C28</f>
         <v>32000</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="B29" s="24" t="n">
+      <c r="A29" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" s="29" t="n">
         <v>15000</v>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="22" t="n">
+      <c r="D29" s="27" t="n">
         <f aca="false">B29*C29</f>
         <v>15000</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="B30" s="24" t="n">
+      <c r="A30" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="B30" s="29" t="n">
         <v>8000</v>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="27" t="n">
         <f aca="false">B30*C30</f>
         <v>8000</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="B31" s="24" t="n">
+      <c r="A31" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="C31" s="20" t="n">
+      <c r="C31" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="22" t="n">
+      <c r="D31" s="27" t="n">
         <f aca="false">B31*C31</f>
         <v>3000</v>
       </c>
@@ -3287,21 +3331,21 @@
       <c r="F31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="B32" s="24" t="n">
+      <c r="A32" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="22" t="n">
+      <c r="D32" s="27" t="n">
         <f aca="false">B32*C32</f>
         <v>0</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
@@ -3309,7 +3353,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -3323,31 +3367,31 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="25"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="26" t="s">
-        <v>176</v>
+      <c r="A35" s="16" t="s">
+        <v>180</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
-        <v>177</v>
+      <c r="A36" s="24" t="s">
+        <v>181</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="22" t="n">
-        <f aca="false">Wyjaśnienia!$B$17+Wyjaśnienia!$B$18*Wyjaśnienia!$B$19</f>
-        <v>390000</v>
+      <c r="D36" s="27" t="n">
+        <f aca="false">Wyjaśnienia!$B$17+Wyjaśnienia!$B$20+Wyjaśnienia!$B$21+Wyjaśnienia!$B$18*Wyjaśnienia!$B$19</f>
+        <v>395000</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -3355,8 +3399,8 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
-        <v>178</v>
+      <c r="A37" s="24" t="s">
+        <v>182</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -3370,8 +3414,8 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
-        <v>179</v>
+      <c r="A38" s="24" t="s">
+        <v>183</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -3385,13 +3429,13 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
-        <v>180</v>
+      <c r="A39" s="24" t="s">
+        <v>184</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="8" t="n">
-        <f aca="false">(D37+D38)*Wyjaśnienia!$B$27</f>
+        <f aca="false">(D37+D38)*Wyjaśnienia!$B$29</f>
         <v>18754.8</v>
       </c>
       <c r="E39" s="3"/>
@@ -3401,13 +3445,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="9" t="n">
         <f aca="false">SUM(D36:D39)</f>
-        <v>565044.8</v>
+        <v>570044.8</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -3415,14 +3459,14 @@
       <c r="H40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="19" t="s">
-        <v>182</v>
+      <c r="A41" s="24" t="s">
+        <v>186</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="8" t="n">
-        <f aca="false">D40*Wyjaśnienia!$B$30</f>
-        <v>129960.304</v>
+        <f aca="false">D40*Wyjaśnienia!$B$32</f>
+        <v>131110.304</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -3431,13 +3475,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="27" t="n">
+      <c r="D42" s="31" t="n">
         <f aca="false">D40+D41</f>
-        <v>695005.104</v>
+        <v>701155.104</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -3556,7 +3600,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3568,7 +3612,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3590,7 +3634,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -3602,209 +3646,209 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="B7" s="20" t="n">
+      <c r="A7" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="25" t="n">
         <v>45</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="26" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$16/60</f>
         <v>45</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="27" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$15</f>
         <v>9900</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="B8" s="20" t="n">
+      <c r="A8" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="26" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$16/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="27" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$15</f>
         <v>8800</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="B9" s="20" t="n">
+      <c r="A9" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$16/60</f>
         <v>10</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="27" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$15</f>
         <v>2200</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="B10" s="20" t="n">
+      <c r="A10" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="26" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$16/60</f>
         <v>50</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="27" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$15</f>
         <v>11000</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="B11" s="20" t="n">
+      <c r="A11" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="26" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$16/60</f>
         <v>25</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="27" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$15</f>
         <v>5500</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="B12" s="20" t="n">
+      <c r="A12" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" s="25" t="n">
         <v>160</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="26" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$16/60</f>
         <v>160</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="27" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$15</f>
         <v>35200</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="B13" s="20" t="n">
+      <c r="A13" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="26" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$16/60</f>
         <v>50</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="27" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$15</f>
         <v>11000</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="B14" s="20" t="n">
+      <c r="A14" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="25" t="n">
         <v>72</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="26" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$16/60</f>
         <v>72</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="27" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$15</f>
         <v>15840</v>
       </c>
@@ -3812,11 +3856,11 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="28" t="n">
         <f aca="false">SUM(D7:D14)</f>
         <v>452</v>
       </c>
@@ -3840,7 +3884,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -3852,283 +3896,283 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="B19" s="24" t="n">
+      <c r="A19" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="B19" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="27" t="n">
         <f aca="false">B19*C19</f>
         <v>3000</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="B20" s="24" t="n">
+      <c r="A20" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" s="29" t="n">
         <v>6000</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="27" t="n">
         <f aca="false">B20*C20</f>
         <v>6000</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="B21" s="24" t="n">
+      <c r="A21" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21" s="29" t="n">
         <v>10000</v>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="27" t="n">
         <f aca="false">B21*C21</f>
         <v>10000</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="B22" s="24" t="n">
+      <c r="A22" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="29" t="n">
         <v>40000</v>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="27" t="n">
         <f aca="false">B22*C22</f>
         <v>40000</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="B23" s="24" t="n">
+      <c r="A23" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B23" s="29" t="n">
         <v>4000</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="27" t="n">
         <f aca="false">B23*C23</f>
         <v>4000</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="B24" s="24" t="n">
+      <c r="A24" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="B24" s="29" t="n">
         <v>3000</v>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="27" t="n">
         <f aca="false">B24*C24</f>
         <v>3000</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="B25" s="24" t="n">
+      <c r="A25" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="B25" s="29" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="22" t="n">
+      <c r="D25" s="27" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="B26" s="24" t="n">
+      <c r="A26" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="27" t="n">
         <f aca="false">B26*C26</f>
         <v>0</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="B27" s="24" t="n">
+      <c r="A27" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="B27" s="29" t="n">
         <v>15000</v>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="22" t="n">
+      <c r="D27" s="27" t="n">
         <f aca="false">B27*C27</f>
         <v>15000</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="B28" s="24" t="n">
+      <c r="A28" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="B28" s="29" t="n">
         <v>6000</v>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="27" t="n">
         <f aca="false">B28*C28</f>
         <v>6000</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="B29" s="24" t="n">
+      <c r="A29" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" s="29" t="n">
         <v>30000</v>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="22" t="n">
+      <c r="D29" s="27" t="n">
         <f aca="false">B29*C29</f>
         <v>30000</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="B30" s="16" t="n">
+      <c r="A30" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="B30" s="20" t="n">
         <v>4500</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">B30*C30</f>
         <v>4500</v>
       </c>
-      <c r="F30" s="28" t="s">
-        <v>224</v>
+      <c r="F30" s="32" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="B31" s="16" t="n">
+      <c r="A31" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="B31" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="8" t="n">
@@ -4136,13 +4180,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F31" s="28"/>
+        <v>230</v>
+      </c>
+      <c r="F31" s="32"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -4156,18 +4200,18 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -4178,8 +4222,8 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
-        <v>178</v>
+      <c r="A35" s="24" t="s">
+        <v>182</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -4193,8 +4237,8 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
-        <v>179</v>
+      <c r="A36" s="24" t="s">
+        <v>183</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -4208,13 +4252,13 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
-        <v>227</v>
+      <c r="A37" s="24" t="s">
+        <v>231</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="8" t="n">
-        <f aca="false">(D35+D36)*Wyjaśnienia!$B$28</f>
+        <f aca="false">(D35+D36)*Wyjaśnienia!$B$30</f>
         <v>67482</v>
       </c>
       <c r="E37" s="3"/>
@@ -4224,7 +4268,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -4238,13 +4282,13 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
-        <v>182</v>
+      <c r="A39" s="24" t="s">
+        <v>186</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="8" t="n">
-        <f aca="false">D38*Wyjaśnienia!$B$30</f>
+        <f aca="false">D38*Wyjaśnienia!$B$32</f>
         <v>67257.06</v>
       </c>
       <c r="E39" s="3"/>
@@ -4254,11 +4298,11 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="27" t="n">
+      <c r="D40" s="31" t="n">
         <f aca="false">D38+D39</f>
         <v>359679.06</v>
       </c>
@@ -4382,7 +4426,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4394,7 +4438,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -4416,7 +4460,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -4428,145 +4472,145 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="20" t="n">
+      <c r="A7" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="B7" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="21" t="n">
-        <f aca="false">B7+C7*Wyjaśnienia!$B$20/60</f>
+      <c r="D7" s="26" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$22/60</f>
         <v>25</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="27" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$15</f>
         <v>5500</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="20" t="n">
+      <c r="A8" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21" t="n">
-        <f aca="false">B8+C8*Wyjaśnienia!$B$20/60</f>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$22/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="27" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$15</f>
         <v>8800</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="B9" s="20" t="n">
+      <c r="A9" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21" t="n">
-        <f aca="false">B9+C9*Wyjaśnienia!$B$20/60</f>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$22/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="27" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$15</f>
         <v>6600</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="B10" s="20" t="n">
+      <c r="A10" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="B10" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21" t="n">
-        <f aca="false">B10+C10*Wyjaśnienia!$B$20/60</f>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$22/60</f>
         <v>20</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="27" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$15</f>
         <v>4400</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="B11" s="20" t="n">
+      <c r="A11" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21" t="n">
-        <f aca="false">B11+C11*Wyjaśnienia!$B$20/60</f>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$22/60</f>
         <v>50</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="27" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$15</f>
         <v>11000</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="28" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>165</v>
       </c>
@@ -4575,7 +4619,7 @@
         <v>36300</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -4592,7 +4636,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -4604,185 +4648,185 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="B16" s="22" t="n">
-        <f aca="false">Wyjaśnienia!$B$21</f>
+      <c r="A16" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="B16" s="27" t="n">
+        <f aca="false">Wyjaśnienia!$B$23</f>
         <v>35000</v>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="27" t="n">
         <f aca="false">B16*C16</f>
         <v>35000</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="B17" s="22" t="n">
-        <f aca="false">Wyjaśnienia!$B$22</f>
+      <c r="A17" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="B17" s="27" t="n">
+        <f aca="false">Wyjaśnienia!$B$24</f>
         <v>4000</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="27" t="n">
         <f aca="false">B17*C17</f>
         <v>4000</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="B18" s="22" t="n">
-        <f aca="false">Wyjaśnienia!$B$23</f>
+      <c r="A18" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="B18" s="27" t="n">
+        <f aca="false">Wyjaśnienia!$B$25</f>
         <v>7500</v>
       </c>
-      <c r="C18" s="21" t="n">
-        <f aca="false">Wyjaśnienia!$B$24</f>
+      <c r="C18" s="26" t="n">
+        <f aca="false">Wyjaśnienia!$B$26</f>
         <v>10</v>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="27" t="n">
         <f aca="false">B18*C18</f>
         <v>75000</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="22" t="n">
-        <f aca="false">Wyjaśnienia!$B$25</f>
+      <c r="A19" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="27" t="n">
+        <f aca="false">Wyjaśnienia!$B$27</f>
         <v>80000</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="27" t="n">
         <f aca="false">B19*C19</f>
         <v>80000</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="B20" s="22" t="n">
-        <f aca="false">Wyjaśnienia!$B$26</f>
+      <c r="A20" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="B20" s="27" t="n">
+        <f aca="false">Wyjaśnienia!$B$28</f>
         <v>1200</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="27" t="n">
         <f aca="false">B20*C20</f>
         <v>1200</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="B21" s="24" t="n">
+      <c r="A21" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="B21" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="27" t="n">
         <f aca="false">B21*C21</f>
         <v>0</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="B22" s="24" t="n">
+      <c r="A22" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="B22" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="27" t="n">
         <f aca="false">B22*C22</f>
         <v>0</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="B23" s="16" t="n">
+      <c r="A23" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -4790,20 +4834,20 @@
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>255</v>
+        <v>258</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
-        <v>256</v>
-      </c>
-      <c r="B24" s="16" t="n">
+      <c r="A24" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="B24" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -4811,17 +4855,17 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F24" s="28"/>
+        <v>261</v>
+      </c>
+      <c r="F24" s="32"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="28" t="n">
         <f aca="false">SUM(D16:D24)</f>
         <v>195200</v>
       </c>
@@ -4831,18 +4875,18 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -4853,13 +4897,13 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>177</v>
+      <c r="A28" s="24" t="s">
+        <v>181</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="22" t="n">
-        <f aca="false">Wyjaśnienia!$B$21+Wyjaśnienia!$B$22</f>
+      <c r="D28" s="27" t="n">
+        <f aca="false">Wyjaśnienia!$B$23+Wyjaśnienia!$B$24</f>
         <v>39000</v>
       </c>
       <c r="E28" s="3"/>
@@ -4868,8 +4912,8 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
-        <v>178</v>
+      <c r="A29" s="24" t="s">
+        <v>182</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -4883,8 +4927,8 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
-        <v>258</v>
+      <c r="A30" s="24" t="s">
+        <v>262</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -4898,13 +4942,13 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
-        <v>180</v>
+      <c r="A31" s="24" t="s">
+        <v>184</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="8" t="n">
-        <f aca="false">(D29+D30)*Wyjaśnienia!$B$29</f>
+        <f aca="false">(D29+D30)*Wyjaśnienia!$B$31</f>
         <v>23100</v>
       </c>
       <c r="E31" s="3"/>
@@ -4914,7 +4958,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -4928,13 +4972,13 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
-        <v>182</v>
+      <c r="A33" s="24" t="s">
+        <v>186</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="8" t="n">
-        <f aca="false">D32*Wyjaśnienia!$B$30</f>
+        <f aca="false">D32*Wyjaśnienia!$B$32</f>
         <v>58558</v>
       </c>
       <c r="E33" s="3"/>
@@ -4944,11 +4988,11 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="27" t="n">
+      <c r="D34" s="31" t="n">
         <f aca="false">D32+D33</f>
         <v>313158</v>
       </c>
@@ -5065,77 +5109,77 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
+      <c r="A2" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
+      <c r="A3" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+      <c r="A5" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B7" s="18" t="n">
+        <v>264</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="31" t="n">
-        <f aca="false">B7+C7*Wyjaśnienia!$B$50/60</f>
+      <c r="D7" s="35" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$52/60</f>
         <v>20</v>
       </c>
       <c r="E7" s="8" t="n">
@@ -5143,19 +5187,19 @@
         <v>4400</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="18" t="n">
+        <v>266</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31" t="n">
-        <f aca="false">B8+C8*Wyjaśnienia!$B$50/60</f>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$52/60</f>
         <v>30</v>
       </c>
       <c r="E8" s="8" t="n">
@@ -5163,19 +5207,19 @@
         <v>6600</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B9" s="18" t="n">
+        <v>239</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31" t="n">
-        <f aca="false">B9+C9*Wyjaśnienia!$B$50/60</f>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$52/60</f>
         <v>20</v>
       </c>
       <c r="E9" s="8" t="n">
@@ -5183,19 +5227,19 @@
         <v>4400</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B10" s="18" t="n">
+        <v>269</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>35</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31" t="n">
-        <f aca="false">B10+C10*Wyjaśnienia!$B$50/60</f>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$52/60</f>
         <v>35</v>
       </c>
       <c r="E10" s="8" t="n">
@@ -5203,19 +5247,19 @@
         <v>7700</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B11" s="18" t="n">
+        <v>271</v>
+      </c>
+      <c r="B11" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31" t="n">
-        <f aca="false">B11+C11*Wyjaśnienia!$B$50/60</f>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$52/60</f>
         <v>15</v>
       </c>
       <c r="E11" s="8" t="n">
@@ -5223,19 +5267,19 @@
         <v>3300</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B12" s="18" t="n">
+        <v>273</v>
+      </c>
+      <c r="B12" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31" t="n">
-        <f aca="false">B12+C12*Wyjaśnienia!$B$50/60</f>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35" t="n">
+        <f aca="false">B12+C12*Wyjaśnienia!$B$52/60</f>
         <v>50</v>
       </c>
       <c r="E12" s="8" t="n">
@@ -5243,19 +5287,19 @@
         <v>11000</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B13" s="18" t="n">
+        <v>275</v>
+      </c>
+      <c r="B13" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31" t="n">
-        <f aca="false">B13+C13*Wyjaśnienia!$B$50/60</f>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35" t="n">
+        <f aca="false">B13+C13*Wyjaśnienia!$B$52/60</f>
         <v>20</v>
       </c>
       <c r="E13" s="8" t="n">
@@ -5263,14 +5307,14 @@
         <v>4400</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" s="32" t="n">
+        <v>153</v>
+      </c>
+      <c r="D14" s="36" t="n">
         <f aca="false">SUM(D7:D13)</f>
         <v>190</v>
       </c>
@@ -5279,45 +5323,45 @@
         <v>41800</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
+      <c r="A16" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B18" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$51</f>
+        <f aca="false">Wyjaśnienia!$B$53</f>
         <v>90000</v>
       </c>
-      <c r="C18" s="31" t="n">
+      <c r="C18" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="8" t="n">
@@ -5325,18 +5369,18 @@
         <v>90000</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B19" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$52</f>
+        <f aca="false">Wyjaśnienia!$B$54</f>
         <v>3000</v>
       </c>
-      <c r="C19" s="31" t="n">
+      <c r="C19" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="8" t="n">
@@ -5344,18 +5388,18 @@
         <v>3000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B20" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$53</f>
+        <f aca="false">Wyjaśnienia!$B$55</f>
         <v>1200</v>
       </c>
-      <c r="C20" s="31" t="n">
+      <c r="C20" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="8" t="n">
@@ -5363,17 +5407,17 @@
         <v>1200</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B21" s="16" t="n">
+        <v>281</v>
+      </c>
+      <c r="B21" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="31" t="n">
+      <c r="C21" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="8" t="n">
@@ -5381,19 +5425,19 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B22" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$58*2</f>
+        <f aca="false">Wyjaśnienia!$B$60*2</f>
         <v>800</v>
       </c>
-      <c r="C22" s="31" t="n">
-        <f aca="false">Wyjaśnienia!$B$57</f>
+      <c r="C22" s="35" t="n">
+        <f aca="false">Wyjaśnienia!$B$59</f>
         <v>10</v>
       </c>
       <c r="D22" s="8" t="n">
@@ -5401,18 +5445,18 @@
         <v>8000</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B23" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$59</f>
+        <f aca="false">Wyjaśnienia!$B$61</f>
         <v>3000</v>
       </c>
-      <c r="C23" s="31" t="n">
+      <c r="C23" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -5420,17 +5464,17 @@
         <v>3000</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B24" s="16" t="n">
+        <v>286</v>
+      </c>
+      <c r="B24" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="31" t="n">
+      <c r="C24" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -5438,17 +5482,17 @@
         <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B25" s="16" t="n">
+        <v>288</v>
+      </c>
+      <c r="B25" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="31" t="n">
+      <c r="C25" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="8" t="n">
@@ -5456,17 +5500,17 @@
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B26" s="16" t="n">
+        <v>290</v>
+      </c>
+      <c r="B26" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="31" t="n">
+      <c r="C26" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="8" t="n">
@@ -5474,12 +5518,12 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D27" s="11" t="n">
         <f aca="false">SUM(D18:D26)</f>
@@ -5487,27 +5531,27 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
+      <c r="A29" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D30" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$51+Wyjaśnienia!$B$52</f>
+        <f aca="false">Wyjaśnienia!$B$53+Wyjaśnienia!$B$54</f>
         <v>93000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D31" s="8" t="n">
         <f aca="false">E14</f>
@@ -5516,7 +5560,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D32" s="8" t="n">
         <f aca="false">D27-D30</f>
@@ -5525,16 +5569,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D33" s="8" t="n">
-        <f aca="false">(D31+D32)*Wyjaśnienia!$B$60</f>
+        <f aca="false">(D31+D32)*Wyjaśnienia!$B$62</f>
         <v>6480</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D34" s="11" t="n">
         <f aca="false">SUM(D30:D33)</f>
@@ -5543,16 +5587,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D35" s="8" t="n">
-        <f aca="false">D34*Wyjaśnienia!$B$30</f>
+        <f aca="false">D34*Wyjaśnienia!$B$32</f>
         <v>35300.4</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D36" s="11" t="n">
         <f aca="false">D34+D35</f>
@@ -5595,669 +5639,669 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="34" t="s">
-        <v>288</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="A2" s="38" t="s">
+        <v>292</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="34" t="s">
-        <v>289</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
+      <c r="A3" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+      <c r="A5" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>291</v>
-      </c>
-      <c r="F6" s="35" t="s">
-        <v>126</v>
+      <c r="A6" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>295</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
-        <v>292</v>
-      </c>
-      <c r="B7" s="37" t="n">
+      <c r="A7" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="B7" s="42" t="n">
         <f aca="false">Wyjaśnienia!$B$16</f>
         <v>150</v>
       </c>
-      <c r="F7" s="28" t="s">
-        <v>293</v>
+      <c r="F7" s="32" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
-        <v>294</v>
-      </c>
-      <c r="B8" s="37" t="n">
-        <f aca="false">Wyjaśnienia!$B$43</f>
+      <c r="A8" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="B8" s="42" t="n">
+        <f aca="false">Wyjaśnienia!$B$45</f>
         <v>2</v>
       </c>
-      <c r="F8" s="28" t="s">
-        <v>295</v>
+      <c r="F8" s="32" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="B9" s="38" t="n">
+      <c r="A9" s="40" t="s">
+        <v>300</v>
+      </c>
+      <c r="B9" s="43" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
-      <c r="F9" s="28" t="s">
-        <v>297</v>
+      <c r="F9" s="32" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="B10" s="37" t="n">
-        <f aca="false">Wyjaśnienia!$B$63</f>
+      <c r="A10" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="B10" s="42" t="n">
+        <f aca="false">Wyjaśnienia!$B$65</f>
         <v>150</v>
       </c>
-      <c r="F10" s="28" t="s">
-        <v>299</v>
+      <c r="F10" s="32" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="B11" s="37" t="n">
-        <f aca="false">Wyjaśnienia!$B$72</f>
+      <c r="A11" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="B11" s="42" t="n">
+        <f aca="false">Wyjaśnienia!$B$74</f>
         <v>2</v>
       </c>
-      <c r="F11" s="28" t="s">
-        <v>301</v>
+      <c r="F11" s="32" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="35" t="s">
-        <v>302</v>
-      </c>
-      <c r="B12" s="38" t="n">
+      <c r="A12" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="B12" s="43" t="n">
         <f aca="false">B10*B11</f>
         <v>300</v>
       </c>
-      <c r="F12" s="28" t="s">
-        <v>303</v>
+      <c r="F12" s="32" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="A14" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="D15" s="36" t="s">
+      <c r="A15" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="F15" s="35" t="s">
-        <v>126</v>
+      <c r="B15" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="F15" s="40" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
-        <v>306</v>
-      </c>
-      <c r="B16" s="39" t="n">
-        <f aca="false">Wyjaśnienia!$B$45</f>
+      <c r="A16" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="B16" s="44" t="n">
+        <f aca="false">Wyjaśnienia!$B$47</f>
         <v>2500</v>
       </c>
-      <c r="C16" s="37" t="n">
-        <f aca="false">Wyjaśnienia!$B$46</f>
+      <c r="C16" s="42" t="n">
+        <f aca="false">Wyjaśnienia!$B$48</f>
         <v>15</v>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D16" s="44" t="n">
         <f aca="false">B16*C16</f>
         <v>37500</v>
       </c>
-      <c r="F16" s="28" t="s">
-        <v>307</v>
+      <c r="F16" s="32" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="s">
-        <v>308</v>
-      </c>
-      <c r="B17" s="39" t="n">
-        <f aca="false">Wyjaśnienia!$B$44</f>
+      <c r="A17" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="B17" s="44" t="n">
+        <f aca="false">Wyjaśnienia!$B$46</f>
         <v>500</v>
       </c>
-      <c r="C17" s="37" t="n">
+      <c r="C17" s="42" t="n">
         <f aca="false">ROUNDUP(B9/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D17" s="44" t="n">
         <f aca="false">B17*C17</f>
         <v>1500</v>
       </c>
-      <c r="F17" s="28" t="s">
-        <v>309</v>
+      <c r="F17" s="32" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="B18" s="39" t="n">
-        <f aca="false">Wyjaśnienia!$B$73</f>
+      <c r="A18" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="B18" s="44" t="n">
+        <f aca="false">Wyjaśnienia!$B$75</f>
         <v>300</v>
       </c>
-      <c r="C18" s="37" t="n">
+      <c r="C18" s="42" t="n">
         <f aca="false">B12</f>
         <v>300</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="44" t="n">
         <f aca="false">B18*C18</f>
         <v>90000</v>
       </c>
-      <c r="F18" s="28" t="s">
-        <v>311</v>
+      <c r="F18" s="32" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="35" t="s">
-        <v>312</v>
-      </c>
-      <c r="D19" s="40" t="n">
+      <c r="A19" s="40" t="s">
+        <v>316</v>
+      </c>
+      <c r="D19" s="45" t="n">
         <f aca="false">SUM(D16:D18)</f>
         <v>129000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
+      <c r="A21" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="36" t="s">
+      <c r="A22" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="F22" s="35" t="s">
-        <v>126</v>
+      <c r="B22" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" s="40" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="B23" s="39" t="n">
+      <c r="A23" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="B23" s="44" t="n">
         <v>2000</v>
       </c>
-      <c r="C23" s="37" t="n">
+      <c r="C23" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D23" s="44" t="n">
         <f aca="false">B23*C23</f>
         <v>2000</v>
       </c>
-      <c r="F23" s="28" t="s">
-        <v>314</v>
+      <c r="F23" s="32" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
-        <v>315</v>
-      </c>
-      <c r="B24" s="39" t="n">
+      <c r="A24" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="B24" s="44" t="n">
         <v>3000</v>
       </c>
-      <c r="C24" s="37" t="n">
+      <c r="C24" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D24" s="44" t="n">
         <f aca="false">B24*C24</f>
         <v>3000</v>
       </c>
-      <c r="F24" s="28" t="s">
-        <v>316</v>
+      <c r="F24" s="32" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="s">
-        <v>317</v>
-      </c>
-      <c r="B25" s="39" t="n">
+      <c r="A25" s="32" t="s">
+        <v>321</v>
+      </c>
+      <c r="B25" s="44" t="n">
         <v>5000</v>
       </c>
-      <c r="C25" s="37" t="n">
+      <c r="C25" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="39" t="n">
+      <c r="D25" s="44" t="n">
         <f aca="false">B25*C25</f>
         <v>5000</v>
       </c>
-      <c r="F25" s="28" t="s">
-        <v>318</v>
+      <c r="F25" s="32" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="B26" s="39" t="n">
+      <c r="A26" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="B26" s="44" t="n">
         <v>4000</v>
       </c>
-      <c r="C26" s="37" t="n">
+      <c r="C26" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D26" s="44" t="n">
         <f aca="false">B26*C26</f>
         <v>4000</v>
       </c>
-      <c r="F26" s="28" t="s">
-        <v>320</v>
+      <c r="F26" s="32" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="D27" s="40" t="n">
+      <c r="A27" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="D27" s="45" t="n">
         <f aca="false">SUM(D23:D26)</f>
         <v>14000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
+      <c r="A29" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28" t="s">
-        <v>321</v>
-      </c>
-      <c r="D30" s="39" t="n">
+      <c r="A30" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="D30" s="44" t="n">
         <f aca="false">D19</f>
         <v>129000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="D31" s="39" t="n">
+      <c r="A31" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="44" t="n">
         <f aca="false">D27</f>
         <v>14000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="28" t="s">
-        <v>322</v>
-      </c>
-      <c r="D32" s="39" t="n">
-        <f aca="false">(D30+D31)*Wyjaśnienia!$B$27</f>
+      <c r="A32" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="D32" s="44" t="n">
+        <f aca="false">(D30+D31)*Wyjaśnienia!$B$29</f>
         <v>17160</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="D33" s="40" t="n">
+      <c r="A33" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="D33" s="45" t="n">
         <f aca="false">SUM(D30:D32)</f>
         <v>160160</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="D34" s="39" t="n">
-        <f aca="false">D33*Wyjaśnienia!$B$30</f>
+      <c r="A34" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" s="44" t="n">
+        <f aca="false">D33*Wyjaśnienia!$B$32</f>
         <v>36836.8</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="40" t="n">
+      <c r="A35" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" s="45" t="n">
         <f aca="false">D33+D34</f>
         <v>196996.8</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
+      <c r="A37" s="39" t="s">
+        <v>327</v>
+      </c>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
     </row>
     <row r="38" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="34" t="s">
-        <v>324</v>
-      </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
+      <c r="A38" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="36" t="s">
-        <v>325</v>
-      </c>
-      <c r="B39" s="36" t="s">
-        <v>326</v>
-      </c>
-      <c r="C39" s="36" t="s">
-        <v>327</v>
-      </c>
-      <c r="D39" s="36" t="s">
-        <v>328</v>
-      </c>
-      <c r="E39" s="36" t="s">
+      <c r="A39" s="41" t="s">
         <v>329</v>
       </c>
+      <c r="B39" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="D39" s="41" t="s">
+        <v>332</v>
+      </c>
+      <c r="E39" s="41" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="37" t="n">
+      <c r="A40" s="42" t="n">
         <v>150</v>
       </c>
-      <c r="B40" s="37" t="n">
-        <f aca="false">A40*Wyjaśnienia!$B$43</f>
+      <c r="B40" s="42" t="n">
+        <f aca="false">A40*Wyjaśnienia!$B$45</f>
         <v>300</v>
       </c>
-      <c r="C40" s="37" t="n">
+      <c r="C40" s="42" t="n">
         <f aca="false">ROUNDUP(B40/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D40" s="39" t="n">
-        <f aca="false">C40*Wyjaśnienia!$B$44</f>
+      <c r="D40" s="44" t="n">
+        <f aca="false">C40*Wyjaśnienia!$B$46</f>
         <v>1500</v>
       </c>
-      <c r="E40" s="37" t="n">
-        <f aca="false">ROUNDUP(B40/Wyjaśnienia!$B$47,0)</f>
+      <c r="E40" s="42" t="n">
+        <f aca="false">ROUNDUP(B40/Wyjaśnienia!$B$49,0)</f>
         <v>15</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="37" t="n">
+      <c r="A41" s="42" t="n">
         <v>1000</v>
       </c>
-      <c r="B41" s="37" t="n">
-        <f aca="false">A41*Wyjaśnienia!$B$43</f>
+      <c r="B41" s="42" t="n">
+        <f aca="false">A41*Wyjaśnienia!$B$45</f>
         <v>2000</v>
       </c>
-      <c r="C41" s="37" t="n">
+      <c r="C41" s="42" t="n">
         <f aca="false">ROUNDUP(B41/100,0)</f>
         <v>20</v>
       </c>
-      <c r="D41" s="39" t="n">
-        <f aca="false">C41*Wyjaśnienia!$B$44</f>
+      <c r="D41" s="44" t="n">
+        <f aca="false">C41*Wyjaśnienia!$B$46</f>
         <v>10000</v>
       </c>
-      <c r="E41" s="37" t="n">
-        <f aca="false">ROUNDUP(B41/Wyjaśnienia!$B$47,0)</f>
+      <c r="E41" s="42" t="n">
+        <f aca="false">ROUNDUP(B41/Wyjaśnienia!$B$49,0)</f>
         <v>100</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="37" t="n">
+      <c r="A42" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="B42" s="37" t="n">
-        <f aca="false">A42*Wyjaśnienia!$B$43</f>
+      <c r="B42" s="42" t="n">
+        <f aca="false">A42*Wyjaśnienia!$B$45</f>
         <v>20000</v>
       </c>
-      <c r="C42" s="37" t="n">
+      <c r="C42" s="42" t="n">
         <f aca="false">ROUNDUP(B42/100,0)</f>
         <v>200</v>
       </c>
-      <c r="D42" s="39" t="n">
-        <f aca="false">C42*Wyjaśnienia!$B$44</f>
+      <c r="D42" s="44" t="n">
+        <f aca="false">C42*Wyjaśnienia!$B$46</f>
         <v>100000</v>
       </c>
-      <c r="E42" s="37" t="n">
-        <f aca="false">ROUNDUP(B42/Wyjaśnienia!$B$47,0)</f>
+      <c r="E42" s="42" t="n">
+        <f aca="false">ROUNDUP(B42/Wyjaśnienia!$B$49,0)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="37" t="n">
+      <c r="A43" s="42" t="n">
         <v>100000</v>
       </c>
-      <c r="B43" s="37" t="n">
-        <f aca="false">A43*Wyjaśnienia!$B$43</f>
+      <c r="B43" s="42" t="n">
+        <f aca="false">A43*Wyjaśnienia!$B$45</f>
         <v>200000</v>
       </c>
-      <c r="C43" s="37" t="n">
+      <c r="C43" s="42" t="n">
         <f aca="false">ROUNDUP(B43/100,0)</f>
         <v>2000</v>
       </c>
-      <c r="D43" s="39" t="n">
-        <f aca="false">C43*Wyjaśnienia!$B$44</f>
+      <c r="D43" s="44" t="n">
+        <f aca="false">C43*Wyjaśnienia!$B$46</f>
         <v>1000000</v>
       </c>
-      <c r="E43" s="37" t="n">
-        <f aca="false">ROUNDUP(B43/Wyjaśnienia!$B$47,0)</f>
+      <c r="E43" s="42" t="n">
+        <f aca="false">ROUNDUP(B43/Wyjaśnienia!$B$49,0)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="37" t="n">
+      <c r="A44" s="42" t="n">
         <v>1000000</v>
       </c>
-      <c r="B44" s="37" t="n">
-        <f aca="false">A44*Wyjaśnienia!$B$43</f>
+      <c r="B44" s="42" t="n">
+        <f aca="false">A44*Wyjaśnienia!$B$45</f>
         <v>2000000</v>
       </c>
-      <c r="C44" s="37" t="n">
+      <c r="C44" s="42" t="n">
         <f aca="false">ROUNDUP(B44/100,0)</f>
         <v>20000</v>
       </c>
-      <c r="D44" s="39" t="n">
-        <f aca="false">C44*Wyjaśnienia!$B$44</f>
+      <c r="D44" s="44" t="n">
+        <f aca="false">C44*Wyjaśnienia!$B$46</f>
         <v>10000000</v>
       </c>
-      <c r="E44" s="37" t="n">
-        <f aca="false">ROUNDUP(B44/Wyjaśnienia!$B$47,0)</f>
+      <c r="E44" s="42" t="n">
+        <f aca="false">ROUNDUP(B44/Wyjaśnienia!$B$49,0)</f>
         <v>100000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="36" t="s">
-        <v>330</v>
-      </c>
-      <c r="B46" s="36" t="s">
-        <v>331</v>
-      </c>
-      <c r="C46" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="D46" s="36" t="s">
-        <v>333</v>
-      </c>
-      <c r="E46" s="36" t="s">
+      <c r="A46" s="41" t="s">
         <v>334</v>
       </c>
+      <c r="B46" s="41" t="s">
+        <v>335</v>
+      </c>
+      <c r="C46" s="41" t="s">
+        <v>336</v>
+      </c>
+      <c r="D46" s="41" t="s">
+        <v>337</v>
+      </c>
+      <c r="E46" s="41" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="37" t="n">
+      <c r="A47" s="42" t="n">
         <v>30</v>
       </c>
-      <c r="B47" s="37" t="n">
-        <f aca="false">A47*Wyjaśnienia!$B$72</f>
+      <c r="B47" s="42" t="n">
+        <f aca="false">A47*Wyjaśnienia!$B$74</f>
         <v>60</v>
       </c>
-      <c r="C47" s="39" t="n">
-        <f aca="false">B47*Wyjaśnienia!$B$73</f>
+      <c r="C47" s="44" t="n">
+        <f aca="false">B47*Wyjaśnienia!$B$75</f>
         <v>18000</v>
       </c>
-      <c r="D47" s="37" t="n">
+      <c r="D47" s="42" t="n">
         <f aca="false">B47*2</f>
         <v>120</v>
       </c>
-      <c r="E47" s="37" t="n">
-        <f aca="false">ROUNDUP(A47/Wyjaśnienia!$B$74,0)</f>
+      <c r="E47" s="42" t="n">
+        <f aca="false">ROUNDUP(A47/Wyjaśnienia!$B$76,0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="37" t="n">
+      <c r="A48" s="42" t="n">
         <v>150</v>
       </c>
-      <c r="B48" s="37" t="n">
-        <f aca="false">A48*Wyjaśnienia!$B$72</f>
+      <c r="B48" s="42" t="n">
+        <f aca="false">A48*Wyjaśnienia!$B$74</f>
         <v>300</v>
       </c>
-      <c r="C48" s="39" t="n">
-        <f aca="false">B48*Wyjaśnienia!$B$73</f>
+      <c r="C48" s="44" t="n">
+        <f aca="false">B48*Wyjaśnienia!$B$75</f>
         <v>90000</v>
       </c>
-      <c r="D48" s="37" t="n">
+      <c r="D48" s="42" t="n">
         <f aca="false">B48*2</f>
         <v>600</v>
       </c>
-      <c r="E48" s="37" t="n">
-        <f aca="false">ROUNDUP(A48/Wyjaśnienia!$B$74,0)</f>
+      <c r="E48" s="42" t="n">
+        <f aca="false">ROUNDUP(A48/Wyjaśnienia!$B$76,0)</f>
         <v>15</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="37" t="n">
+      <c r="A49" s="42" t="n">
         <v>500</v>
       </c>
-      <c r="B49" s="37" t="n">
-        <f aca="false">A49*Wyjaśnienia!$B$72</f>
+      <c r="B49" s="42" t="n">
+        <f aca="false">A49*Wyjaśnienia!$B$74</f>
         <v>1000</v>
       </c>
-      <c r="C49" s="39" t="n">
-        <f aca="false">B49*Wyjaśnienia!$B$73</f>
+      <c r="C49" s="44" t="n">
+        <f aca="false">B49*Wyjaśnienia!$B$75</f>
         <v>300000</v>
       </c>
-      <c r="D49" s="37" t="n">
+      <c r="D49" s="42" t="n">
         <f aca="false">B49*2</f>
         <v>2000</v>
       </c>
-      <c r="E49" s="37" t="n">
-        <f aca="false">ROUNDUP(A49/Wyjaśnienia!$B$74,0)</f>
+      <c r="E49" s="42" t="n">
+        <f aca="false">ROUNDUP(A49/Wyjaśnienia!$B$76,0)</f>
         <v>50</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="37" t="n">
+      <c r="A50" s="42" t="n">
         <v>2000</v>
       </c>
-      <c r="B50" s="37" t="n">
-        <f aca="false">A50*Wyjaśnienia!$B$72</f>
+      <c r="B50" s="42" t="n">
+        <f aca="false">A50*Wyjaśnienia!$B$74</f>
         <v>4000</v>
       </c>
-      <c r="C50" s="39" t="n">
-        <f aca="false">B50*Wyjaśnienia!$B$73</f>
+      <c r="C50" s="44" t="n">
+        <f aca="false">B50*Wyjaśnienia!$B$75</f>
         <v>1200000</v>
       </c>
-      <c r="D50" s="37" t="n">
+      <c r="D50" s="42" t="n">
         <f aca="false">B50*2</f>
         <v>8000</v>
       </c>
-      <c r="E50" s="37" t="n">
-        <f aca="false">ROUNDUP(A50/Wyjaśnienia!$B$74,0)</f>
+      <c r="E50" s="42" t="n">
+        <f aca="false">ROUNDUP(A50/Wyjaśnienia!$B$76,0)</f>
         <v>200</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="37" t="n">
+      <c r="A51" s="42" t="n">
         <v>10000</v>
       </c>
-      <c r="B51" s="37" t="n">
-        <f aca="false">A51*Wyjaśnienia!$B$72</f>
+      <c r="B51" s="42" t="n">
+        <f aca="false">A51*Wyjaśnienia!$B$74</f>
         <v>20000</v>
       </c>
-      <c r="C51" s="39" t="n">
-        <f aca="false">B51*Wyjaśnienia!$B$73</f>
+      <c r="C51" s="44" t="n">
+        <f aca="false">B51*Wyjaśnienia!$B$75</f>
         <v>6000000</v>
       </c>
-      <c r="D51" s="37" t="n">
+      <c r="D51" s="42" t="n">
         <f aca="false">B51*2</f>
         <v>40000</v>
       </c>
-      <c r="E51" s="37" t="n">
-        <f aca="false">ROUNDUP(A51/Wyjaśnienia!$B$74,0)</f>
+      <c r="E51" s="42" t="n">
+        <f aca="false">ROUNDUP(A51/Wyjaśnienia!$B$76,0)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="34" t="s">
-        <v>335</v>
-      </c>
-      <c r="B53" s="34"/>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
+      <c r="A53" s="38" t="s">
+        <v>339</v>
+      </c>
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6299,77 +6343,77 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>336</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
+      <c r="A2" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>337</v>
-      </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
+      <c r="A3" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+      <c r="A5" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B7" s="18" t="n">
+        <v>342</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="31" t="n">
-        <f aca="false">B7+C7*Wyjaśnienia!$B$63/60</f>
+      <c r="D7" s="35" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$65/60</f>
         <v>30</v>
       </c>
       <c r="E7" s="8" t="n">
@@ -6377,19 +6421,19 @@
         <v>6600</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B8" s="18" t="n">
+        <v>344</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="31" t="n">
-        <f aca="false">B8+C8*Wyjaśnienia!$B$63/60</f>
+      <c r="C8" s="22"/>
+      <c r="D8" s="35" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$65/60</f>
         <v>25</v>
       </c>
       <c r="E8" s="8" t="n">
@@ -6397,19 +6441,19 @@
         <v>5500</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B9" s="18" t="n">
+        <v>346</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="31" t="n">
-        <f aca="false">B9+C9*Wyjaśnienia!$B$63/60</f>
+      <c r="C9" s="22"/>
+      <c r="D9" s="35" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$65/60</f>
         <v>60</v>
       </c>
       <c r="E9" s="8" t="n">
@@ -6417,19 +6461,19 @@
         <v>13200</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B10" s="18" t="n">
+        <v>239</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="31" t="n">
-        <f aca="false">B10+C10*Wyjaśnienia!$B$63/60</f>
+      <c r="C10" s="22"/>
+      <c r="D10" s="35" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$65/60</f>
         <v>20</v>
       </c>
       <c r="E10" s="8" t="n">
@@ -6437,19 +6481,19 @@
         <v>4400</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B11" s="18" t="n">
+        <v>348</v>
+      </c>
+      <c r="B11" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="31" t="n">
-        <f aca="false">B11+C11*Wyjaśnienia!$B$63/60</f>
+      <c r="C11" s="22"/>
+      <c r="D11" s="35" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$65/60</f>
         <v>40</v>
       </c>
       <c r="E11" s="8" t="n">
@@ -6457,19 +6501,19 @@
         <v>8800</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B12" s="18" t="n">
+        <v>350</v>
+      </c>
+      <c r="B12" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="31" t="n">
-        <f aca="false">B12+C12*Wyjaśnienia!$B$63/60</f>
+      <c r="C12" s="22"/>
+      <c r="D12" s="35" t="n">
+        <f aca="false">B12+C12*Wyjaśnienia!$B$65/60</f>
         <v>40</v>
       </c>
       <c r="E12" s="8" t="n">
@@ -6477,19 +6521,19 @@
         <v>8800</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B13" s="18" t="n">
+        <v>352</v>
+      </c>
+      <c r="B13" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="31" t="n">
-        <f aca="false">B13+C13*Wyjaśnienia!$B$63/60</f>
+      <c r="C13" s="22"/>
+      <c r="D13" s="35" t="n">
+        <f aca="false">B13+C13*Wyjaśnienia!$B$65/60</f>
         <v>25</v>
       </c>
       <c r="E13" s="8" t="n">
@@ -6497,19 +6541,19 @@
         <v>5500</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B14" s="18" t="n">
+        <v>354</v>
+      </c>
+      <c r="B14" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="31" t="n">
-        <f aca="false">B14+C14*Wyjaśnienia!$B$63/60</f>
+      <c r="C14" s="22"/>
+      <c r="D14" s="35" t="n">
+        <f aca="false">B14+C14*Wyjaśnienia!$B$65/60</f>
         <v>50</v>
       </c>
       <c r="E14" s="8" t="n">
@@ -6517,16 +6561,16 @@
         <v>11000</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="32" t="n">
+        <v>153</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="36" t="n">
         <f aca="false">SUM(D7:D14)</f>
         <v>290</v>
       </c>
@@ -6535,45 +6579,45 @@
         <v>63800</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
+      <c r="A17" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B19" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$64</f>
+        <f aca="false">Wyjaśnienia!$B$66</f>
         <v>180000</v>
       </c>
-      <c r="C19" s="31" t="n">
+      <c r="C19" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="8" t="n">
@@ -6581,18 +6625,18 @@
         <v>180000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B20" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$65</f>
+        <f aca="false">Wyjaśnienia!$B$67</f>
         <v>3000</v>
       </c>
-      <c r="C20" s="31" t="n">
+      <c r="C20" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="8" t="n">
@@ -6600,18 +6644,18 @@
         <v>3000</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B21" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$66</f>
+        <f aca="false">Wyjaśnienia!$B$68</f>
         <v>1200</v>
       </c>
-      <c r="C21" s="31" t="n">
+      <c r="C21" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="8" t="n">
@@ -6619,17 +6663,17 @@
         <v>1200</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="31" t="n">
+      <c r="C22" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="8" t="n">
@@ -6637,17 +6681,17 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="31" t="n">
+      <c r="C23" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -6655,17 +6699,17 @@
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="31" t="n">
+      <c r="C24" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -6673,17 +6717,17 @@
         <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="31" t="n">
+      <c r="C25" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="8" t="n">
@@ -6691,17 +6735,17 @@
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="31" t="n">
+      <c r="C26" s="35" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="8" t="n">
@@ -6709,42 +6753,42 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B27" s="8"/>
-      <c r="C27" s="31"/>
+      <c r="C27" s="35"/>
       <c r="D27" s="11" t="n">
         <f aca="false">SUM(D19:D26)</f>
         <v>184200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
+      <c r="A29" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D30" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$64+Wyjaśnienia!$B$65</f>
+        <f aca="false">Wyjaśnienia!$B$66+Wyjaśnienia!$B$67</f>
         <v>183000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D31" s="8" t="n">
         <f aca="false">E15</f>
@@ -6753,7 +6797,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D32" s="8" t="n">
         <f aca="false">D27-D30</f>
@@ -6762,16 +6806,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D33" s="8" t="n">
-        <f aca="false">(D31+D32)*Wyjaśnienia!$B$71</f>
+        <f aca="false">(D31+D32)*Wyjaśnienia!$B$73</f>
         <v>7800</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D34" s="11" t="n">
         <f aca="false">SUM(D30:D33)</f>
@@ -6780,16 +6824,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D35" s="8" t="n">
-        <f aca="false">D34*Wyjaśnienia!$B$30</f>
+        <f aca="false">D34*Wyjaśnienia!$B$32</f>
         <v>58834</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D36" s="11" t="n">
         <f aca="false">D34+D35</f>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Budżet Plakatu" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Budżet Akademii" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Budżet Filmu" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Budżet Gali" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="378">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -46,7 +47,7 @@
     <t xml:space="preserve">Kwota netto</t>
   </si>
   <si>
-    <t xml:space="preserve">Budżet Nagrody - nagroda i gala</t>
+    <t xml:space="preserve">Budżet Nagrody - nagrody, ocena i promocja</t>
   </si>
   <si>
     <t xml:space="preserve">Fundator puli nagród</t>
@@ -82,6 +83,12 @@
     <t xml:space="preserve">Sponsor plebiscytu filmu</t>
   </si>
   <si>
+    <t xml:space="preserve">Budżet Gali - gala rozstrzygnięcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sponsor gali</t>
+  </si>
+  <si>
     <t xml:space="preserve">RAZEM</t>
   </si>
   <si>
@@ -199,18 +206,12 @@
     <t xml:space="preserve">Podatek od nagród (ryczałt)</t>
   </si>
   <si>
-    <t xml:space="preserve">Art. 30 ust. 1 pkt 2 PIT; potrącany przy wypłacie laureatowi.</t>
-  </si>
-  <si>
     <t xml:space="preserve">CZEGO JESZCZE NIE MA</t>
   </si>
   <si>
     <t xml:space="preserve">Honoraria jury plebiscytu</t>
   </si>
   <si>
-    <t xml:space="preserve">stoją na zerze - czekają na wycenę Michała Sołtana</t>
-  </si>
-  <si>
     <t xml:space="preserve">Realizacja części artystycznej gali</t>
   </si>
   <si>
@@ -256,9 +257,6 @@
     <t xml:space="preserve">Maksimum zgłoszeń na czytelnika</t>
   </si>
   <si>
-    <t xml:space="preserve">Z regulaminu. Wyznacza, ilu ludzi trzeba przy danym wolumenie.</t>
-  </si>
-  <si>
     <t xml:space="preserve">PLAKAT - PARAMETRY</t>
   </si>
   <si>
@@ -322,60 +320,60 @@
     <t xml:space="preserve">Rezerwa w Budżecie Plakatu</t>
   </si>
   <si>
+    <t xml:space="preserve">FILM - PARAMETRY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liczba zgłoszeń filmów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wpływa na koszt kontroli formalnej i na wielkość Akademii filmu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagrody filmu łącznie (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 tys. + 50 tys. + 30 tys. dla czołowej trójki.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagroda publiczności filmu (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jedna nagroda, dla filmu z największą liczbą głosów.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medal zwycięzcy i dyplomy filmu (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten sam mosiężny medal co w pozostałych plebiscytach; dyplomy dla pięciu finalistów.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liczba filmów finałowych</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pięciu finalistów, bo tyle minutowych emisji mieści się na gali.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liczba jurorów filmu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotwica, nie decyzja: pozycja honorariów w Budżecie Filmu stoi na zerze jako DO USTALENIA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Godzin oceny na jurora filmu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jury ogląda listę węższą po Akademii, ale filmy trwają do 90 minut - stąd więcej godzin niż przy plakacie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stawka jury filmu za godzinę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezerwa w Budżecie Filmu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Narzut na nieprzewidziane, jak w pozostałych budżetach.</t>
   </si>
   <si>
-    <t xml:space="preserve">FILM - PARAMETRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liczba zgłoszeń filmów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wpływa na koszt kontroli formalnej i na wielkość Akademii filmu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagrody filmu łącznie (brutto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 tys. + 50 tys. + 30 tys. dla czołowej trójki.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagroda publiczności filmu (brutto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jedna nagroda, dla filmu z największą liczbą głosów.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medal zwycięzcy i dyplomy filmu (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ten sam mosiężny medal co w pozostałych plebiscytach; dyplomy dla pięciu finalistów.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liczba filmów finałowych</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pięciu finalistów, bo tyle minutowych emisji mieści się na gali.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liczba jurorów filmu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotwica, nie decyzja: pozycja honorariów w Budżecie Filmu stoi na zerze jako DO USTALENIA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Godzin oceny na jurora filmu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jury ogląda listę węższą po Akademii, ale filmy trwają do 90 minut - stąd więcej godzin niż przy plakacie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stawka jury filmu za godzinę (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rezerwa w Budżecie Filmu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Obejrzeń jednego filmu w Akademii</t>
   </si>
   <si>
@@ -469,36 +467,657 @@
     <t xml:space="preserve">prowadzi Organizator osobiście</t>
   </si>
   <si>
+    <t xml:space="preserve">Rozliczenia, podatki, sprawozdanie dla sponsorów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z księgowym</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Komunikacja, media, strona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">przez cały rok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razem praca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KOSZTY TWARDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cena jednostkowa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ilość</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medal laureata i dyplomy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mosiądz grawerowany, 10 dyplomów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa księgowa projektu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ponad bieżącą obsługę działalności</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domeny konstela.org i konstela.pl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opłacone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honoraria jury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 czytelników po 2 500 zł, 4 jurorów po 8 000 zł</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 jurorów po 8 000 zł; honoraria Akademii przeniesione do Budżetu Akademii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promocja naboru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">materiały, obsługa prasowa przy starcie i rozstrzygnięciu, płatne dotarcie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagroda publiczności</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ubezpieczenie OC organizatora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">do ustalenia po konsultacji prawnej; na razie pokryte rezerwą</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razem koszty twarde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PODSUMOWANIE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagrody (brutto dla laureatów, bez VAT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Praca organizatora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koszty twarde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezerwa (od pracy i kosztów, bez nagród)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAZEM NETTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO ZAPŁATY BRUTTO - ta liczba trafia na fakturę</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finansuje: Partner wydawniczy / sponsor organizacyjny. Kwoty netto, chyba że napisano inaczej.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antologia: redakcja not jury i uzupełnienia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noty pisze jury (§ 8 ust. 13a)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skład, korekta autorska, EPUB i PDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">szablon przygotowany w styczniu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozstrzyganie zgłoszeń oznaczonych przez oceniających</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oznaczanie zastrzeżeń prawnych robi Akademia przy czytaniu (regulamin § 8 ust. 3a), bo skaluje się razem z naborem. Organizator rozstrzyga co do zgłoszeń oznaczonych oraz co do przypadków, w których otrzymał konkretny sygnał albo sam powziął wiadomość o problemie, wraz z zawiadomieniem uczestnika. Wpisane 4 minuty na zgłoszenie są uśrednieniem: przy części zgłoszeń nie ma nic do rozstrzygania, przy oznaczonych rozstrzygnięcie i korespondencja zajmują kilkadziesiąt minut.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skraper i kopia archiwalna zgłoszenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Playwright: PDF, pełny HTML, zrzut, znacznik czasu, suma kontrolna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narzędzie do oceny formalnej</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liczenie słów i wypowiedzi, wykluczanie kodu, język, ciągłość wątku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel oceny dla Akademii i jury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">konta, przydziały, karta oceny, rozbieżności, trzeci odczyt, ślad audytowy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publiczne archiwum rozmów na stronie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generowanie stron z kopii, nawigacja, tryb redakcji fragmentów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koordynacja podcastu: goście, terminy, publikacja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powołanie fundacji-organizatora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notariusz, statut, wpis do KRS, fundusz założycielski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsultacja prawna przed otwarciem naboru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sześć obszarów, w tym licencja i archiwum; obowiązkowa przed naborem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sześć obszarów, w tym licencja i archiwum; kwota z zapasem wobec ofert kancelarii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domeny, poczta, hosting, magazyn kopii archiwalnych</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magazyn obiektowy w UE z kopią zapasową, retencja min. 5 lat, PDF/HTML/zrzuty/EPUB; w tym skrzynka pocztowa w domenie wraz z aliasami (kontakt@, imienny) - rzędu 150-450 zł rocznie, aliasy bez dopłaty; przejście na własną skrzynkę przenosi MX i wyłącza Cloudflare Email Routing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koordynator wydania i moderacji I-IV 2028 (B2B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pełne zaangażowanie I-III 2028, moderacja archiwum i obsługa zgłoszeń przy dużym napływie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korekta językowa antologii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">korekta dziesięciu rozmów i not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skład i przygotowanie do druku (DTP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">szablon plus obsługa wydania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krótki nakład antologii na galę (100 egz.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gwarantowany przez organizatora, niezależny od partnera wydawniczego; nakład handlowy jest po stronie partnera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nadanie ISBN i egzemplarz obowiązkowy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nadanie bezpłatne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przebudowa strony: UI/UX i teksty (agencja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projekt i wdrożenie strony Nagrody wraz z copywritingiem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa fundacji za pierwszy rok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">księgowość, sprawozdanie finansowe i sprawozdanie dla ministra nadzorującego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narzędzia AI i licencje oprogramowania (rok)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dostęp do narzędzi AI, bez których 937 godzin pracy organizatora nie jest wykonalne; rzędu 2,5 tys. zł miesięcznie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejestracja znaku towarowego Konstela w EUIPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jedna klasa, ochrona w całej Unii; opłaty urzędowe około 850 euro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkcja podcastu wraz z honorarium prowadzącego (24 odcinki)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - nagranie, montaż, dźwięk, wersja wideo i dystrybucja; honorarium prowadzącego nieustalone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marża (od pracy i kosztów, bez nagród)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finansuje: Sponsor plebiscytu. Kwoty netto, chyba że napisano inaczej.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrola formalna zgłoszeń plebiscytu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 minut na zgłoszenie; przy dużych liczbach część kontroli automatyzowana.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koordynacja nagrań studyjnych dziesięciu finalistów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">umowy, terminy w studiu, przekazanie praw autorom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa jury plebiscytu: przydziały, obrady, werdykt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w tym preselekcja powyżej progu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa głosowania publiczności i ogłoszenie wyniku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bramka SMS, ukryte liczniki, ogłoszenie na gali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Komunikacja plebiscytu i dotarcie do wykonawców</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grupy muzyków, szkoły muzyczne, scena coverowa, radia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powyżej progu zgłoszeń pierwsze przejście oceny przechodzi na Akademię, tak jak w konkursie rozmów - dlatego te godziny nie rosną z naborem. Minuty na zgłoszenie dotyczą wyłącznie kontroli formalnej.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagrody plebiscytu (brutto dla laureatów)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">czołowa trójka; podatek 10% jak przy Nagrodzie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagrody publiczności (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dla wykonawcy oraz za najlepsze uzasadnienie wyboru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagrania studyjne dziesięciu finalistów (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prawa do nagrań przechodzą na autorów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nagranie i premiera na początku 2027, otwiera nabór</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medalion zwycięzcy i dyplomy finalistów (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ten sam medalion, który otrzymuje laureat konkursu rozmów; dyplomy dla całej dziesiątki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honoraria jury plebiscytu za ocenę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO USTALENIA - kotwica: stawka jury ok. 290 zł/h, ok. 15 h na jurora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizacja części artystycznej gali (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - zależy od miejsca gali, które nie jest wybrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa prawna plebiscytu (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - zakres plebiscytowy nie był objęty wyceną z 22.10.2026; osobne zlecenie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">odrębne zlecenie na pytania plebiscytowe; kwota z zapasem wobec ofert kancelarii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dojazd i nocleg dziesięciu finalistów na galę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - udział czołowej trójki obowiązkowy (§ 14 regulaminu plebiscytu), pokrycie dla całej dziesiątki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koszty twarde bez nagród</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finansuje: Mecenas konkursu plakatu. Kwoty netto, chyba że napisano inaczej.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrola formalna zgłoszeń plakatów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">format, proporcje, rozdzielczość, oświadczenia; 8 minut na zgłoszenie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa jury plakatu: przydziały, preselekcja, obrady, werdykt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">werdykt zapada przed galą, bo okładka antologii idzie do druku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ukryte liczniki, ogłoszenie na gali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przyjęcie, ewidencja i zwrot oryginałów finalistów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dwie lokalizacje: wystawa przy gali i wernisaż w galerii sztuki (regulamin § 10 ust. 3a), więc protokoły, przewóz między miejscami i ubezpieczenie na dłuższy okres - do 120 dni od dostarczenia pracy. Przy wycenie sprawdzić, czy 35 godzin wystarcza.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uzgodnienie okładki antologii ze zwycięzcą</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zgoda w 7 dni po werdykcie, typografia, kadrowanie, redakcja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dotarcie do szkół artystycznych i środowiska ilustratorów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASP, licea plastyczne, grupy ilustratorów, konkursy plakatowe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa licytacji: warunki, zgody, rozliczenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propozycja po zamknięciu ocen, podział 50/50, rozliczenie na piśmie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagrody plakatu (brutto dla laureatów)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">czołowa trójka: 50, 25 i 15 tys.; podatek 10% jak przy Nagrodzie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagroda publiczności (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jedna nagroda, dla pracy z największą liczbą głosów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honoraria jury plakatu za ocenę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO USTALENIA - stawka godzinowa jest przy nazwisku złym narzędziem; kotwica z Wyjaśnień (5 osób x 10 h x 290 zł) dałaby 14 500 zł</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transport oryginałów w obie strony (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">szacunek, nie oferta; organizator pokrywa obie strony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">szacunek przy sumie deklarowanej rzędu 100 tys. zł</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realizacja wystawy przy gali i wernisażu w galerii (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - zawieszenie, oświetlenie, opisy prac w dwóch miejscach, przewóz między nimi, obsługa wernisażu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa prawna regulaminu plakatu (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - odrębne zlecenie kancelarii, nie złożone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dojazd i nocleg finalistów na galę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - jak przy plebiscycie piosenki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finansuje: Sponsor Akademii. Kwoty netto. Vouchery są świadczeniem rzeczowym i rosną wprost z liczbą ocenionych rozmów.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na żółto pola do edycji w zakładce Wyjaśnienia. Praca organizatora przy prowadzeniu Akademii została w budżetach poszczególnych plebiscytów, żeby nie liczyć jej dwa razy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILE PRACY TRZEBA WYKONAĆ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liczba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zgłoszenia rozmów do Nagrody</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarium obejmuje także oznaczanie zastrzeżeń prawnych przy czytaniu (regulamin § 8 ust. 3a): dane osób trzecich, całe cudze utwory krótkie, wgrane cudze materiały. Oznaczenie nie wpływa na punktację.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odczytów na jedno zgłoszenie rozmowy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulamin § 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razem odczytów rozmów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to jest praca, którą finansuje sponsor Akademii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zgłoszenia filmów do plebiscytu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akademia filmu działa od pierwszej edycji, a nie po przekroczeniu progu: film trwa do 90 minut, więc pierwszego przejścia nie da się zrobić kilkuosobowym jury (regulamin filmu § 8 ust. 4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obejrzeń jednego filmu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dwa niezależne obejrzenia, jak dwa odczyty rozmowy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razem obejrzeń filmów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">każde obejrzenie to film do 90 minut plus karta oceny, czyli około 2 godzin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WYNAGRODZENIE OCENIAJĄCYCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stawka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarium podstawowe czytelników rozmów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">przeniesione z Budżetu Nagrody</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vouchery za oceniane rozmowy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jeden voucher za każde rozpoczęte 100 odczytów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarium oceniających filmy, za jedno obejrzenie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 zł za obejrzenie z wypełnieniem karty oceny, czyli około 150 zł za godzinę. Ustalenie z 26.10.2026; kwota rośnie wprost z liczbą zgłoszonych filmów.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razem dla oceniających</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa i rozliczenie voucherów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ewidencja, PIT-11 dla czytelników, korespondencja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiały kalibracyjne i szkolenie czytelników rozmów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trzy rozmowy kotwiczne, instrukcja, spotkanie wprowadzające</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiały kalibracyjne i szkolenie oceniających filmy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trzy filmy kotwiczne z rozpisaną punktacją, instrukcja oznaczania zastrzeżeń i spotkanie wprowadzające; droższe niż przy rozmowach, bo materiał kotwiczny trzeba obejrzeć, a nie przeczytać</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel oceniających: hosting, konta, obsługa odnośników</t>
+  </si>
+  <si>
+    <t xml:space="preserve">filmów nie trzymamy u siebie, ale panel musi je kolejkować, odtwarzać z kanału autora i wyłapywać odnośniki, które przestały działać</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wynagrodzenie oceniających</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezerwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAK TO SIĘ SKALUJE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vouchery i honoraria za obejrzenia rosną wprost z liczbą zgłoszeń, więc sponsor płaci za wykonaną pracę, a nie za prognozę. Ludzi trzeba jednak znaleźć osobno: kolumny Potrzebnych liczą osoby od liczby ODCZYTÓW i OBEJRZEŃ, nie od liczby zgłoszeń. Tabela przy większych wolumenach nie modeluje odrębnie trybu jednoosobowego, drugich odczytów poniżej progu ani audytu losowego - te trzy rzeczy trzeba policzyć osobno przed ogłoszeniem progu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zgłoszeń w edycji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odczytów rozmów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voucherów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koszt voucherów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potrzebnych czytelników</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filmów w edycji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obejrzeń</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honoraria za obejrzenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Godzin oglądania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potrzebnych oceniających</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przy filmie granica jest twardsza niż przy rozmowach: 10 tys. zgłoszeń to 20 tys. obejrzeń i 40 tys. godzin oglądania, czyli praca, której nie da się kupić za honoraria. Zanim nabór filmu przekroczy kilkaset zgłoszeń, trzeba zmienić konstrukcję pierwszego przejścia, a nie mnożyć stawkę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finansuje: Sponsor plebiscytu filmu. Kwoty netto, chyba że napisano inaczej.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na żółto pola do edycji w zakładce Wyjaśnienia. Pierwsze przejście oceny prowadzi Akademia filmu i jej koszt stoi w zakładce Budżet Akademii, żeby nie liczyć go dwa razy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrola formalna zgłoszeń filmów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">czas trwania, język, data ukończenia, działający odnośnik, miniatura, deklaracja, oświadczenia; 12 minut na zgłoszenie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weryfikacja historii zgłoszonego filmu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulamin § 3a: film powstaje na potrzeby plebiscytu, więc sprawdzamy datę publikacji i publicznie dostępne wyniki konkursów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa Akademii filmu i jury: przydziały, karty, obrady, werdykt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dwa przejścia oceny, pięciu finalistów, kolejność trójki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zebranie fragmentów od finalistów i przygotowanie emisji galowych</t>
+  </si>
+  <si>
+    <t xml:space="preserve">autor wybiera fragment w terminie nie krótszym niż 14 dni; organizator zbiera, sprawdza format i układa kolejność</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organizacja pełnych pokazów filmów finałowych poza galą</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulamin § 10 ust. 4: termin i miejsce ogłaszane najpóźniej w dniu gali, udział za zgodą autora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prowadzenie Projektorni i archiwum filmów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wpisy po ocenie formalnej, oznaczanie odnośników, które przestały działać</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dotarcie do szkół filmowych, kół filmowych i festiwali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PWSFTviT, wydziały filmowe, festiwale krótkiego metrażu, domy kultury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minuty na zgłoszenie dotyczą wyłącznie kontroli formalnej. Godziny obsługi oceny nie rosną wprost z naborem, bo pierwsze przejście wykonuje Akademia filmu - jej koszt rośnie i stoi w Budżecie Akademii.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nagrody filmu (brutto dla laureatów)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">czołowa trójka: 100, 50 i 30 tys.; podatek 10% jak przy Nagrodzie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jedna nagroda, dla filmu z największą liczbą głosów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ten sam medalion, który otrzymują zwycięzcy pozostałych plebiscytów; dyplomy dla pięciu finalistów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honoraria jury filmu za ocenę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO USTALENIA - stawka godzinowa jest przy nazwisku złym narzędziem; kotwica z Wyjaśnień (5 osób x 25 h x 290 zł) dałaby 36 250 zł</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opracowanie techniczne minutowych emisji na galę (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - pobranie materiału w jakości emisyjnej, zgodność formatów, napisy, montaż bloku pięciu emisji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pełne pokazy filmów finałowych (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - sala, projekcja, obsługa; regulamin § 10 ust. 4 wymaga ogłoszenia terminu najpóźniej w dniu gali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - jak przy plebiscycie piosenki; pięciu finalistów, często ze składem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa prawna regulaminu filmu (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - odrębne zlecenie kancelarii, nie złożone; siedem miejsc wypisanych na końcu regulaminu, w tym status filmu wygenerowanego w całości</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budżet Gali - gala rozstrzygnięcia pierwszej edycji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finansuje: Sponsor gali. Kwoty netto, chyba że napisano inaczej.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gala: organizacja, zdjęcia, wysyłki</t>
   </si>
   <si>
     <t xml:space="preserve">z koordynatorem po stronie B jest mniej</t>
   </si>
   <si>
-    <t xml:space="preserve">Rozliczenia, podatki, sprawozdanie dla sponsorów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z księgowym</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Komunikacja, media, strona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">przez cały rok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razem praca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KOSZTY TWARDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cena jednostkowa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ilość</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gala: sala, obsługa, poczęstunek</t>
   </si>
   <si>
@@ -511,631 +1130,37 @@
     <t xml:space="preserve">zdjęcie grupowe i dokumentacja</t>
   </si>
   <si>
-    <t xml:space="preserve">Medal laureata i dyplomy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mosiądz grawerowany, 10 dyplomów</t>
-  </si>
-  <si>
     <t xml:space="preserve">Przejazdy i noclegi jury</t>
   </si>
   <si>
     <t xml:space="preserve">zwrot kosztów</t>
   </si>
   <si>
-    <t xml:space="preserve">Obsługa księgowa projektu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ponad bieżącą obsługę działalności</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domeny konstela.org i konstela.pl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opłacone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honoraria jury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 czytelników po 2 500 zł, 4 jurorów po 8 000 zł</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 jurorów po 8 000 zł; honoraria Akademii przeniesione do Budżetu Akademii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promocja naboru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">materiały, obsługa prasowa przy starcie i rozstrzygnięciu, płatne dotarcie</t>
-  </si>
-  <si>
     <t xml:space="preserve">Przejazdy i noclegi finalistów na galę</t>
   </si>
   <si>
     <t xml:space="preserve">dziesięć osób, przejazd i nocleg</t>
   </si>
   <si>
-    <t xml:space="preserve">Nagroda publiczności</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ubezpieczenie OC organizatora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">do ustalenia po konsultacji prawnej; na razie pokryte rezerwą</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razem koszty twarde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PODSUMOWANIE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagrody (brutto dla laureatów, bez VAT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Praca organizatora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koszty twarde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rezerwa (od pracy i kosztów, bez nagród)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAZEM NETTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO ZAPŁATY BRUTTO - ta liczba trafia na fakturę</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finansuje: Partner wydawniczy / sponsor organizacyjny. Kwoty netto, chyba że napisano inaczej.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antologia: redakcja not jury i uzupełnienia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noty pisze jury (§ 8 ust. 13a)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skład, korekta autorska, EPUB i PDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">szablon przygotowany w styczniu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rozstrzyganie zgłoszeń oznaczonych przez oceniających</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oznaczanie zastrzeżeń prawnych robi Akademia przy czytaniu (regulamin § 8 ust. 3a), bo skaluje się razem z naborem. Organizator rozstrzyga co do zgłoszeń oznaczonych oraz co do przypadków, w których otrzymał konkretny sygnał albo sam powziął wiadomość o problemie, wraz z zawiadomieniem uczestnika. Wpisane 4 minuty na zgłoszenie są uśrednieniem: przy części zgłoszeń nie ma nic do rozstrzygania, przy oznaczonych rozstrzygnięcie i korespondencja zajmują kilkadziesiąt minut.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skraper i kopia archiwalna zgłoszenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Playwright: PDF, pełny HTML, zrzut, znacznik czasu, suma kontrolna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narzędzie do oceny formalnej</t>
-  </si>
-  <si>
-    <t xml:space="preserve">liczenie słów i wypowiedzi, wykluczanie kodu, język, ciągłość wątku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel oceny dla Akademii i jury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">konta, przydziały, karta oceny, rozbieżności, trzeci odczyt, ślad audytowy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publiczne archiwum rozmów na stronie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">generowanie stron z kopii, nawigacja, tryb redakcji fragmentów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koordynacja podcastu: goście, terminy, publikacja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Powołanie fundacji-organizatora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notariusz, statut, wpis do KRS, fundusz założycielski</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konsultacja prawna przed otwarciem naboru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sześć obszarów, w tym licencja i archiwum; obowiązkowa przed naborem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sześć obszarów, w tym licencja i archiwum; kwota z zapasem wobec ofert kancelarii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domeny, poczta, hosting, magazyn kopii archiwalnych</t>
-  </si>
-  <si>
-    <t xml:space="preserve">magazyn obiektowy w UE z kopią zapasową, retencja min. 5 lat, PDF/HTML/zrzuty/EPUB; w tym skrzynka pocztowa w domenie wraz z aliasami (kontakt@, imienny) - rzędu 150-450 zł rocznie, aliasy bez dopłaty; przejście na własną skrzynkę przenosi MX i wyłącza Cloudflare Email Routing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koordynator wydania i moderacji I-IV 2028 (B2B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pełne zaangażowanie I-III 2028, moderacja archiwum i obsługa zgłoszeń przy dużym napływie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korekta językowa antologii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">korekta dziesięciu rozmów i not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skład i przygotowanie do druku (DTP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">szablon plus obsługa wydania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Krótki nakład antologii na galę (100 egz.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gwarantowany przez organizatora, niezależny od partnera wydawniczego; nakład handlowy jest po stronie partnera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nadanie ISBN i egzemplarz obowiązkowy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nadanie bezpłatne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przebudowa strony: UI/UX i teksty (agencja)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projekt i wdrożenie strony Nagrody wraz z copywritingiem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsługa fundacji za pierwszy rok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">księgowość, sprawozdanie finansowe i sprawozdanie dla ministra nadzorującego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narzędzia AI i licencje oprogramowania (rok)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dostęp do narzędzi AI, bez których 937 godzin pracy organizatora nie jest wykonalne; rzędu 2,5 tys. zł miesięcznie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejestracja znaku towarowego Konstela w EUIPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jedna klasa, ochrona w całej Unii; opłaty urzędowe około 850 euro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Produkcja podcastu wraz z honorarium prowadzącego (24 odcinki)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - nagranie, montaż, dźwięk, wersja wideo i dystrybucja; honorarium prowadzącego nieustalone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marża (od pracy i kosztów, bez nagród)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finansuje: Sponsor plebiscytu. Kwoty netto, chyba że napisano inaczej.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontrola formalna zgłoszeń plebiscytu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 minut na zgłoszenie; przy dużych liczbach część kontroli automatyzowana.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koordynacja nagrań studyjnych dziesięciu finalistów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">umowy, terminy w studiu, przekazanie praw autorom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsługa jury plebiscytu: przydziały, obrady, werdykt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w tym preselekcja powyżej progu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsługa głosowania publiczności i ogłoszenie wyniku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bramka SMS, ukryte liczniki, ogłoszenie na gali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Komunikacja plebiscytu i dotarcie do wykonawców</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grupy muzyków, szkoły muzyczne, scena coverowa, radia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Powyżej progu zgłoszeń pierwsze przejście oceny przechodzi na Akademię, tak jak w konkursie rozmów - dlatego te godziny nie rosną z naborem. Minuty na zgłoszenie dotyczą wyłącznie kontroli formalnej.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagrody plebiscytu (brutto dla laureatów)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">czołowa trójka; podatek 10% jak przy Nagrodzie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagrody publiczności (brutto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dla wykonawcy oraz za najlepsze uzasadnienie wyboru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagrania studyjne dziesięciu finalistów (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prawa do nagrań przechodzą na autorów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nagranie i premiera na początku 2027, otwiera nabór</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medalion zwycięzcy i dyplomy finalistów (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ten sam medalion, który otrzymuje laureat konkursu rozmów; dyplomy dla całej dziesiątki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honoraria jury plebiscytu za ocenę (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO USTALENIA - kotwica: stawka jury ok. 290 zł/h, ok. 15 h na jurora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizacja części artystycznej gali (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - zależy od miejsca gali, które nie jest wybrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsługa prawna plebiscytu (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - zakres plebiscytowy nie był objęty wyceną z 22.10.2026; osobne zlecenie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">odrębne zlecenie na pytania plebiscytowe; kwota z zapasem wobec ofert kancelarii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dojazd i nocleg dziesięciu finalistów na galę (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - udział czołowej trójki obowiązkowy (§ 14 regulaminu plebiscytu), pokrycie dla całej dziesiątki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koszty twarde bez nagród</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finansuje: Mecenas konkursu plakatu. Kwoty netto, chyba że napisano inaczej.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontrola formalna zgłoszeń plakatów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">format, proporcje, rozdzielczość, oświadczenia; 8 minut na zgłoszenie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsługa jury plakatu: przydziały, preselekcja, obrady, werdykt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">werdykt zapada przed galą, bo okładka antologii idzie do druku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ukryte liczniki, ogłoszenie na gali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przyjęcie, ewidencja i zwrot oryginałów finalistów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dwie lokalizacje: wystawa przy gali i wernisaż w galerii sztuki (regulamin § 10 ust. 3a), więc protokoły, przewóz między miejscami i ubezpieczenie na dłuższy okres - do 120 dni od dostarczenia pracy. Przy wycenie sprawdzić, czy 35 godzin wystarcza.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uzgodnienie okładki antologii ze zwycięzcą</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zgoda w 7 dni po werdykcie, typografia, kadrowanie, redakcja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dotarcie do szkół artystycznych i środowiska ilustratorów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASP, licea plastyczne, grupy ilustratorów, konkursy plakatowe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsługa licytacji: warunki, zgody, rozliczenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propozycja po zamknięciu ocen, podział 50/50, rozliczenie na piśmie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagrody plakatu (brutto dla laureatów)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">czołowa trójka: 50, 25 i 15 tys.; podatek 10% jak przy Nagrodzie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagroda publiczności (brutto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jedna nagroda, dla pracy z największą liczbą głosów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honoraria jury plakatu za ocenę (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO USTALENIA - stawka godzinowa jest przy nazwisku złym narzędziem; kotwica z Wyjaśnień (5 osób x 10 h x 290 zł) dałaby 14 500 zł</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport oryginałów w obie strony (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">szacunek, nie oferta; organizator pokrywa obie strony</t>
-  </si>
-  <si>
-    <t xml:space="preserve">szacunek przy sumie deklarowanej rzędu 100 tys. zł</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realizacja wystawy przy gali i wernisażu w galerii (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - zawieszenie, oświetlenie, opisy prac w dwóch miejscach, przewóz między nimi, obsługa wernisażu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsługa prawna regulaminu plakatu (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - odrębne zlecenie kancelarii, nie złożone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dojazd i nocleg finalistów na galę (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - jak przy plebiscycie piosenki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finansuje: Sponsor Akademii. Kwoty netto. Vouchery są świadczeniem rzeczowym i rosną wprost z liczbą ocenionych rozmów.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na żółto pola do edycji w zakładce Wyjaśnienia. Praca organizatora przy prowadzeniu Akademii została w budżetach poszczególnych plebiscytów, żeby nie liczyć jej dwa razy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILE PRACY TRZEBA WYKONAĆ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liczba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zgłoszenia rozmów do Nagrody</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honorarium obejmuje także oznaczanie zastrzeżeń prawnych przy czytaniu (regulamin § 8 ust. 3a): dane osób trzecich, całe cudze utwory krótkie, wgrane cudze materiały. Oznaczenie nie wpływa na punktację.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odczytów na jedno zgłoszenie rozmowy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulamin § 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razem odczytów rozmów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">to jest praca, którą finansuje sponsor Akademii</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zgłoszenia filmów do plebiscytu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akademia filmu działa od pierwszej edycji, a nie po przekroczeniu progu: film trwa do 90 minut, więc pierwszego przejścia nie da się zrobić kilkuosobowym jury (regulamin filmu § 8 ust. 4).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obejrzeń jednego filmu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dwa niezależne obejrzenia, jak dwa odczyty rozmowy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razem obejrzeń filmów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">każde obejrzenie to film do 90 minut plus karta oceny, czyli około 2 godzin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WYNAGRODZENIE OCENIAJĄCYCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stawka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honorarium podstawowe czytelników rozmów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">przeniesione z Budżetu Nagrody</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vouchery za oceniane rozmowy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jeden voucher za każde rozpoczęte 100 odczytów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honorarium oceniających filmy, za jedno obejrzenie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300 zł za obejrzenie z wypełnieniem karty oceny, czyli około 150 zł za godzinę. Ustalenie z 26.10.2026; kwota rośnie wprost z liczbą zgłoszonych filmów.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razem dla oceniających</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsługa i rozliczenie voucherów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ewidencja, PIT-11 dla czytelników, korespondencja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiały kalibracyjne i szkolenie czytelników rozmów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trzy rozmowy kotwiczne, instrukcja, spotkanie wprowadzające</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiały kalibracyjne i szkolenie oceniających filmy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trzy filmy kotwiczne z rozpisaną punktacją, instrukcja oznaczania zastrzeżeń i spotkanie wprowadzające; droższe niż przy rozmowach, bo materiał kotwiczny trzeba obejrzeć, a nie przeczytać</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel oceniających: hosting, konta, obsługa odnośników</t>
-  </si>
-  <si>
-    <t xml:space="preserve">filmów nie trzymamy u siebie, ale panel musi je kolejkować, odtwarzać z kanału autora i wyłapywać odnośniki, które przestały działać</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wynagrodzenie oceniających</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rezerwa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JAK TO SIĘ SKALUJE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vouchery i honoraria za obejrzenia rosną wprost z liczbą zgłoszeń, więc sponsor płaci za wykonaną pracę, a nie za prognozę. Ludzi trzeba jednak znaleźć osobno: kolumny Potrzebnych liczą osoby od liczby ODCZYTÓW i OBEJRZEŃ, nie od liczby zgłoszeń. Tabela przy większych wolumenach nie modeluje odrębnie trybu jednoosobowego, drugich odczytów poniżej progu ani audytu losowego - te trzy rzeczy trzeba policzyć osobno przed ogłoszeniem progu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zgłoszeń w edycji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odczytów rozmów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voucherów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koszt voucherów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Potrzebnych czytelników</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filmów w edycji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obejrzeń</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honoraria za obejrzenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Godzin oglądania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Potrzebnych oceniających</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Przy filmie granica jest twardsza niż przy rozmowach: 10 tys. zgłoszeń to 20 tys. obejrzeń i 40 tys. godzin oglądania, czyli praca, której nie da się kupić za honoraria. Zanim nabór filmu przekroczy kilkaset zgłoszeń, trzeba zmienić konstrukcję pierwszego przejścia, a nie mnożyć stawkę.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finansuje: Sponsor plebiscytu filmu. Kwoty netto, chyba że napisano inaczej.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na żółto pola do edycji w zakładce Wyjaśnienia. Pierwsze przejście oceny prowadzi Akademia filmu i jej koszt stoi w zakładce Budżet Akademii, żeby nie liczyć go dwa razy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontrola formalna zgłoszeń filmów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">czas trwania, język, data ukończenia, działający odnośnik, miniatura, deklaracja, oświadczenia; 12 minut na zgłoszenie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weryfikacja historii zgłoszonego filmu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulamin § 3a: film powstaje na potrzeby plebiscytu, więc sprawdzamy datę publikacji i publicznie dostępne wyniki konkursów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsługa Akademii filmu i jury: przydziały, karty, obrady, werdykt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dwa przejścia oceny, pięciu finalistów, kolejność trójki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zebranie fragmentów od finalistów i przygotowanie emisji galowych</t>
-  </si>
-  <si>
-    <t xml:space="preserve">autor wybiera fragment w terminie nie krótszym niż 14 dni; organizator zbiera, sprawdza format i układa kolejność</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organizacja pełnych pokazów filmów finałowych poza galą</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulamin § 10 ust. 4: termin i miejsce ogłaszane najpóźniej w dniu gali, udział za zgodą autora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prowadzenie Projektorni i archiwum filmów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wpisy po ocenie formalnej, oznaczanie odnośników, które przestały działać</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dotarcie do szkół filmowych, kół filmowych i festiwali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PWSFTviT, wydziały filmowe, festiwale krótkiego metrażu, domy kultury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minuty na zgłoszenie dotyczą wyłącznie kontroli formalnej. Godziny obsługi oceny nie rosną wprost z naborem, bo pierwsze przejście wykonuje Akademia filmu - jej koszt rośnie i stoi w Budżecie Akademii.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagrody filmu (brutto dla laureatów)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">czołowa trójka: 100, 50 i 30 tys.; podatek 10% jak przy Nagrodzie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jedna nagroda, dla filmu z największą liczbą głosów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ten sam medalion, który otrzymują zwycięzcy pozostałych plebiscytów; dyplomy dla pięciu finalistów</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honoraria jury filmu za ocenę (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO USTALENIA - stawka godzinowa jest przy nazwisku złym narzędziem; kotwica z Wyjaśnień (5 osób x 25 h x 290 zł) dałaby 36 250 zł</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opracowanie techniczne minutowych emisji na galę (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - pobranie materiału w jakości emisyjnej, zgodność formatów, napisy, montaż bloku pięciu emisji</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pełne pokazy filmów finałowych (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - sala, projekcja, obsługa; regulamin § 10 ust. 4 wymaga ogłoszenia terminu najpóźniej w dniu gali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - jak przy plebiscycie piosenki; pięciu finalistów, często ze składem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsługa prawna regulaminu filmu (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - odrębne zlecenie kancelarii, nie złożone; siedem miejsc wypisanych na końcu regulaminu, w tym status filmu wygenerowanego w całości</t>
+    <t xml:space="preserve">Oprawa artystyczna gali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">technika, nagłośnienie, światło, honoraria za występ - do wyceny po wyborze miejsca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejestracja wideo i udostępnienie zapisu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zapis udostępniany bezpłatnie - do wyceny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prowadzenie gali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">do wyceny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezerwa (od pracy i kosztów)</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1317,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1341,6 +1366,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1351,22 +1384,6 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1382,10 +1399,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1413,10 +1426,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1426,6 +1435,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1807,8 +1820,8 @@
         <v>7</v>
       </c>
       <c r="C6" s="8" t="n">
-        <f aca="false">'Budżet Nagrody'!$D$40</f>
-        <v>570044.8</v>
+        <f aca="false">'Budżet Nagrody'!$D$35</f>
+        <v>534876.8</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -1892,25 +1905,25 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <f aca="false">'Budżet Nagrody'!$D$40+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$34</f>
+      <c r="B12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <f aca="false">'Budżet Gali'!$D$25</f>
+        <v>35168</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <f aca="false">'Budżet Nagrody'!$D$35+'Budżet Gali'!$D$25+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$34</f>
         <v>1686506.8</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1918,11 +1931,9 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="A14" s="12" t="s">
+        <v>21</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -1930,13 +1941,7 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>220</v>
-      </c>
-      <c r="C15" s="13" t="s">
+      <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="3"/>
@@ -1949,10 +1954,10 @@
       <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="C16" s="13" t="s">
+      <c r="B16" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="3"/>
@@ -1965,10 +1970,10 @@
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="12" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="3"/>
@@ -1981,10 +1986,10 @@
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C18" s="13" t="s">
+      <c r="B18" s="14" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="3"/>
@@ -1997,10 +2002,10 @@
       <c r="A19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="3"/>
@@ -2013,21 +2018,26 @@
       <c r="A20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C20" s="13" t="s">
+      <c r="B20" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>32</v>
       </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C21" s="13" t="s">
+      <c r="B21" s="14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2035,26 +2045,21 @@
       <c r="A22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="C22" s="13" t="s">
+      <c r="B22" s="14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="C23" s="13" t="s">
+      <c r="B23" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>38</v>
       </c>
       <c r="D23" s="3"/>
@@ -2067,10 +2072,10 @@
       <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C24" s="13" t="s">
+      <c r="B24" s="14" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D24" s="3"/>
@@ -2083,10 +2088,10 @@
       <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="12" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C25" s="13" t="s">
+      <c r="B25" s="14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>42</v>
       </c>
       <c r="D25" s="3"/>
@@ -2099,10 +2104,10 @@
       <c r="A26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="C26" s="13" t="s">
+      <c r="B26" s="14" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D26" s="3"/>
@@ -2115,10 +2120,10 @@
       <c r="A27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="12" t="n">
-        <v>80000</v>
-      </c>
-      <c r="C27" s="13" t="s">
+      <c r="B27" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>46</v>
       </c>
       <c r="D27" s="3"/>
@@ -2131,10 +2136,10 @@
       <c r="A28" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="12" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C28" s="13" t="s">
+      <c r="B28" s="14" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>48</v>
       </c>
       <c r="D28" s="3"/>
@@ -2148,9 +2153,9 @@
         <v>49</v>
       </c>
       <c r="B29" s="14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C29" s="13" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>50</v>
       </c>
       <c r="D29" s="3"/>
@@ -2163,10 +2168,10 @@
       <c r="A30" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B30" s="14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C30" s="13" t="s">
+      <c r="B30" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>52</v>
       </c>
       <c r="D30" s="3"/>
@@ -2179,11 +2184,11 @@
       <c r="A31" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B31" s="14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>50</v>
+      <c r="B31" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>54</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -2193,13 +2198,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="14" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="C32" s="13" t="s">
         <v>55</v>
+      </c>
+      <c r="B32" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -2208,11 +2213,11 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="15" t="n">
-        <v>0.1</v>
+      <c r="B33" s="16" t="n">
+        <v>0.23</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>57</v>
@@ -2224,7 +2229,9 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3"/>
+      <c r="A34" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2232,9 +2239,7 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="s">
-        <v>58</v>
-      </c>
+      <c r="A35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2242,13 +2247,9 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="17"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2257,7 +2258,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -2266,11 +2267,9 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
+      <c r="A38" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2278,9 +2277,9 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
+      <c r="A39" s="13" t="s">
+        <v>62</v>
+      </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2288,11 +2287,7 @@
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
+      <c r="A40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -2300,8 +2295,8 @@
       <c r="H40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="s">
-        <v>64</v>
+      <c r="A41" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -2310,344 +2305,345 @@
       <c r="H41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
+      <c r="A42" s="13" t="s">
+        <v>64</v>
+      </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="20" t="n">
-        <v>500</v>
+        <v>67</v>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B47" s="20" t="n">
-        <v>2500</v>
+        <v>69</v>
+      </c>
+      <c r="B47" s="18" t="n">
+        <v>500</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B48" s="12" t="n">
+      <c r="B49" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B49" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="C49" s="15" t="s">
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="19" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B52" s="22" t="n">
-        <v>150</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B53" s="20" t="n">
-        <v>90000</v>
+        <v>150</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" s="20" t="n">
-        <v>3000</v>
+        <v>79</v>
+      </c>
+      <c r="B54" s="18" t="n">
+        <v>90000</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B55" s="20" t="n">
-        <v>1200</v>
+        <v>81</v>
+      </c>
+      <c r="B55" s="18" t="n">
+        <v>3000</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B56" s="22" t="n">
-        <v>5</v>
+        <v>83</v>
+      </c>
+      <c r="B56" s="18" t="n">
+        <v>1200</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B57" s="22" t="n">
-        <v>10</v>
+        <v>84</v>
+      </c>
+      <c r="B57" s="20" t="n">
+        <v>5</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B58" s="20" t="n">
-        <v>290</v>
+        <v>10</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B59" s="22" t="n">
-        <v>10</v>
+        <v>88</v>
+      </c>
+      <c r="B59" s="18" t="n">
+        <v>290</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B60" s="20" t="n">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B61" s="18" t="n">
+        <v>400</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B62" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B61" s="20" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C61" s="1" t="s">
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="23" t="s">
+      <c r="B63" s="18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="19" t="s">
         <v>97</v>
-      </c>
-      <c r="B62" s="23" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C62" s="23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="21" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B65" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B66" s="12" t="n">
-        <v>180000</v>
+        <v>98</v>
+      </c>
+      <c r="B66" s="14" t="n">
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B67" s="12" t="n">
-        <v>3000</v>
+        <v>100</v>
+      </c>
+      <c r="B67" s="14" t="n">
+        <v>180000</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B68" s="12" t="n">
-        <v>1200</v>
+        <v>102</v>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>3000</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B69" s="12" t="n">
-        <v>5</v>
+        <v>104</v>
+      </c>
+      <c r="B69" s="14" t="n">
+        <v>1200</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B70" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="B70" s="14" t="n">
         <v>5</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B71" s="12" t="n">
-        <v>25</v>
+        <v>108</v>
+      </c>
+      <c r="B71" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B72" s="12" t="n">
-        <v>290</v>
+        <v>110</v>
+      </c>
+      <c r="B72" s="14" t="n">
+        <v>25</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B73" s="12" t="n">
-        <v>0.12</v>
+        <v>112</v>
+      </c>
+      <c r="B73" s="14" t="n">
+        <v>290</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B74" s="12" t="n">
-        <v>2</v>
+        <v>113</v>
+      </c>
+      <c r="B74" s="14" t="n">
+        <v>0.12</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B75" s="12" t="n">
-        <v>300</v>
+        <v>115</v>
+      </c>
+      <c r="B75" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B77" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B76" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2677,20 +2673,10 @@
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A62:C62"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2732,7 +2718,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2744,7 +2730,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2766,7 +2752,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2778,428 +2764,426 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$17/60</f>
+        <v>60</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <f aca="false">D7*Wyjaśnienia!$B$16</f>
+        <v>13200</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>131</v>
-      </c>
-      <c r="B7" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="26" t="n">
-        <f aca="false">B7+C7*Wyjaśnienia!$B$16/60</f>
-        <v>60</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <f aca="false">D7*Wyjaśnienia!$B$15</f>
-        <v>13200</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>132</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$17/60</f>
+        <v>24</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <f aca="false">D8*Wyjaśnienia!$B$16</f>
+        <v>5280</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>133</v>
-      </c>
-      <c r="B8" s="25" t="n">
-        <v>24</v>
-      </c>
-      <c r="C8" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="26" t="n">
-        <f aca="false">B8+C8*Wyjaśnienia!$B$16/60</f>
-        <v>24</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <f aca="false">D8*Wyjaśnienia!$B$15</f>
-        <v>5280</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$17/60</f>
+        <v>50</v>
+      </c>
+      <c r="E9" s="24" t="n">
+        <f aca="false">D9*Wyjaśnienia!$B$16</f>
+        <v>11000</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>135</v>
-      </c>
-      <c r="B9" s="25" t="n">
-        <v>50</v>
-      </c>
-      <c r="C9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="26" t="n">
-        <f aca="false">B9+C9*Wyjaśnienia!$B$16/60</f>
-        <v>50</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <f aca="false">D9*Wyjaśnienia!$B$15</f>
-        <v>11000</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>136</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="23" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$17/60</f>
+        <v>23</v>
+      </c>
+      <c r="E10" s="24" t="n">
+        <f aca="false">D10*Wyjaśnienia!$B$16</f>
+        <v>5060</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>137</v>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="26" t="n">
-        <f aca="false">B10+C10*Wyjaśnienia!$B$16/60</f>
-        <v>23</v>
-      </c>
-      <c r="E10" s="27" t="n">
-        <f aca="false">D10*Wyjaśnienia!$B$15</f>
-        <v>5060</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>138</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$17/60</f>
+        <v>20</v>
+      </c>
+      <c r="E11" s="24" t="n">
+        <f aca="false">D11*Wyjaśnienia!$B$16</f>
+        <v>4400</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>139</v>
-      </c>
-      <c r="B11" s="25" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="26" t="n">
-        <f aca="false">B11+C11*Wyjaśnienia!$B$16/60</f>
-        <v>20</v>
-      </c>
-      <c r="E11" s="27" t="n">
-        <f aca="false">D11*Wyjaśnienia!$B$15</f>
-        <v>4400</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>140</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <f aca="false">B12+C12*Wyjaśnienia!$B$17/60</f>
+        <v>20</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <f aca="false">D12*Wyjaśnienia!$B$16</f>
+        <v>4400</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>141</v>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="26" t="n">
-        <f aca="false">B12+C12*Wyjaśnienia!$B$16/60</f>
-        <v>20</v>
-      </c>
-      <c r="E12" s="27" t="n">
-        <f aca="false">D12*Wyjaśnienia!$B$15</f>
-        <v>4400</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>142</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <f aca="false">B13+C13*Wyjaśnienia!$B$17/60</f>
+        <v>40</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <f aca="false">D13*Wyjaśnienia!$B$16</f>
+        <v>8800</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>143</v>
-      </c>
-      <c r="B13" s="25" t="n">
-        <v>40</v>
-      </c>
-      <c r="C13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="26" t="n">
-        <f aca="false">B13+C13*Wyjaśnienia!$B$16/60</f>
-        <v>40</v>
-      </c>
-      <c r="E13" s="27" t="n">
-        <f aca="false">D13*Wyjaśnienia!$B$15</f>
-        <v>8800</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>144</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="23" t="n">
+        <f aca="false">B14+C14*Wyjaśnienia!$B$17/60</f>
+        <v>25</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <f aca="false">D14*Wyjaśnienia!$B$16</f>
+        <v>5500</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>145</v>
-      </c>
-      <c r="B14" s="25" t="n">
-        <v>25</v>
-      </c>
-      <c r="C14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="26" t="n">
-        <f aca="false">B14+C14*Wyjaśnienia!$B$16/60</f>
-        <v>25</v>
-      </c>
-      <c r="E14" s="27" t="n">
-        <f aca="false">D14*Wyjaśnienia!$B$15</f>
-        <v>5500</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>146</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <f aca="false">B15+C15*Wyjaśnienia!$B$17/60</f>
+        <v>25</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <f aca="false">D15*Wyjaśnienia!$B$16</f>
+        <v>5500</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>147</v>
-      </c>
-      <c r="B15" s="25" t="n">
-        <v>45</v>
-      </c>
-      <c r="C15" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="26" t="n">
-        <f aca="false">B15+C15*Wyjaśnienia!$B$16/60</f>
-        <v>45</v>
-      </c>
-      <c r="E15" s="27" t="n">
-        <f aca="false">D15*Wyjaśnienia!$B$15</f>
-        <v>9900</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>148</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <f aca="false">B16+C16*Wyjaśnienia!$B$17/60</f>
+        <v>40</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <f aca="false">D16*Wyjaśnienia!$B$16</f>
+        <v>8800</v>
+      </c>
+      <c r="F16" s="15" t="s">
         <v>149</v>
-      </c>
-      <c r="B16" s="25" t="n">
-        <v>25</v>
-      </c>
-      <c r="C16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="26" t="n">
-        <f aca="false">B16+C16*Wyjaśnienia!$B$16/60</f>
-        <v>25</v>
-      </c>
-      <c r="E16" s="27" t="n">
-        <f aca="false">D16*Wyjaśnienia!$B$15</f>
-        <v>5500</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>150</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="B17" s="25" t="n">
-        <v>40</v>
-      </c>
-      <c r="C17" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="26" t="n">
-        <f aca="false">B17+C17*Wyjaśnienia!$B$16/60</f>
-        <v>40</v>
-      </c>
-      <c r="E17" s="27" t="n">
-        <f aca="false">D17*Wyjaśnienia!$B$15</f>
-        <v>8800</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>152</v>
-      </c>
+      <c r="A17" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="25" t="n">
+        <f aca="false">SUM(D7:D16)</f>
+        <v>327</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <f aca="false">SUM(E7:E16)</f>
+        <v>71940</v>
+      </c>
+      <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>153</v>
-      </c>
+      <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="28" t="n">
-        <f aca="false">SUM(D7:D17)</f>
-        <v>372</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <f aca="false">SUM(E7:E17)</f>
-        <v>81840</v>
-      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="A19" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="A20" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="A21" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B21" s="26" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="24" t="n">
+        <f aca="false">B21*C21</f>
+        <v>1200</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>155</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" s="26" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <f aca="false">B22*C22</f>
+        <v>1500</v>
+      </c>
+      <c r="E22" s="15" t="s">
         <v>157</v>
-      </c>
-      <c r="B22" s="29" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C22" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="27" t="n">
-        <f aca="false">B22*C22</f>
-        <v>8000</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>158</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="26" t="n">
+        <v>250</v>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="24" t="n">
+        <f aca="false">B23*C23</f>
+        <v>250</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>159</v>
-      </c>
-      <c r="B23" s="29" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C23" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="27" t="n">
-        <f aca="false">B23*C23</f>
-        <v>1500</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>160</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B24" s="26" t="n">
+        <v>32000</v>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="24" t="n">
+        <f aca="false">B24*C24</f>
+        <v>32000</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B24" s="29" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C24" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="27" t="n">
-        <f aca="false">B24*C24</f>
-        <v>1200</v>
-      </c>
-      <c r="E24" s="13" t="s">
+      <c r="F24" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="B25" s="29" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C25" s="25" t="n">
+      <c r="B25" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C25" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="27" t="n">
+      <c r="D25" s="24" t="n">
         <f aca="false">B25*C25</f>
-        <v>4000</v>
-      </c>
-      <c r="E25" s="13" t="s">
+        <v>15000</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>164</v>
       </c>
       <c r="F25" s="3"/>
@@ -3207,159 +3191,114 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="29" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C26" s="25" t="n">
+      <c r="B26" s="26" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C26" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="27" t="n">
+      <c r="D26" s="24" t="n">
         <f aca="false">B26*C26</f>
-        <v>1500</v>
-      </c>
-      <c r="E26" s="13" t="s">
+        <v>3000</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="s">
+      <c r="B27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="24" t="n">
+        <f aca="false">B27*C27</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>167</v>
-      </c>
-      <c r="B27" s="29" t="n">
-        <v>250</v>
-      </c>
-      <c r="C27" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="27" t="n">
-        <f aca="false">B27*C27</f>
-        <v>250</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>168</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="B28" s="29" t="n">
-        <v>32000</v>
-      </c>
-      <c r="C28" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="27" t="n">
-        <f aca="false">B28*C28</f>
-        <v>32000</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="A28" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="9" t="n">
+        <f aca="false">SUM(D21:D27)</f>
+        <v>52950</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="B29" s="29" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C29" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="27" t="n">
-        <f aca="false">B29*C29</f>
-        <v>15000</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="F29" s="3"/>
+      <c r="A29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="B30" s="29" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C30" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="27" t="n">
-        <f aca="false">B30*C30</f>
-        <v>8000</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="F30" s="3"/>
+      <c r="A30" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="B31" s="29" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C31" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="27" t="n">
-        <f aca="false">B31*C31</f>
-        <v>3000</v>
-      </c>
-      <c r="E31" s="13"/>
+      <c r="A31" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="24" t="n">
+        <f aca="false">Wyjaśnienia!$B$18+Wyjaśnienia!$B$21+Wyjaśnienia!$B$22+Wyjaśnienia!$B$19*Wyjaśnienia!$B$20</f>
+        <v>395000</v>
+      </c>
+      <c r="E31" s="3"/>
       <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="B32" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="27" t="n">
-        <f aca="false">B32*C32</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>178</v>
-      </c>
+      <c r="A32" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="8" t="n">
+        <f aca="false">E17</f>
+        <v>71940</v>
+      </c>
+      <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>179</v>
+      <c r="A33" s="21" t="s">
+        <v>172</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="9" t="n">
-        <f aca="false">SUM(D22:D32)</f>
-        <v>74450</v>
+      <c r="D33" s="8" t="n">
+        <f aca="false">D28</f>
+        <v>52950</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -3367,31 +3306,40 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
+      <c r="A34" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <f aca="false">(D32+D33)*Wyjaśnienia!$B$30</f>
+        <v>14986.8</v>
+      </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="s">
-        <v>180</v>
-      </c>
+      <c r="A35" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="9" t="n">
+        <f aca="false">SUM(D31:D34)</f>
+        <v>534876.8</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24" t="s">
-        <v>181</v>
+      <c r="A36" s="21" t="s">
+        <v>175</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="27" t="n">
-        <f aca="false">Wyjaśnienia!$B$17+Wyjaśnienia!$B$20+Wyjaśnienia!$B$21+Wyjaśnienia!$B$18*Wyjaśnienia!$B$19</f>
-        <v>395000</v>
+      <c r="D36" s="8" t="n">
+        <f aca="false">D35*Wyjaśnienia!$B$33</f>
+        <v>123021.664</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -3399,95 +3347,25 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="24" t="s">
-        <v>182</v>
+      <c r="A37" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="8" t="n">
-        <f aca="false">E18</f>
-        <v>81840</v>
+      <c r="D37" s="27" t="n">
+        <f aca="false">D35+D36</f>
+        <v>657898.464</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="8" t="n">
-        <f aca="false">D33</f>
-        <v>74450</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="8" t="n">
-        <f aca="false">(D37+D38)*Wyjaśnienia!$B$29</f>
-        <v>18754.8</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="9" t="n">
-        <f aca="false">SUM(D36:D39)</f>
-        <v>570044.8</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="8" t="n">
-        <f aca="false">D40*Wyjaśnienia!$B$32</f>
-        <v>131110.304</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="31" t="n">
-        <f aca="false">D40+D41</f>
-        <v>701155.104</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3557,8 +3435,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3600,7 +3478,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3612,7 +3490,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -3634,7 +3512,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -3646,221 +3524,221 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="25" t="n">
+      <c r="A7" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <v>45</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="26" t="n">
-        <f aca="false">B7+C7*Wyjaśnienia!$B$16/60</f>
+      <c r="D7" s="23" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$17/60</f>
         <v>45</v>
       </c>
-      <c r="E7" s="27" t="n">
-        <f aca="false">D7*Wyjaśnienia!$B$15</f>
+      <c r="E7" s="24" t="n">
+        <f aca="false">D7*Wyjaśnienia!$B$16</f>
         <v>9900</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>190</v>
+      <c r="F7" s="15" t="s">
+        <v>179</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="25" t="n">
+      <c r="A8" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="26" t="n">
-        <f aca="false">B8+C8*Wyjaśnienia!$B$16/60</f>
+      <c r="D8" s="23" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$17/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="27" t="n">
-        <f aca="false">D8*Wyjaśnienia!$B$15</f>
+      <c r="E8" s="24" t="n">
+        <f aca="false">D8*Wyjaśnienia!$B$16</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>192</v>
+      <c r="F8" s="15" t="s">
+        <v>181</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="25" t="n">
+      <c r="A9" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="26" t="n">
-        <f aca="false">B9+C9*Wyjaśnienia!$B$16/60</f>
+      <c r="D9" s="23" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$17/60</f>
         <v>10</v>
       </c>
-      <c r="E9" s="27" t="n">
-        <f aca="false">D9*Wyjaśnienia!$B$15</f>
+      <c r="E9" s="24" t="n">
+        <f aca="false">D9*Wyjaśnienia!$B$16</f>
         <v>2200</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>194</v>
+      <c r="F9" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" s="25" t="n">
+      <c r="A10" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="26" t="n">
-        <f aca="false">B10+C10*Wyjaśnienia!$B$16/60</f>
+      <c r="D10" s="23" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$17/60</f>
         <v>50</v>
       </c>
-      <c r="E10" s="27" t="n">
-        <f aca="false">D10*Wyjaśnienia!$B$15</f>
+      <c r="E10" s="24" t="n">
+        <f aca="false">D10*Wyjaśnienia!$B$16</f>
         <v>11000</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>196</v>
+      <c r="F10" s="15" t="s">
+        <v>185</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="B11" s="25" t="n">
+      <c r="A11" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="26" t="n">
-        <f aca="false">B11+C11*Wyjaśnienia!$B$16/60</f>
+      <c r="D11" s="23" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$17/60</f>
         <v>25</v>
       </c>
-      <c r="E11" s="27" t="n">
-        <f aca="false">D11*Wyjaśnienia!$B$15</f>
+      <c r="E11" s="24" t="n">
+        <f aca="false">D11*Wyjaśnienia!$B$16</f>
         <v>5500</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>198</v>
+      <c r="F11" s="15" t="s">
+        <v>187</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="B12" s="25" t="n">
+      <c r="A12" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" s="22" t="n">
         <v>160</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="26" t="n">
-        <f aca="false">B12+C12*Wyjaśnienia!$B$16/60</f>
+      <c r="D12" s="23" t="n">
+        <f aca="false">B12+C12*Wyjaśnienia!$B$17/60</f>
         <v>160</v>
       </c>
-      <c r="E12" s="27" t="n">
-        <f aca="false">D12*Wyjaśnienia!$B$15</f>
+      <c r="E12" s="24" t="n">
+        <f aca="false">D12*Wyjaśnienia!$B$16</f>
         <v>35200</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>200</v>
+      <c r="F12" s="15" t="s">
+        <v>189</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="B13" s="25" t="n">
+      <c r="A13" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="26" t="n">
-        <f aca="false">B13+C13*Wyjaśnienia!$B$16/60</f>
+      <c r="D13" s="23" t="n">
+        <f aca="false">B13+C13*Wyjaśnienia!$B$17/60</f>
         <v>50</v>
       </c>
-      <c r="E13" s="27" t="n">
-        <f aca="false">D13*Wyjaśnienia!$B$15</f>
+      <c r="E13" s="24" t="n">
+        <f aca="false">D13*Wyjaśnienia!$B$16</f>
         <v>11000</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>202</v>
+      <c r="F13" s="15" t="s">
+        <v>191</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B14" s="25" t="n">
+      <c r="A14" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14" s="22" t="n">
         <v>72</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="26" t="n">
-        <f aca="false">B14+C14*Wyjaśnienia!$B$16/60</f>
+      <c r="D14" s="23" t="n">
+        <f aca="false">B14+C14*Wyjaśnienia!$B$17/60</f>
         <v>72</v>
       </c>
-      <c r="E14" s="27" t="n">
-        <f aca="false">D14*Wyjaśnienia!$B$15</f>
+      <c r="E14" s="24" t="n">
+        <f aca="false">D14*Wyjaśnienia!$B$16</f>
         <v>15840</v>
       </c>
-      <c r="F14" s="13"/>
+      <c r="F14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="25" t="n">
         <f aca="false">SUM(D7:D14)</f>
         <v>452</v>
       </c>
@@ -3884,7 +3762,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -3896,283 +3774,283 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="B19" s="29" t="n">
+      <c r="A19" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B19" s="26" t="n">
         <v>3000</v>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D19" s="24" t="n">
         <f aca="false">B19*C19</f>
         <v>3000</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>205</v>
+      <c r="E19" s="15" t="s">
+        <v>194</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="B20" s="29" t="n">
+      <c r="A20" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="B20" s="26" t="n">
         <v>6000</v>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="24" t="n">
         <f aca="false">B20*C20</f>
         <v>6000</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>207</v>
+      <c r="E20" s="15" t="s">
+        <v>196</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="B21" s="29" t="n">
+      <c r="A21" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" s="26" t="n">
         <v>10000</v>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="27" t="n">
+      <c r="D21" s="24" t="n">
         <f aca="false">B21*C21</f>
         <v>10000</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>210</v>
+      <c r="E21" s="15" t="s">
+        <v>199</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="B22" s="29" t="n">
+      <c r="A22" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="26" t="n">
         <v>40000</v>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="27" t="n">
+      <c r="D22" s="24" t="n">
         <f aca="false">B22*C22</f>
         <v>40000</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>212</v>
+      <c r="E22" s="15" t="s">
+        <v>201</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="B23" s="29" t="n">
+      <c r="A23" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="B23" s="26" t="n">
         <v>4000</v>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="27" t="n">
+      <c r="D23" s="24" t="n">
         <f aca="false">B23*C23</f>
         <v>4000</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>214</v>
+      <c r="E23" s="15" t="s">
+        <v>203</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="B24" s="29" t="n">
+      <c r="A24" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B24" s="26" t="n">
         <v>3000</v>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="27" t="n">
+      <c r="D24" s="24" t="n">
         <f aca="false">B24*C24</f>
         <v>3000</v>
       </c>
-      <c r="E24" s="13" t="s">
-        <v>216</v>
+      <c r="E24" s="15" t="s">
+        <v>205</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="B25" s="29" t="n">
+      <c r="A25" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="B25" s="26" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="25" t="n">
+      <c r="C25" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="27" t="n">
+      <c r="D25" s="24" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
-      <c r="E25" s="13" t="s">
-        <v>218</v>
+      <c r="E25" s="15" t="s">
+        <v>207</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="B26" s="29" t="n">
+      <c r="A26" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B26" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="27" t="n">
+      <c r="D26" s="24" t="n">
         <f aca="false">B26*C26</f>
         <v>0</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>220</v>
+      <c r="E26" s="15" t="s">
+        <v>209</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="B27" s="29" t="n">
+      <c r="A27" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="26" t="n">
         <v>15000</v>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="27" t="n">
+      <c r="D27" s="24" t="n">
         <f aca="false">B27*C27</f>
         <v>15000</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>222</v>
+      <c r="E27" s="15" t="s">
+        <v>211</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="B28" s="29" t="n">
+      <c r="A28" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" s="26" t="n">
         <v>6000</v>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="27" t="n">
+      <c r="D28" s="24" t="n">
         <f aca="false">B28*C28</f>
         <v>6000</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>224</v>
+      <c r="E28" s="15" t="s">
+        <v>213</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="B29" s="29" t="n">
+      <c r="A29" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="B29" s="26" t="n">
         <v>30000</v>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C29" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="27" t="n">
+      <c r="D29" s="24" t="n">
         <f aca="false">B29*C29</f>
         <v>30000</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>226</v>
+      <c r="E29" s="15" t="s">
+        <v>215</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="B30" s="20" t="n">
+      <c r="A30" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="B30" s="18" t="n">
         <v>4500</v>
       </c>
-      <c r="C30" s="33" t="n">
+      <c r="C30" s="29" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">B30*C30</f>
         <v>4500</v>
       </c>
-      <c r="F30" s="32" t="s">
-        <v>228</v>
+      <c r="F30" s="28" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="B31" s="20" t="n">
+      <c r="A31" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="B31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="33" t="n">
+      <c r="C31" s="29" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="8" t="n">
@@ -4180,13 +4058,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="F31" s="32"/>
+        <v>219</v>
+      </c>
+      <c r="F31" s="28"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -4211,7 +4089,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -4222,8 +4100,8 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="24" t="s">
-        <v>182</v>
+      <c r="A35" s="21" t="s">
+        <v>171</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -4237,8 +4115,8 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24" t="s">
-        <v>183</v>
+      <c r="A36" s="21" t="s">
+        <v>172</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -4252,13 +4130,13 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="24" t="s">
-        <v>231</v>
+      <c r="A37" s="21" t="s">
+        <v>220</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="8" t="n">
-        <f aca="false">(D35+D36)*Wyjaśnienia!$B$30</f>
+        <f aca="false">(D35+D36)*Wyjaśnienia!$B$31</f>
         <v>67482</v>
       </c>
       <c r="E37" s="3"/>
@@ -4268,7 +4146,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -4282,13 +4160,13 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24" t="s">
-        <v>186</v>
+      <c r="A39" s="21" t="s">
+        <v>175</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="8" t="n">
-        <f aca="false">D38*Wyjaśnienia!$B$32</f>
+        <f aca="false">D38*Wyjaśnienia!$B$33</f>
         <v>67257.06</v>
       </c>
       <c r="E39" s="3"/>
@@ -4298,11 +4176,11 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="31" t="n">
+      <c r="D40" s="27" t="n">
         <f aca="false">D38+D39</f>
         <v>359679.06</v>
       </c>
@@ -4426,7 +4304,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4438,7 +4316,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -4460,7 +4338,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -4472,145 +4350,145 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="B7" s="25" t="n">
+      <c r="A7" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="26" t="n">
-        <f aca="false">B7+C7*Wyjaśnienia!$B$22/60</f>
+      <c r="D7" s="23" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$23/60</f>
         <v>25</v>
       </c>
-      <c r="E7" s="27" t="n">
-        <f aca="false">D7*Wyjaśnienia!$B$15</f>
+      <c r="E7" s="24" t="n">
+        <f aca="false">D7*Wyjaśnienia!$B$16</f>
         <v>5500</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>234</v>
+      <c r="F7" s="15" t="s">
+        <v>223</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="B8" s="25" t="n">
+      <c r="A8" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26" t="n">
-        <f aca="false">B8+C8*Wyjaśnienia!$B$22/60</f>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$23/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="27" t="n">
-        <f aca="false">D8*Wyjaśnienia!$B$15</f>
+      <c r="E8" s="24" t="n">
+        <f aca="false">D8*Wyjaśnienia!$B$16</f>
         <v>8800</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>236</v>
+      <c r="F8" s="15" t="s">
+        <v>225</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="B9" s="25" t="n">
+      <c r="A9" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26" t="n">
-        <f aca="false">B9+C9*Wyjaśnienia!$B$22/60</f>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$23/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="27" t="n">
-        <f aca="false">D9*Wyjaśnienia!$B$15</f>
+      <c r="E9" s="24" t="n">
+        <f aca="false">D9*Wyjaśnienia!$B$16</f>
         <v>6600</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>238</v>
+      <c r="F9" s="15" t="s">
+        <v>227</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="B10" s="25" t="n">
+      <c r="A10" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26" t="n">
-        <f aca="false">B10+C10*Wyjaśnienia!$B$22/60</f>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$23/60</f>
         <v>20</v>
       </c>
-      <c r="E10" s="27" t="n">
-        <f aca="false">D10*Wyjaśnienia!$B$15</f>
+      <c r="E10" s="24" t="n">
+        <f aca="false">D10*Wyjaśnienia!$B$16</f>
         <v>4400</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>240</v>
+      <c r="F10" s="15" t="s">
+        <v>229</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="B11" s="25" t="n">
+      <c r="A11" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B11" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26" t="n">
-        <f aca="false">B11+C11*Wyjaśnienia!$B$22/60</f>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$23/60</f>
         <v>50</v>
       </c>
-      <c r="E11" s="27" t="n">
-        <f aca="false">D11*Wyjaśnienia!$B$15</f>
+      <c r="E11" s="24" t="n">
+        <f aca="false">D11*Wyjaśnienia!$B$16</f>
         <v>11000</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>242</v>
+      <c r="F11" s="15" t="s">
+        <v>231</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="25" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>165</v>
       </c>
@@ -4619,7 +4497,7 @@
         <v>36300</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -4636,7 +4514,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -4648,185 +4526,185 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="B16" s="27" t="n">
-        <f aca="false">Wyjaśnienia!$B$23</f>
+      <c r="A16" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <f aca="false">Wyjaśnienia!$B$24</f>
         <v>35000</v>
       </c>
-      <c r="C16" s="25" t="n">
+      <c r="C16" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="24" t="n">
         <f aca="false">B16*C16</f>
         <v>35000</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>245</v>
+      <c r="E16" s="15" t="s">
+        <v>234</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="B17" s="27" t="n">
-        <f aca="false">Wyjaśnienia!$B$24</f>
+      <c r="A17" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <f aca="false">Wyjaśnienia!$B$25</f>
         <v>4000</v>
       </c>
-      <c r="C17" s="25" t="n">
+      <c r="C17" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="27" t="n">
+      <c r="D17" s="24" t="n">
         <f aca="false">B17*C17</f>
         <v>4000</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>247</v>
+      <c r="E17" s="15" t="s">
+        <v>236</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="B18" s="27" t="n">
-        <f aca="false">Wyjaśnienia!$B$25</f>
+      <c r="A18" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <f aca="false">Wyjaśnienia!$B$26</f>
         <v>7500</v>
       </c>
-      <c r="C18" s="26" t="n">
-        <f aca="false">Wyjaśnienia!$B$26</f>
+      <c r="C18" s="23" t="n">
+        <f aca="false">Wyjaśnienia!$B$27</f>
         <v>10</v>
       </c>
-      <c r="D18" s="27" t="n">
+      <c r="D18" s="24" t="n">
         <f aca="false">B18*C18</f>
         <v>75000</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>249</v>
+      <c r="E18" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="27" t="n">
-        <f aca="false">Wyjaśnienia!$B$27</f>
+      <c r="A19" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <f aca="false">Wyjaśnienia!$B$28</f>
         <v>80000</v>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D19" s="24" t="n">
         <f aca="false">B19*C19</f>
         <v>80000</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>250</v>
+      <c r="E19" s="15" t="s">
+        <v>239</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="B20" s="27" t="n">
-        <f aca="false">Wyjaśnienia!$B$28</f>
+      <c r="A20" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <f aca="false">Wyjaśnienia!$B$29</f>
         <v>1200</v>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="24" t="n">
         <f aca="false">B20*C20</f>
         <v>1200</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>252</v>
+      <c r="E20" s="15" t="s">
+        <v>241</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="B21" s="29" t="n">
+      <c r="A21" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="B21" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="27" t="n">
+      <c r="D21" s="24" t="n">
         <f aca="false">B21*C21</f>
         <v>0</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>254</v>
+      <c r="E21" s="15" t="s">
+        <v>243</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="B22" s="29" t="n">
+      <c r="A22" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="B22" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="27" t="n">
+      <c r="D22" s="24" t="n">
         <f aca="false">B22*C22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>256</v>
+      <c r="E22" s="15" t="s">
+        <v>245</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="B23" s="20" t="n">
+      <c r="A23" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="B23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="33" t="n">
+      <c r="C23" s="29" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -4834,20 +4712,20 @@
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>259</v>
+        <v>247</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="B24" s="20" t="n">
+      <c r="A24" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="B24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="33" t="n">
+      <c r="C24" s="29" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -4855,17 +4733,17 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="F24" s="32"/>
+        <v>250</v>
+      </c>
+      <c r="F24" s="28"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="28" t="n">
+      <c r="D25" s="25" t="n">
         <f aca="false">SUM(D16:D24)</f>
         <v>195200</v>
       </c>
@@ -4886,7 +4764,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -4897,13 +4775,13 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
-        <v>181</v>
+      <c r="A28" s="21" t="s">
+        <v>170</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="27" t="n">
-        <f aca="false">Wyjaśnienia!$B$23+Wyjaśnienia!$B$24</f>
+      <c r="D28" s="24" t="n">
+        <f aca="false">Wyjaśnienia!$B$24+Wyjaśnienia!$B$25</f>
         <v>39000</v>
       </c>
       <c r="E28" s="3"/>
@@ -4912,8 +4790,8 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="s">
-        <v>182</v>
+      <c r="A29" s="21" t="s">
+        <v>171</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -4927,8 +4805,8 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24" t="s">
-        <v>262</v>
+      <c r="A30" s="21" t="s">
+        <v>251</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -4942,13 +4820,13 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24" t="s">
-        <v>184</v>
+      <c r="A31" s="21" t="s">
+        <v>173</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="8" t="n">
-        <f aca="false">(D29+D30)*Wyjaśnienia!$B$31</f>
+        <f aca="false">(D29+D30)*Wyjaśnienia!$B$32</f>
         <v>23100</v>
       </c>
       <c r="E31" s="3"/>
@@ -4958,7 +4836,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -4972,13 +4850,13 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24" t="s">
-        <v>186</v>
+      <c r="A33" s="21" t="s">
+        <v>175</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="8" t="n">
-        <f aca="false">D32*Wyjaśnienia!$B$32</f>
+        <f aca="false">D32*Wyjaśnienia!$B$33</f>
         <v>58558</v>
       </c>
       <c r="E33" s="3"/>
@@ -4988,11 +4866,11 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="31" t="n">
+      <c r="D34" s="27" t="n">
         <f aca="false">D32+D33</f>
         <v>313158</v>
       </c>
@@ -5109,18 +4987,18 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="30" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -5130,7 +5008,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -5139,182 +5017,182 @@
       <c r="F3" s="30"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
+      <c r="A5" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="C6" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B7" s="22" t="n">
+        <v>253</v>
+      </c>
+      <c r="B7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="35" t="n">
-        <f aca="false">B7+C7*Wyjaśnienia!$B$52/60</f>
+      <c r="D7" s="32" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$53/60</f>
         <v>20</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">D7*Wyjaśnienia!$B$15</f>
+        <f aca="false">D7*Wyjaśnienia!$B$16</f>
         <v>4400</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B8" s="22" t="n">
+        <v>255</v>
+      </c>
+      <c r="B8" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35" t="n">
-        <f aca="false">B8+C8*Wyjaśnienia!$B$52/60</f>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$53/60</f>
         <v>30</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">D8*Wyjaśnienia!$B$15</f>
+        <f aca="false">D8*Wyjaśnienia!$B$16</f>
         <v>6600</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B9" s="22" t="n">
+        <v>228</v>
+      </c>
+      <c r="B9" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35" t="n">
-        <f aca="false">B9+C9*Wyjaśnienia!$B$52/60</f>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$53/60</f>
         <v>20</v>
       </c>
       <c r="E9" s="8" t="n">
-        <f aca="false">D9*Wyjaśnienia!$B$15</f>
+        <f aca="false">D9*Wyjaśnienia!$B$16</f>
         <v>4400</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B10" s="22" t="n">
+        <v>258</v>
+      </c>
+      <c r="B10" s="20" t="n">
         <v>35</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35" t="n">
-        <f aca="false">B10+C10*Wyjaśnienia!$B$52/60</f>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$53/60</f>
         <v>35</v>
       </c>
       <c r="E10" s="8" t="n">
-        <f aca="false">D10*Wyjaśnienia!$B$15</f>
+        <f aca="false">D10*Wyjaśnienia!$B$16</f>
         <v>7700</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B11" s="22" t="n">
+        <v>260</v>
+      </c>
+      <c r="B11" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35" t="n">
-        <f aca="false">B11+C11*Wyjaśnienia!$B$52/60</f>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$53/60</f>
         <v>15</v>
       </c>
       <c r="E11" s="8" t="n">
-        <f aca="false">D11*Wyjaśnienia!$B$15</f>
+        <f aca="false">D11*Wyjaśnienia!$B$16</f>
         <v>3300</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B12" s="22" t="n">
+        <v>262</v>
+      </c>
+      <c r="B12" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35" t="n">
-        <f aca="false">B12+C12*Wyjaśnienia!$B$52/60</f>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32" t="n">
+        <f aca="false">B12+C12*Wyjaśnienia!$B$53/60</f>
         <v>50</v>
       </c>
       <c r="E12" s="8" t="n">
-        <f aca="false">D12*Wyjaśnienia!$B$15</f>
+        <f aca="false">D12*Wyjaśnienia!$B$16</f>
         <v>11000</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B13" s="22" t="n">
+        <v>264</v>
+      </c>
+      <c r="B13" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35" t="n">
-        <f aca="false">B13+C13*Wyjaśnienia!$B$52/60</f>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32" t="n">
+        <f aca="false">B13+C13*Wyjaśnienia!$B$53/60</f>
         <v>20</v>
       </c>
       <c r="E13" s="8" t="n">
-        <f aca="false">D13*Wyjaśnienia!$B$15</f>
+        <f aca="false">D13*Wyjaśnienia!$B$16</f>
         <v>4400</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="D14" s="36" t="n">
+        <v>150</v>
+      </c>
+      <c r="D14" s="33" t="n">
         <f aca="false">SUM(D7:D13)</f>
         <v>190</v>
       </c>
@@ -5323,45 +5201,45 @@
         <v>41800</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
+      <c r="A16" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D17" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="B18" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$53</f>
+        <f aca="false">Wyjaśnienia!$B$54</f>
         <v>90000</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="8" t="n">
@@ -5369,18 +5247,18 @@
         <v>90000</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="B19" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$54</f>
+        <f aca="false">Wyjaśnienia!$B$55</f>
         <v>3000</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="8" t="n">
@@ -5388,18 +5266,18 @@
         <v>3000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B20" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$55</f>
+        <f aca="false">Wyjaśnienia!$B$56</f>
         <v>1200</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="8" t="n">
@@ -5407,17 +5285,17 @@
         <v>1200</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B21" s="20" t="n">
+        <v>270</v>
+      </c>
+      <c r="B21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="8" t="n">
@@ -5425,19 +5303,19 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B22" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$60*2</f>
+        <f aca="false">Wyjaśnienia!$B$61*2</f>
         <v>800</v>
       </c>
-      <c r="C22" s="35" t="n">
-        <f aca="false">Wyjaśnienia!$B$59</f>
+      <c r="C22" s="32" t="n">
+        <f aca="false">Wyjaśnienia!$B$60</f>
         <v>10</v>
       </c>
       <c r="D22" s="8" t="n">
@@ -5445,18 +5323,18 @@
         <v>8000</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$61</f>
+        <f aca="false">Wyjaśnienia!$B$62</f>
         <v>3000</v>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -5464,17 +5342,17 @@
         <v>3000</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B24" s="20" t="n">
+        <v>275</v>
+      </c>
+      <c r="B24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="35" t="n">
+      <c r="C24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -5482,17 +5360,17 @@
         <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B25" s="20" t="n">
+        <v>277</v>
+      </c>
+      <c r="B25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="8" t="n">
@@ -5500,17 +5378,17 @@
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B26" s="20" t="n">
+        <v>279</v>
+      </c>
+      <c r="B26" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="35" t="n">
+      <c r="C26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="8" t="n">
@@ -5518,12 +5396,12 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="D27" s="11" t="n">
         <f aca="false">SUM(D18:D26)</f>
@@ -5531,27 +5409,27 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
+      <c r="A29" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="D30" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$53+Wyjaśnienia!$B$54</f>
+        <f aca="false">Wyjaśnienia!$B$54+Wyjaśnienia!$B$55</f>
         <v>93000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D31" s="8" t="n">
         <f aca="false">E14</f>
@@ -5560,7 +5438,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="D32" s="8" t="n">
         <f aca="false">D27-D30</f>
@@ -5569,16 +5447,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D33" s="8" t="n">
-        <f aca="false">(D31+D32)*Wyjaśnienia!$B$62</f>
+        <f aca="false">(D31+D32)*Wyjaśnienia!$B$63</f>
         <v>6480</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D34" s="11" t="n">
         <f aca="false">SUM(D30:D33)</f>
@@ -5587,16 +5465,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D35" s="8" t="n">
-        <f aca="false">D34*Wyjaśnienia!$B$32</f>
+        <f aca="false">D34*Wyjaśnienia!$B$33</f>
         <v>35300.4</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D36" s="11" t="n">
         <f aca="false">D34+D35</f>
@@ -5639,669 +5517,669 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
-        <v>292</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="A2" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="38" t="s">
-        <v>293</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
+      <c r="A3" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
+      <c r="A5" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="B6" s="41" t="s">
-        <v>295</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>130</v>
+      <c r="A6" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32" t="s">
-        <v>296</v>
-      </c>
-      <c r="B7" s="42" t="n">
-        <f aca="false">Wyjaśnienia!$B$16</f>
+      <c r="A7" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="39" t="n">
+        <f aca="false">Wyjaśnienia!$B$17</f>
         <v>150</v>
       </c>
-      <c r="F7" s="32" t="s">
-        <v>297</v>
+      <c r="F7" s="28" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="s">
-        <v>298</v>
-      </c>
-      <c r="B8" s="42" t="n">
-        <f aca="false">Wyjaśnienia!$B$45</f>
+      <c r="A8" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8" s="39" t="n">
+        <f aca="false">Wyjaśnienia!$B$46</f>
         <v>2</v>
       </c>
-      <c r="F8" s="32" t="s">
-        <v>299</v>
+      <c r="F8" s="28" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="40" t="s">
-        <v>300</v>
-      </c>
-      <c r="B9" s="43" t="n">
+      <c r="A9" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="B9" s="40" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
-      <c r="F9" s="32" t="s">
-        <v>301</v>
+      <c r="F9" s="28" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32" t="s">
-        <v>302</v>
-      </c>
-      <c r="B10" s="42" t="n">
-        <f aca="false">Wyjaśnienia!$B$65</f>
+      <c r="A10" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" s="39" t="n">
+        <f aca="false">Wyjaśnienia!$B$66</f>
         <v>150</v>
       </c>
-      <c r="F10" s="32" t="s">
-        <v>303</v>
+      <c r="F10" s="28" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="B11" s="42" t="n">
-        <f aca="false">Wyjaśnienia!$B$74</f>
+      <c r="A11" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="B11" s="39" t="n">
+        <f aca="false">Wyjaśnienia!$B$75</f>
         <v>2</v>
       </c>
-      <c r="F11" s="32" t="s">
-        <v>305</v>
+      <c r="F11" s="28" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="40" t="s">
-        <v>306</v>
-      </c>
-      <c r="B12" s="43" t="n">
+      <c r="A12" s="37" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12" s="40" t="n">
         <f aca="false">B10*B11</f>
         <v>300</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>307</v>
+      <c r="F12" s="28" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="39" t="s">
-        <v>308</v>
-      </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
+      <c r="A14" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="B15" s="41" t="s">
-        <v>309</v>
-      </c>
-      <c r="C15" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="D15" s="41" t="s">
+      <c r="A15" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>298</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="F15" s="40" t="s">
-        <v>130</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32" t="s">
-        <v>310</v>
-      </c>
-      <c r="B16" s="44" t="n">
-        <f aca="false">Wyjaśnienia!$B$47</f>
+      <c r="A16" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="B16" s="41" t="n">
+        <f aca="false">Wyjaśnienia!$B$48</f>
         <v>2500</v>
       </c>
-      <c r="C16" s="42" t="n">
-        <f aca="false">Wyjaśnienia!$B$48</f>
+      <c r="C16" s="39" t="n">
+        <f aca="false">Wyjaśnienia!$B$49</f>
         <v>15</v>
       </c>
-      <c r="D16" s="44" t="n">
+      <c r="D16" s="41" t="n">
         <f aca="false">B16*C16</f>
         <v>37500</v>
       </c>
-      <c r="F16" s="32" t="s">
-        <v>311</v>
+      <c r="F16" s="28" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="32" t="s">
-        <v>312</v>
-      </c>
-      <c r="B17" s="44" t="n">
-        <f aca="false">Wyjaśnienia!$B$46</f>
+      <c r="A17" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="B17" s="41" t="n">
+        <f aca="false">Wyjaśnienia!$B$47</f>
         <v>500</v>
       </c>
-      <c r="C17" s="42" t="n">
+      <c r="C17" s="39" t="n">
         <f aca="false">ROUNDUP(B9/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D17" s="44" t="n">
+      <c r="D17" s="41" t="n">
         <f aca="false">B17*C17</f>
         <v>1500</v>
       </c>
-      <c r="F17" s="32" t="s">
-        <v>313</v>
+      <c r="F17" s="28" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="32" t="s">
-        <v>314</v>
-      </c>
-      <c r="B18" s="44" t="n">
-        <f aca="false">Wyjaśnienia!$B$75</f>
+      <c r="A18" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="B18" s="41" t="n">
+        <f aca="false">Wyjaśnienia!$B$76</f>
         <v>300</v>
       </c>
-      <c r="C18" s="42" t="n">
+      <c r="C18" s="39" t="n">
         <f aca="false">B12</f>
         <v>300</v>
       </c>
-      <c r="D18" s="44" t="n">
+      <c r="D18" s="41" t="n">
         <f aca="false">B18*C18</f>
         <v>90000</v>
       </c>
-      <c r="F18" s="32" t="s">
-        <v>315</v>
+      <c r="F18" s="28" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="40" t="s">
-        <v>316</v>
-      </c>
-      <c r="D19" s="45" t="n">
+      <c r="A19" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="D19" s="42" t="n">
         <f aca="false">SUM(D16:D18)</f>
         <v>129000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
+      <c r="A21" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="D22" s="41" t="s">
+      <c r="A22" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="F22" s="40" t="s">
-        <v>130</v>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="B23" s="44" t="n">
+      <c r="A23" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="B23" s="41" t="n">
         <v>2000</v>
       </c>
-      <c r="C23" s="42" t="n">
+      <c r="C23" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="44" t="n">
+      <c r="D23" s="41" t="n">
         <f aca="false">B23*C23</f>
         <v>2000</v>
       </c>
-      <c r="F23" s="32" t="s">
-        <v>318</v>
+      <c r="F23" s="28" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32" t="s">
-        <v>319</v>
-      </c>
-      <c r="B24" s="44" t="n">
+      <c r="A24" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="B24" s="41" t="n">
         <v>3000</v>
       </c>
-      <c r="C24" s="42" t="n">
+      <c r="C24" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="44" t="n">
+      <c r="D24" s="41" t="n">
         <f aca="false">B24*C24</f>
         <v>3000</v>
       </c>
-      <c r="F24" s="32" t="s">
-        <v>320</v>
+      <c r="F24" s="28" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="B25" s="44" t="n">
+      <c r="A25" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="B25" s="41" t="n">
         <v>5000</v>
       </c>
-      <c r="C25" s="42" t="n">
+      <c r="C25" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="44" t="n">
+      <c r="D25" s="41" t="n">
         <f aca="false">B25*C25</f>
         <v>5000</v>
       </c>
-      <c r="F25" s="32" t="s">
-        <v>322</v>
+      <c r="F25" s="28" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="B26" s="44" t="n">
+      <c r="A26" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="B26" s="41" t="n">
         <v>4000</v>
       </c>
-      <c r="C26" s="42" t="n">
+      <c r="C26" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="44" t="n">
+      <c r="D26" s="41" t="n">
         <f aca="false">B26*C26</f>
         <v>4000</v>
       </c>
-      <c r="F26" s="32" t="s">
-        <v>324</v>
+      <c r="F26" s="28" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="D27" s="45" t="n">
+      <c r="A27" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="42" t="n">
         <f aca="false">SUM(D23:D26)</f>
         <v>14000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
+      <c r="A29" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="s">
-        <v>325</v>
-      </c>
-      <c r="D30" s="44" t="n">
+      <c r="A30" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="D30" s="41" t="n">
         <f aca="false">D19</f>
         <v>129000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="44" t="n">
+      <c r="A31" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" s="41" t="n">
         <f aca="false">D27</f>
         <v>14000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="D32" s="44" t="n">
-        <f aca="false">(D30+D31)*Wyjaśnienia!$B$29</f>
+      <c r="A32" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="D32" s="41" t="n">
+        <f aca="false">(D30+D31)*Wyjaśnienia!$B$30</f>
         <v>17160</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="D33" s="45" t="n">
+      <c r="A33" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" s="42" t="n">
         <f aca="false">SUM(D30:D32)</f>
         <v>160160</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="D34" s="44" t="n">
-        <f aca="false">D33*Wyjaśnienia!$B$32</f>
+      <c r="A34" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" s="41" t="n">
+        <f aca="false">D33*Wyjaśnienia!$B$33</f>
         <v>36836.8</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="D35" s="45" t="n">
+      <c r="A35" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="D35" s="42" t="n">
         <f aca="false">D33+D34</f>
         <v>196996.8</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="39" t="s">
-        <v>327</v>
-      </c>
-      <c r="B37" s="39"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
+      <c r="A37" s="36" t="s">
+        <v>316</v>
+      </c>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
     </row>
     <row r="38" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="38" t="s">
-        <v>328</v>
-      </c>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
+      <c r="A38" s="35" t="s">
+        <v>317</v>
+      </c>
+      <c r="B38" s="35"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="41" t="s">
-        <v>329</v>
-      </c>
-      <c r="B39" s="41" t="s">
-        <v>330</v>
-      </c>
-      <c r="C39" s="41" t="s">
-        <v>331</v>
-      </c>
-      <c r="D39" s="41" t="s">
-        <v>332</v>
-      </c>
-      <c r="E39" s="41" t="s">
-        <v>333</v>
+      <c r="A39" s="38" t="s">
+        <v>318</v>
+      </c>
+      <c r="B39" s="38" t="s">
+        <v>319</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="D39" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="E39" s="38" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="42" t="n">
+      <c r="A40" s="39" t="n">
         <v>150</v>
       </c>
-      <c r="B40" s="42" t="n">
-        <f aca="false">A40*Wyjaśnienia!$B$45</f>
+      <c r="B40" s="39" t="n">
+        <f aca="false">A40*Wyjaśnienia!$B$46</f>
         <v>300</v>
       </c>
-      <c r="C40" s="42" t="n">
+      <c r="C40" s="39" t="n">
         <f aca="false">ROUNDUP(B40/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D40" s="44" t="n">
-        <f aca="false">C40*Wyjaśnienia!$B$46</f>
+      <c r="D40" s="41" t="n">
+        <f aca="false">C40*Wyjaśnienia!$B$47</f>
         <v>1500</v>
       </c>
-      <c r="E40" s="42" t="n">
-        <f aca="false">ROUNDUP(B40/Wyjaśnienia!$B$49,0)</f>
-        <v>15</v>
+      <c r="E40" s="39" t="e">
+        <f aca="false">ROUNDUP(B40/Wyjaśnienia!$B$50,0)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="42" t="n">
+      <c r="A41" s="39" t="n">
         <v>1000</v>
       </c>
-      <c r="B41" s="42" t="n">
-        <f aca="false">A41*Wyjaśnienia!$B$45</f>
+      <c r="B41" s="39" t="n">
+        <f aca="false">A41*Wyjaśnienia!$B$46</f>
         <v>2000</v>
       </c>
-      <c r="C41" s="42" t="n">
+      <c r="C41" s="39" t="n">
         <f aca="false">ROUNDUP(B41/100,0)</f>
         <v>20</v>
       </c>
-      <c r="D41" s="44" t="n">
-        <f aca="false">C41*Wyjaśnienia!$B$46</f>
+      <c r="D41" s="41" t="n">
+        <f aca="false">C41*Wyjaśnienia!$B$47</f>
         <v>10000</v>
       </c>
-      <c r="E41" s="42" t="n">
-        <f aca="false">ROUNDUP(B41/Wyjaśnienia!$B$49,0)</f>
-        <v>100</v>
+      <c r="E41" s="39" t="e">
+        <f aca="false">ROUNDUP(B41/Wyjaśnienia!$B$50,0)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="42" t="n">
+      <c r="A42" s="39" t="n">
         <v>10000</v>
       </c>
-      <c r="B42" s="42" t="n">
-        <f aca="false">A42*Wyjaśnienia!$B$45</f>
+      <c r="B42" s="39" t="n">
+        <f aca="false">A42*Wyjaśnienia!$B$46</f>
         <v>20000</v>
       </c>
-      <c r="C42" s="42" t="n">
+      <c r="C42" s="39" t="n">
         <f aca="false">ROUNDUP(B42/100,0)</f>
         <v>200</v>
       </c>
-      <c r="D42" s="44" t="n">
-        <f aca="false">C42*Wyjaśnienia!$B$46</f>
+      <c r="D42" s="41" t="n">
+        <f aca="false">C42*Wyjaśnienia!$B$47</f>
         <v>100000</v>
       </c>
-      <c r="E42" s="42" t="n">
-        <f aca="false">ROUNDUP(B42/Wyjaśnienia!$B$49,0)</f>
-        <v>1000</v>
+      <c r="E42" s="39" t="e">
+        <f aca="false">ROUNDUP(B42/Wyjaśnienia!$B$50,0)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="42" t="n">
+      <c r="A43" s="39" t="n">
         <v>100000</v>
       </c>
-      <c r="B43" s="42" t="n">
-        <f aca="false">A43*Wyjaśnienia!$B$45</f>
+      <c r="B43" s="39" t="n">
+        <f aca="false">A43*Wyjaśnienia!$B$46</f>
         <v>200000</v>
       </c>
-      <c r="C43" s="42" t="n">
+      <c r="C43" s="39" t="n">
         <f aca="false">ROUNDUP(B43/100,0)</f>
         <v>2000</v>
       </c>
-      <c r="D43" s="44" t="n">
-        <f aca="false">C43*Wyjaśnienia!$B$46</f>
+      <c r="D43" s="41" t="n">
+        <f aca="false">C43*Wyjaśnienia!$B$47</f>
         <v>1000000</v>
       </c>
-      <c r="E43" s="42" t="n">
-        <f aca="false">ROUNDUP(B43/Wyjaśnienia!$B$49,0)</f>
-        <v>10000</v>
+      <c r="E43" s="39" t="e">
+        <f aca="false">ROUNDUP(B43/Wyjaśnienia!$B$50,0)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="42" t="n">
+      <c r="A44" s="39" t="n">
         <v>1000000</v>
       </c>
-      <c r="B44" s="42" t="n">
-        <f aca="false">A44*Wyjaśnienia!$B$45</f>
+      <c r="B44" s="39" t="n">
+        <f aca="false">A44*Wyjaśnienia!$B$46</f>
         <v>2000000</v>
       </c>
-      <c r="C44" s="42" t="n">
+      <c r="C44" s="39" t="n">
         <f aca="false">ROUNDUP(B44/100,0)</f>
         <v>20000</v>
       </c>
-      <c r="D44" s="44" t="n">
-        <f aca="false">C44*Wyjaśnienia!$B$46</f>
+      <c r="D44" s="41" t="n">
+        <f aca="false">C44*Wyjaśnienia!$B$47</f>
         <v>10000000</v>
       </c>
-      <c r="E44" s="42" t="n">
-        <f aca="false">ROUNDUP(B44/Wyjaśnienia!$B$49,0)</f>
-        <v>100000</v>
+      <c r="E44" s="39" t="e">
+        <f aca="false">ROUNDUP(B44/Wyjaśnienia!$B$50,0)</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="41" t="s">
-        <v>334</v>
-      </c>
-      <c r="B46" s="41" t="s">
-        <v>335</v>
-      </c>
-      <c r="C46" s="41" t="s">
-        <v>336</v>
-      </c>
-      <c r="D46" s="41" t="s">
-        <v>337</v>
-      </c>
-      <c r="E46" s="41" t="s">
-        <v>338</v>
+      <c r="A46" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="D46" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="E46" s="38" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="42" t="n">
+      <c r="A47" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="B47" s="42" t="n">
-        <f aca="false">A47*Wyjaśnienia!$B$74</f>
+      <c r="B47" s="39" t="n">
+        <f aca="false">A47*Wyjaśnienia!$B$75</f>
         <v>60</v>
       </c>
-      <c r="C47" s="44" t="n">
-        <f aca="false">B47*Wyjaśnienia!$B$75</f>
+      <c r="C47" s="41" t="n">
+        <f aca="false">B47*Wyjaśnienia!$B$76</f>
         <v>18000</v>
       </c>
-      <c r="D47" s="42" t="n">
+      <c r="D47" s="39" t="n">
         <f aca="false">B47*2</f>
         <v>120</v>
       </c>
-      <c r="E47" s="42" t="n">
-        <f aca="false">ROUNDUP(A47/Wyjaśnienia!$B$76,0)</f>
+      <c r="E47" s="39" t="n">
+        <f aca="false">ROUNDUP(A47/Wyjaśnienia!$B$77,0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="42" t="n">
+      <c r="A48" s="39" t="n">
         <v>150</v>
       </c>
-      <c r="B48" s="42" t="n">
-        <f aca="false">A48*Wyjaśnienia!$B$74</f>
+      <c r="B48" s="39" t="n">
+        <f aca="false">A48*Wyjaśnienia!$B$75</f>
         <v>300</v>
       </c>
-      <c r="C48" s="44" t="n">
-        <f aca="false">B48*Wyjaśnienia!$B$75</f>
+      <c r="C48" s="41" t="n">
+        <f aca="false">B48*Wyjaśnienia!$B$76</f>
         <v>90000</v>
       </c>
-      <c r="D48" s="42" t="n">
+      <c r="D48" s="39" t="n">
         <f aca="false">B48*2</f>
         <v>600</v>
       </c>
-      <c r="E48" s="42" t="n">
-        <f aca="false">ROUNDUP(A48/Wyjaśnienia!$B$76,0)</f>
+      <c r="E48" s="39" t="n">
+        <f aca="false">ROUNDUP(A48/Wyjaśnienia!$B$77,0)</f>
         <v>15</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="42" t="n">
+      <c r="A49" s="39" t="n">
         <v>500</v>
       </c>
-      <c r="B49" s="42" t="n">
-        <f aca="false">A49*Wyjaśnienia!$B$74</f>
+      <c r="B49" s="39" t="n">
+        <f aca="false">A49*Wyjaśnienia!$B$75</f>
         <v>1000</v>
       </c>
-      <c r="C49" s="44" t="n">
-        <f aca="false">B49*Wyjaśnienia!$B$75</f>
+      <c r="C49" s="41" t="n">
+        <f aca="false">B49*Wyjaśnienia!$B$76</f>
         <v>300000</v>
       </c>
-      <c r="D49" s="42" t="n">
+      <c r="D49" s="39" t="n">
         <f aca="false">B49*2</f>
         <v>2000</v>
       </c>
-      <c r="E49" s="42" t="n">
-        <f aca="false">ROUNDUP(A49/Wyjaśnienia!$B$76,0)</f>
+      <c r="E49" s="39" t="n">
+        <f aca="false">ROUNDUP(A49/Wyjaśnienia!$B$77,0)</f>
         <v>50</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="42" t="n">
+      <c r="A50" s="39" t="n">
         <v>2000</v>
       </c>
-      <c r="B50" s="42" t="n">
-        <f aca="false">A50*Wyjaśnienia!$B$74</f>
+      <c r="B50" s="39" t="n">
+        <f aca="false">A50*Wyjaśnienia!$B$75</f>
         <v>4000</v>
       </c>
-      <c r="C50" s="44" t="n">
-        <f aca="false">B50*Wyjaśnienia!$B$75</f>
+      <c r="C50" s="41" t="n">
+        <f aca="false">B50*Wyjaśnienia!$B$76</f>
         <v>1200000</v>
       </c>
-      <c r="D50" s="42" t="n">
+      <c r="D50" s="39" t="n">
         <f aca="false">B50*2</f>
         <v>8000</v>
       </c>
-      <c r="E50" s="42" t="n">
-        <f aca="false">ROUNDUP(A50/Wyjaśnienia!$B$76,0)</f>
+      <c r="E50" s="39" t="n">
+        <f aca="false">ROUNDUP(A50/Wyjaśnienia!$B$77,0)</f>
         <v>200</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="42" t="n">
+      <c r="A51" s="39" t="n">
         <v>10000</v>
       </c>
-      <c r="B51" s="42" t="n">
-        <f aca="false">A51*Wyjaśnienia!$B$74</f>
+      <c r="B51" s="39" t="n">
+        <f aca="false">A51*Wyjaśnienia!$B$75</f>
         <v>20000</v>
       </c>
-      <c r="C51" s="44" t="n">
-        <f aca="false">B51*Wyjaśnienia!$B$75</f>
+      <c r="C51" s="41" t="n">
+        <f aca="false">B51*Wyjaśnienia!$B$76</f>
         <v>6000000</v>
       </c>
-      <c r="D51" s="42" t="n">
+      <c r="D51" s="39" t="n">
         <f aca="false">B51*2</f>
         <v>40000</v>
       </c>
-      <c r="E51" s="42" t="n">
-        <f aca="false">ROUNDUP(A51/Wyjaśnienia!$B$76,0)</f>
+      <c r="E51" s="39" t="n">
+        <f aca="false">ROUNDUP(A51/Wyjaśnienia!$B$77,0)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="38" t="s">
-        <v>339</v>
-      </c>
-      <c r="B53" s="38"/>
-      <c r="C53" s="38"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
+      <c r="A53" s="35" t="s">
+        <v>328</v>
+      </c>
+      <c r="B53" s="35"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6343,18 +6221,18 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="30" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -6364,7 +6242,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -6373,204 +6251,204 @@
       <c r="F3" s="30"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
+      <c r="A5" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="C6" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B7" s="22" t="n">
+        <v>331</v>
+      </c>
+      <c r="B7" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="35" t="n">
-        <f aca="false">B7+C7*Wyjaśnienia!$B$65/60</f>
+      <c r="D7" s="32" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$66/60</f>
         <v>30</v>
       </c>
       <c r="E7" s="8" t="n">
-        <f aca="false">D7*Wyjaśnienia!$B$15</f>
+        <f aca="false">D7*Wyjaśnienia!$B$16</f>
         <v>6600</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B8" s="22" t="n">
+        <v>333</v>
+      </c>
+      <c r="B8" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="35" t="n">
-        <f aca="false">B8+C8*Wyjaśnienia!$B$65/60</f>
+      <c r="C8" s="20"/>
+      <c r="D8" s="32" t="n">
+        <f aca="false">B8+C8*Wyjaśnienia!$B$66/60</f>
         <v>25</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">D8*Wyjaśnienia!$B$15</f>
+        <f aca="false">D8*Wyjaśnienia!$B$16</f>
         <v>5500</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B9" s="22" t="n">
+        <v>335</v>
+      </c>
+      <c r="B9" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="35" t="n">
-        <f aca="false">B9+C9*Wyjaśnienia!$B$65/60</f>
+      <c r="C9" s="20"/>
+      <c r="D9" s="32" t="n">
+        <f aca="false">B9+C9*Wyjaśnienia!$B$66/60</f>
         <v>60</v>
       </c>
       <c r="E9" s="8" t="n">
-        <f aca="false">D9*Wyjaśnienia!$B$15</f>
+        <f aca="false">D9*Wyjaśnienia!$B$16</f>
         <v>13200</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B10" s="22" t="n">
+        <v>228</v>
+      </c>
+      <c r="B10" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="35" t="n">
-        <f aca="false">B10+C10*Wyjaśnienia!$B$65/60</f>
+      <c r="C10" s="20"/>
+      <c r="D10" s="32" t="n">
+        <f aca="false">B10+C10*Wyjaśnienia!$B$66/60</f>
         <v>20</v>
       </c>
       <c r="E10" s="8" t="n">
-        <f aca="false">D10*Wyjaśnienia!$B$15</f>
+        <f aca="false">D10*Wyjaśnienia!$B$16</f>
         <v>4400</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B11" s="22" t="n">
+        <v>337</v>
+      </c>
+      <c r="B11" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="35" t="n">
-        <f aca="false">B11+C11*Wyjaśnienia!$B$65/60</f>
+      <c r="C11" s="20"/>
+      <c r="D11" s="32" t="n">
+        <f aca="false">B11+C11*Wyjaśnienia!$B$66/60</f>
         <v>40</v>
       </c>
       <c r="E11" s="8" t="n">
-        <f aca="false">D11*Wyjaśnienia!$B$15</f>
+        <f aca="false">D11*Wyjaśnienia!$B$16</f>
         <v>8800</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B12" s="22" t="n">
+        <v>339</v>
+      </c>
+      <c r="B12" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="35" t="n">
-        <f aca="false">B12+C12*Wyjaśnienia!$B$65/60</f>
+      <c r="C12" s="20"/>
+      <c r="D12" s="32" t="n">
+        <f aca="false">B12+C12*Wyjaśnienia!$B$66/60</f>
         <v>40</v>
       </c>
       <c r="E12" s="8" t="n">
-        <f aca="false">D12*Wyjaśnienia!$B$15</f>
+        <f aca="false">D12*Wyjaśnienia!$B$16</f>
         <v>8800</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B13" s="22" t="n">
+        <v>341</v>
+      </c>
+      <c r="B13" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="35" t="n">
-        <f aca="false">B13+C13*Wyjaśnienia!$B$65/60</f>
+      <c r="C13" s="20"/>
+      <c r="D13" s="32" t="n">
+        <f aca="false">B13+C13*Wyjaśnienia!$B$66/60</f>
         <v>25</v>
       </c>
       <c r="E13" s="8" t="n">
-        <f aca="false">D13*Wyjaśnienia!$B$15</f>
+        <f aca="false">D13*Wyjaśnienia!$B$16</f>
         <v>5500</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B14" s="22" t="n">
+        <v>343</v>
+      </c>
+      <c r="B14" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="35" t="n">
-        <f aca="false">B14+C14*Wyjaśnienia!$B$65/60</f>
+      <c r="C14" s="20"/>
+      <c r="D14" s="32" t="n">
+        <f aca="false">B14+C14*Wyjaśnienia!$B$66/60</f>
         <v>50</v>
       </c>
       <c r="E14" s="8" t="n">
-        <f aca="false">D14*Wyjaśnienia!$B$15</f>
+        <f aca="false">D14*Wyjaśnienia!$B$16</f>
         <v>11000</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="36" t="n">
+        <v>150</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="33" t="n">
         <f aca="false">SUM(D7:D14)</f>
         <v>290</v>
       </c>
@@ -6579,45 +6457,45 @@
         <v>63800</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
+      <c r="A17" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D18" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>129</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B19" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$66</f>
+        <f aca="false">Wyjaśnienia!$B$67</f>
         <v>180000</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="8" t="n">
@@ -6625,18 +6503,18 @@
         <v>180000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="B20" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$67</f>
+        <f aca="false">Wyjaśnienia!$B$68</f>
         <v>3000</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="8" t="n">
@@ -6644,18 +6522,18 @@
         <v>3000</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B21" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$68</f>
+        <f aca="false">Wyjaśnienia!$B$69</f>
         <v>1200</v>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="8" t="n">
@@ -6663,17 +6541,17 @@
         <v>1200</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="35" t="n">
+      <c r="C22" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="8" t="n">
@@ -6681,17 +6559,17 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -6699,17 +6577,17 @@
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="35" t="n">
+      <c r="C24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -6717,17 +6595,17 @@
         <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="8" t="n">
@@ -6735,17 +6613,17 @@
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="35" t="n">
+      <c r="C26" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="8" t="n">
@@ -6753,42 +6631,42 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B27" s="8"/>
-      <c r="C27" s="35"/>
+      <c r="C27" s="32"/>
       <c r="D27" s="11" t="n">
         <f aca="false">SUM(D19:D26)</f>
         <v>184200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
+      <c r="A29" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="D30" s="8" t="n">
-        <f aca="false">Wyjaśnienia!$B$66+Wyjaśnienia!$B$67</f>
+        <f aca="false">Wyjaśnienia!$B$67+Wyjaśnienia!$B$68</f>
         <v>183000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D31" s="8" t="n">
         <f aca="false">E15</f>
@@ -6797,7 +6675,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="D32" s="8" t="n">
         <f aca="false">D27-D30</f>
@@ -6806,16 +6684,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D33" s="8" t="n">
-        <f aca="false">(D31+D32)*Wyjaśnienia!$B$73</f>
+        <f aca="false">(D31+D32)*Wyjaśnienia!$B$74</f>
         <v>7800</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D34" s="11" t="n">
         <f aca="false">SUM(D30:D33)</f>
@@ -6824,16 +6702,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D35" s="8" t="n">
-        <f aca="false">D34*Wyjaśnienia!$B$32</f>
+        <f aca="false">D34*Wyjaśnienia!$B$33</f>
         <v>58834</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="D36" s="11" t="n">
         <f aca="false">D34+D35</f>
@@ -6857,4 +6735,537 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H105"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="B7" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="C7" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <f aca="false">B7+C7*Wyjaśnienia!$B$17/60</f>
+        <v>45</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <f aca="false">D7*Wyjaśnienia!$B$16</f>
+        <v>9900</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="25" t="n">
+        <f aca="false">SUM(D7:D7)</f>
+        <v>45</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <f aca="false">SUM(E7:E7)</f>
+        <v>9900</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <f aca="false">B12*C12</f>
+        <v>8000</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="B13" s="26" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <f aca="false">B13*C13</f>
+        <v>1500</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="B14" s="26" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <f aca="false">B14*C14</f>
+        <v>4000</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="B15" s="26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <f aca="false">B15*C15</f>
+        <v>8000</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="B16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <f aca="false">B16*C16</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="B17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <f aca="false">B17*C17</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="B18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <f aca="false">B18*C18</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="9" t="n">
+        <f aca="false">SUM(D12:D18)</f>
+        <v>21500</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <f aca="false">E8</f>
+        <v>9900</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="8" t="n">
+        <f aca="false">D19</f>
+        <v>21500</v>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="8" t="n">
+        <f aca="false">(D22+D23)*Wyjaśnienia!$B$30</f>
+        <v>3768</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="9" t="n">
+        <f aca="false">SUM(D22:D24)</f>
+        <v>35168</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="8" t="n">
+        <f aca="false">D25*Wyjaśnienia!$B$33</f>
+        <v>8088.64</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="27" t="n">
+        <f aca="false">D25+D26</f>
+        <v>43256.64</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A21:F21"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -332,7 +332,7 @@
     <t xml:space="preserve">Nagrody filmu łącznie (brutto)</t>
   </si>
   <si>
-    <t xml:space="preserve">100 tys. + 50 tys. + 30 tys. dla czołowej trójki.</t>
+    <t xml:space="preserve">100 tys. + 50 tys. + 30 tys. dla czołowej trójki. Siedem wyróżnień nie jest pieniężnych.</t>
   </si>
   <si>
     <t xml:space="preserve">Nagroda publiczności filmu (brutto)</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">Medal zwycięzcy i dyplomy filmu (netto)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ten sam mosiężny medal co w pozostałych plebiscytach; dyplomy dla pięciu finalistów.</t>
+    <t xml:space="preserve">Ten sam medal co w pozostałych plebiscytach; dyplomy dla dziesięciu finalistów.</t>
   </si>
   <si>
     <t xml:space="preserve">Liczba filmów finałowych</t>
   </si>
   <si>
-    <t xml:space="preserve">Pięciu finalistów, bo tyle minutowych emisji mieści się na gali.</t>
+    <t xml:space="preserve">Dziesięciu finalistów: trójka z nagrodami pieniężnymi i siedem wyróżnień. Minutowe skróty na gali dostaje pięć najwyżej ocenionych.</t>
   </si>
   <si>
     <t xml:space="preserve">Liczba jurorów filmu</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">Godzin oceny na jurora filmu</t>
   </si>
   <si>
-    <t xml:space="preserve">Jury ogląda listę węższą po Akademii, ale filmy trwają do 90 minut - stąd więcej godzin niż przy plakacie.</t>
+    <t xml:space="preserve">Akademia przekazuje jury nie więcej niż dwadzieścia filmów (§ 8 ust. 5a); dwadzieścia filmów po najwyżej 90 minut to 30 godzin samego oglądania, reszta na karty oceny, obrady i werdykt.</t>
   </si>
   <si>
     <t xml:space="preserve">Stawka jury filmu za godzinę (netto)</t>
@@ -749,10 +749,10 @@
     <t xml:space="preserve">nagranie i premiera na początku 2027, otwiera nabór</t>
   </si>
   <si>
-    <t xml:space="preserve">Medalion zwycięzcy i dyplomy finalistów (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ten sam medalion, który otrzymuje laureat konkursu rozmów; dyplomy dla całej dziesiątki</t>
+    <t xml:space="preserve">Medal zwycięzcy i dyplomy finalistów (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ten sam medal, który otrzymuje laureat plebiscytu rozmów; dyplomy dla całej dziesiątki</t>
   </si>
   <si>
     <t xml:space="preserve">Honoraria jury plebiscytu za ocenę (netto)</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">dwa przejścia oceny, pięciu finalistów, kolejność trójki</t>
   </si>
   <si>
-    <t xml:space="preserve">Zebranie fragmentów od finalistów i przygotowanie emisji galowych</t>
+    <t xml:space="preserve">Zebranie fragmentów od piątki i przygotowanie skrótów galowych</t>
   </si>
   <si>
     <t xml:space="preserve">autor wybiera fragment w terminie nie krótszym niż 14 dni; organizator zbiera, sprawdza format i układa kolejność</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">Nagrody filmu (brutto dla laureatów)</t>
   </si>
   <si>
-    <t xml:space="preserve">czołowa trójka: 100, 50 i 30 tys.; podatek 10% jak przy Nagrodzie</t>
+    <t xml:space="preserve">czołowa trójka: 100, 50 i 30 tys.; siedem wyróżnień bez nagrody pieniężnej; podatek 10% jak przy Nagrodzie</t>
   </si>
   <si>
     <t xml:space="preserve">jedna nagroda, dla filmu z największą liczbą głosów</t>
   </si>
   <si>
-    <t xml:space="preserve">ten sam medalion, który otrzymują zwycięzcy pozostałych plebiscytów; dyplomy dla pięciu finalistów</t>
+    <t xml:space="preserve">ten sam medal, który otrzymują zwycięzcy pozostałych plebiscytów; dyplomy dla dziesięciu finalistów</t>
   </si>
   <si>
     <t xml:space="preserve">Honoraria jury filmu za ocenę (netto)</t>
   </si>
   <si>
-    <t xml:space="preserve">DO USTALENIA - stawka godzinowa jest przy nazwisku złym narzędziem; kotwica z Wyjaśnień (5 osób x 25 h x 290 zł) dałaby 36 250 zł</t>
+    <t xml:space="preserve">DO USTALENIA - kotwica z Wyjaśnień (5 osób x 40 h x 290 zł) dałaby 58 000 zł; 40 h to 30 h oglądania dwudziestu filmów przekazanych jury plus karty, obrady i werdykt</t>
   </si>
   <si>
     <t xml:space="preserve">Opracowanie techniczne minutowych emisji na galę (netto)</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">DO WYCENY - sala, projekcja, obsługa; regulamin § 10 ust. 4 wymaga ogłoszenia terminu najpóźniej w dniu gali</t>
   </si>
   <si>
-    <t xml:space="preserve">DO WYCENY - jak przy plebiscycie piosenki; pięciu finalistów, często ze składem</t>
+    <t xml:space="preserve">DO WYCENY - jak przy plebiscycie piosenki; dziesięciu finalistów, często z ekipą</t>
   </si>
   <si>
     <t xml:space="preserve">Obsługa prawna regulaminu filmu (netto)</t>
@@ -2561,7 +2561,7 @@
         <v>106</v>
       </c>
       <c r="B70" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>107</v>
@@ -2583,7 +2583,7 @@
         <v>110</v>
       </c>
       <c r="B72" s="14" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>111</v>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">dwa przejścia oceny, pięciu finalistów, kolejność trójki</t>
   </si>
   <si>
-    <t xml:space="preserve">Zebranie fragmentów od piątki i przygotowanie skrótów galowych</t>
+    <t xml:space="preserve">Zebranie zwiastunów piątki i przygotowanie bloku galowego</t>
   </si>
   <si>
     <t xml:space="preserve">autor wybiera fragment w terminie nie krótszym niż 14 dni; organizator zbiera, sprawdza format i układa kolejność</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">DO USTALENIA - kotwica z Wyjaśnień (5 osób x 40 h x 290 zł) dałaby 58 000 zł; 40 h to 30 h oglądania dwudziestu filmów przekazanych jury plus karty, obrady i werdykt</t>
   </si>
   <si>
-    <t xml:space="preserve">Opracowanie techniczne minutowych emisji na galę (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - pobranie materiału w jakości emisyjnej, zgodność formatów, napisy, montaż bloku pięciu emisji</t>
+    <t xml:space="preserve">Przygotowanie techniczne zwiastunów do emisji galowej (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - pobranie pięciu zwiastunów w jakości emisyjnej, zgodność formatów, normalizacja dźwięku, plansze z tytułami; zwiastun dostarcza autor, Organizator nie montuje fragmentów filmów</t>
   </si>
   <si>
     <t xml:space="preserve">Pełne pokazy filmów finałowych (netto)</t>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="380">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -1158,6 +1158,12 @@
   </si>
   <si>
     <t xml:space="preserve">do wyceny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tantiemy dla organizacji zbiorowego zarządzania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - publiczne wykonanie muzyki na gali: hymn i trzy piosenki na żywo oraz muzyka w zwiastunach piątki filmów; obowiązek po stronie Organizatora, nieprzenoszony na uczestników (§ 12 ust. 2a regulaminu filmu)</t>
   </si>
   <si>
     <t xml:space="preserve">Rezerwa (od pracy i kosztów)</t>
@@ -1912,7 +1918,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false">'Budżet Gali'!$D$25</f>
+        <f aca="false">'Budżet Gali'!$D$26</f>
         <v>35168</v>
       </c>
     </row>
@@ -1921,7 +1927,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="11" t="n">
-        <f aca="false">'Budżet Nagrody'!$D$35+'Budżet Gali'!$D$25+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$34</f>
+        <f aca="false">'Budżet Nagrody'!$D$35+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$34</f>
         <v>1686506.8</v>
       </c>
       <c r="D13" s="3"/>
@@ -7056,72 +7062,75 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="B19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="24" t="n">
+        <f aca="false">B19*C19</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="9" t="n">
-        <f aca="false">SUM(D12:D18)</f>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="9" t="n">
+        <f aca="false">SUM(D12:D19)</f>
         <v>21500</v>
       </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="A21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D23" s="8" t="n">
         <f aca="false">E8</f>
         <v>9900</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="8" t="n">
-        <f aca="false">D19</f>
-        <v>21500</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>377</v>
+        <v>172</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="8" t="n">
-        <f aca="false">(D22+D23)*Wyjaśnienia!$B$30</f>
-        <v>3768</v>
+        <f aca="false">D20</f>
+        <v>21500</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -7129,14 +7138,14 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>174</v>
+      <c r="A25" s="21" t="s">
+        <v>379</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="9" t="n">
-        <f aca="false">SUM(D22:D24)</f>
-        <v>35168</v>
+      <c r="D25" s="8" t="n">
+        <f aca="false">(D23+D24)*Wyjaśnienia!$B$30</f>
+        <v>3768</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -7144,14 +7153,14 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
-        <v>175</v>
+      <c r="A26" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="8" t="n">
-        <f aca="false">D25*Wyjaśnienia!$B$33</f>
-        <v>8088.64</v>
+      <c r="D26" s="9" t="n">
+        <f aca="false">SUM(D23:D25)</f>
+        <v>35168</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -7159,21 +7168,35 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>176</v>
+      <c r="A27" s="21" t="s">
+        <v>175</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="27" t="n">
-        <f aca="false">D25+D26</f>
-        <v>43256.64</v>
+      <c r="D27" s="8" t="n">
+        <f aca="false">D26*Wyjaśnienia!$B$33</f>
+        <v>8088.64</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="27" t="n">
+        <f aca="false">D26+D27</f>
+        <v>43256.64</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+    </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7258,7 +7281,7 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">autor wybiera fragment w terminie nie krótszym niż 14 dni; organizator zbiera, sprawdza format i układa kolejność</t>
   </si>
   <si>
-    <t xml:space="preserve">Organizacja pełnych pokazów filmów finałowych poza galą</t>
+    <t xml:space="preserve">Złożenie zestawu dziesiątki i rozmowy z dystrybutorami</t>
   </si>
   <si>
     <t xml:space="preserve">regulamin § 10 ust. 4: termin i miejsce ogłaszane najpóźniej w dniu gali, udział za zgodą autora</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">DO WYCENY - pobranie pięciu zwiastunów w jakości emisyjnej, zgodność formatów, normalizacja dźwięku, plansze z tytułami; zwiastun dostarcza autor, Organizator nie montuje fragmentów filmów</t>
   </si>
   <si>
-    <t xml:space="preserve">Pełne pokazy filmów finałowych (netto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO WYCENY - sala, projekcja, obsługa; regulamin § 10 ust. 4 wymaga ogłoszenia terminu najpóźniej w dniu gali</t>
+    <t xml:space="preserve">Pokazy kinowe filmów finałowych (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - opracowanie techniczne kopii, napisy i materiały informacyjne dla zestawu dziesiątki; zależy od pozyskania dystrybutora (§ 10 ust. 4), z którym Organizator może uzgodnić pokrycie tych kosztów</t>
   </si>
   <si>
     <t xml:space="preserve">DO WYCENY - jak przy plebiscycie piosenki; dziesięciu finalistów, często z ekipą</t>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="380">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">Nagrody publiczności łącznie (brutto)</t>
   </si>
   <si>
-    <t xml:space="preserve">3 tys. dla wykonawcy, 1 tys. za uzasadnienie. Do potwierdzenia.</t>
+    <t xml:space="preserve">3 000 zł dla wykonawcy oraz 1 000 zł za najlepsze uzasadnienie wyboru. Uzasadnienie jest obowiązkowe przy każdym głosie (§ 11 ust. 2 regulaminu).</t>
   </si>
   <si>
     <t xml:space="preserve">Nagranie studyjne - koszt za utwór (netto)</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">50 tys. + 25 tys. + 15 tys. dla czołowej trójki.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nagroda publiczności plakatu (brutto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jedna nagroda, bez nagrody za uzasadnienie.</t>
+    <t xml:space="preserve">Nagrody publiczności plakatu łącznie (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 000 zł dla pracy z największą liczbą głosów oraz 1 000 zł za najlepsze uzasadnienie wyboru (§ 12 ust. 6).</t>
   </si>
   <si>
     <t xml:space="preserve">Medal zwycięzcy i dyplomy plakatu (netto)</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">100 tys. + 50 tys. + 30 tys. dla czołowej trójki. Siedem wyróżnień nie jest pieniężnych.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nagroda publiczności filmu (brutto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jedna nagroda, dla filmu z największą liczbą głosów.</t>
+    <t xml:space="preserve">Nagrody publiczności filmu łącznie (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 000 zł dla filmu z największą liczbą głosów oraz 1 000 zł za najlepsze uzasadnienie wyboru (§ 11a ust. 5).</t>
   </si>
   <si>
     <t xml:space="preserve">Medal zwycięzcy i dyplomy filmu (netto)</t>
@@ -524,7 +524,10 @@
     <t xml:space="preserve">materiały, obsługa prasowa przy starcie i rozstrzygnięciu, płatne dotarcie</t>
   </si>
   <si>
-    <t xml:space="preserve">Nagroda publiczności</t>
+    <t xml:space="preserve">Nagrody publiczności (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 000 zł dla zgłoszenia z największą liczbą głosów oraz 1 000 zł za najlepsze uzasadnienie wyboru (§ 11 ust. 8a)</t>
   </si>
   <si>
     <t xml:space="preserve">Ubezpieczenie OC organizatora</t>
@@ -732,9 +735,6 @@
   </si>
   <si>
     <t xml:space="preserve">czołowa trójka; podatek 10% jak przy Nagrodzie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nagrody publiczności (brutto)</t>
   </si>
   <si>
     <t xml:space="preserve">dla wykonawcy oraz za najlepsze uzasadnienie wyboru</t>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">'Budżet Nagrody'!$D$35</f>
-        <v>534876.8</v>
+        <v>535996.8</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">'Budżet Plakatu'!$D$34</f>
-        <v>153480</v>
+        <v>154480</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">'Budżet Filmu'!$D$34</f>
-        <v>255800</v>
+        <v>256800</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="C13" s="11" t="n">
         <f aca="false">'Budżet Nagrody'!$D$35+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$34</f>
-        <v>1686506.8</v>
+        <v>1689626.8</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -2418,7 +2418,7 @@
         <v>81</v>
       </c>
       <c r="B55" s="18" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>82</v>
@@ -2545,7 +2545,7 @@
         <v>102</v>
       </c>
       <c r="B68" s="14" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>103</v>
@@ -3201,21 +3201,23 @@
         <v>165</v>
       </c>
       <c r="B26" s="26" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="24" t="n">
         <f aca="false">B26*C26</f>
-        <v>3000</v>
-      </c>
-      <c r="E26" s="15"/>
+        <v>4000</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>166</v>
+      </c>
       <c r="F26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B27" s="26" t="n">
         <v>0</v>
@@ -3228,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -3236,13 +3238,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="9" t="n">
         <f aca="false">SUM(D21:D27)</f>
-        <v>52950</v>
+        <v>53950</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -3256,7 +3258,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -3268,7 +3270,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -3283,7 +3285,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -3298,13 +3300,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="8" t="n">
         <f aca="false">D28</f>
-        <v>52950</v>
+        <v>53950</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -3313,24 +3315,24 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D34" s="3" t="n">
         <f aca="false">(D32+D33)*Wyjaśnienia!$B$30</f>
-        <v>14986.8</v>
+        <v>15106.8</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="9" t="n">
         <f aca="false">SUM(D31:D34)</f>
-        <v>534876.8</v>
+        <v>535996.8</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -3339,13 +3341,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="8" t="n">
         <f aca="false">D35*Wyjaśnienia!$B$33</f>
-        <v>123021.664</v>
+        <v>123279.264</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -3354,13 +3356,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="27" t="n">
         <f aca="false">D35+D36</f>
-        <v>657898.464</v>
+        <v>659276.064</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -3484,7 +3486,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3552,7 +3554,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B7" s="22" t="n">
         <v>45</v>
@@ -3569,14 +3571,14 @@
         <v>9900</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B8" s="22" t="n">
         <v>40</v>
@@ -3593,14 +3595,14 @@
         <v>8800</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B9" s="22" t="n">
         <v>0</v>
@@ -3617,14 +3619,14 @@
         <v>2200</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B10" s="22" t="n">
         <v>50</v>
@@ -3641,14 +3643,14 @@
         <v>11000</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B11" s="22" t="n">
         <v>25</v>
@@ -3665,14 +3667,14 @@
         <v>5500</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B12" s="22" t="n">
         <v>160</v>
@@ -3689,14 +3691,14 @@
         <v>35200</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B13" s="22" t="n">
         <v>50</v>
@@ -3713,14 +3715,14 @@
         <v>11000</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B14" s="22" t="n">
         <v>72</v>
@@ -3800,7 +3802,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" s="26" t="n">
         <v>3000</v>
@@ -3813,7 +3815,7 @@
         <v>3000</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -3821,7 +3823,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="26" t="n">
         <v>6000</v>
@@ -3834,17 +3836,17 @@
         <v>6000</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B21" s="26" t="n">
         <v>10000</v>
@@ -3857,7 +3859,7 @@
         <v>10000</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -3865,7 +3867,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B22" s="26" t="n">
         <v>40000</v>
@@ -3878,7 +3880,7 @@
         <v>40000</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -3886,7 +3888,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B23" s="26" t="n">
         <v>4000</v>
@@ -3899,7 +3901,7 @@
         <v>4000</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -3907,7 +3909,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B24" s="26" t="n">
         <v>3000</v>
@@ -3920,7 +3922,7 @@
         <v>3000</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -3928,7 +3930,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B25" s="26" t="n">
         <v>4000</v>
@@ -3941,7 +3943,7 @@
         <v>4000</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -3949,7 +3951,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B26" s="26" t="n">
         <v>0</v>
@@ -3962,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -3970,7 +3972,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B27" s="26" t="n">
         <v>15000</v>
@@ -3983,7 +3985,7 @@
         <v>15000</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -3991,7 +3993,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B28" s="26" t="n">
         <v>6000</v>
@@ -4004,7 +4006,7 @@
         <v>6000</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -4012,7 +4014,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B29" s="26" t="n">
         <v>30000</v>
@@ -4025,7 +4027,7 @@
         <v>30000</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -4033,7 +4035,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B30" s="18" t="n">
         <v>4500</v>
@@ -4046,12 +4048,12 @@
         <v>4500</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B31" s="18" t="n">
         <v>0</v>
@@ -4064,13 +4066,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F31" s="28"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -4095,7 +4097,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -4107,7 +4109,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -4122,7 +4124,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -4137,7 +4139,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -4152,7 +4154,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -4167,7 +4169,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -4182,7 +4184,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -4310,7 +4312,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4378,7 +4380,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B7" s="22" t="n">
         <v>0</v>
@@ -4395,14 +4397,14 @@
         <v>5500</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B8" s="22" t="n">
         <v>40</v>
@@ -4417,14 +4419,14 @@
         <v>8800</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B9" s="22" t="n">
         <v>30</v>
@@ -4439,14 +4441,14 @@
         <v>6600</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B10" s="22" t="n">
         <v>20</v>
@@ -4461,14 +4463,14 @@
         <v>4400</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B11" s="22" t="n">
         <v>50</v>
@@ -4483,7 +4485,7 @@
         <v>11000</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -4503,7 +4505,7 @@
         <v>36300</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -4552,7 +4554,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B16" s="24" t="n">
         <f aca="false">Wyjaśnienia!$B$24</f>
@@ -4566,7 +4568,7 @@
         <v>35000</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -4574,7 +4576,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>235</v>
+        <v>165</v>
       </c>
       <c r="B17" s="24" t="n">
         <f aca="false">Wyjaśnienia!$B$25</f>
@@ -4745,7 +4747,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -4770,7 +4772,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -4782,7 +4784,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -4797,7 +4799,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -4827,7 +4829,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -4842,7 +4844,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -4857,7 +4859,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -4872,7 +4874,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -5096,7 +5098,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B9" s="20" t="n">
         <v>20</v>
@@ -5207,7 +5209,7 @@
         <v>41800</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5262,14 +5264,14 @@
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$55</f>
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C19" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="8" t="n">
         <f aca="false">B19*C19</f>
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>269</v>
@@ -5407,16 +5409,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D27" s="11" t="n">
         <f aca="false">SUM(D18:D26)</f>
-        <v>105200</v>
+        <v>106200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
@@ -5426,16 +5428,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$54+Wyjaśnienia!$B$55</f>
-        <v>93000</v>
+        <v>94000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D31" s="8" t="n">
         <f aca="false">E14</f>
@@ -5453,7 +5455,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D33" s="8" t="n">
         <f aca="false">(D31+D32)*Wyjaśnienia!$B$63</f>
@@ -5462,29 +5464,29 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D34" s="11" t="n">
         <f aca="false">SUM(D30:D33)</f>
-        <v>153480</v>
+        <v>154480</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D35" s="8" t="n">
         <f aca="false">D34*Wyjaśnienia!$B$33</f>
-        <v>35300.4</v>
+        <v>35530.4</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D36" s="11" t="n">
         <f aca="false">D34+D35</f>
-        <v>188780.4</v>
+        <v>190010.4</v>
       </c>
     </row>
   </sheetData>
@@ -5842,7 +5844,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D27" s="42" t="n">
         <f aca="false">SUM(D23:D26)</f>
@@ -5851,7 +5853,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B29" s="36"/>
       <c r="C29" s="36"/>
@@ -5870,7 +5872,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D31" s="41" t="n">
         <f aca="false">D27</f>
@@ -5888,7 +5890,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="37" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D33" s="42" t="n">
         <f aca="false">SUM(D30:D32)</f>
@@ -5897,7 +5899,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D34" s="41" t="n">
         <f aca="false">D33*Wyjaśnienia!$B$33</f>
@@ -5906,7 +5908,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D35" s="42" t="n">
         <f aca="false">D33+D34</f>
@@ -6350,7 +6352,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B10" s="20" t="n">
         <v>20</v>
@@ -6518,14 +6520,14 @@
       </c>
       <c r="B20" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$68</f>
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C20" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="8" t="n">
         <f aca="false">B20*C20</f>
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>348</v>
@@ -6642,18 +6644,18 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="32"/>
       <c r="D27" s="11" t="n">
         <f aca="false">SUM(D19:D26)</f>
-        <v>184200</v>
+        <v>185200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
@@ -6663,16 +6665,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$67+Wyjaśnienia!$B$68</f>
-        <v>183000</v>
+        <v>184000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D31" s="8" t="n">
         <f aca="false">E15</f>
@@ -6690,7 +6692,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D33" s="8" t="n">
         <f aca="false">(D31+D32)*Wyjaśnienia!$B$74</f>
@@ -6699,29 +6701,29 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D34" s="11" t="n">
         <f aca="false">SUM(D30:D33)</f>
-        <v>255800</v>
+        <v>256800</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D35" s="8" t="n">
         <f aca="false">D34*Wyjaśnienia!$B$33</f>
-        <v>58834</v>
+        <v>59064</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D36" s="11" t="n">
         <f aca="false">D34+D35</f>
-        <v>314634</v>
+        <v>315864</v>
       </c>
     </row>
   </sheetData>
@@ -7081,7 +7083,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -7101,7 +7103,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -7113,7 +7115,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D23" s="8" t="n">
         <f aca="false">E8</f>
@@ -7124,7 +7126,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -7154,7 +7156,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -7169,7 +7171,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -7184,7 +7186,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -155,7 +155,7 @@
     <t xml:space="preserve">Nagrody publiczności łącznie (brutto)</t>
   </si>
   <si>
-    <t xml:space="preserve">3 000 zł dla wykonawcy oraz 1 000 zł za najlepsze uzasadnienie wyboru. Uzasadnienie jest obowiązkowe przy każdym głosie (§ 11 ust. 2 regulaminu).</t>
+    <t xml:space="preserve">3 000 zł dla wykonawcy oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych piosenek. Uzasadnienie jest obowiązkowe przy każdym głosie, od 200 do 1500 znaków (§ 11 ust. 2 regulaminu).</t>
   </si>
   <si>
     <t xml:space="preserve">Nagranie studyjne - koszt za utwór (netto)</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">Nagrody publiczności plakatu łącznie (brutto)</t>
   </si>
   <si>
-    <t xml:space="preserve">3 000 zł dla pracy z największą liczbą głosów oraz 1 000 zł za najlepsze uzasadnienie wyboru (§ 12 ust. 6).</t>
+    <t xml:space="preserve">3 000 zł dla pracy z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych plakatów (§ 12 ust. 6).</t>
   </si>
   <si>
     <t xml:space="preserve">Medal zwycięzcy i dyplomy plakatu (netto)</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">Nagrody publiczności filmu łącznie (brutto)</t>
   </si>
   <si>
-    <t xml:space="preserve">3 000 zł dla filmu z największą liczbą głosów oraz 1 000 zł za najlepsze uzasadnienie wyboru (§ 11a ust. 5).</t>
+    <t xml:space="preserve">3 000 zł dla filmu z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych filmów (§ 11a ust. 5).</t>
   </si>
   <si>
     <t xml:space="preserve">Medal zwycięzcy i dyplomy filmu (netto)</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">Nagrody publiczności (brutto)</t>
   </si>
   <si>
-    <t xml:space="preserve">3 000 zł dla zgłoszenia z największą liczbą głosów oraz 1 000 zł za najlepsze uzasadnienie wyboru (§ 11 ust. 8a)</t>
+    <t xml:space="preserve">3 000 zł dla zgłoszenia z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych rozmów (§ 11 ust. 8a)</t>
   </si>
   <si>
     <t xml:space="preserve">Ubezpieczenie OC organizatora</t>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="382">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">Realizacja części artystycznej gali</t>
   </si>
   <si>
-    <t xml:space="preserve">Po wpisaniu tych kwot rosną Budżet Plebiscytu, Budżet Plakatu i Budżet Filmu. W Budżecie Plakatu czekają na wycenę trzy pozycje, w Budżecie Filmu pięć - wszystkie opisane w kolumnie Uwagi.</t>
+    <t xml:space="preserve">Po wpisaniu tych kwot rosną Budżet Plebiscytu, Budżet Plakatu i Budżet Filmu. W Budżecie Plakatu czekają na wycenę cztery pozycje, w Budżecie Filmu pięć - wszystkie opisane w kolumnie Uwagi.</t>
   </si>
   <si>
     <t xml:space="preserve">JAK CZYTAĆ BUDŻETY</t>
@@ -870,6 +870,12 @@
   </si>
   <si>
     <t xml:space="preserve">DO WYCENY - jak przy plebiscycie piosenki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polisa: wycena prac, rozszerzenie na przechowywanie i okres po sprzedaży (netto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO WYCENY - polisa ma objąć cały uzgodniony okres: transport w obie strony, przechowywanie u organizatora, obie wystawy oraz czas po sprzedaży do wydania pracy nabywcy; do ustalenia suma ubezpieczenia na pracę, udział własny i procedura zgłoszenia szkody</t>
   </si>
   <si>
     <t xml:space="preserve">Finansuje: Sponsor Akademii. Kwoty netto. Vouchery są świadczeniem rzeczowym i rosną wprost z liczbą ocenionych rozmów.</t>
@@ -1889,7 +1895,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">'Budżet Plakatu'!$D$34</f>
+        <f aca="false">'Budżet Plakatu'!$D$35</f>
         <v>154480</v>
       </c>
       <c r="D10" s="3"/>
@@ -1927,7 +1933,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="11" t="n">
-        <f aca="false">'Budżet Nagrody'!$D$35+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$34+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$34</f>
+        <f aca="false">'Budżet Nagrody'!$D$35+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$32+'Budżet Plakatu'!$D$35+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$34</f>
         <v>1689626.8</v>
       </c>
       <c r="D13" s="3"/>
@@ -4983,7 +4989,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="54"/>
@@ -5408,84 +5414,105 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <f aca="false">B27*C27</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D27" s="11" t="n">
-        <f aca="false">SUM(D18:D26)</f>
+      <c r="D28" s="11" t="n">
+        <f aca="false">SUM(D18:D27)</f>
         <v>106200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D31" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$54+Wyjaśnienia!$B$55</f>
         <v>94000</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D32" s="8" t="n">
         <f aca="false">E14</f>
         <v>41800</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <f aca="false">D27-D30</f>
-        <v>12200</v>
-      </c>
-    </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <f aca="false">D28-D31</f>
+        <v>12200</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D33" s="8" t="n">
-        <f aca="false">(D31+D32)*Wyjaśnienia!$B$63</f>
+      <c r="D34" s="8" t="n">
+        <f aca="false">(D32+D33)*Wyjaśnienia!$B$63</f>
         <v>6480</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="D34" s="11" t="n">
-        <f aca="false">SUM(D30:D33)</f>
+      <c r="D35" s="11" t="n">
+        <f aca="false">SUM(D31:D34)</f>
         <v>154480</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D35" s="8" t="n">
-        <f aca="false">D34*Wyjaśnienia!$B$33</f>
+      <c r="D36" s="8" t="n">
+        <f aca="false">D35*Wyjaśnienia!$B$33</f>
         <v>35530.4</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="11" t="n">
-        <f aca="false">D34+D35</f>
+      <c r="D37" s="11" t="n">
+        <f aca="false">D35+D36</f>
         <v>190010.4</v>
       </c>
     </row>
@@ -5536,7 +5563,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B2" s="35"/>
       <c r="C2" s="35"/>
@@ -5546,7 +5573,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="35" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B3" s="35"/>
       <c r="C3" s="35"/>
@@ -5556,7 +5583,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="36" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -5569,7 +5596,7 @@
         <v>124</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F6" s="37" t="s">
         <v>129</v>
@@ -5577,79 +5604,79 @@
     </row>
     <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B7" s="39" t="n">
         <f aca="false">Wyjaśnienia!$B$17</f>
         <v>150</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B8" s="39" t="n">
         <f aca="false">Wyjaśnienia!$B$46</f>
         <v>2</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="37" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B9" s="40" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B10" s="39" t="n">
         <f aca="false">Wyjaśnienia!$B$66</f>
         <v>150</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B11" s="39" t="n">
         <f aca="false">Wyjaśnienia!$B$75</f>
         <v>2</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B12" s="40" t="n">
         <f aca="false">B10*B11</f>
         <v>300</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
@@ -5662,7 +5689,7 @@
         <v>124</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>153</v>
@@ -5676,7 +5703,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B16" s="41" t="n">
         <f aca="false">Wyjaśnienia!$B$48</f>
@@ -5691,12 +5718,12 @@
         <v>37500</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="28" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B17" s="41" t="n">
         <f aca="false">Wyjaśnienia!$B$47</f>
@@ -5711,12 +5738,12 @@
         <v>1500</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B18" s="41" t="n">
         <f aca="false">Wyjaśnienia!$B$76</f>
@@ -5731,12 +5758,12 @@
         <v>90000</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D19" s="42" t="n">
         <f aca="false">SUM(D16:D18)</f>
@@ -5772,7 +5799,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B23" s="41" t="n">
         <v>2000</v>
@@ -5785,12 +5812,12 @@
         <v>2000</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B24" s="41" t="n">
         <v>3000</v>
@@ -5803,12 +5830,12 @@
         <v>3000</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="28" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B25" s="41" t="n">
         <v>5000</v>
@@ -5821,12 +5848,12 @@
         <v>5000</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B26" s="41" t="n">
         <v>4000</v>
@@ -5839,7 +5866,7 @@
         <v>4000</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5863,7 +5890,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D30" s="41" t="n">
         <f aca="false">D19</f>
@@ -5881,7 +5908,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D32" s="41" t="n">
         <f aca="false">(D30+D31)*Wyjaśnienia!$B$30</f>
@@ -5917,7 +5944,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="36" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B37" s="36"/>
       <c r="C37" s="36"/>
@@ -5927,7 +5954,7 @@
     </row>
     <row r="38" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="35" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B38" s="35"/>
       <c r="C38" s="35"/>
@@ -5937,19 +5964,19 @@
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="38" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6059,19 +6086,19 @@
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="38" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6181,7 +6208,7 @@
     </row>
     <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="35" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B53" s="35"/>
       <c r="C53" s="35"/>
@@ -6240,7 +6267,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="30" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -6250,7 +6277,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -6290,7 +6317,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B7" s="20" t="n">
         <v>0</v>
@@ -6307,12 +6334,12 @@
         <v>6600</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B8" s="20" t="n">
         <v>25</v>
@@ -6327,12 +6354,12 @@
         <v>5500</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B9" s="20" t="n">
         <v>60</v>
@@ -6347,7 +6374,7 @@
         <v>13200</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6372,7 +6399,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B11" s="20" t="n">
         <v>40</v>
@@ -6387,12 +6414,12 @@
         <v>8800</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B12" s="20" t="n">
         <v>40</v>
@@ -6407,12 +6434,12 @@
         <v>8800</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B13" s="20" t="n">
         <v>25</v>
@@ -6427,12 +6454,12 @@
         <v>5500</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B14" s="20" t="n">
         <v>50</v>
@@ -6447,7 +6474,7 @@
         <v>11000</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6465,7 +6492,7 @@
         <v>63800</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6497,7 +6524,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$67</f>
@@ -6511,7 +6538,7 @@
         <v>180000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6530,7 +6557,7 @@
         <v>4000</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6549,12 +6576,12 @@
         <v>1200</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>0</v>
@@ -6567,12 +6594,12 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>0</v>
@@ -6585,12 +6612,12 @@
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>0</v>
@@ -6603,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6621,12 +6648,12 @@
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>0</v>
@@ -6639,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6763,7 +6790,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6775,7 +6802,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -6843,7 +6870,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B7" s="22" t="n">
         <v>45</v>
@@ -6860,7 +6887,7 @@
         <v>9900</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -6927,7 +6954,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B12" s="26" t="n">
         <v>8000</v>
@@ -6940,7 +6967,7 @@
         <v>8000</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -6948,7 +6975,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B13" s="26" t="n">
         <v>1500</v>
@@ -6961,7 +6988,7 @@
         <v>1500</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -6969,7 +6996,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B14" s="26" t="n">
         <v>4000</v>
@@ -6982,7 +7009,7 @@
         <v>4000</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
@@ -6990,7 +7017,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B15" s="26" t="n">
         <v>8000</v>
@@ -7003,7 +7030,7 @@
         <v>8000</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
@@ -7011,7 +7038,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B16" s="26" t="n">
         <v>0</v>
@@ -7024,12 +7051,12 @@
         <v>0</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B17" s="26" t="n">
         <v>0</v>
@@ -7042,12 +7069,12 @@
         <v>0</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B18" s="26" t="n">
         <v>0</v>
@@ -7060,12 +7087,12 @@
         <v>0</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B19" s="26" t="n">
         <v>0</v>
@@ -7078,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7141,7 +7168,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -1279,7 +1279,7 @@
     <row r="37" ht="15" customHeight="1" s="44">
       <c r="A37" s="49" t="inlineStr">
         <is>
-          <t>Honoraria jury plebiscytu</t>
+          <t>Honoraria jury plebiscytu piosenki - osobno za ocenę zgłoszeń i za etap przygotowania karty oceny</t>
         </is>
       </c>
       <c r="D37" s="46" t="n"/>
@@ -4167,7 +4167,7 @@
           <t>Razem koszty twarde</t>
         </is>
       </c>
-      <c r="D26">
+      <c r="D26" s="46">
         <f>SUM(D16:D25)</f>
         <v/>
       </c>
@@ -4382,10 +4382,10 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="C6" s="51">
-        <f>'Budżet Nagrody'!$D$35</f>
+        <f>'Budżet Nagrody'!$D$36</f>
         <v/>
       </c>
       <c r="D6" s="46" t="n"/>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="C10" s="52">
-        <f>'Budżet Plakatu'!$D$35</f>
+        <f>'Budżet Plakatu'!$D$36</f>
         <v/>
       </c>
       <c r="D10" s="46" t="n"/>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="C11" s="52">
-        <f>'Budżet Filmu'!$D$34</f>
+        <f>'Budżet Filmu'!$D$35</f>
         <v/>
       </c>
     </row>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="C13" s="54">
-        <f>'Budżet Nagrody'!$D$35+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$33+'Budżet Plakatu'!$D$35+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$34</f>
+        <f>'Budżet Nagrody'!$D$36+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$33+'Budżet Plakatu'!$D$36+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$35</f>
         <v/>
       </c>
       <c r="D13" s="46" t="n"/>
@@ -1279,7 +1279,7 @@
     <row r="37" ht="15" customHeight="1" s="44">
       <c r="A37" s="49" t="inlineStr">
         <is>
-          <t>Honoraria jury plebiscytu piosenki - osobno za ocenę zgłoszeń i za etap przygotowania karty oceny</t>
+          <t>Honoraria jury we wszystkich plebiscytach - osobno za ocenę zgłoszeń i za etap przygotowania karty oceny</t>
         </is>
       </c>
       <c r="D37" s="46" t="n"/>
@@ -1838,7 +1838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="54" customWidth="1" style="43" min="1" max="1"/>
@@ -2384,11 +2384,11 @@
     <row r="25" ht="15" customHeight="1" s="44">
       <c r="A25" s="62" t="inlineStr">
         <is>
-          <t>Promocja naboru</t>
+          <t>Honoraria jury za etap przygotowawczy: karta oceny i wagi kryteriów (netto)</t>
         </is>
       </c>
       <c r="B25" s="67" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="C25" s="63" t="n">
         <v>1</v>
@@ -2399,21 +2399,19 @@
       </c>
       <c r="E25" s="56" t="inlineStr">
         <is>
-          <t>materiały, obsługa prasowa przy starcie i rozstrzygnięciu, płatne dotarcie</t>
+          <t>DO USTALENIA - etap przed naborem, osobny od oceny zgłoszeń; obejmuje opisy przedziałów punktowych i przykłady ich zastosowania</t>
         </is>
       </c>
       <c r="F25" s="46" t="n"/>
-      <c r="G25" s="46" t="n"/>
-      <c r="H25" s="46" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="44">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>Nagrody publiczności (brutto)</t>
+          <t>Promocja naboru</t>
         </is>
       </c>
       <c r="B26" s="67" t="n">
-        <v>4000</v>
+        <v>15000</v>
       </c>
       <c r="C26" s="63" t="n">
         <v>1</v>
@@ -2424,19 +2422,21 @@
       </c>
       <c r="E26" s="56" t="inlineStr">
         <is>
-          <t>3 000 zł dla zgłoszenia z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych rozmów (§ 11 ust. 8a)</t>
+          <t>materiały, obsługa prasowa przy starcie i rozstrzygnięciu, płatne dotarcie</t>
         </is>
       </c>
       <c r="F26" s="46" t="n"/>
+      <c r="G26" s="46" t="n"/>
+      <c r="H26" s="46" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="44">
       <c r="A27" s="62" t="inlineStr">
         <is>
-          <t>Ubezpieczenie OC organizatora</t>
+          <t>Nagrody publiczności (brutto)</t>
         </is>
       </c>
       <c r="B27" s="67" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="C27" s="63" t="n">
         <v>1</v>
@@ -2447,71 +2447,77 @@
       </c>
       <c r="E27" s="56" t="inlineStr">
         <is>
+          <t>3 000 zł dla zgłoszenia z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych rozmów (§ 11 ust. 8a)</t>
+        </is>
+      </c>
+      <c r="F27" s="46" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="44">
+      <c r="A28" s="62" t="inlineStr">
+        <is>
+          <t>Ubezpieczenie OC organizatora</t>
+        </is>
+      </c>
+      <c r="B28" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="65">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="56" t="inlineStr">
+        <is>
           <t>do ustalenia po konsultacji prawnej; na razie pokryte rezerwą</t>
         </is>
       </c>
-      <c r="F27" s="46" t="n"/>
-      <c r="G27" s="46" t="n"/>
-      <c r="H27" s="46" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="44">
-      <c r="A28" s="49" t="inlineStr">
-        <is>
-          <t>Razem koszty twarde</t>
-        </is>
-      </c>
-      <c r="B28" s="46" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="52">
-        <f>SUM(D21:D27)</f>
-        <v/>
-      </c>
-      <c r="E28" s="46" t="n"/>
       <c r="F28" s="46" t="n"/>
       <c r="G28" s="46" t="n"/>
       <c r="H28" s="46" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="44">
-      <c r="A29" s="46" t="n"/>
+      <c r="A29" s="49" t="inlineStr">
+        <is>
+          <t>Razem koszty twarde</t>
+        </is>
+      </c>
+      <c r="B29" s="46" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="52">
+        <f>SUM(D21:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="46" t="n"/>
+      <c r="F29" s="46" t="n"/>
       <c r="G29" s="46" t="n"/>
       <c r="H29" s="46" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="44">
-      <c r="A30" s="48" t="inlineStr">
-        <is>
-          <t>PODSUMOWANIE</t>
-        </is>
-      </c>
+      <c r="A30" s="46" t="n"/>
       <c r="G30" s="46" t="n"/>
       <c r="H30" s="46" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="44">
-      <c r="A31" s="62" t="inlineStr">
-        <is>
-          <t>Nagrody (brutto dla laureatów, bez VAT)</t>
-        </is>
-      </c>
-      <c r="B31" s="46" t="n"/>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="65">
-        <f>Wyjaśnienia!$B$18+Wyjaśnienia!$B$21+Wyjaśnienia!$B$22+Wyjaśnienia!$B$19*Wyjaśnienia!$B$20</f>
-        <v/>
-      </c>
-      <c r="E31" s="46" t="n"/>
-      <c r="F31" s="46" t="n"/>
+      <c r="A31" s="48" t="inlineStr">
+        <is>
+          <t>PODSUMOWANIE</t>
+        </is>
+      </c>
       <c r="G31" s="46" t="n"/>
       <c r="H31" s="46" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="44">
       <c r="A32" s="62" t="inlineStr">
         <is>
-          <t>Praca organizatora</t>
+          <t>Nagrody (brutto dla laureatów, bez VAT)</t>
         </is>
       </c>
       <c r="B32" s="46" t="n"/>
       <c r="C32" s="46" t="n"/>
-      <c r="D32" s="51">
-        <f>E17</f>
+      <c r="D32" s="65">
+        <f>Wyjaśnienia!$B$18+Wyjaśnienia!$B$21+Wyjaśnienia!$B$22+Wyjaśnienia!$B$19*Wyjaśnienia!$B$20</f>
         <v/>
       </c>
       <c r="E32" s="46" t="n"/>
@@ -2522,13 +2528,13 @@
     <row r="33" ht="15" customHeight="1" s="44">
       <c r="A33" s="62" t="inlineStr">
         <is>
-          <t>Koszty twarde</t>
+          <t>Praca organizatora</t>
         </is>
       </c>
       <c r="B33" s="46" t="n"/>
       <c r="C33" s="46" t="n"/>
       <c r="D33" s="51">
-        <f>D28</f>
+        <f>E17</f>
         <v/>
       </c>
       <c r="E33" s="46" t="n"/>
@@ -2539,43 +2545,43 @@
     <row r="34" ht="15" customHeight="1" s="44">
       <c r="A34" s="62" t="inlineStr">
         <is>
-          <t>Rezerwa (od pracy i kosztów, bez nagród)</t>
-        </is>
-      </c>
-      <c r="D34" s="46">
-        <f>(D32+D33)*Wyjaśnienia!$B$30</f>
-        <v/>
-      </c>
+          <t>Koszty twarde</t>
+        </is>
+      </c>
+      <c r="B34" s="46" t="n"/>
+      <c r="C34" s="46" t="n"/>
+      <c r="D34" s="51">
+        <f>D29</f>
+        <v/>
+      </c>
+      <c r="E34" s="46" t="n"/>
+      <c r="F34" s="46" t="n"/>
       <c r="G34" s="46" t="n"/>
       <c r="H34" s="46" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="44">
-      <c r="A35" s="49" t="inlineStr">
-        <is>
-          <t>RAZEM NETTO</t>
-        </is>
-      </c>
-      <c r="B35" s="46" t="n"/>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="52">
-        <f>SUM(D31:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="46" t="n"/>
-      <c r="F35" s="46" t="n"/>
+      <c r="A35" s="62" t="inlineStr">
+        <is>
+          <t>Rezerwa (od pracy i kosztów, bez nagród)</t>
+        </is>
+      </c>
+      <c r="D35" s="46">
+        <f>(D33+D34)*Wyjaśnienia!$B$30</f>
+        <v/>
+      </c>
       <c r="G35" s="46" t="n"/>
       <c r="H35" s="46" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="44">
-      <c r="A36" s="62" t="inlineStr">
-        <is>
-          <t>VAT</t>
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>RAZEM NETTO</t>
         </is>
       </c>
       <c r="B36" s="46" t="n"/>
       <c r="C36" s="46" t="n"/>
-      <c r="D36" s="51">
-        <f>D35*Wyjaśnienia!$B$33</f>
+      <c r="D36" s="52">
+        <f>SUM(D32:D35)</f>
         <v/>
       </c>
       <c r="E36" s="46" t="n"/>
@@ -2584,15 +2590,15 @@
       <c r="H36" s="46" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="44">
-      <c r="A37" s="49" t="inlineStr">
-        <is>
-          <t>DO ZAPŁATY BRUTTO - ta liczba trafia na fakturę</t>
+      <c r="A37" s="62" t="inlineStr">
+        <is>
+          <t>VAT</t>
         </is>
       </c>
       <c r="B37" s="46" t="n"/>
       <c r="C37" s="46" t="n"/>
-      <c r="D37" s="68">
-        <f>D35+D36</f>
+      <c r="D37" s="51">
+        <f>D36*Wyjaśnienia!$B$33</f>
         <v/>
       </c>
       <c r="E37" s="46" t="n"/>
@@ -2600,7 +2606,23 @@
       <c r="G37" s="46" t="n"/>
       <c r="H37" s="46" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1" s="44"/>
+    <row r="38" ht="15" customHeight="1" s="44">
+      <c r="A38" s="49" t="inlineStr">
+        <is>
+          <t>DO ZAPŁATY BRUTTO - ta liczba trafia na fakturę</t>
+        </is>
+      </c>
+      <c r="B38" s="46" t="n"/>
+      <c r="C38" s="46" t="n"/>
+      <c r="D38" s="68">
+        <f>D36+D37</f>
+        <v/>
+      </c>
+      <c r="E38" s="46" t="n"/>
+      <c r="F38" s="46" t="n"/>
+      <c r="G38" s="46" t="n"/>
+      <c r="H38" s="46" t="n"/>
+    </row>
     <row r="39" ht="15" customHeight="1" s="44"/>
     <row r="40" ht="15" customHeight="1" s="44"/>
     <row r="41" ht="15" customHeight="1" s="44"/>
@@ -2674,8 +2696,8 @@
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4399,7 +4421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="54" customWidth="1" style="46" min="1" max="1"/>
@@ -4788,16 +4810,14 @@
     <row r="22" ht="15" customHeight="1" s="44">
       <c r="A22" s="46" t="inlineStr">
         <is>
-          <t>Transport oryginałów w obie strony (netto)</t>
-        </is>
-      </c>
-      <c r="B22" s="51">
-        <f>Wyjaśnienia!$B$61*2</f>
-        <v/>
-      </c>
-      <c r="C22" s="71">
-        <f>Wyjaśnienia!$B$60</f>
-        <v/>
+          <t>Honoraria jury za etap przygotowawczy: karta oceny i wagi kryteriów (netto)</t>
+        </is>
+      </c>
+      <c r="B22" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="71" t="n">
+        <v>1</v>
       </c>
       <c r="D22" s="51">
         <f>B22*C22</f>
@@ -4805,22 +4825,23 @@
       </c>
       <c r="E22" s="46" t="inlineStr">
         <is>
-          <t>szacunek, nie oferta; organizator pokrywa obie strony</t>
+          <t>DO USTALENIA - etap przed naborem, osobny od oceny zgłoszeń; obejmuje opisy przedziałów punktowych i przykłady ich zastosowania</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="44">
       <c r="A23" s="46" t="inlineStr">
         <is>
-          <t>Ubezpieczenie prac na czas wystawy (netto)</t>
+          <t>Transport oryginałów w obie strony (netto)</t>
         </is>
       </c>
       <c r="B23" s="51">
-        <f>Wyjaśnienia!$B$62</f>
-        <v/>
-      </c>
-      <c r="C23" s="71" t="n">
-        <v>1</v>
+        <f>Wyjaśnienia!$B$61*2</f>
+        <v/>
+      </c>
+      <c r="C23" s="71">
+        <f>Wyjaśnienia!$B$60</f>
+        <v/>
       </c>
       <c r="D23" s="51">
         <f>B23*C23</f>
@@ -4828,18 +4849,19 @@
       </c>
       <c r="E23" s="46" t="inlineStr">
         <is>
-          <t>szacunek przy sumie deklarowanej rzędu 100 tys. zł</t>
+          <t>szacunek, nie oferta; organizator pokrywa obie strony</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="44">
       <c r="A24" s="46" t="inlineStr">
         <is>
-          <t>Realizacja wystawy przy gali i wernisażu w galerii (netto)</t>
-        </is>
-      </c>
-      <c r="B24" s="59" t="n">
-        <v>0</v>
+          <t>Ubezpieczenie prac na czas wystawy (netto)</t>
+        </is>
+      </c>
+      <c r="B24" s="51">
+        <f>Wyjaśnienia!$B$62</f>
+        <v/>
       </c>
       <c r="C24" s="71" t="n">
         <v>1</v>
@@ -4850,14 +4872,14 @@
       </c>
       <c r="E24" s="46" t="inlineStr">
         <is>
-          <t>DO WYCENY - zawieszenie, oświetlenie, opisy prac w dwóch miejscach, przewóz między nimi, obsługa wernisażu</t>
+          <t>szacunek przy sumie deklarowanej rzędu 100 tys. zł</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="44">
       <c r="A25" s="46" t="inlineStr">
         <is>
-          <t>Obsługa prawna regulaminu plakatu (netto)</t>
+          <t>Realizacja wystawy przy gali i wernisażu w galerii (netto)</t>
         </is>
       </c>
       <c r="B25" s="59" t="n">
@@ -4872,14 +4894,14 @@
       </c>
       <c r="E25" s="46" t="inlineStr">
         <is>
-          <t>DO WYCENY - odrębne zlecenie kancelarii, nie złożone</t>
+          <t>DO WYCENY - zawieszenie, oświetlenie, opisy prac w dwóch miejscach, przewóz między nimi, obsługa wernisażu</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="44">
       <c r="A26" s="46" t="inlineStr">
         <is>
-          <t>Dojazd i nocleg finalistów na galę (netto)</t>
+          <t>Obsługa prawna regulaminu plakatu (netto)</t>
         </is>
       </c>
       <c r="B26" s="59" t="n">
@@ -4894,14 +4916,14 @@
       </c>
       <c r="E26" s="46" t="inlineStr">
         <is>
-          <t>DO WYCENY - jak przy plebiscycie piosenki</t>
+          <t>DO WYCENY - odrębne zlecenie kancelarii, nie złożone</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="44">
       <c r="A27" s="46" t="inlineStr">
         <is>
-          <t>Polisa: wycena prac, rozszerzenie na przechowywanie i okres po sprzedaży (netto)</t>
+          <t>Dojazd i nocleg finalistów na galę (netto)</t>
         </is>
       </c>
       <c r="B27" s="59" t="n">
@@ -4916,105 +4938,127 @@
       </c>
       <c r="E27" s="46" t="inlineStr">
         <is>
+          <t>DO WYCENY - jak przy plebiscycie piosenki</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="44">
+      <c r="A28" s="46" t="inlineStr">
+        <is>
+          <t>Polisa: wycena prac, rozszerzenie na przechowywanie i okres po sprzedaży (netto)</t>
+        </is>
+      </c>
+      <c r="B28" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="51">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="46" t="inlineStr">
+        <is>
           <t>DO WYCENY - polisa ma objąć cały uzgodniony okres: transport w obie strony, przechowywanie u organizatora, obie wystawy oraz czas po sprzedaży do wydania pracy nabywcy; do ustalenia suma ubezpieczenia na pracę, udział własny i procedura zgłoszenia szkody</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="44">
-      <c r="A28" s="53" t="inlineStr">
+    <row r="29" ht="15" customHeight="1" s="44">
+      <c r="A29" s="53" t="inlineStr">
         <is>
           <t>Razem koszty twarde</t>
         </is>
       </c>
-      <c r="D28" s="54">
-        <f>SUM(D18:D27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="44">
-      <c r="A29" s="46" t="n"/>
+      <c r="D29">
+        <f>SUM(D18:D28)</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="44">
-      <c r="A30" s="53" t="inlineStr">
+      <c r="A30" s="46" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="44">
+      <c r="A31" s="53" t="inlineStr">
         <is>
           <t>PODSUMOWANIE</t>
         </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="44">
-      <c r="A31" s="46" t="inlineStr">
-        <is>
-          <t>Nagrody (brutto dla laureatów, bez VAT)</t>
-        </is>
-      </c>
-      <c r="D31" s="51">
-        <f>Wyjaśnienia!$B$54+Wyjaśnienia!$B$55</f>
-        <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="44">
       <c r="A32" s="46" t="inlineStr">
         <is>
-          <t>Praca organizatora</t>
+          <t>Nagrody (brutto dla laureatów, bez VAT)</t>
         </is>
       </c>
       <c r="D32" s="51">
-        <f>E14</f>
+        <f>Wyjaśnienia!$B$54+Wyjaśnienia!$B$55</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="44">
       <c r="A33" s="46" t="inlineStr">
         <is>
-          <t>Koszty twarde bez nagród</t>
+          <t>Praca organizatora</t>
         </is>
       </c>
       <c r="D33" s="51">
-        <f>D28-D31</f>
+        <f>E14</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="44">
       <c r="A34" s="46" t="inlineStr">
         <is>
+          <t>Koszty twarde bez nagród</t>
+        </is>
+      </c>
+      <c r="D34" s="51">
+        <f>D29-D32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="44">
+      <c r="A35" s="46" t="inlineStr">
+        <is>
           <t>Rezerwa (od pracy i kosztów, bez nagród)</t>
         </is>
       </c>
-      <c r="D34" s="51">
-        <f>(D32+D33)*Wyjaśnienia!$B$63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="44">
-      <c r="A35" s="53" t="inlineStr">
+      <c r="D35" s="51">
+        <f>(D33+D34)*Wyjaśnienia!$B$63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="44">
+      <c r="A36" s="53" t="inlineStr">
         <is>
           <t>RAZEM NETTO</t>
         </is>
       </c>
-      <c r="D35" s="54">
-        <f>SUM(D31:D34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="44">
-      <c r="A36" s="46" t="inlineStr">
+      <c r="D36" s="54">
+        <f>SUM(D32:D35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="44">
+      <c r="A37" s="46" t="inlineStr">
         <is>
           <t>VAT</t>
         </is>
       </c>
-      <c r="D36" s="51">
-        <f>D35*Wyjaśnienia!$B$33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="44">
-      <c r="A37" s="53" t="inlineStr">
+      <c r="D37" s="51">
+        <f>D36*Wyjaśnienia!$B$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="53" t="inlineStr">
         <is>
           <t>DO ZAPŁATY BRUTTO - ta liczba trafia na fakturę</t>
         </is>
       </c>
-      <c r="D37" s="54">
-        <f>D35+D36</f>
+      <c r="D38" s="54">
+        <f>D36+D37</f>
         <v/>
       </c>
     </row>
@@ -5025,7 +5069,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5824,7 +5868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="54" customWidth="1" style="46" min="1" max="1"/>
@@ -6239,7 +6283,7 @@
     <row r="23" ht="15" customHeight="1" s="44">
       <c r="A23" s="46" t="inlineStr">
         <is>
-          <t>Przygotowanie techniczne zwiastunów do emisji galowej (netto)</t>
+          <t>Honoraria jury za etap przygotowawczy: karta oceny i wagi kryteriów (netto)</t>
         </is>
       </c>
       <c r="B23" s="51" t="n">
@@ -6254,14 +6298,14 @@
       </c>
       <c r="E23" s="46" t="inlineStr">
         <is>
-          <t>DO WYCENY - pobranie pięciu zwiastunów w jakości emisyjnej, zgodność formatów, normalizacja dźwięku, plansze z tytułami; zwiastun dostarcza autor, Organizator nie montuje fragmentów filmów</t>
+          <t>DO USTALENIA - etap przed naborem, osobny od oceny zgłoszeń; obejmuje opisy przedziałów punktowych i przykłady ich zastosowania</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="44">
       <c r="A24" s="46" t="inlineStr">
         <is>
-          <t>Pokazy kinowe filmów finałowych (netto)</t>
+          <t>Przygotowanie techniczne zwiastunów do emisji galowej (netto)</t>
         </is>
       </c>
       <c r="B24" s="51" t="n">
@@ -6276,14 +6320,14 @@
       </c>
       <c r="E24" s="46" t="inlineStr">
         <is>
-          <t>DO WYCENY - opracowanie techniczne kopii, napisy i materiały informacyjne dla zestawu dziesiątki; zależy od pozyskania dystrybutora (§ 10 ust. 4), z którym Organizator może uzgodnić pokrycie tych kosztów</t>
+          <t>DO WYCENY - pobranie pięciu zwiastunów w jakości emisyjnej, zgodność formatów, normalizacja dźwięku, plansze z tytułami; zwiastun dostarcza autor, Organizator nie montuje fragmentów filmów</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="44">
       <c r="A25" s="46" t="inlineStr">
         <is>
-          <t>Dojazd i nocleg finalistów na galę (netto)</t>
+          <t>Pokazy kinowe filmów finałowych (netto)</t>
         </is>
       </c>
       <c r="B25" s="51" t="n">
@@ -6298,14 +6342,14 @@
       </c>
       <c r="E25" s="46" t="inlineStr">
         <is>
-          <t>DO WYCENY - jak przy plebiscycie piosenki; dziesięciu finalistów, często z ekipą</t>
+          <t>DO WYCENY - opracowanie techniczne kopii, napisy i materiały informacyjne dla zestawu dziesiątki; zależy od pozyskania dystrybutora (§ 10 ust. 4), z którym Organizator może uzgodnić pokrycie tych kosztów</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="44">
       <c r="A26" s="46" t="inlineStr">
         <is>
-          <t>Obsługa prawna regulaminu filmu (netto)</t>
+          <t>Dojazd i nocleg finalistów na galę (netto)</t>
         </is>
       </c>
       <c r="B26" s="51" t="n">
@@ -6320,104 +6364,127 @@
       </c>
       <c r="E26" s="46" t="inlineStr">
         <is>
+          <t>DO WYCENY - jak przy plebiscycie piosenki; dziesięciu finalistów, często z ekipą</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="44">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>Obsługa prawna regulaminu filmu (netto)</t>
+        </is>
+      </c>
+      <c r="B27" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="51">
+        <f>B27*C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="46" t="inlineStr">
+        <is>
           <t>DO WYCENY - odrębne zlecenie kancelarii, nie złożone; siedem miejsc wypisanych na końcu regulaminu, w tym status filmu wygenerowanego w całości</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="44">
-      <c r="A27" s="53" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="53" t="inlineStr">
         <is>
           <t>Razem koszty twarde</t>
         </is>
       </c>
-      <c r="B27" s="51" t="n"/>
-      <c r="C27" s="71" t="n"/>
-      <c r="D27" s="54">
-        <f>SUM(D19:D26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="44">
-      <c r="A29" s="53" t="inlineStr">
+      <c r="B28" s="51" t="n"/>
+      <c r="C28" s="71" t="n"/>
+      <c r="D28" s="54">
+        <f>SUM(D19:D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="44"/>
+    <row r="30" ht="15" customHeight="1" s="44">
+      <c r="A30" s="53" t="inlineStr">
         <is>
           <t>PODSUMOWANIE</t>
         </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="44">
-      <c r="A30" s="46" t="inlineStr">
-        <is>
-          <t>Nagrody (brutto dla laureatów, bez VAT)</t>
-        </is>
-      </c>
-      <c r="D30" s="51">
-        <f>Wyjaśnienia!$B$67+Wyjaśnienia!$B$68</f>
-        <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="44">
       <c r="A31" s="46" t="inlineStr">
         <is>
-          <t>Praca organizatora</t>
+          <t>Nagrody (brutto dla laureatów, bez VAT)</t>
         </is>
       </c>
       <c r="D31" s="51">
-        <f>E15</f>
+        <f>Wyjaśnienia!$B$67+Wyjaśnienia!$B$68</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="44">
       <c r="A32" s="46" t="inlineStr">
         <is>
-          <t>Koszty twarde bez nagród</t>
+          <t>Praca organizatora</t>
         </is>
       </c>
       <c r="D32" s="51">
-        <f>D27-D30</f>
+        <f>E15</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="44">
       <c r="A33" s="46" t="inlineStr">
         <is>
+          <t>Koszty twarde bez nagród</t>
+        </is>
+      </c>
+      <c r="D33" s="51">
+        <f>D28-D31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="44">
+      <c r="A34" s="46" t="inlineStr">
+        <is>
           <t>Rezerwa (od pracy i kosztów, bez nagród)</t>
         </is>
       </c>
-      <c r="D33" s="51">
-        <f>(D31+D32)*Wyjaśnienia!$B$74</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="44">
-      <c r="A34" s="53" t="inlineStr">
+      <c r="D34" s="51">
+        <f>(D32+D33)*Wyjaśnienia!$B$74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="44">
+      <c r="A35" s="53" t="inlineStr">
         <is>
           <t>RAZEM NETTO</t>
         </is>
       </c>
-      <c r="D34" s="54">
-        <f>SUM(D30:D33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="44">
-      <c r="A35" s="46" t="inlineStr">
+      <c r="D35" s="54">
+        <f>SUM(D31:D34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="44">
+      <c r="A36" s="46" t="inlineStr">
         <is>
           <t>VAT</t>
         </is>
       </c>
-      <c r="D35" s="51">
-        <f>D34*Wyjaśnienia!$B$33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="44">
-      <c r="A36" s="53" t="inlineStr">
+      <c r="D36" s="51">
+        <f>D35*Wyjaśnienia!$B$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="53" t="inlineStr">
         <is>
           <t>DO ZAPŁATY BRUTTO - ta liczba trafia na fakturę</t>
         </is>
       </c>
-      <c r="D36" s="54">
-        <f>D34+D35</f>
+      <c r="D37" s="54">
+        <f>D35+D36</f>
         <v/>
       </c>
     </row>
@@ -6428,7 +6495,7 @@
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -4027,7 +4027,7 @@
       </c>
       <c r="E19" s="56" t="inlineStr">
         <is>
-          <t>nagranie i premiera na początku 2027, otwiera nabór</t>
+          <t>premiera w czasie trwania naboru w 2027; otwarcie edycji nie jest od niej uzależnione</t>
         </is>
       </c>
       <c r="F19" s="46" t="n"/>
@@ -4970,7 +4970,7 @@
           <t>Razem koszty twarde</t>
         </is>
       </c>
-      <c r="D29">
+      <c r="D29" s="46">
         <f>SUM(D18:D28)</f>
         <v/>
       </c>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B19" s="55" t="n">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="C19" s="56" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="B21" s="55" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="C21" s="56" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="B22" s="55" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="C22" s="56" t="inlineStr">
         <is>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="B10" s="46" t="inlineStr">
         <is>
-          <t>Mecenas konkursu plakatu</t>
+          <t>Mecenas plebiscytu na plakat</t>
         </is>
       </c>
       <c r="C10" s="52">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C29" s="56" t="inlineStr">
         <is>
-          <t>Ten sam mosiężny medal co w konkursie rozmów, cena jak w Budżecie Nagrody.</t>
+          <t>Ten sam mosiężny medal co w plebiscycie na rozmowę, cena jak w Budżecie Nagrody.</t>
         </is>
       </c>
       <c r="D29" s="46" t="n"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C56" s="43" t="inlineStr">
         <is>
-          <t>Ten sam mosiężny medal co w konkursie rozmów, cena jak w Budżecie Nagrody.</t>
+          <t>Ten sam mosiężny medal co w plebiscycie na rozmowę, cena jak w Budżecie Nagrody.</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F12" s="46" t="inlineStr">
         <is>
-          <t>Powyżej progu zgłoszeń pierwsze przejście oceny przechodzi na Akademię, tak jak w konkursie rozmów - dlatego te godziny nie rosną z naborem. Minuty na zgłoszenie dotyczą wyłącznie kontroli formalnej.</t>
+          <t>Powyżej progu zgłoszeń pierwsze przejście oceny przechodzi na Akademię, tak jak w plebiscycie na rozmowę - dlatego te godziny nie rosną z naborem. Minuty na zgłoszenie dotyczą wyłącznie kontroli formalnej.</t>
         </is>
       </c>
       <c r="G12" s="46" t="n"/>
@@ -4442,7 +4442,7 @@
     <row r="2" ht="15" customHeight="1" s="44">
       <c r="A2" s="46" t="inlineStr">
         <is>
-          <t>Finansuje: Mecenas konkursu plakatu. Kwoty netto, chyba że napisano inaczej.</t>
+          <t>Finansuje: Mecenas plebiscytu na plakat. Kwoty netto, chyba że napisano inaczej.</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="F14" s="46" t="inlineStr">
         <is>
-          <t>Powyżej progu zgłoszeń pierwsze przejście oceny przechodzi na Akademię, tak jak w konkursie rozmów - dlatego te godziny nie rosną z naborem. Minuty na zgłoszenie dotyczą wyłącznie kontroli formalnej.</t>
+          <t>Powyżej progu zgłoszeń pierwsze przejście oceny przechodzi na Akademię, tak jak w plebiscycie na rozmowę - dlatego te godziny nie rosną z naborem. Minuty na zgłoszenie dotyczą wyłącznie kontroli formalnej.</t>
         </is>
       </c>
     </row>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -254,7 +254,7 @@
     <t xml:space="preserve">Maksymalnie 20 zgłoszeń na czytelnika (regulamin § 8).</t>
   </si>
   <si>
-    <t xml:space="preserve">Maksimum zgłoszeń na czytelnika</t>
+    <t xml:space="preserve">Czas na jeden odczyt rozmowy wraz z kartą oceny (minut)</t>
   </si>
   <si>
     <t xml:space="preserve">PLAKAT - PARAMETRY</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">JAK TO SIĘ SKALUJE</t>
   </si>
   <si>
-    <t xml:space="preserve">Vouchery i honoraria za obejrzenia rosną wprost z liczbą zgłoszeń, więc sponsor płaci za wykonaną pracę, a nie za prognozę. Ludzi trzeba jednak znaleźć osobno: kolumny Potrzebnych liczą osoby od liczby ODCZYTÓW i OBEJRZEŃ, nie od liczby zgłoszeń. Tabela przy większych wolumenach nie modeluje odrębnie trybu jednoosobowego, drugich odczytów poniżej progu ani audytu losowego - te trzy rzeczy trzeba policzyć osobno przed ogłoszeniem progu.</t>
+    <t xml:space="preserve">Vouchery i honoraria za obejrzenia rosną wprost z liczbą zgłoszeń, więc sponsor płaci za wykonaną pracę, a nie za prognozę. Kolumna godzin liczy pracę akademii od liczby ODCZYTÓW, po przyjętym czasie jednego odczytu z zakładki Wyjaśnienia; ilu osób to wymaga, zależy od tego, ile godzin daje pojedynczy czytelnik, i tego tabela nie przesądza. Przy większych wolumenach nie modeluje też odrębnie trybu jednoosobowego, drugich odczytów poniżej progu ani audytu losowego - te trzy rzeczy trzeba policzyć osobno przed ogłoszeniem progu.</t>
   </si>
   <si>
     <t xml:space="preserve">Zgłoszeń w edycji</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">Koszt voucherów</t>
   </si>
   <si>
-    <t xml:space="preserve">Potrzebnych czytelników</t>
+    <t xml:space="preserve">Godzin pracy akademii</t>
   </si>
   <si>
     <t xml:space="preserve">Filmów w edycji</t>
@@ -1338,7 +1338,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1412,6 +1412,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2399,10 +2403,13 @@
       <c r="A50" s="3" t="s">
         <v>75</v>
       </c>
+      <c r="B50" s="19" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="19" t="s">
+      <c r="A52" s="20" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2410,7 +2417,7 @@
       <c r="A53" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B53" s="20" t="n">
+      <c r="B53" s="21" t="n">
         <v>150</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -2454,7 +2461,7 @@
       <c r="A57" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B57" s="20" t="n">
+      <c r="B57" s="21" t="n">
         <v>5</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -2465,7 +2472,7 @@
       <c r="A58" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B58" s="20" t="n">
+      <c r="B58" s="21" t="n">
         <v>10</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -2487,7 +2494,7 @@
       <c r="A60" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B60" s="20" t="n">
+      <c r="B60" s="21" t="n">
         <v>10</v>
       </c>
       <c r="C60" s="1" t="s">
@@ -2529,7 +2536,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="19" t="s">
+      <c r="A65" s="20" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2806,20 +2813,20 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>60</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="24" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$17/60</f>
         <v>60</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="25" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$16</f>
         <v>13200</v>
       </c>
@@ -2830,20 +2837,20 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="24" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$17/60</f>
         <v>24</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="25" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$16</f>
         <v>5280</v>
       </c>
@@ -2854,20 +2861,20 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="24" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$17/60</f>
         <v>50</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="25" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$16</f>
         <v>11000</v>
       </c>
@@ -2878,20 +2885,20 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="24" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$17/60</f>
         <v>23</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="25" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$16</f>
         <v>5060</v>
       </c>
@@ -2902,20 +2909,20 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="24" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$17/60</f>
         <v>20</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="25" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$16</f>
         <v>4400</v>
       </c>
@@ -2926,20 +2933,20 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="24" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$17/60</f>
         <v>20</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="25" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$16</f>
         <v>4400</v>
       </c>
@@ -2950,20 +2957,20 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="24" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$17/60</f>
         <v>40</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="25" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$16</f>
         <v>8800</v>
       </c>
@@ -2974,20 +2981,20 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="24" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$17/60</f>
         <v>25</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="25" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$16</f>
         <v>5500</v>
       </c>
@@ -2998,20 +3005,20 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="24" t="n">
         <f aca="false">B15+C15*Wyjaśnienia!$B$17/60</f>
         <v>25</v>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="25" t="n">
         <f aca="false">D15*Wyjaśnienia!$B$16</f>
         <v>5500</v>
       </c>
@@ -3022,20 +3029,20 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="24" t="n">
         <f aca="false">B16+C16*Wyjaśnienia!$B$17/60</f>
         <v>40</v>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="E16" s="25" t="n">
         <f aca="false">D16*Wyjaśnienia!$B$16</f>
         <v>8800</v>
       </c>
@@ -3051,7 +3058,7 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="26" t="n">
         <f aca="false">SUM(D7:D16)</f>
         <v>327</v>
       </c>
@@ -3105,16 +3112,16 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>1200</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="25" t="n">
         <f aca="false">B21*C21</f>
         <v>1200</v>
       </c>
@@ -3126,16 +3133,16 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D22" s="25" t="n">
         <f aca="false">B22*C22</f>
         <v>1500</v>
       </c>
@@ -3147,16 +3154,16 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D23" s="25" t="n">
         <f aca="false">B23*C23</f>
         <v>250</v>
       </c>
@@ -3168,16 +3175,16 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>32000</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="24" t="n">
+      <c r="D24" s="25" t="n">
         <f aca="false">B24*C24</f>
         <v>32000</v>
       </c>
@@ -3191,16 +3198,16 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="25" t="n">
         <f aca="false">B25*C25</f>
         <v>0</v>
       </c>
@@ -3210,16 +3217,16 @@
       <c r="F25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <v>15000</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="24" t="n">
+      <c r="D26" s="25" t="n">
         <f aca="false">B26*C26</f>
         <v>15000</v>
       </c>
@@ -3231,16 +3238,16 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <v>4000</v>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C27" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="24" t="n">
+      <c r="D27" s="25" t="n">
         <f aca="false">B27*C27</f>
         <v>4000</v>
       </c>
@@ -3250,16 +3257,16 @@
       <c r="F27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="24" t="n">
+      <c r="D28" s="25" t="n">
         <f aca="false">B28*C28</f>
         <v>0</v>
       </c>
@@ -3303,12 +3310,12 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="22" t="s">
         <v>173</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="24" t="n">
+      <c r="D32" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$18+Wyjaśnienia!$B$21+Wyjaśnienia!$B$22+Wyjaśnienia!$B$19*Wyjaśnienia!$B$20</f>
         <v>371000</v>
       </c>
@@ -3318,7 +3325,7 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="22" t="s">
         <v>174</v>
       </c>
       <c r="B33" s="3"/>
@@ -3333,7 +3340,7 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="22" t="s">
         <v>175</v>
       </c>
       <c r="B34" s="3"/>
@@ -3348,7 +3355,7 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="22" t="s">
         <v>176</v>
       </c>
       <c r="D35" s="3" t="n">
@@ -3374,7 +3381,7 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="22" t="s">
         <v>178</v>
       </c>
       <c r="B37" s="3"/>
@@ -3394,7 +3401,7 @@
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="27" t="n">
+      <c r="D38" s="28" t="n">
         <f aca="false">D36+D37</f>
         <v>629756.064</v>
       </c>
@@ -3586,20 +3593,20 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
         <v>181</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>45</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="24" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$17/60</f>
         <v>45</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="25" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$16</f>
         <v>9900</v>
       </c>
@@ -3610,20 +3617,20 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="24" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$17/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="25" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$16</f>
         <v>8800</v>
       </c>
@@ -3634,20 +3641,20 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="24" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$17/60</f>
         <v>10</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="25" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$16</f>
         <v>2200</v>
       </c>
@@ -3658,20 +3665,20 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="24" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$17/60</f>
         <v>50</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="25" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$16</f>
         <v>11000</v>
       </c>
@@ -3682,20 +3689,20 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="24" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$17/60</f>
         <v>25</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="25" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$16</f>
         <v>5500</v>
       </c>
@@ -3706,20 +3713,20 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="23" t="n">
         <v>160</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="24" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$17/60</f>
         <v>160</v>
       </c>
-      <c r="E12" s="24" t="n">
+      <c r="E12" s="25" t="n">
         <f aca="false">D12*Wyjaśnienia!$B$16</f>
         <v>35200</v>
       </c>
@@ -3730,20 +3737,20 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="24" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$17/60</f>
         <v>50</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="25" t="n">
         <f aca="false">D13*Wyjaśnienia!$B$16</f>
         <v>11000</v>
       </c>
@@ -3754,20 +3761,20 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="23" t="n">
         <v>72</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="24" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$17/60</f>
         <v>72</v>
       </c>
-      <c r="E14" s="24" t="n">
+      <c r="E14" s="25" t="n">
         <f aca="false">D14*Wyjaśnienia!$B$16</f>
         <v>15840</v>
       </c>
@@ -3779,7 +3786,7 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="26" t="n">
         <f aca="false">SUM(D7:D14)</f>
         <v>452</v>
       </c>
@@ -3834,16 +3841,16 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>3000</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="25" t="n">
         <f aca="false">B19*C19</f>
         <v>3000</v>
       </c>
@@ -3855,16 +3862,16 @@
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>6000</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="25" t="n">
         <f aca="false">B20*C20</f>
         <v>6000</v>
       </c>
@@ -3878,16 +3885,16 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>10000</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="25" t="n">
         <f aca="false">B21*C21</f>
         <v>10000</v>
       </c>
@@ -3899,16 +3906,16 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>40000</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D22" s="25" t="n">
         <f aca="false">B22*C22</f>
         <v>40000</v>
       </c>
@@ -3920,16 +3927,16 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>4000</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D23" s="25" t="n">
         <f aca="false">B23*C23</f>
         <v>4000</v>
       </c>
@@ -3941,16 +3948,16 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>3000</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="24" t="n">
+      <c r="D24" s="25" t="n">
         <f aca="false">B24*C24</f>
         <v>3000</v>
       </c>
@@ -3962,16 +3969,16 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <v>4000</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="25" t="n">
         <f aca="false">B25*C25</f>
         <v>4000</v>
       </c>
@@ -3983,16 +3990,16 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="24" t="n">
+      <c r="D26" s="25" t="n">
         <f aca="false">B26*C26</f>
         <v>0</v>
       </c>
@@ -4004,16 +4011,16 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <v>15000</v>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C27" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="24" t="n">
+      <c r="D27" s="25" t="n">
         <f aca="false">B27*C27</f>
         <v>15000</v>
       </c>
@@ -4025,16 +4032,16 @@
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <v>6000</v>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="24" t="n">
+      <c r="D28" s="25" t="n">
         <f aca="false">B28*C28</f>
         <v>6000</v>
       </c>
@@ -4046,16 +4053,16 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="27" t="n">
         <v>30000</v>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="24" t="n">
+      <c r="D29" s="25" t="n">
         <f aca="false">B29*C29</f>
         <v>30000</v>
       </c>
@@ -4067,31 +4074,31 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="29" t="s">
         <v>219</v>
       </c>
       <c r="B30" s="18" t="n">
         <v>4500</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="30" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">B30*C30</f>
         <v>4500</v>
       </c>
-      <c r="F30" s="28" t="s">
+      <c r="F30" s="29" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="29" t="s">
         <v>221</v>
       </c>
       <c r="B31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="30" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="8" t="n">
@@ -4101,7 +4108,7 @@
       <c r="E31" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F31" s="28"/>
+      <c r="F31" s="29"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
@@ -4119,12 +4126,12 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
+      <c r="A33" s="31"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
@@ -4141,7 +4148,7 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="22" t="s">
         <v>174</v>
       </c>
       <c r="B35" s="3"/>
@@ -4156,7 +4163,7 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="22" t="s">
         <v>175</v>
       </c>
       <c r="B36" s="3"/>
@@ -4171,7 +4178,7 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="22" t="s">
         <v>223</v>
       </c>
       <c r="B37" s="3"/>
@@ -4201,7 +4208,7 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="22" t="s">
         <v>178</v>
       </c>
       <c r="B39" s="3"/>
@@ -4221,7 +4228,7 @@
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="27" t="n">
+      <c r="D40" s="28" t="n">
         <f aca="false">D38+D39</f>
         <v>359679.06</v>
       </c>
@@ -4412,20 +4419,20 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="24" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$23/60</f>
         <v>25</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="25" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$16</f>
         <v>5500</v>
       </c>
@@ -4436,18 +4443,18 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>227</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="23" t="n">
         <v>40</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23" t="n">
+      <c r="C8" s="24"/>
+      <c r="D8" s="24" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$23/60</f>
         <v>40</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="25" t="n">
         <f aca="false">D8*Wyjaśnienia!$B$16</f>
         <v>8800</v>
       </c>
@@ -4458,18 +4465,18 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23" t="n">
+      <c r="C9" s="24"/>
+      <c r="D9" s="24" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$23/60</f>
         <v>30</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="25" t="n">
         <f aca="false">D9*Wyjaśnienia!$B$16</f>
         <v>6600</v>
       </c>
@@ -4480,18 +4487,18 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23" t="n">
+      <c r="C10" s="24"/>
+      <c r="D10" s="24" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$23/60</f>
         <v>20</v>
       </c>
-      <c r="E10" s="24" t="n">
+      <c r="E10" s="25" t="n">
         <f aca="false">D10*Wyjaśnienia!$B$16</f>
         <v>4400</v>
       </c>
@@ -4502,18 +4509,18 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23" t="n">
+      <c r="C11" s="24"/>
+      <c r="D11" s="24" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$23/60</f>
         <v>50</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="25" t="n">
         <f aca="false">D11*Wyjaśnienia!$B$16</f>
         <v>11000</v>
       </c>
@@ -4529,7 +4536,7 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="26" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>165</v>
       </c>
@@ -4586,17 +4593,17 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$24</f>
         <v>35000</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="25" t="n">
         <f aca="false">B16*C16</f>
         <v>35000</v>
       </c>
@@ -4608,17 +4615,17 @@
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$25</f>
         <v>4000</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="25" t="n">
         <f aca="false">B17*C17</f>
         <v>4000</v>
       </c>
@@ -4630,18 +4637,18 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$26</f>
         <v>7500</v>
       </c>
-      <c r="C18" s="23" t="n">
+      <c r="C18" s="24" t="n">
         <f aca="false">Wyjaśnienia!$B$27</f>
         <v>10</v>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="25" t="n">
         <f aca="false">B18*C18</f>
         <v>75000</v>
       </c>
@@ -4653,17 +4660,17 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$28</f>
         <v>80000</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="25" t="n">
         <f aca="false">B19*C19</f>
         <v>80000</v>
       </c>
@@ -4675,17 +4682,17 @@
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$29</f>
         <v>1200</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="25" t="n">
         <f aca="false">B20*C20</f>
         <v>1200</v>
       </c>
@@ -4697,16 +4704,16 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="25" t="n">
         <f aca="false">B21*C21</f>
         <v>0</v>
       </c>
@@ -4718,16 +4725,16 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D22" s="25" t="n">
         <f aca="false">B22*C22</f>
         <v>0</v>
       </c>
@@ -4737,16 +4744,16 @@
       <c r="F22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D23" s="25" t="n">
         <f aca="false">B23*C23</f>
         <v>0</v>
       </c>
@@ -4758,13 +4765,13 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="29" t="s">
         <v>249</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="30" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -4774,18 +4781,18 @@
       <c r="E24" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="29" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="29" t="s">
         <v>252</v>
       </c>
       <c r="B25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="30" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="8" t="n">
@@ -4795,7 +4802,7 @@
       <c r="E25" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="F25" s="28"/>
+      <c r="F25" s="29"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
@@ -4809,12 +4816,12 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
+      <c r="A27" s="31"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
@@ -4831,12 +4838,12 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="22" t="s">
         <v>173</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="24" t="n">
+      <c r="D29" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$24+Wyjaśnienia!$B$25</f>
         <v>39000</v>
       </c>
@@ -4846,7 +4853,7 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="22" t="s">
         <v>174</v>
       </c>
       <c r="B30" s="3"/>
@@ -4861,7 +4868,7 @@
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="22" t="s">
         <v>254</v>
       </c>
       <c r="B31" s="3"/>
@@ -4876,7 +4883,7 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="22" t="s">
         <v>176</v>
       </c>
       <c r="B32" s="3"/>
@@ -4906,7 +4913,7 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="22" t="s">
         <v>178</v>
       </c>
       <c r="B34" s="3"/>
@@ -4926,7 +4933,7 @@
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="27" t="n">
+      <c r="D35" s="28" t="n">
         <f aca="false">D33+D34</f>
         <v>313158</v>
       </c>
@@ -5042,44 +5049,44 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
@@ -5105,13 +5112,13 @@
       <c r="A7" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="33" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$53/60</f>
         <v>20</v>
       </c>
@@ -5127,11 +5134,11 @@
       <c r="A8" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32" t="n">
+      <c r="C8" s="33"/>
+      <c r="D8" s="33" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$53/60</f>
         <v>30</v>
       </c>
@@ -5147,11 +5154,11 @@
       <c r="A9" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32" t="n">
+      <c r="C9" s="33"/>
+      <c r="D9" s="33" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$53/60</f>
         <v>20</v>
       </c>
@@ -5167,11 +5174,11 @@
       <c r="A10" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="21" t="n">
         <v>35</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32" t="n">
+      <c r="C10" s="33"/>
+      <c r="D10" s="33" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$53/60</f>
         <v>35</v>
       </c>
@@ -5187,11 +5194,11 @@
       <c r="A11" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32" t="n">
+      <c r="C11" s="33"/>
+      <c r="D11" s="33" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$53/60</f>
         <v>15</v>
       </c>
@@ -5207,11 +5214,11 @@
       <c r="A12" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32" t="n">
+      <c r="C12" s="33"/>
+      <c r="D12" s="33" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$53/60</f>
         <v>50</v>
       </c>
@@ -5227,11 +5234,11 @@
       <c r="A13" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32" t="n">
+      <c r="C13" s="33"/>
+      <c r="D13" s="33" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$53/60</f>
         <v>20</v>
       </c>
@@ -5247,7 +5254,7 @@
       <c r="A14" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="34" t="n">
         <f aca="false">SUM(D7:D13)</f>
         <v>190</v>
       </c>
@@ -5260,14 +5267,14 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
@@ -5294,7 +5301,7 @@
         <f aca="false">Wyjaśnienia!$B$54</f>
         <v>90000</v>
       </c>
-      <c r="C18" s="32" t="n">
+      <c r="C18" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="8" t="n">
@@ -5313,7 +5320,7 @@
         <f aca="false">Wyjaśnienia!$B$55</f>
         <v>4000</v>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="8" t="n">
@@ -5332,7 +5339,7 @@
         <f aca="false">Wyjaśnienia!$B$56</f>
         <v>1200</v>
       </c>
-      <c r="C20" s="32" t="n">
+      <c r="C20" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="8" t="n">
@@ -5350,7 +5357,7 @@
       <c r="B21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="32" t="n">
+      <c r="C21" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="8" t="n">
@@ -5368,7 +5375,7 @@
       <c r="B22" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="32" t="n">
+      <c r="C22" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="8" t="n">
@@ -5387,7 +5394,7 @@
         <f aca="false">Wyjaśnienia!$B$61*2</f>
         <v>800</v>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="33" t="n">
         <f aca="false">Wyjaśnienia!$B$60</f>
         <v>10</v>
       </c>
@@ -5407,7 +5414,7 @@
         <f aca="false">Wyjaśnienia!$B$62</f>
         <v>3000</v>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C24" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -5425,7 +5432,7 @@
       <c r="B25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="32" t="n">
+      <c r="C25" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="8" t="n">
@@ -5443,7 +5450,7 @@
       <c r="B26" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="32" t="n">
+      <c r="C26" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="8" t="n">
@@ -5461,7 +5468,7 @@
       <c r="B27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="32" t="n">
+      <c r="C27" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="8" t="n">
@@ -5479,7 +5486,7 @@
       <c r="B28" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="32" t="n">
+      <c r="C28" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="8" t="n">
@@ -5500,12 +5507,12 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="30"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
@@ -5566,7 +5573,7 @@
         <v>35530.4</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
         <v>179</v>
       </c>
@@ -5611,669 +5618,669 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="36" t="s">
         <v>286</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="36" t="s">
         <v>287</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="37" t="s">
         <v>288</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="38" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="29" t="s">
         <v>290</v>
       </c>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$17</f>
         <v>150</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="29" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="29" t="s">
         <v>292</v>
       </c>
-      <c r="B8" s="39" t="n">
+      <c r="B8" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$46</f>
         <v>2</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="29" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="38" t="s">
         <v>294</v>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="41" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="29" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="29" t="s">
         <v>296</v>
       </c>
-      <c r="B10" s="39" t="n">
+      <c r="B10" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$66</f>
         <v>150</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="29" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="B11" s="39" t="n">
+      <c r="B11" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$75</f>
         <v>2</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="29" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="38" t="s">
         <v>300</v>
       </c>
-      <c r="B12" s="40" t="n">
+      <c r="B12" s="41" t="n">
         <f aca="false">B10*B11</f>
         <v>300</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="29" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="37" t="s">
         <v>302</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="38" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="29" t="s">
         <v>304</v>
       </c>
-      <c r="B16" s="41" t="n">
+      <c r="B16" s="42" t="n">
         <f aca="false">Wyjaśnienia!$B$48</f>
         <v>2500</v>
       </c>
-      <c r="C16" s="39" t="n">
+      <c r="C16" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$49</f>
         <v>15</v>
       </c>
-      <c r="D16" s="41" t="n">
+      <c r="D16" s="42" t="n">
         <f aca="false">B16*C16</f>
         <v>37500</v>
       </c>
-      <c r="F16" s="28" t="s">
+      <c r="F16" s="29" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="29" t="s">
         <v>306</v>
       </c>
-      <c r="B17" s="41" t="n">
+      <c r="B17" s="42" t="n">
         <f aca="false">Wyjaśnienia!$B$47</f>
         <v>500</v>
       </c>
-      <c r="C17" s="39" t="n">
+      <c r="C17" s="40" t="n">
         <f aca="false">ROUNDUP(B9/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D17" s="41" t="n">
+      <c r="D17" s="42" t="n">
         <f aca="false">B17*C17</f>
         <v>1500</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="29" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="B18" s="41" t="n">
+      <c r="B18" s="42" t="n">
         <f aca="false">Wyjaśnienia!$B$76</f>
         <v>300</v>
       </c>
-      <c r="C18" s="39" t="n">
+      <c r="C18" s="40" t="n">
         <f aca="false">B12</f>
         <v>300</v>
       </c>
-      <c r="D18" s="41" t="n">
+      <c r="D18" s="42" t="n">
         <f aca="false">B18*C18</f>
         <v>90000</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="29" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="38" t="s">
         <v>310</v>
       </c>
-      <c r="D19" s="42" t="n">
+      <c r="D19" s="43" t="n">
         <f aca="false">SUM(D16:D18)</f>
         <v>129000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="39" t="s">
         <v>152</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="F22" s="37" t="s">
+      <c r="F22" s="38" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="29" t="s">
         <v>311</v>
       </c>
-      <c r="B23" s="41" t="n">
+      <c r="B23" s="42" t="n">
         <v>2000</v>
       </c>
-      <c r="C23" s="39" t="n">
+      <c r="C23" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="41" t="n">
+      <c r="D23" s="42" t="n">
         <f aca="false">B23*C23</f>
         <v>2000</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="29" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="29" t="s">
         <v>313</v>
       </c>
-      <c r="B24" s="41" t="n">
+      <c r="B24" s="42" t="n">
         <v>3000</v>
       </c>
-      <c r="C24" s="39" t="n">
+      <c r="C24" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="41" t="n">
+      <c r="D24" s="42" t="n">
         <f aca="false">B24*C24</f>
         <v>3000</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="29" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="29" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="41" t="n">
+      <c r="B25" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="C25" s="39" t="n">
+      <c r="C25" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="41" t="n">
+      <c r="D25" s="42" t="n">
         <f aca="false">B25*C25</f>
         <v>5000</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="29" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="B26" s="41" t="n">
+      <c r="B26" s="42" t="n">
         <v>4000</v>
       </c>
-      <c r="C26" s="39" t="n">
+      <c r="C26" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="41" t="n">
+      <c r="D26" s="42" t="n">
         <f aca="false">B26*C26</f>
         <v>4000</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="29" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="37" t="s">
+      <c r="A27" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="D27" s="42" t="n">
+      <c r="D27" s="43" t="n">
         <f aca="false">SUM(D23:D26)</f>
         <v>14000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="29" t="s">
         <v>319</v>
       </c>
-      <c r="D30" s="41" t="n">
+      <c r="D30" s="42" t="n">
         <f aca="false">D19</f>
         <v>129000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="D31" s="41" t="n">
+      <c r="D31" s="42" t="n">
         <f aca="false">D27</f>
         <v>14000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="29" t="s">
         <v>320</v>
       </c>
-      <c r="D32" s="41" t="n">
+      <c r="D32" s="42" t="n">
         <f aca="false">(D30+D31)*Wyjaśnienia!$B$30</f>
         <v>17160</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D33" s="42" t="n">
+      <c r="D33" s="43" t="n">
         <f aca="false">SUM(D30:D32)</f>
         <v>160160</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="D34" s="41" t="n">
+      <c r="D34" s="42" t="n">
         <f aca="false">D33*Wyjaśnienia!$B$33</f>
         <v>36836.8</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="D35" s="42" t="n">
+      <c r="D35" s="43" t="n">
         <f aca="false">D33+D34</f>
         <v>196996.8</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="36" t="s">
+      <c r="A37" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
     </row>
     <row r="38" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="35" t="s">
+      <c r="A38" s="36" t="s">
         <v>322</v>
       </c>
-      <c r="B38" s="35"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="38" t="s">
+      <c r="A39" s="39" t="s">
         <v>323</v>
       </c>
-      <c r="B39" s="38" t="s">
+      <c r="B39" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="38" t="s">
+      <c r="C39" s="39" t="s">
         <v>325</v>
       </c>
-      <c r="D39" s="38" t="s">
+      <c r="D39" s="39" t="s">
         <v>326</v>
       </c>
-      <c r="E39" s="38" t="s">
+      <c r="E39" s="39" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="39" t="n">
+      <c r="A40" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="B40" s="39" t="n">
+      <c r="B40" s="40" t="n">
         <f aca="false">A40*Wyjaśnienia!$B$46</f>
         <v>300</v>
       </c>
-      <c r="C40" s="39" t="n">
+      <c r="C40" s="40" t="n">
         <f aca="false">ROUNDUP(B40/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D40" s="41" t="n">
+      <c r="D40" s="42" t="n">
         <f aca="false">C40*Wyjaśnienia!$B$47</f>
         <v>1500</v>
       </c>
-      <c r="E40" s="39" t="e">
-        <f aca="false">ROUNDUP(B40/Wyjaśnienia!$B$50,0)</f>
-        <v>#DIV/0!</v>
+      <c r="E40" s="40" t="n">
+        <f aca="false">ROUNDUP(B40*Wyjaśnienia!$B$50/60,0)</f>
+        <v>150</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="39" t="n">
+      <c r="A41" s="40" t="n">
         <v>1000</v>
       </c>
-      <c r="B41" s="39" t="n">
+      <c r="B41" s="40" t="n">
         <f aca="false">A41*Wyjaśnienia!$B$46</f>
         <v>2000</v>
       </c>
-      <c r="C41" s="39" t="n">
+      <c r="C41" s="40" t="n">
         <f aca="false">ROUNDUP(B41/100,0)</f>
         <v>20</v>
       </c>
-      <c r="D41" s="41" t="n">
+      <c r="D41" s="42" t="n">
         <f aca="false">C41*Wyjaśnienia!$B$47</f>
         <v>10000</v>
       </c>
-      <c r="E41" s="39" t="e">
-        <f aca="false">ROUNDUP(B41/Wyjaśnienia!$B$50,0)</f>
-        <v>#DIV/0!</v>
+      <c r="E41" s="40" t="n">
+        <f aca="false">ROUNDUP(B41*Wyjaśnienia!$B$50/60,0)</f>
+        <v>1000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="39" t="n">
+      <c r="A42" s="40" t="n">
         <v>10000</v>
       </c>
-      <c r="B42" s="39" t="n">
+      <c r="B42" s="40" t="n">
         <f aca="false">A42*Wyjaśnienia!$B$46</f>
         <v>20000</v>
       </c>
-      <c r="C42" s="39" t="n">
+      <c r="C42" s="40" t="n">
         <f aca="false">ROUNDUP(B42/100,0)</f>
         <v>200</v>
       </c>
-      <c r="D42" s="41" t="n">
+      <c r="D42" s="42" t="n">
         <f aca="false">C42*Wyjaśnienia!$B$47</f>
         <v>100000</v>
       </c>
-      <c r="E42" s="39" t="e">
-        <f aca="false">ROUNDUP(B42/Wyjaśnienia!$B$50,0)</f>
-        <v>#DIV/0!</v>
+      <c r="E42" s="40" t="n">
+        <f aca="false">ROUNDUP(B42*Wyjaśnienia!$B$50/60,0)</f>
+        <v>10000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="39" t="n">
+      <c r="A43" s="40" t="n">
         <v>100000</v>
       </c>
-      <c r="B43" s="39" t="n">
+      <c r="B43" s="40" t="n">
         <f aca="false">A43*Wyjaśnienia!$B$46</f>
         <v>200000</v>
       </c>
-      <c r="C43" s="39" t="n">
+      <c r="C43" s="40" t="n">
         <f aca="false">ROUNDUP(B43/100,0)</f>
         <v>2000</v>
       </c>
-      <c r="D43" s="41" t="n">
+      <c r="D43" s="42" t="n">
         <f aca="false">C43*Wyjaśnienia!$B$47</f>
         <v>1000000</v>
       </c>
-      <c r="E43" s="39" t="e">
-        <f aca="false">ROUNDUP(B43/Wyjaśnienia!$B$50,0)</f>
-        <v>#DIV/0!</v>
+      <c r="E43" s="40" t="n">
+        <f aca="false">ROUNDUP(B43*Wyjaśnienia!$B$50/60,0)</f>
+        <v>100000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="39" t="n">
+      <c r="A44" s="40" t="n">
         <v>1000000</v>
       </c>
-      <c r="B44" s="39" t="n">
+      <c r="B44" s="40" t="n">
         <f aca="false">A44*Wyjaśnienia!$B$46</f>
         <v>2000000</v>
       </c>
-      <c r="C44" s="39" t="n">
+      <c r="C44" s="40" t="n">
         <f aca="false">ROUNDUP(B44/100,0)</f>
         <v>20000</v>
       </c>
-      <c r="D44" s="41" t="n">
+      <c r="D44" s="42" t="n">
         <f aca="false">C44*Wyjaśnienia!$B$47</f>
         <v>10000000</v>
       </c>
-      <c r="E44" s="39" t="e">
-        <f aca="false">ROUNDUP(B44/Wyjaśnienia!$B$50,0)</f>
-        <v>#DIV/0!</v>
+      <c r="E44" s="40" t="n">
+        <f aca="false">ROUNDUP(B44*Wyjaśnienia!$B$50/60,0)</f>
+        <v>1000000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="39" t="s">
         <v>328</v>
       </c>
-      <c r="B46" s="38" t="s">
+      <c r="B46" s="39" t="s">
         <v>329</v>
       </c>
-      <c r="C46" s="38" t="s">
+      <c r="C46" s="39" t="s">
         <v>330</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="39" t="s">
         <v>331</v>
       </c>
-      <c r="E46" s="38" t="s">
+      <c r="E46" s="39" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="39" t="n">
+      <c r="A47" s="40" t="n">
         <v>30</v>
       </c>
-      <c r="B47" s="39" t="n">
+      <c r="B47" s="40" t="n">
         <f aca="false">A47*Wyjaśnienia!$B$75</f>
         <v>60</v>
       </c>
-      <c r="C47" s="41" t="n">
+      <c r="C47" s="42" t="n">
         <f aca="false">B47*Wyjaśnienia!$B$76</f>
         <v>18000</v>
       </c>
-      <c r="D47" s="39" t="n">
+      <c r="D47" s="40" t="n">
         <f aca="false">B47*2</f>
         <v>120</v>
       </c>
-      <c r="E47" s="39" t="n">
+      <c r="E47" s="40" t="n">
         <f aca="false">ROUNDUP(A47/Wyjaśnienia!$B$77,0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="39" t="n">
+      <c r="A48" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="B48" s="39" t="n">
+      <c r="B48" s="40" t="n">
         <f aca="false">A48*Wyjaśnienia!$B$75</f>
         <v>300</v>
       </c>
-      <c r="C48" s="41" t="n">
+      <c r="C48" s="42" t="n">
         <f aca="false">B48*Wyjaśnienia!$B$76</f>
         <v>90000</v>
       </c>
-      <c r="D48" s="39" t="n">
+      <c r="D48" s="40" t="n">
         <f aca="false">B48*2</f>
         <v>600</v>
       </c>
-      <c r="E48" s="39" t="n">
+      <c r="E48" s="40" t="n">
         <f aca="false">ROUNDUP(A48/Wyjaśnienia!$B$77,0)</f>
         <v>15</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="39" t="n">
+      <c r="A49" s="40" t="n">
         <v>500</v>
       </c>
-      <c r="B49" s="39" t="n">
+      <c r="B49" s="40" t="n">
         <f aca="false">A49*Wyjaśnienia!$B$75</f>
         <v>1000</v>
       </c>
-      <c r="C49" s="41" t="n">
+      <c r="C49" s="42" t="n">
         <f aca="false">B49*Wyjaśnienia!$B$76</f>
         <v>300000</v>
       </c>
-      <c r="D49" s="39" t="n">
+      <c r="D49" s="40" t="n">
         <f aca="false">B49*2</f>
         <v>2000</v>
       </c>
-      <c r="E49" s="39" t="n">
+      <c r="E49" s="40" t="n">
         <f aca="false">ROUNDUP(A49/Wyjaśnienia!$B$77,0)</f>
         <v>50</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="39" t="n">
+      <c r="A50" s="40" t="n">
         <v>2000</v>
       </c>
-      <c r="B50" s="39" t="n">
+      <c r="B50" s="40" t="n">
         <f aca="false">A50*Wyjaśnienia!$B$75</f>
         <v>4000</v>
       </c>
-      <c r="C50" s="41" t="n">
+      <c r="C50" s="42" t="n">
         <f aca="false">B50*Wyjaśnienia!$B$76</f>
         <v>1200000</v>
       </c>
-      <c r="D50" s="39" t="n">
+      <c r="D50" s="40" t="n">
         <f aca="false">B50*2</f>
         <v>8000</v>
       </c>
-      <c r="E50" s="39" t="n">
+      <c r="E50" s="40" t="n">
         <f aca="false">ROUNDUP(A50/Wyjaśnienia!$B$77,0)</f>
         <v>200</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="39" t="n">
+      <c r="A51" s="40" t="n">
         <v>10000</v>
       </c>
-      <c r="B51" s="39" t="n">
+      <c r="B51" s="40" t="n">
         <f aca="false">A51*Wyjaśnienia!$B$75</f>
         <v>20000</v>
       </c>
-      <c r="C51" s="41" t="n">
+      <c r="C51" s="42" t="n">
         <f aca="false">B51*Wyjaśnienia!$B$76</f>
         <v>6000000</v>
       </c>
-      <c r="D51" s="39" t="n">
+      <c r="D51" s="40" t="n">
         <f aca="false">B51*2</f>
         <v>40000</v>
       </c>
-      <c r="E51" s="39" t="n">
+      <c r="E51" s="40" t="n">
         <f aca="false">ROUNDUP(A51/Wyjaśnienia!$B$77,0)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="35" t="s">
+      <c r="A53" s="36" t="s">
         <v>333</v>
       </c>
-      <c r="B53" s="35"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6315,44 +6322,44 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="31" t="s">
         <v>335</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
@@ -6378,13 +6385,13 @@
       <c r="A7" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="33" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$66/60</f>
         <v>30</v>
       </c>
@@ -6400,11 +6407,11 @@
       <c r="A8" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="32" t="n">
+      <c r="C8" s="21"/>
+      <c r="D8" s="33" t="n">
         <f aca="false">B8+C8*Wyjaśnienia!$B$66/60</f>
         <v>25</v>
       </c>
@@ -6420,11 +6427,11 @@
       <c r="A9" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="32" t="n">
+      <c r="C9" s="21"/>
+      <c r="D9" s="33" t="n">
         <f aca="false">B9+C9*Wyjaśnienia!$B$66/60</f>
         <v>60</v>
       </c>
@@ -6440,11 +6447,11 @@
       <c r="A10" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="32" t="n">
+      <c r="C10" s="21"/>
+      <c r="D10" s="33" t="n">
         <f aca="false">B10+C10*Wyjaśnienia!$B$66/60</f>
         <v>20</v>
       </c>
@@ -6460,11 +6467,11 @@
       <c r="A11" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="32" t="n">
+      <c r="C11" s="21"/>
+      <c r="D11" s="33" t="n">
         <f aca="false">B11+C11*Wyjaśnienia!$B$66/60</f>
         <v>40</v>
       </c>
@@ -6480,11 +6487,11 @@
       <c r="A12" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="32" t="n">
+      <c r="C12" s="21"/>
+      <c r="D12" s="33" t="n">
         <f aca="false">B12+C12*Wyjaśnienia!$B$66/60</f>
         <v>40</v>
       </c>
@@ -6500,11 +6507,11 @@
       <c r="A13" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="32" t="n">
+      <c r="C13" s="21"/>
+      <c r="D13" s="33" t="n">
         <f aca="false">B13+C13*Wyjaśnienia!$B$66/60</f>
         <v>25</v>
       </c>
@@ -6520,11 +6527,11 @@
       <c r="A14" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="32" t="n">
+      <c r="C14" s="21"/>
+      <c r="D14" s="33" t="n">
         <f aca="false">B14+C14*Wyjaśnienia!$B$66/60</f>
         <v>50</v>
       </c>
@@ -6540,9 +6547,9 @@
       <c r="A15" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="33" t="n">
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="34" t="n">
         <f aca="false">SUM(D7:D14)</f>
         <v>290</v>
       </c>
@@ -6555,14 +6562,14 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
@@ -6589,7 +6596,7 @@
         <f aca="false">Wyjaśnienia!$B$67</f>
         <v>180000</v>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="8" t="n">
@@ -6608,7 +6615,7 @@
         <f aca="false">Wyjaśnienia!$B$68</f>
         <v>4000</v>
       </c>
-      <c r="C20" s="32" t="n">
+      <c r="C20" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="8" t="n">
@@ -6627,7 +6634,7 @@
         <f aca="false">Wyjaśnienia!$B$69</f>
         <v>1200</v>
       </c>
-      <c r="C21" s="32" t="n">
+      <c r="C21" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="8" t="n">
@@ -6645,7 +6652,7 @@
       <c r="B22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="32" t="n">
+      <c r="C22" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="8" t="n">
@@ -6663,7 +6670,7 @@
       <c r="B23" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -6681,7 +6688,7 @@
       <c r="B24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C24" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -6699,7 +6706,7 @@
       <c r="B25" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="32" t="n">
+      <c r="C25" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="8" t="n">
@@ -6717,7 +6724,7 @@
       <c r="B26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="32" t="n">
+      <c r="C26" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="8" t="n">
@@ -6735,7 +6742,7 @@
       <c r="B27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="32" t="n">
+      <c r="C27" s="33" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="8" t="n">
@@ -6746,12 +6753,12 @@
         <v>363</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
         <v>171</v>
       </c>
       <c r="B28" s="8"/>
-      <c r="C28" s="32"/>
+      <c r="C28" s="33"/>
       <c r="D28" s="11" t="n">
         <f aca="false">SUM(D19:D27)</f>
         <v>185200</v>
@@ -6759,14 +6766,14 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
@@ -6822,7 +6829,7 @@
         <v>59064</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
         <v>179</v>
       </c>
@@ -6947,20 +6954,20 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
         <v>366</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>45</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="24" t="n">
         <f aca="false">B7+C7*Wyjaśnienia!$B$17/60</f>
         <v>45</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="25" t="n">
         <f aca="false">D7*Wyjaśnienia!$B$16</f>
         <v>9900</v>
       </c>
@@ -6976,7 +6983,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="26" t="n">
         <f aca="false">SUM(D7:D7)</f>
         <v>45</v>
       </c>
@@ -7031,16 +7038,16 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="22" t="s">
         <v>368</v>
       </c>
-      <c r="B12" s="26" t="n">
+      <c r="B12" s="27" t="n">
         <v>8000</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="24" t="n">
+      <c r="D12" s="25" t="n">
         <f aca="false">B12*C12</f>
         <v>8000</v>
       </c>
@@ -7052,16 +7059,16 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="22" t="s">
         <v>370</v>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <f aca="false">B13*C13</f>
         <v>1500</v>
       </c>
@@ -7073,16 +7080,16 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="22" t="s">
         <v>372</v>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>4000</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="25" t="n">
         <f aca="false">B14*C14</f>
         <v>4000</v>
       </c>
@@ -7094,16 +7101,16 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="22" t="s">
         <v>374</v>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>8000</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="25" t="n">
         <f aca="false">B15*C15</f>
         <v>8000</v>
       </c>
@@ -7115,16 +7122,16 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="22" t="s">
         <v>376</v>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="25" t="n">
         <f aca="false">B16*C16</f>
         <v>0</v>
       </c>
@@ -7133,16 +7140,16 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="22" t="s">
         <v>378</v>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="25" t="n">
         <f aca="false">B17*C17</f>
         <v>0</v>
       </c>
@@ -7151,16 +7158,16 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="22" t="s">
         <v>380</v>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="25" t="n">
         <f aca="false">B18*C18</f>
         <v>0</v>
       </c>
@@ -7169,16 +7176,16 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="22" t="s">
         <v>382</v>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="25" t="n">
         <f aca="false">B19*C19</f>
         <v>0</v>
       </c>
@@ -7219,7 +7226,7 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="22" t="s">
         <v>174</v>
       </c>
       <c r="D23" s="8" t="n">
@@ -7230,7 +7237,7 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="22" t="s">
         <v>175</v>
       </c>
       <c r="B24" s="3"/>
@@ -7245,7 +7252,7 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="22" t="s">
         <v>384</v>
       </c>
       <c r="B25" s="3"/>
@@ -7275,7 +7282,7 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="22" t="s">
         <v>178</v>
       </c>
       <c r="B27" s="3"/>
@@ -7295,7 +7302,7 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="27" t="n">
+      <c r="D28" s="28" t="n">
         <f aca="false">D26+D27</f>
         <v>43256.64</v>
       </c>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -1364,7 +1364,7 @@
       <c r="H43" s="47" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="45">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>Kolumna "Rok kosztu" w każdej zakładce mówi, na który rok edycji przypada dana pozycja: 2027 to rok naboru, 2028 to ocena jury, nagrody, produkcja antologii, gala i wystawy. Rezerwa i marża dzielą się proporcjonalnie do kosztów danego roku. Podział w tym układzie pokazuje załącznik "Zestawienie zadania".</t>
         </is>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="E25" s="57" t="inlineStr">
         <is>
-          <t>DO USTALENIA - etap przed naborem, osobny od oceny zgłoszeń; obejmuje opisy przedziałów punktowych i przykłady ich zastosowania</t>
+          <t>DO USTALENIA - etap przed naborem, osobny od oceny zgłoszeń; obejmuje opisy przedziałów punktowych i przykłady ich zastosowania Rok kosztu: 2027 - karta oceny powstaje przed otwarciem naboru. Jeżeli zapłata nastąpi później, pozycję trzeba przypisać do roku wypłaty.</t>
         </is>
       </c>
       <c r="F25" s="47" t="n"/>
       <c r="G25" s="82" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="45">
@@ -5296,7 +5296,7 @@
     <row r="41">
       <c r="A41" s="47" t="inlineStr">
         <is>
-          <t>Wystawa w galerii sztuki jest celem, nie zobowiązaniem regulaminowym, i ma własne źródło finansowania. Pozycje poniżej nie wchodzą do sum powyżej i nie są objęte pytaniem do Ministerstwa.</t>
+          <t>Wystawa w galerii sztuki jest celem, nie zobowiązaniem regulaminowym, i ma własne źródło finansowania. Pierwsza pozycja poniżej nie wchodzi do sum powyżej, bo czeka na wycenę. Druga powtarza godziny już policzone w wierszu 13 i również nie jest do sum dodawana - pokazuje tylko, ile z pracy organizatora przypada na część poza pytaniem do MKiDN.</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="E44" s="47" t="inlineStr">
         <is>
-          <t>Te same 20 godzin, które są wykazane w wierszu 13 powyżej. Tutaj dla pokazania, ile z pracy organizatora przypada na część poza pytaniem - nie dodawać drugi raz.</t>
+          <t>Te same 20 godzin, które są policzone w wierszu 13 i w sumie głównej. Tutaj wyłącznie dla pokazania, ile z pracy organizatora przypada na część poza pytaniem - nie dodawać drugi raz.</t>
         </is>
       </c>
     </row>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -3362,7 +3362,7 @@
       </c>
       <c r="E25" s="57" t="inlineStr">
         <is>
-          <t>gwarantowany przez organizatora, niezależny od partnera wydawniczego; nakład handlowy jest po stronie partnera</t>
+          <t>gwarantowany przez organizatora, niezależny od partnera wydawniczego; nakład handlowy jest po stronie partnera. Pozycja ponoszona wyłącznie wtedy, gdy wydanie księgarskie nie będzie gotowe na dzień gali - jeżeli partner dostarczy książkę na premierę, egzemplarze dla laureatów i jury pochodzą z jego nakładu. Przy 100 egzemplarzach egzemplarz obowiązkowy to 2 sztuki (Biblioteka Narodowa i Jagiellońska); powyżej 100 egzemplarzy ustawa wymaga 17 sztuk, co jest osobnym powodem, by nie przekraczać setki. ISBN dla tego druku nie jest potrzebny, bo nie trafia do sprzedaży.</t>
         </is>
       </c>
       <c r="F25" s="47" t="n"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="405">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">Nagrody publiczności (brutto)</t>
   </si>
   <si>
-    <t xml:space="preserve">3 000 zł dla zgłoszenia z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych rozmów (§ 11 ust. 8a)</t>
+    <t xml:space="preserve">10 000 zł dla zgłoszenia z największą liczbą głosów oraz 2 000 zł za najlepsze uzasadnienie oddanego głosu</t>
   </si>
   <si>
     <t xml:space="preserve">Ubezpieczenie OC organizatora</t>
@@ -755,9 +755,6 @@
     <t xml:space="preserve">czołowa trójka; podatek 10% jak przy Nagrodzie</t>
   </si>
   <si>
-    <t xml:space="preserve">dla wykonawcy oraz za najlepsze uzasadnienie wyboru</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nagrania studyjne dziesięciu finalistów (netto)</t>
   </si>
   <si>
@@ -857,9 +854,6 @@
     <t xml:space="preserve">Nagroda publiczności (brutto)</t>
   </si>
   <si>
-    <t xml:space="preserve">jedna nagroda, dla pracy z największą liczbą głosów</t>
-  </si>
-  <si>
     <t xml:space="preserve">Honoraria jury plakatu za ocenę (netto)</t>
   </si>
   <si>
@@ -1155,9 +1149,6 @@
   </si>
   <si>
     <t xml:space="preserve">czołowa trójka: 100, 50 i 30 tys.; siedem wyróżnień bez nagrody pieniężnej; podatek 10% jak przy Nagrodzie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jedna nagroda, dla filmu z największą liczbą głosów</t>
   </si>
   <si>
     <t xml:space="preserve">ten sam medal, który otrzymują zwycięzcy pozostałych plebiscytów; dyplomy dla dziesięciu finalistów</t>
@@ -1407,7 +1398,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1521,10 +1512,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1919,7 +1906,7 @@
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">'Budżet Nagrody'!$D$37</f>
-        <v>523196.8</v>
+        <v>532156.8</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -1953,7 +1940,7 @@
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">'Budżet Plebiscytu'!$D$33</f>
-        <v>254600</v>
+        <v>262600</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -1982,7 +1969,7 @@
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">'Budżet Plakatu'!$D$36</f>
-        <v>154480</v>
+        <v>162480</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1999,7 +1986,7 @@
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">'Budżet Filmu'!$D$35</f>
-        <v>256800</v>
+        <v>264800</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2020,7 +2007,7 @@
       </c>
       <c r="C13" s="11" t="n">
         <f aca="false">'Budżet Nagrody'!$D$37+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$33+'Budżet Plakatu'!$D$36+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$35</f>
-        <v>1676826.8</v>
+        <v>1709786.8</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -2187,7 +2174,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="14" t="n">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>42</v>
@@ -2517,7 +2504,7 @@
         <v>82</v>
       </c>
       <c r="B55" s="18" t="n">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>83</v>
@@ -2644,7 +2631,7 @@
         <v>103</v>
       </c>
       <c r="B68" s="14" t="n">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>104</v>
@@ -2807,7 +2794,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2819,7 +2806,6 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2831,7 +2817,6 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2843,7 +2828,6 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2853,7 +2837,6 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2865,7 +2848,6 @@
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3167,7 +3149,6 @@
         <v>71940</v>
       </c>
       <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3177,7 +3158,6 @@
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3189,7 +3169,6 @@
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3325,7 +3304,7 @@
         <v>166</v>
       </c>
       <c r="F25" s="3"/>
-      <c r="G25" s="29" t="n">
+      <c r="G25" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
@@ -3357,20 +3336,20 @@
         <v>169</v>
       </c>
       <c r="B27" s="28" t="n">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="C27" s="23" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="25" t="n">
         <f aca="false">B27*C27</f>
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>170</v>
       </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="29" t="n">
+      <c r="G27" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -3415,7 +3394,7 @@
         <v>174</v>
       </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="29" t="n">
+      <c r="G29" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -3427,28 +3406,25 @@
       <c r="C30" s="3"/>
       <c r="D30" s="9" t="n">
         <f aca="false">SUM(D21:D29)</f>
-        <v>63950</v>
+        <v>71950</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="30"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="3"/>
+      <c r="A31" s="29"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3463,7 +3439,6 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3478,7 +3453,6 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3489,11 +3463,10 @@
       <c r="C35" s="3"/>
       <c r="D35" s="8" t="n">
         <f aca="false">D30</f>
-        <v>63950</v>
+        <v>71950</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3502,9 +3475,8 @@
       </c>
       <c r="D36" s="3" t="n">
         <f aca="false">(D34+D35)*Wyjaśnienia!$B$30</f>
-        <v>16306.8</v>
-      </c>
-      <c r="G36" s="3"/>
+        <v>17266.8</v>
+      </c>
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3515,11 +3487,10 @@
       <c r="C37" s="3"/>
       <c r="D37" s="9" t="n">
         <f aca="false">SUM(D33:D36)</f>
-        <v>523196.8</v>
+        <v>532156.8</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3530,11 +3501,10 @@
       <c r="C38" s="3"/>
       <c r="D38" s="8" t="n">
         <f aca="false">D37*Wyjaśnienia!$B$33</f>
-        <v>120335.264</v>
+        <v>122396.064</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3543,13 +3513,12 @@
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="31" t="n">
+      <c r="D39" s="30" t="n">
         <f aca="false">D37+D38</f>
-        <v>643532.064</v>
+        <v>654552.864</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3651,7 +3620,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3663,7 +3632,6 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3675,7 +3643,6 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3687,7 +3654,6 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3697,7 +3663,6 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3709,7 +3674,6 @@
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3937,7 +3901,7 @@
         <v>15840</v>
       </c>
       <c r="F14" s="15"/>
-      <c r="G14" s="29" t="n">
+      <c r="G14" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
@@ -3956,7 +3920,6 @@
         <v>99440</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3966,7 +3929,6 @@
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3978,7 +3940,6 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4259,34 +4220,34 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="31" t="s">
         <v>223</v>
       </c>
       <c r="B30" s="18" t="n">
         <v>4500</v>
       </c>
-      <c r="C30" s="33" t="n">
+      <c r="C30" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="8" t="n">
         <f aca="false">B30*C30</f>
         <v>4500</v>
       </c>
-      <c r="F30" s="32" t="s">
+      <c r="F30" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="G30" s="29" t="n">
+      <c r="G30" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="31" t="s">
         <v>225</v>
       </c>
       <c r="B31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="33" t="n">
+      <c r="C31" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="8" t="n">
@@ -4296,8 +4257,8 @@
       <c r="E31" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="F31" s="32"/>
-      <c r="G31" s="29" t="n">
+      <c r="F31" s="31"/>
+      <c r="G31" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
@@ -4313,17 +4274,15 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="3"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4335,7 +4294,6 @@
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
-      <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4350,7 +4308,6 @@
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4365,7 +4322,6 @@
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4380,7 +4336,6 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4395,7 +4350,6 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4410,7 +4364,6 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4419,13 +4372,12 @@
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="31" t="n">
+      <c r="D40" s="30" t="n">
         <f aca="false">D38+D39</f>
         <v>359679.06</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
       <c r="H40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4527,7 +4479,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4539,7 +4491,6 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4551,7 +4502,6 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4563,7 +4513,6 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4573,7 +4522,6 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4585,7 +4533,6 @@
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4751,7 +4698,6 @@
       <c r="F12" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4761,7 +4707,6 @@
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4773,7 +4718,6 @@
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4828,17 +4772,17 @@
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$25</f>
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="C17" s="23" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="25" t="n">
         <f aca="false">B17*C17</f>
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>242</v>
+        <v>170</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="26" t="n">
@@ -4848,7 +4792,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$26</f>
@@ -4863,7 +4807,7 @@
         <v>75000</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="26" t="n">
@@ -4887,7 +4831,7 @@
         <v>80000</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="26" t="n">
@@ -4897,7 +4841,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$29</f>
@@ -4911,7 +4855,7 @@
         <v>1200</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="26" t="n">
@@ -4921,7 +4865,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B21" s="28" t="n">
         <v>0</v>
@@ -4934,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="26" t="n">
@@ -4957,16 +4901,16 @@
         <v>0</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F22" s="3"/>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B23" s="28" t="n">
         <v>0</v>
@@ -4979,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="26" t="n">
@@ -4988,13 +4932,13 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32" t="s">
-        <v>253</v>
+      <c r="A24" s="31" t="s">
+        <v>252</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="33" t="n">
+      <c r="C24" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="8" t="n">
@@ -5002,23 +4946,23 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F24" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="F24" s="32" t="s">
+      <c r="G24" s="26" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="G24" s="29" t="n">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32" t="s">
-        <v>256</v>
-      </c>
       <c r="B25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C25" s="33" t="n">
+      <c r="C25" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="8" t="n">
@@ -5026,10 +4970,10 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F25" s="32"/>
-      <c r="G25" s="29" t="n">
+        <v>256</v>
+      </c>
+      <c r="F25" s="31"/>
+      <c r="G25" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -5039,19 +4983,17 @@
       </c>
       <c r="D26" s="3" t="n">
         <f aca="false">SUM(D16:D25)</f>
-        <v>195200</v>
-      </c>
-      <c r="G26" s="3"/>
+        <v>203200</v>
+      </c>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="3"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5063,7 +5005,6 @@
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
-      <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5074,11 +5015,10 @@
       <c r="C29" s="3"/>
       <c r="D29" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$24+Wyjaśnienia!$B$25</f>
-        <v>39000</v>
+        <v>47000</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5093,12 +5033,11 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -5108,7 +5047,6 @@
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5123,7 +5061,6 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5134,11 +5071,10 @@
       <c r="C33" s="3"/>
       <c r="D33" s="9" t="n">
         <f aca="false">SUM(D29:D32)</f>
-        <v>254600</v>
+        <v>262600</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5149,11 +5085,10 @@
       <c r="C34" s="3"/>
       <c r="D34" s="8" t="n">
         <f aca="false">D33*Wyjaśnienia!$B$33</f>
-        <v>58558</v>
+        <v>60398</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5162,13 +5097,12 @@
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="31" t="n">
+      <c r="D35" s="30" t="n">
         <f aca="false">D33+D34</f>
-        <v>313158</v>
+        <v>322998</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5275,48 +5209,48 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="A2" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
@@ -5343,7 +5277,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>0</v>
@@ -5360,15 +5294,15 @@
         <v>4400</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G7" s="29" t="n">
+        <v>260</v>
+      </c>
+      <c r="G7" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>30</v>
@@ -5383,9 +5317,9 @@
         <v>6600</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G8" s="29" t="n">
+        <v>262</v>
+      </c>
+      <c r="G8" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -5406,15 +5340,15 @@
         <v>4400</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G9" s="29" t="n">
+        <v>263</v>
+      </c>
+      <c r="G9" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B10" s="21" t="n">
         <v>35</v>
@@ -5429,15 +5363,15 @@
         <v>7700</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="G10" s="29" t="n">
+        <v>265</v>
+      </c>
+      <c r="G10" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B11" s="21" t="n">
         <v>15</v>
@@ -5452,15 +5386,15 @@
         <v>3300</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="G11" s="29" t="n">
+        <v>267</v>
+      </c>
+      <c r="G11" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B12" s="21" t="n">
         <v>50</v>
@@ -5475,15 +5409,15 @@
         <v>11000</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="G12" s="29" t="n">
+        <v>269</v>
+      </c>
+      <c r="G12" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B13" s="21" t="n">
         <v>20</v>
@@ -5498,9 +5432,9 @@
         <v>4400</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G13" s="29" t="n">
+        <v>271</v>
+      </c>
+      <c r="G13" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -5508,7 +5442,7 @@
       <c r="A14" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="34" t="n">
         <f aca="false">SUM(D7:D13)</f>
         <v>190</v>
       </c>
@@ -5521,14 +5455,14 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
@@ -5552,7 +5486,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B18" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$54</f>
@@ -5566,37 +5500,37 @@
         <v>90000</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G18" s="29" t="n">
+        <v>273</v>
+      </c>
+      <c r="G18" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$55</f>
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="C19" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="8" t="n">
         <f aca="false">B19*C19</f>
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="G19" s="29" t="n">
+        <v>170</v>
+      </c>
+      <c r="G19" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B20" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$56</f>
@@ -5610,15 +5544,15 @@
         <v>1200</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G20" s="29" t="n">
+        <v>246</v>
+      </c>
+      <c r="G20" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>0</v>
@@ -5631,9 +5565,9 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G21" s="29" t="n">
+        <v>276</v>
+      </c>
+      <c r="G21" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -5652,15 +5586,15 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G22" s="29" t="n">
+        <v>277</v>
+      </c>
+      <c r="G22" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B23" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$61*2</f>
@@ -5675,9 +5609,9 @@
         <v>8000</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G23" s="29" t="n">
+        <v>279</v>
+      </c>
+      <c r="G23" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -5697,15 +5631,15 @@
         <v>3000</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="G24" s="29" t="n">
+        <v>280</v>
+      </c>
+      <c r="G24" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B25" s="18" t="n">
         <v>0</v>
@@ -5718,15 +5652,15 @@
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="G25" s="29" t="n">
+        <v>282</v>
+      </c>
+      <c r="G25" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>0</v>
@@ -5739,15 +5673,15 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="G26" s="29" t="n">
+        <v>284</v>
+      </c>
+      <c r="G26" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B27" s="18" t="n">
         <v>0</v>
@@ -5760,15 +5694,15 @@
         <v>0</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G27" s="29" t="n">
+        <v>286</v>
+      </c>
+      <c r="G27" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B28" s="18" t="n">
         <v>0</v>
@@ -5781,9 +5715,9 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G28" s="29" t="n">
+        <v>288</v>
+      </c>
+      <c r="G28" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -5793,16 +5727,16 @@
       </c>
       <c r="D29" s="3" t="n">
         <f aca="false">SUM(D18:D28)</f>
-        <v>106200</v>
+        <v>114200</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="30"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
@@ -5815,7 +5749,7 @@
       </c>
       <c r="D32" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$54+Wyjaśnienia!$B$55</f>
-        <v>94000</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5829,7 +5763,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D34" s="8" t="n">
         <f aca="false">D29-D32</f>
@@ -5851,7 +5785,7 @@
       </c>
       <c r="D36" s="11" t="n">
         <f aca="false">SUM(D32:D35)</f>
-        <v>154480</v>
+        <v>162480</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5860,7 +5794,7 @@
       </c>
       <c r="D37" s="8" t="n">
         <f aca="false">D36*Wyjaśnienia!$B$33</f>
-        <v>35530.4</v>
+        <v>37370.4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5869,20 +5803,20 @@
       </c>
       <c r="D38" s="11" t="n">
         <f aca="false">D36+D37</f>
-        <v>190010.4</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>199850.4</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
         <v>125</v>
       </c>
@@ -5902,9 +5836,9 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B43" s="8" t="n">
         <v>0</v>
@@ -5917,12 +5851,12 @@
         <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B44" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$16</f>
@@ -5936,7 +5870,7 @@
         <v>4400</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -5972,822 +5906,822 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="37" t="s">
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+      <c r="F6" s="38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="31" t="s">
         <v>299</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>300</v>
-      </c>
-      <c r="F6" s="39" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32" t="s">
-        <v>301</v>
-      </c>
-      <c r="B7" s="41" t="n">
+      <c r="B7" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$17</f>
         <v>150</v>
       </c>
-      <c r="F7" s="32" t="s">
-        <v>302</v>
+      <c r="F7" s="31" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="s">
-        <v>303</v>
-      </c>
-      <c r="B8" s="41" t="n">
+      <c r="A8" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$46</f>
         <v>2</v>
       </c>
-      <c r="F8" s="32" t="s">
-        <v>304</v>
+      <c r="F8" s="31" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="s">
-        <v>305</v>
-      </c>
-      <c r="B9" s="42" t="n">
+      <c r="A9" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="B9" s="41" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
-      <c r="F9" s="32" t="s">
-        <v>306</v>
+      <c r="F9" s="31" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="B10" s="41" t="n">
+      <c r="A10" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="B10" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$66</f>
         <v>150</v>
       </c>
-      <c r="F10" s="32" t="s">
-        <v>308</v>
+      <c r="F10" s="31" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="B11" s="41" t="n">
+      <c r="A11" s="31" t="s">
+        <v>307</v>
+      </c>
+      <c r="B11" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$75</f>
         <v>2</v>
       </c>
-      <c r="F11" s="32" t="s">
-        <v>310</v>
+      <c r="F11" s="31" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="39" t="s">
-        <v>311</v>
-      </c>
-      <c r="B12" s="42" t="n">
+      <c r="A12" s="38" t="s">
+        <v>309</v>
+      </c>
+      <c r="B12" s="41" t="n">
         <f aca="false">B10*B11</f>
         <v>300</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="31" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="39" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="38" t="s">
+      <c r="C15" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="31" t="s">
         <v>313</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="B15" s="40" t="s">
-        <v>314</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="G15" s="39" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32" t="s">
-        <v>315</v>
-      </c>
-      <c r="B16" s="43" t="n">
+      <c r="B16" s="42" t="n">
         <f aca="false">Wyjaśnienia!$B$48</f>
         <v>2500</v>
       </c>
-      <c r="C16" s="41" t="n">
+      <c r="C16" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$49</f>
         <v>15</v>
       </c>
-      <c r="D16" s="43" t="n">
+      <c r="D16" s="42" t="n">
         <f aca="false">B16*C16</f>
         <v>37500</v>
       </c>
-      <c r="F16" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="G16" s="29" t="n">
+      <c r="F16" s="31" t="s">
+        <v>314</v>
+      </c>
+      <c r="G16" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="B17" s="43" t="n">
+      <c r="A17" s="31" t="s">
+        <v>315</v>
+      </c>
+      <c r="B17" s="42" t="n">
         <f aca="false">Wyjaśnienia!$B$47</f>
         <v>500</v>
       </c>
-      <c r="C17" s="41" t="n">
+      <c r="C17" s="40" t="n">
         <f aca="false">ROUNDUP(B9/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D17" s="43" t="n">
+      <c r="D17" s="42" t="n">
         <f aca="false">B17*C17</f>
         <v>1500</v>
       </c>
-      <c r="F17" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="G17" s="29" t="n">
+      <c r="F17" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="G17" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="32" t="s">
-        <v>319</v>
-      </c>
-      <c r="B18" s="43" t="n">
+      <c r="A18" s="31" t="s">
+        <v>317</v>
+      </c>
+      <c r="B18" s="42" t="n">
         <f aca="false">Wyjaśnienia!$B$76</f>
         <v>300</v>
       </c>
-      <c r="C18" s="41" t="n">
+      <c r="C18" s="40" t="n">
         <f aca="false">B12</f>
         <v>300</v>
       </c>
-      <c r="D18" s="43" t="n">
+      <c r="D18" s="42" t="n">
         <f aca="false">B18*C18</f>
         <v>90000</v>
       </c>
-      <c r="F18" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="G18" s="29" t="n">
+      <c r="F18" s="31" t="s">
+        <v>318</v>
+      </c>
+      <c r="G18" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="39" t="s">
-        <v>321</v>
-      </c>
-      <c r="D19" s="44" t="n">
+      <c r="A19" s="38" t="s">
+        <v>319</v>
+      </c>
+      <c r="D19" s="43" t="n">
         <f aca="false">SUM(D16:D18)</f>
         <v>129000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="F22" s="39" t="s">
+      <c r="F22" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="G22" s="39" t="s">
+      <c r="G22" s="38" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32" t="s">
-        <v>322</v>
-      </c>
-      <c r="B23" s="43" t="n">
+      <c r="A23" s="31" t="s">
+        <v>320</v>
+      </c>
+      <c r="B23" s="42" t="n">
         <v>2000</v>
       </c>
-      <c r="C23" s="41" t="n">
+      <c r="C23" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="43" t="n">
+      <c r="D23" s="42" t="n">
         <f aca="false">B23*C23</f>
         <v>2000</v>
       </c>
-      <c r="F23" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="G23" s="29" t="n">
+      <c r="F23" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="G23" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32" t="s">
-        <v>324</v>
-      </c>
-      <c r="B24" s="43" t="n">
+      <c r="A24" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="B24" s="42" t="n">
         <v>3000</v>
       </c>
-      <c r="C24" s="41" t="n">
+      <c r="C24" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="43" t="n">
+      <c r="D24" s="42" t="n">
         <f aca="false">B24*C24</f>
         <v>3000</v>
       </c>
-      <c r="F24" s="32" t="s">
-        <v>325</v>
-      </c>
-      <c r="G24" s="29" t="n">
+      <c r="F24" s="31" t="s">
+        <v>323</v>
+      </c>
+      <c r="G24" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="B25" s="43" t="n">
+      <c r="A25" s="31" t="s">
+        <v>324</v>
+      </c>
+      <c r="B25" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="C25" s="41" t="n">
+      <c r="C25" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="43" t="n">
+      <c r="D25" s="42" t="n">
         <f aca="false">B25*C25</f>
         <v>5000</v>
       </c>
-      <c r="F25" s="32" t="s">
-        <v>327</v>
-      </c>
-      <c r="G25" s="29" t="n">
+      <c r="F25" s="31" t="s">
+        <v>325</v>
+      </c>
+      <c r="G25" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32" t="s">
-        <v>328</v>
-      </c>
-      <c r="B26" s="43" t="n">
+      <c r="A26" s="31" t="s">
+        <v>326</v>
+      </c>
+      <c r="B26" s="42" t="n">
         <v>4000</v>
       </c>
-      <c r="C26" s="41" t="n">
+      <c r="C26" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="43" t="n">
+      <c r="D26" s="42" t="n">
         <f aca="false">B26*C26</f>
         <v>4000</v>
       </c>
-      <c r="F26" s="32" t="s">
-        <v>329</v>
-      </c>
-      <c r="G26" s="29" t="n">
+      <c r="F26" s="31" t="s">
+        <v>327</v>
+      </c>
+      <c r="G26" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="D27" s="44" t="n">
+      <c r="D27" s="43" t="n">
         <f aca="false">SUM(D23:D26)</f>
         <v>14000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="38" t="s">
+      <c r="A29" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32" t="s">
-        <v>330</v>
-      </c>
-      <c r="D30" s="43" t="n">
+      <c r="A30" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="D30" s="42" t="n">
         <f aca="false">D19</f>
         <v>129000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="D31" s="43" t="n">
+      <c r="D31" s="42" t="n">
         <f aca="false">D27</f>
         <v>14000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="32" t="s">
-        <v>331</v>
-      </c>
-      <c r="D32" s="43" t="n">
+      <c r="A32" s="31" t="s">
+        <v>329</v>
+      </c>
+      <c r="D32" s="42" t="n">
         <f aca="false">(D30+D31)*Wyjaśnienia!$B$30</f>
         <v>17160</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="39" t="s">
+      <c r="A33" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="D33" s="44" t="n">
+      <c r="D33" s="43" t="n">
         <f aca="false">SUM(D30:D32)</f>
         <v>160160</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="D34" s="43" t="n">
+      <c r="D34" s="42" t="n">
         <f aca="false">D33*Wyjaśnienia!$B$33</f>
         <v>36836.8</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="39" t="s">
+      <c r="A35" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="D35" s="44" t="n">
+      <c r="D35" s="43" t="n">
         <f aca="false">D33+D34</f>
         <v>196996.8</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="38" t="s">
+      <c r="A37" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+    </row>
+    <row r="38" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="36" t="s">
+        <v>331</v>
+      </c>
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+    </row>
+    <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="39" t="s">
         <v>332</v>
       </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-    </row>
-    <row r="38" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="37" t="s">
+      <c r="B39" s="39" t="s">
         <v>333</v>
       </c>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-    </row>
-    <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="40" t="s">
+      <c r="C39" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="B39" s="40" t="s">
+      <c r="D39" s="39" t="s">
         <v>335</v>
       </c>
-      <c r="C39" s="40" t="s">
+      <c r="E39" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="D39" s="40" t="s">
-        <v>337</v>
-      </c>
-      <c r="E39" s="40" t="s">
-        <v>338</v>
-      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="41" t="n">
+      <c r="A40" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="B40" s="41" t="n">
+      <c r="B40" s="40" t="n">
         <f aca="false">A40*Wyjaśnienia!$B$46</f>
         <v>300</v>
       </c>
-      <c r="C40" s="41" t="n">
+      <c r="C40" s="40" t="n">
         <f aca="false">ROUNDUP(B40/100,0)</f>
         <v>3</v>
       </c>
-      <c r="D40" s="43" t="n">
+      <c r="D40" s="42" t="n">
         <f aca="false">C40*Wyjaśnienia!$B$47</f>
         <v>1500</v>
       </c>
-      <c r="E40" s="41" t="n">
+      <c r="E40" s="40" t="n">
         <f aca="false">ROUNDUP(B40*Wyjaśnienia!$B$50/60,0)</f>
         <v>150</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="41" t="n">
+      <c r="A41" s="40" t="n">
         <v>1000</v>
       </c>
-      <c r="B41" s="41" t="n">
+      <c r="B41" s="40" t="n">
         <f aca="false">A41*Wyjaśnienia!$B$46</f>
         <v>2000</v>
       </c>
-      <c r="C41" s="41" t="n">
+      <c r="C41" s="40" t="n">
         <f aca="false">ROUNDUP(B41/100,0)</f>
         <v>20</v>
       </c>
-      <c r="D41" s="43" t="n">
+      <c r="D41" s="42" t="n">
         <f aca="false">C41*Wyjaśnienia!$B$47</f>
         <v>10000</v>
       </c>
-      <c r="E41" s="41" t="n">
+      <c r="E41" s="40" t="n">
         <f aca="false">ROUNDUP(B41*Wyjaśnienia!$B$50/60,0)</f>
         <v>1000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="41" t="n">
+      <c r="A42" s="40" t="n">
         <v>10000</v>
       </c>
-      <c r="B42" s="41" t="n">
+      <c r="B42" s="40" t="n">
         <f aca="false">A42*Wyjaśnienia!$B$46</f>
         <v>20000</v>
       </c>
-      <c r="C42" s="41" t="n">
+      <c r="C42" s="40" t="n">
         <f aca="false">ROUNDUP(B42/100,0)</f>
         <v>200</v>
       </c>
-      <c r="D42" s="43" t="n">
+      <c r="D42" s="42" t="n">
         <f aca="false">C42*Wyjaśnienia!$B$47</f>
         <v>100000</v>
       </c>
-      <c r="E42" s="41" t="n">
+      <c r="E42" s="40" t="n">
         <f aca="false">ROUNDUP(B42*Wyjaśnienia!$B$50/60,0)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="41" t="n">
+      <c r="A43" s="40" t="n">
         <v>100000</v>
       </c>
-      <c r="B43" s="41" t="n">
+      <c r="B43" s="40" t="n">
         <f aca="false">A43*Wyjaśnienia!$B$46</f>
         <v>200000</v>
       </c>
-      <c r="C43" s="41" t="n">
+      <c r="C43" s="40" t="n">
         <f aca="false">ROUNDUP(B43/100,0)</f>
         <v>2000</v>
       </c>
-      <c r="D43" s="43" t="n">
+      <c r="D43" s="42" t="n">
         <f aca="false">C43*Wyjaśnienia!$B$47</f>
         <v>1000000</v>
       </c>
-      <c r="E43" s="41" t="n">
+      <c r="E43" s="40" t="n">
         <f aca="false">ROUNDUP(B43*Wyjaśnienia!$B$50/60,0)</f>
         <v>100000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="41" t="n">
+      <c r="A44" s="40" t="n">
         <v>1000000</v>
       </c>
-      <c r="B44" s="41" t="n">
+      <c r="B44" s="40" t="n">
         <f aca="false">A44*Wyjaśnienia!$B$46</f>
         <v>2000000</v>
       </c>
-      <c r="C44" s="41" t="n">
+      <c r="C44" s="40" t="n">
         <f aca="false">ROUNDUP(B44/100,0)</f>
         <v>20000</v>
       </c>
-      <c r="D44" s="43" t="n">
+      <c r="D44" s="42" t="n">
         <f aca="false">C44*Wyjaśnienia!$B$47</f>
         <v>10000000</v>
       </c>
-      <c r="E44" s="41" t="n">
+      <c r="E44" s="40" t="n">
         <f aca="false">ROUNDUP(B44*Wyjaśnienia!$B$50/60,0)</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="40" t="s">
+      <c r="A46" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="B46" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="C46" s="39" t="s">
         <v>339</v>
       </c>
-      <c r="B46" s="40" t="s">
+      <c r="D46" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="C46" s="40" t="s">
+      <c r="E46" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="D46" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="E46" s="40" t="s">
-        <v>343</v>
-      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="41" t="n">
+      <c r="A47" s="40" t="n">
         <v>30</v>
       </c>
-      <c r="B47" s="41" t="n">
+      <c r="B47" s="40" t="n">
         <f aca="false">A47*Wyjaśnienia!$B$75</f>
         <v>60</v>
       </c>
-      <c r="C47" s="43" t="n">
+      <c r="C47" s="42" t="n">
         <f aca="false">B47*Wyjaśnienia!$B$76</f>
         <v>18000</v>
       </c>
-      <c r="D47" s="41" t="n">
+      <c r="D47" s="40" t="n">
         <f aca="false">B47*2</f>
         <v>120</v>
       </c>
-      <c r="E47" s="41" t="n">
+      <c r="E47" s="40" t="n">
         <f aca="false">ROUNDUP(B47/Wyjaśnienia!$B$77,0)</f>
         <v>6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="41" t="n">
+      <c r="A48" s="40" t="n">
         <v>150</v>
       </c>
-      <c r="B48" s="41" t="n">
+      <c r="B48" s="40" t="n">
         <f aca="false">A48*Wyjaśnienia!$B$75</f>
         <v>300</v>
       </c>
-      <c r="C48" s="43" t="n">
+      <c r="C48" s="42" t="n">
         <f aca="false">B48*Wyjaśnienia!$B$76</f>
         <v>90000</v>
       </c>
-      <c r="D48" s="41" t="n">
+      <c r="D48" s="40" t="n">
         <f aca="false">B48*2</f>
         <v>600</v>
       </c>
-      <c r="E48" s="41" t="n">
+      <c r="E48" s="40" t="n">
         <f aca="false">ROUNDUP(B48/Wyjaśnienia!$B$77,0)</f>
         <v>30</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="41" t="n">
+      <c r="A49" s="40" t="n">
         <v>500</v>
       </c>
-      <c r="B49" s="41" t="n">
+      <c r="B49" s="40" t="n">
         <f aca="false">A49*Wyjaśnienia!$B$75</f>
         <v>1000</v>
       </c>
-      <c r="C49" s="43" t="n">
+      <c r="C49" s="42" t="n">
         <f aca="false">B49*Wyjaśnienia!$B$76</f>
         <v>300000</v>
       </c>
-      <c r="D49" s="41" t="n">
+      <c r="D49" s="40" t="n">
         <f aca="false">B49*2</f>
         <v>2000</v>
       </c>
-      <c r="E49" s="41" t="n">
+      <c r="E49" s="40" t="n">
         <f aca="false">ROUNDUP(B49/Wyjaśnienia!$B$77,0)</f>
         <v>100</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="41" t="n">
+      <c r="A50" s="40" t="n">
         <v>2000</v>
       </c>
-      <c r="B50" s="41" t="n">
+      <c r="B50" s="40" t="n">
         <f aca="false">A50*Wyjaśnienia!$B$75</f>
         <v>4000</v>
       </c>
-      <c r="C50" s="43" t="n">
+      <c r="C50" s="42" t="n">
         <f aca="false">B50*Wyjaśnienia!$B$76</f>
         <v>1200000</v>
       </c>
-      <c r="D50" s="41" t="n">
+      <c r="D50" s="40" t="n">
         <f aca="false">B50*2</f>
         <v>8000</v>
       </c>
-      <c r="E50" s="41" t="n">
+      <c r="E50" s="40" t="n">
         <f aca="false">ROUNDUP(B50/Wyjaśnienia!$B$77,0)</f>
         <v>400</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="41" t="n">
+      <c r="A51" s="40" t="n">
         <v>10000</v>
       </c>
-      <c r="B51" s="41" t="n">
+      <c r="B51" s="40" t="n">
         <f aca="false">A51*Wyjaśnienia!$B$75</f>
         <v>20000</v>
       </c>
-      <c r="C51" s="43" t="n">
+      <c r="C51" s="42" t="n">
         <f aca="false">B51*Wyjaśnienia!$B$76</f>
         <v>6000000</v>
       </c>
-      <c r="D51" s="41" t="n">
+      <c r="D51" s="40" t="n">
         <f aca="false">B51*2</f>
         <v>40000</v>
       </c>
-      <c r="E51" s="41" t="n">
+      <c r="E51" s="40" t="n">
         <f aca="false">ROUNDUP(B51/Wyjaśnienia!$B$77,0)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="37" t="s">
+      <c r="A53" s="36" t="s">
+        <v>342</v>
+      </c>
+      <c r="B53" s="36"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+    </row>
+    <row r="55" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="17" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B53" s="37"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
-    </row>
-    <row r="55" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="17" t="s">
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="C57" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="D57" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="F57" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="G57" s="38" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="B57" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="C57" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="D57" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="F57" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="G57" s="39" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B58" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" s="41" t="n">
+      <c r="B58" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$23*2</f>
         <v>300</v>
       </c>
-      <c r="D58" s="43" t="n">
+      <c r="D58" s="42" t="n">
         <f aca="false">B58*C58</f>
         <v>0</v>
       </c>
-      <c r="F58" s="32" t="s">
-        <v>348</v>
-      </c>
-      <c r="G58" s="29" t="n">
+      <c r="F58" s="31" t="s">
+        <v>346</v>
+      </c>
+      <c r="G58" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B59" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="41" t="n">
+        <v>347</v>
+      </c>
+      <c r="B59" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$53*2</f>
         <v>300</v>
       </c>
-      <c r="D59" s="43" t="n">
+      <c r="D59" s="42" t="n">
         <f aca="false">B59*C59</f>
         <v>0</v>
       </c>
-      <c r="F59" s="32" t="s">
+      <c r="F59" s="31" t="s">
+        <v>348</v>
+      </c>
+      <c r="G59" s="26" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B60" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="40" t="s">
         <v>350</v>
       </c>
-      <c r="G59" s="29" t="n">
+      <c r="D60" s="42" t="n">
+        <f aca="false">B60*C60</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="31" t="s">
+        <v>351</v>
+      </c>
+      <c r="G60" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B60" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="41" t="s">
+    <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="D60" s="43" t="n">
-        <f aca="false">B60*C60</f>
-        <v>0</v>
-      </c>
-      <c r="F60" s="32" t="s">
+      <c r="B61" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="40" t="s">
+        <v>350</v>
+      </c>
+      <c r="D61" s="42" t="n">
+        <f aca="false">B61*C61</f>
+        <v>0</v>
+      </c>
+      <c r="F61" s="31" t="s">
         <v>353</v>
       </c>
-      <c r="G60" s="29" t="n">
+      <c r="G61" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="38" t="s">
         <v>354</v>
       </c>
-      <c r="B61" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="41" t="s">
-        <v>352</v>
-      </c>
-      <c r="D61" s="43" t="n">
-        <f aca="false">B61*C61</f>
-        <v>0</v>
-      </c>
-      <c r="F61" s="32" t="s">
-        <v>355</v>
-      </c>
-      <c r="G61" s="29" t="n">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="39" t="s">
-        <v>356</v>
-      </c>
-      <c r="D62" s="44" t="n">
+      <c r="D62" s="43" t="n">
         <f aca="false">SUM(D58:D61)</f>
         <v>0</v>
       </c>
@@ -6829,48 +6763,48 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30" t="s">
-        <v>357</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="A2" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="s">
-        <v>358</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
+      <c r="A3" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
@@ -6897,7 +6831,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>0</v>
@@ -6914,15 +6848,15 @@
         <v>6600</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="G7" s="29" t="n">
+        <v>358</v>
+      </c>
+      <c r="G7" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>25</v>
@@ -6937,15 +6871,15 @@
         <v>5500</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="G8" s="29" t="n">
+        <v>360</v>
+      </c>
+      <c r="G8" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B9" s="21" t="n">
         <v>60</v>
@@ -6960,9 +6894,9 @@
         <v>13200</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="G9" s="29" t="n">
+        <v>362</v>
+      </c>
+      <c r="G9" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -6983,15 +6917,15 @@
         <v>4400</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G10" s="29" t="n">
+        <v>263</v>
+      </c>
+      <c r="G10" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B11" s="21" t="n">
         <v>40</v>
@@ -7006,15 +6940,15 @@
         <v>8800</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="G11" s="29" t="n">
+        <v>364</v>
+      </c>
+      <c r="G11" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B12" s="21" t="n">
         <v>40</v>
@@ -7029,15 +6963,15 @@
         <v>8800</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="G12" s="29" t="n">
+        <v>366</v>
+      </c>
+      <c r="G12" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B13" s="21" t="n">
         <v>25</v>
@@ -7052,15 +6986,15 @@
         <v>5500</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G13" s="29" t="n">
+        <v>368</v>
+      </c>
+      <c r="G13" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B14" s="21" t="n">
         <v>50</v>
@@ -7075,9 +7009,9 @@
         <v>11000</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="G14" s="29" t="n">
+        <v>370</v>
+      </c>
+      <c r="G14" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
@@ -7087,7 +7021,7 @@
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="34" t="n">
         <f aca="false">SUM(D7:D14)</f>
         <v>290</v>
       </c>
@@ -7096,18 +7030,18 @@
         <v>63800</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
@@ -7131,7 +7065,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$67</f>
@@ -7145,37 +7079,37 @@
         <v>180000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="G19" s="29" t="n">
+        <v>373</v>
+      </c>
+      <c r="G19" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B20" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$68</f>
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="C20" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="8" t="n">
         <f aca="false">B20*C20</f>
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="G20" s="29" t="n">
+        <v>170</v>
+      </c>
+      <c r="G20" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$69</f>
@@ -7189,15 +7123,15 @@
         <v>1200</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="G21" s="29" t="n">
+        <v>374</v>
+      </c>
+      <c r="G21" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>0</v>
@@ -7210,9 +7144,9 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="G22" s="29" t="n">
+        <v>376</v>
+      </c>
+      <c r="G22" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -7231,15 +7165,15 @@
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G23" s="29" t="n">
+        <v>277</v>
+      </c>
+      <c r="G23" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>0</v>
@@ -7252,15 +7186,15 @@
         <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="G24" s="29" t="n">
+        <v>378</v>
+      </c>
+      <c r="G24" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>0</v>
@@ -7273,15 +7207,15 @@
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="G25" s="29" t="n">
+        <v>380</v>
+      </c>
+      <c r="G25" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>0</v>
@@ -7294,15 +7228,15 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="G26" s="29" t="n">
+        <v>381</v>
+      </c>
+      <c r="G26" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>0</v>
@@ -7315,9 +7249,9 @@
         <v>0</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="G27" s="29" t="n">
+        <v>383</v>
+      </c>
+      <c r="G27" s="26" t="n">
         <v>2027</v>
       </c>
     </row>
@@ -7329,19 +7263,19 @@
       <c r="C28" s="26"/>
       <c r="D28" s="11" t="n">
         <f aca="false">SUM(D19:D27)</f>
-        <v>185200</v>
+        <v>193200</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34" t="s">
+      <c r="A30" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
@@ -7349,7 +7283,7 @@
       </c>
       <c r="D31" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$67+Wyjaśnienia!$B$68</f>
-        <v>184000</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7363,7 +7297,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D33" s="8" t="n">
         <f aca="false">D28-D31</f>
@@ -7385,7 +7319,7 @@
       </c>
       <c r="D35" s="11" t="n">
         <f aca="false">SUM(D31:D34)</f>
-        <v>256800</v>
+        <v>264800</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7394,7 +7328,7 @@
       </c>
       <c r="D36" s="8" t="n">
         <f aca="false">D35*Wyjaśnienia!$B$33</f>
-        <v>59064</v>
+        <v>60904</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7403,7 +7337,7 @@
       </c>
       <c r="D37" s="11" t="n">
         <f aca="false">D35+D36</f>
-        <v>315864</v>
+        <v>325704</v>
       </c>
     </row>
   </sheetData>
@@ -7439,31 +7373,29 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7475,7 +7407,6 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7485,7 +7416,6 @@
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7497,7 +7427,6 @@
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7526,7 +7455,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B7" s="23" t="n">
         <v>45</v>
@@ -7543,7 +7472,7 @@
         <v>9900</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>2028</v>
@@ -7565,7 +7494,6 @@
         <v>9900</v>
       </c>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7575,7 +7503,6 @@
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7587,7 +7514,6 @@
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7614,7 +7540,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B12" s="28" t="n">
         <v>8000</v>
@@ -7627,7 +7553,7 @@
         <v>8000</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="26" t="n">
@@ -7637,7 +7563,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B13" s="28" t="n">
         <v>1500</v>
@@ -7650,7 +7576,7 @@
         <v>1500</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="26" t="n">
@@ -7660,7 +7586,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B14" s="28" t="n">
         <v>4000</v>
@@ -7673,7 +7599,7 @@
         <v>4000</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="26" t="n">
@@ -7683,7 +7609,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B15" s="28" t="n">
         <v>8000</v>
@@ -7696,7 +7622,7 @@
         <v>8000</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="26" t="n">
@@ -7706,7 +7632,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B16" s="28" t="n">
         <v>0</v>
@@ -7719,15 +7645,15 @@
         <v>0</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="G16" s="29" t="n">
+        <v>397</v>
+      </c>
+      <c r="G16" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B17" s="28" t="n">
         <v>0</v>
@@ -7740,15 +7666,15 @@
         <v>0</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="G17" s="29" t="n">
+        <v>399</v>
+      </c>
+      <c r="G17" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B18" s="28" t="n">
         <v>0</v>
@@ -7761,15 +7687,15 @@
         <v>0</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="G18" s="29" t="n">
+        <v>401</v>
+      </c>
+      <c r="G18" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B19" s="28" t="n">
         <v>0</v>
@@ -7782,9 +7708,9 @@
         <v>0</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="G19" s="29" t="n">
+        <v>403</v>
+      </c>
+      <c r="G19" s="26" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -7800,12 +7726,10 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
-      <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7817,7 +7741,6 @@
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
-      <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7828,7 +7751,6 @@
         <f aca="false">E8</f>
         <v>9900</v>
       </c>
-      <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7843,12 +7765,11 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -7858,7 +7779,6 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7873,7 +7793,6 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7888,7 +7807,6 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7897,13 +7815,12 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="31" t="n">
+      <c r="D28" s="30" t="n">
         <f aca="false">D26+D27</f>
         <v>43256.64</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="406">
   <si>
     <t xml:space="preserve">Budżet pierwszej edycji Nagrody Konstela</t>
   </si>
@@ -570,6 +570,9 @@
   </si>
   <si>
     <t xml:space="preserve">Rezerwa (od pracy i kosztów, bez nagród)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liczona od pracy i kosztów twardych z wyłączeniem nagród publiczności i Nagrody Uczniowskiej - tak samo jak w pozostałych budżetach, gdzie rezerwa nagród nie obejmuje</t>
   </si>
   <si>
     <t xml:space="preserve">RAZEM NETTO</t>
@@ -1906,7 +1909,7 @@
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">'Budżet Nagrody'!$D$37</f>
-        <v>532156.8</v>
+        <v>529516.8</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -2007,7 +2010,7 @@
       </c>
       <c r="C13" s="11" t="n">
         <f aca="false">'Budżet Nagrody'!$D$37+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$33+'Budżet Plakatu'!$D$36+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$35</f>
-        <v>1709786.8</v>
+        <v>1707146.8</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -3474,20 +3477,23 @@
         <v>180</v>
       </c>
       <c r="D36" s="3" t="n">
-        <f aca="false">(D34+D35)*Wyjaśnienia!$B$30</f>
-        <v>17266.8</v>
+        <f aca="false">(D34+D35-D27-D29)*Wyjaśnienia!$B$30</f>
+        <v>14626.8</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="H36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="9" t="n">
         <f aca="false">SUM(D33:D36)</f>
-        <v>532156.8</v>
+        <v>529516.8</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -3495,13 +3501,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="8" t="n">
         <f aca="false">D37*Wyjaśnienia!$B$33</f>
-        <v>122396.064</v>
+        <v>121788.864</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -3509,13 +3515,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="30" t="n">
         <f aca="false">D37+D38</f>
-        <v>654552.864</v>
+        <v>651305.664</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -3636,7 +3642,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -3702,7 +3708,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B7" s="23" t="n">
         <v>45</v>
@@ -3719,7 +3725,7 @@
         <v>9900</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>2028</v>
@@ -3728,7 +3734,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B8" s="23" t="n">
         <v>40</v>
@@ -3745,7 +3751,7 @@
         <v>8800</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G8" s="26" t="n">
         <v>2028</v>
@@ -3754,7 +3760,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B9" s="23" t="n">
         <v>0</v>
@@ -3771,7 +3777,7 @@
         <v>2200</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G9" s="26" t="n">
         <v>2027</v>
@@ -3780,7 +3786,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B10" s="23" t="n">
         <v>50</v>
@@ -3797,7 +3803,7 @@
         <v>11000</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G10" s="26" t="n">
         <v>2027</v>
@@ -3806,7 +3812,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B11" s="23" t="n">
         <v>25</v>
@@ -3823,7 +3829,7 @@
         <v>5500</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G11" s="26" t="n">
         <v>2027</v>
@@ -3832,7 +3838,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B12" s="23" t="n">
         <v>160</v>
@@ -3849,7 +3855,7 @@
         <v>35200</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G12" s="26" t="n">
         <v>2027</v>
@@ -3858,7 +3864,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B13" s="23" t="n">
         <v>50</v>
@@ -3875,7 +3881,7 @@
         <v>11000</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G13" s="26" t="n">
         <v>2027</v>
@@ -3884,7 +3890,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B14" s="23" t="n">
         <v>72</v>
@@ -3966,7 +3972,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" s="28" t="n">
         <v>3000</v>
@@ -3979,7 +3985,7 @@
         <v>3000</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="26" t="n">
@@ -3989,7 +3995,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" s="28" t="n">
         <v>6000</v>
@@ -4002,10 +4008,10 @@
         <v>6000</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G20" s="26" t="n">
         <v>2027</v>
@@ -4014,7 +4020,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B21" s="28" t="n">
         <v>10000</v>
@@ -4027,7 +4033,7 @@
         <v>10000</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="26" t="n">
@@ -4037,7 +4043,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B22" s="28" t="n">
         <v>40000</v>
@@ -4050,7 +4056,7 @@
         <v>40000</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="26" t="n">
@@ -4060,7 +4066,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B23" s="28" t="n">
         <v>4000</v>
@@ -4073,7 +4079,7 @@
         <v>4000</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="26" t="n">
@@ -4083,7 +4089,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B24" s="28" t="n">
         <v>3000</v>
@@ -4096,7 +4102,7 @@
         <v>3000</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="26" t="n">
@@ -4106,7 +4112,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B25" s="28" t="n">
         <v>4000</v>
@@ -4119,7 +4125,7 @@
         <v>4000</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="26" t="n">
@@ -4129,7 +4135,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B26" s="28" t="n">
         <v>0</v>
@@ -4142,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="26" t="n">
@@ -4152,7 +4158,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B27" s="28" t="n">
         <v>15000</v>
@@ -4165,7 +4171,7 @@
         <v>15000</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="26" t="n">
@@ -4175,7 +4181,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B28" s="28" t="n">
         <v>6000</v>
@@ -4188,7 +4194,7 @@
         <v>6000</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="26" t="n">
@@ -4198,7 +4204,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B29" s="28" t="n">
         <v>30000</v>
@@ -4211,7 +4217,7 @@
         <v>30000</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="26" t="n">
@@ -4221,7 +4227,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B30" s="18" t="n">
         <v>4500</v>
@@ -4234,7 +4240,7 @@
         <v>4500</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G30" s="26" t="n">
         <v>2027</v>
@@ -4242,7 +4248,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B31" s="18" t="n">
         <v>0</v>
@@ -4255,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F31" s="31"/>
       <c r="G31" s="26" t="n">
@@ -4326,7 +4332,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -4340,7 +4346,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -4354,7 +4360,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -4368,7 +4374,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -4495,7 +4501,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4561,7 +4567,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B7" s="23" t="n">
         <v>0</v>
@@ -4578,7 +4584,7 @@
         <v>5500</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>2027</v>
@@ -4587,7 +4593,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B8" s="23" t="n">
         <v>40</v>
@@ -4602,7 +4608,7 @@
         <v>8800</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G8" s="26" t="n">
         <v>2028</v>
@@ -4611,7 +4617,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B9" s="23" t="n">
         <v>30</v>
@@ -4626,7 +4632,7 @@
         <v>6600</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G9" s="26" t="n">
         <v>2028</v>
@@ -4635,7 +4641,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B10" s="23" t="n">
         <v>20</v>
@@ -4650,7 +4656,7 @@
         <v>4400</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G10" s="26" t="n">
         <v>2028</v>
@@ -4659,7 +4665,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B11" s="23" t="n">
         <v>50</v>
@@ -4674,7 +4680,7 @@
         <v>11000</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G11" s="26" t="n">
         <v>2027</v>
@@ -4696,7 +4702,7 @@
         <v>36300</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H12" s="3"/>
     </row>
@@ -4744,7 +4750,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$24</f>
@@ -4758,7 +4764,7 @@
         <v>35000</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="26" t="n">
@@ -4792,7 +4798,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$26</f>
@@ -4807,7 +4813,7 @@
         <v>75000</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="26" t="n">
@@ -4831,7 +4837,7 @@
         <v>80000</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="26" t="n">
@@ -4841,7 +4847,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">Wyjaśnienia!$B$29</f>
@@ -4855,7 +4861,7 @@
         <v>1200</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="26" t="n">
@@ -4865,7 +4871,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B21" s="28" t="n">
         <v>0</v>
@@ -4878,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="26" t="n">
@@ -4901,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="26" t="n">
@@ -4910,7 +4916,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B23" s="28" t="n">
         <v>0</v>
@@ -4923,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="26" t="n">
@@ -4933,7 +4939,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>0</v>
@@ -4946,10 +4952,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G24" s="26" t="n">
         <v>2027</v>
@@ -4957,7 +4963,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B25" s="18" t="n">
         <v>0</v>
@@ -4970,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F25" s="31"/>
       <c r="G25" s="26" t="n">
@@ -5037,7 +5043,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -5065,7 +5071,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -5079,7 +5085,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -5093,7 +5099,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -5224,7 +5230,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="29" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -5277,7 +5283,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>0</v>
@@ -5294,7 +5300,7 @@
         <v>4400</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>2027</v>
@@ -5302,7 +5308,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>30</v>
@@ -5317,7 +5323,7 @@
         <v>6600</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G8" s="26" t="n">
         <v>2028</v>
@@ -5325,7 +5331,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B9" s="21" t="n">
         <v>20</v>
@@ -5340,7 +5346,7 @@
         <v>4400</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G9" s="26" t="n">
         <v>2028</v>
@@ -5348,7 +5354,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B10" s="21" t="n">
         <v>35</v>
@@ -5363,7 +5369,7 @@
         <v>7700</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G10" s="26" t="n">
         <v>2028</v>
@@ -5371,7 +5377,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B11" s="21" t="n">
         <v>15</v>
@@ -5386,7 +5392,7 @@
         <v>3300</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G11" s="26" t="n">
         <v>2028</v>
@@ -5394,7 +5400,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B12" s="21" t="n">
         <v>50</v>
@@ -5409,7 +5415,7 @@
         <v>11000</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G12" s="26" t="n">
         <v>2027</v>
@@ -5417,7 +5423,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B13" s="21" t="n">
         <v>20</v>
@@ -5432,7 +5438,7 @@
         <v>4400</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G13" s="26" t="n">
         <v>2028</v>
@@ -5451,7 +5457,7 @@
         <v>41800</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5486,7 +5492,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B18" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$54</f>
@@ -5500,7 +5506,7 @@
         <v>90000</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G18" s="26" t="n">
         <v>2028</v>
@@ -5508,7 +5514,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$55</f>
@@ -5530,7 +5536,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B20" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$56</f>
@@ -5544,7 +5550,7 @@
         <v>1200</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G20" s="26" t="n">
         <v>2028</v>
@@ -5552,7 +5558,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>0</v>
@@ -5565,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G21" s="26" t="n">
         <v>2028</v>
@@ -5586,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G22" s="26" t="n">
         <v>2027</v>
@@ -5594,7 +5600,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B23" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$61*2</f>
@@ -5609,7 +5615,7 @@
         <v>8000</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G23" s="26" t="n">
         <v>2028</v>
@@ -5631,7 +5637,7 @@
         <v>3000</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G24" s="26" t="n">
         <v>2028</v>
@@ -5639,7 +5645,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B25" s="18" t="n">
         <v>0</v>
@@ -5652,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G25" s="26" t="n">
         <v>2028</v>
@@ -5660,7 +5666,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>0</v>
@@ -5673,7 +5679,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G26" s="26" t="n">
         <v>2027</v>
@@ -5681,7 +5687,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B27" s="18" t="n">
         <v>0</v>
@@ -5694,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G27" s="26" t="n">
         <v>2028</v>
@@ -5702,7 +5708,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B28" s="18" t="n">
         <v>0</v>
@@ -5715,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G28" s="26" t="n">
         <v>2028</v>
@@ -5763,7 +5769,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D34" s="8" t="n">
         <f aca="false">D29-D32</f>
@@ -5781,7 +5787,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D36" s="11" t="n">
         <f aca="false">SUM(D32:D35)</f>
@@ -5790,7 +5796,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D37" s="8" t="n">
         <f aca="false">D36*Wyjaśnienia!$B$33</f>
@@ -5799,7 +5805,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D38" s="11" t="n">
         <f aca="false">D36+D37</f>
@@ -5808,12 +5814,12 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5838,7 +5844,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B43" s="8" t="n">
         <v>0</v>
@@ -5851,12 +5857,12 @@
         <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B44" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$16</f>
@@ -5870,7 +5876,7 @@
         <v>4400</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -5921,7 +5927,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -5931,7 +5937,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B3" s="36"/>
       <c r="C3" s="36"/>
@@ -5941,7 +5947,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="37"/>
@@ -5954,7 +5960,7 @@
         <v>125</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>130</v>
@@ -5962,79 +5968,79 @@
     </row>
     <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="31" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B7" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$17</f>
         <v>150</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B8" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$46</f>
         <v>2</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="38" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B9" s="41" t="n">
         <f aca="false">B7*B8</f>
         <v>300</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B10" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$66</f>
         <v>150</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B11" s="40" t="n">
         <f aca="false">Wyjaśnienia!$B$75</f>
         <v>2</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B12" s="41" t="n">
         <f aca="false">B10*B11</f>
         <v>300</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="37" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B14" s="37"/>
       <c r="C14" s="37"/>
@@ -6047,7 +6053,7 @@
         <v>125</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C15" s="39" t="s">
         <v>155</v>
@@ -6064,7 +6070,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B16" s="42" t="n">
         <f aca="false">Wyjaśnienia!$B$48</f>
@@ -6079,7 +6085,7 @@
         <v>37500</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G16" s="26" t="n">
         <v>2027</v>
@@ -6087,7 +6093,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B17" s="42" t="n">
         <f aca="false">Wyjaśnienia!$B$47</f>
@@ -6102,7 +6108,7 @@
         <v>1500</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G17" s="26" t="n">
         <v>2027</v>
@@ -6110,7 +6116,7 @@
     </row>
     <row r="18" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B18" s="42" t="n">
         <f aca="false">Wyjaśnienia!$B$76</f>
@@ -6125,7 +6131,7 @@
         <v>90000</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G18" s="26" t="n">
         <v>2028</v>
@@ -6133,7 +6139,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D19" s="43" t="n">
         <f aca="false">SUM(D16:D18)</f>
@@ -6172,7 +6178,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B23" s="42" t="n">
         <v>2000</v>
@@ -6185,7 +6191,7 @@
         <v>2000</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G23" s="26" t="n">
         <v>2027</v>
@@ -6193,7 +6199,7 @@
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B24" s="42" t="n">
         <v>3000</v>
@@ -6206,7 +6212,7 @@
         <v>3000</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G24" s="26" t="n">
         <v>2027</v>
@@ -6214,7 +6220,7 @@
     </row>
     <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B25" s="42" t="n">
         <v>5000</v>
@@ -6227,7 +6233,7 @@
         <v>5000</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G25" s="26" t="n">
         <v>2027</v>
@@ -6235,7 +6241,7 @@
     </row>
     <row r="26" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B26" s="42" t="n">
         <v>4000</v>
@@ -6248,7 +6254,7 @@
         <v>4000</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G26" s="26" t="n">
         <v>2027</v>
@@ -6275,7 +6281,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D30" s="42" t="n">
         <f aca="false">D19</f>
@@ -6293,7 +6299,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="31" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D32" s="42" t="n">
         <f aca="false">(D30+D31)*Wyjaśnienia!$B$30</f>
@@ -6302,7 +6308,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="38" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D33" s="43" t="n">
         <f aca="false">SUM(D30:D32)</f>
@@ -6311,7 +6317,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D34" s="42" t="n">
         <f aca="false">D33*Wyjaśnienia!$B$33</f>
@@ -6320,7 +6326,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D35" s="43" t="n">
         <f aca="false">D33+D34</f>
@@ -6329,7 +6335,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" s="37"/>
       <c r="C37" s="37"/>
@@ -6339,7 +6345,7 @@
     </row>
     <row r="38" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="36" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38" s="36"/>
       <c r="C38" s="36"/>
@@ -6349,19 +6355,19 @@
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="39" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D39" s="39" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E39" s="39" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6471,19 +6477,19 @@
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="39" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C46" s="39" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D46" s="39" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6593,7 +6599,7 @@
     </row>
     <row r="53" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="36" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B53" s="36"/>
       <c r="C53" s="36"/>
@@ -6603,12 +6609,12 @@
     </row>
     <row r="55" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6616,7 +6622,7 @@
         <v>125</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C57" s="38" t="s">
         <v>155</v>
@@ -6633,7 +6639,7 @@
     </row>
     <row r="58" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B58" s="42" t="n">
         <v>0</v>
@@ -6647,7 +6653,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="31" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G58" s="26" t="n">
         <v>2027</v>
@@ -6655,7 +6661,7 @@
     </row>
     <row r="59" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B59" s="42" t="n">
         <v>0</v>
@@ -6669,7 +6675,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G59" s="26" t="n">
         <v>2027</v>
@@ -6677,20 +6683,20 @@
     </row>
     <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B60" s="42" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="40" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D60" s="42" t="n">
         <f aca="false">B60*C60</f>
         <v>0</v>
       </c>
       <c r="F60" s="31" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G60" s="26" t="n">
         <v>2027</v>
@@ -6698,20 +6704,20 @@
     </row>
     <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B61" s="42" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="40" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D61" s="42" t="n">
         <f aca="false">B61*C61</f>
         <v>0</v>
       </c>
       <c r="F61" s="31" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G61" s="26" t="n">
         <v>2027</v>
@@ -6719,7 +6725,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="38" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D62" s="43" t="n">
         <f aca="false">SUM(D58:D61)</f>
@@ -6778,7 +6784,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -6788,7 +6794,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -6831,7 +6837,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>0</v>
@@ -6848,7 +6854,7 @@
         <v>6600</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>2027</v>
@@ -6856,7 +6862,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>25</v>
@@ -6871,7 +6877,7 @@
         <v>5500</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G8" s="26" t="n">
         <v>2027</v>
@@ -6879,7 +6885,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B9" s="21" t="n">
         <v>60</v>
@@ -6894,7 +6900,7 @@
         <v>13200</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G9" s="26" t="n">
         <v>2028</v>
@@ -6902,7 +6908,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B10" s="21" t="n">
         <v>20</v>
@@ -6917,7 +6923,7 @@
         <v>4400</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G10" s="26" t="n">
         <v>2028</v>
@@ -6925,7 +6931,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B11" s="21" t="n">
         <v>40</v>
@@ -6940,7 +6946,7 @@
         <v>8800</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G11" s="26" t="n">
         <v>2028</v>
@@ -6948,7 +6954,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B12" s="21" t="n">
         <v>40</v>
@@ -6963,7 +6969,7 @@
         <v>8800</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G12" s="26" t="n">
         <v>2028</v>
@@ -6971,7 +6977,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B13" s="21" t="n">
         <v>25</v>
@@ -6986,7 +6992,7 @@
         <v>5500</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G13" s="26" t="n">
         <v>2027</v>
@@ -6994,7 +7000,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B14" s="21" t="n">
         <v>50</v>
@@ -7009,7 +7015,7 @@
         <v>11000</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G14" s="26" t="n">
         <v>2027</v>
@@ -7030,7 +7036,7 @@
         <v>63800</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7065,7 +7071,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$67</f>
@@ -7079,7 +7085,7 @@
         <v>180000</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G19" s="26" t="n">
         <v>2028</v>
@@ -7087,7 +7093,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B20" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$68</f>
@@ -7109,7 +7115,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B21" s="8" t="n">
         <f aca="false">Wyjaśnienia!$B$69</f>
@@ -7123,7 +7129,7 @@
         <v>1200</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G21" s="26" t="n">
         <v>2028</v>
@@ -7131,7 +7137,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>0</v>
@@ -7144,7 +7150,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G22" s="26" t="n">
         <v>2028</v>
@@ -7165,7 +7171,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G23" s="26" t="n">
         <v>2027</v>
@@ -7173,7 +7179,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>0</v>
@@ -7186,7 +7192,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G24" s="26" t="n">
         <v>2028</v>
@@ -7194,7 +7200,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>0</v>
@@ -7207,7 +7213,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G25" s="26" t="n">
         <v>2028</v>
@@ -7215,7 +7221,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>0</v>
@@ -7228,7 +7234,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G26" s="26" t="n">
         <v>2028</v>
@@ -7236,7 +7242,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>0</v>
@@ -7249,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G27" s="26" t="n">
         <v>2027</v>
@@ -7297,7 +7303,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D33" s="8" t="n">
         <f aca="false">D28-D31</f>
@@ -7315,7 +7321,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D35" s="11" t="n">
         <f aca="false">SUM(D31:D34)</f>
@@ -7324,7 +7330,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D36" s="8" t="n">
         <f aca="false">D35*Wyjaśnienia!$B$33</f>
@@ -7333,7 +7339,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D37" s="11" t="n">
         <f aca="false">D35+D36</f>
@@ -7378,7 +7384,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7389,7 +7395,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -7455,7 +7461,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B7" s="23" t="n">
         <v>45</v>
@@ -7472,7 +7478,7 @@
         <v>9900</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>2028</v>
@@ -7540,7 +7546,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B12" s="28" t="n">
         <v>8000</v>
@@ -7553,7 +7559,7 @@
         <v>8000</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="26" t="n">
@@ -7563,7 +7569,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B13" s="28" t="n">
         <v>1500</v>
@@ -7576,7 +7582,7 @@
         <v>1500</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="26" t="n">
@@ -7586,7 +7592,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B14" s="28" t="n">
         <v>4000</v>
@@ -7599,7 +7605,7 @@
         <v>4000</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="26" t="n">
@@ -7609,7 +7615,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B15" s="28" t="n">
         <v>8000</v>
@@ -7622,7 +7628,7 @@
         <v>8000</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="26" t="n">
@@ -7632,7 +7638,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B16" s="28" t="n">
         <v>0</v>
@@ -7645,7 +7651,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G16" s="26" t="n">
         <v>2028</v>
@@ -7653,7 +7659,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B17" s="28" t="n">
         <v>0</v>
@@ -7666,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G17" s="26" t="n">
         <v>2028</v>
@@ -7674,7 +7680,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B18" s="28" t="n">
         <v>0</v>
@@ -7687,7 +7693,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G18" s="26" t="n">
         <v>2028</v>
@@ -7695,7 +7701,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B19" s="28" t="n">
         <v>0</v>
@@ -7708,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G19" s="26" t="n">
         <v>2028</v>
@@ -7769,7 +7775,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -7783,7 +7789,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -7797,7 +7803,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -7811,7 +7817,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="45.4" customWidth="1" style="44" min="1" max="1"/>
@@ -1093,35 +1093,25 @@
     <row r="26" ht="15" customHeight="1" s="45">
       <c r="A26" s="47" t="inlineStr">
         <is>
-          <t>Nagranie studyjne - koszt za utwór (netto)</t>
+          <t>Nagrody publiczności rozmowy łącznie (brutto)</t>
         </is>
       </c>
       <c r="B26" s="56" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C26" s="57" t="inlineStr">
-        <is>
-          <t>Środek widełek 5-10 tys. Do wyceny przez Michała Sołtana.</t>
-        </is>
-      </c>
-      <c r="D26" s="47" t="n"/>
-      <c r="E26" s="47" t="n"/>
-      <c r="F26" s="47" t="n"/>
-      <c r="G26" s="47" t="n"/>
-      <c r="H26" s="47" t="n"/>
+        <v>12000</v>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="45">
       <c r="A27" s="47" t="inlineStr">
         <is>
-          <t>Liczba nagrań studyjnych</t>
+          <t>Nagranie studyjne - koszt za utwór (netto)</t>
         </is>
       </c>
       <c r="B27" s="56" t="n">
-        <v>10</v>
+        <v>7500</v>
       </c>
       <c r="C27" s="57" t="inlineStr">
         <is>
-          <t>Dziesięciu finalistów; te nagrania trafiają na płytę.</t>
+          <t>Środek widełek 5-10 tys. Do wyceny przez Michała Sołtana.</t>
         </is>
       </c>
       <c r="D27" s="47" t="n"/>
@@ -1133,15 +1123,15 @@
     <row r="28" ht="15" customHeight="1" s="45">
       <c r="A28" s="47" t="inlineStr">
         <is>
-          <t>Hymn z teledyskiem (netto)</t>
+          <t>Liczba nagrań studyjnych</t>
         </is>
       </c>
       <c r="B28" s="56" t="n">
-        <v>80000</v>
+        <v>10</v>
       </c>
       <c r="C28" s="57" t="inlineStr">
         <is>
-          <t>Środek widełek 60-100 tys. Górny koniec przy szerszym składzie.</t>
+          <t>Dziesięciu finalistów; te nagrania trafiają na płytę.</t>
         </is>
       </c>
       <c r="D28" s="47" t="n"/>
@@ -1153,15 +1143,15 @@
     <row r="29" ht="15" customHeight="1" s="45">
       <c r="A29" s="47" t="inlineStr">
         <is>
-          <t>Medal zwycięzcy i dyplomy piosenki (netto)</t>
+          <t>Hymn z teledyskiem (netto)</t>
         </is>
       </c>
       <c r="B29" s="56" t="n">
-        <v>1200</v>
+        <v>80000</v>
       </c>
       <c r="C29" s="57" t="inlineStr">
         <is>
-          <t>Ten sam medal co w plebiscycie na rozmowę, cena jak w Budżecie Nagrody.</t>
+          <t>Środek widełek 60-100 tys. Górny koniec przy szerszym składzie.</t>
         </is>
       </c>
       <c r="D29" s="47" t="n"/>
@@ -1173,15 +1163,15 @@
     <row r="30" ht="15" customHeight="1" s="45">
       <c r="A30" s="47" t="inlineStr">
         <is>
-          <t>Rezerwa w Budżecie Nagrody</t>
-        </is>
-      </c>
-      <c r="B30" s="58" t="n">
-        <v>0.12</v>
+          <t>Medal zwycięzcy i dyplomy piosenki (netto)</t>
+        </is>
+      </c>
+      <c r="B30" s="56" t="n">
+        <v>1200</v>
       </c>
       <c r="C30" s="57" t="inlineStr">
         <is>
-          <t>Narzut na nieprzewidziane.</t>
+          <t>Ten sam medal co w plebiscycie na rozmowę, cena jak w Budżecie Nagrody.</t>
         </is>
       </c>
       <c r="D30" s="47" t="n"/>
@@ -1193,15 +1183,15 @@
     <row r="31" ht="15" customHeight="1" s="45">
       <c r="A31" s="47" t="inlineStr">
         <is>
-          <t>Marża w Budżecie Antologii</t>
+          <t>Rezerwa w Budżecie Nagrody</t>
         </is>
       </c>
       <c r="B31" s="58" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="C31" s="57" t="inlineStr">
         <is>
-          <t>Narzut wynagrodzenia podmiotu, który wykona tę część, liczony od pracy i kosztów twardych. Nie są to środki pozostające u Organizatora ani rezerwa. W kosztorysie dotacyjnym pozycja ta nie wystąpi.</t>
+          <t>Narzut na nieprzewidziane.</t>
         </is>
       </c>
       <c r="D31" s="47" t="n"/>
@@ -1213,15 +1203,15 @@
     <row r="32" ht="15" customHeight="1" s="45">
       <c r="A32" s="47" t="inlineStr">
         <is>
-          <t>Rezerwa w Budżecie Plebiscytu</t>
+          <t>Marża w Budżecie Antologii</t>
         </is>
       </c>
       <c r="B32" s="58" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="C32" s="57" t="inlineStr">
         <is>
-          <t>Narzut na nieprzewidziane.</t>
+          <t>Narzut wynagrodzenia podmiotu, który wykona tę część, liczony od pracy i kosztów twardych. Nie są to środki pozostające u Organizatora ani rezerwa. W kosztorysie dotacyjnym pozycja ta nie wystąpi.</t>
         </is>
       </c>
       <c r="D32" s="47" t="n"/>
@@ -1233,15 +1223,15 @@
     <row r="33" ht="15" customHeight="1" s="45">
       <c r="A33" s="47" t="inlineStr">
         <is>
-          <t>Stawka VAT</t>
+          <t>Rezerwa w Budżecie Plebiscytu</t>
         </is>
       </c>
       <c r="B33" s="58" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="C33" s="57" t="inlineStr">
         <is>
-          <t>Dotyczy faktur wystawianych sponsorom.</t>
+          <t>Narzut na nieprzewidziane.</t>
         </is>
       </c>
       <c r="D33" s="47" t="n"/>
@@ -1253,7 +1243,15 @@
     <row r="34" ht="15" customHeight="1" s="45">
       <c r="A34" s="47" t="inlineStr">
         <is>
-          <t>Podatek od nagród (ryczałt)</t>
+          <t>Stawka VAT</t>
+        </is>
+      </c>
+      <c r="B34" s="58" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C34" s="57" t="inlineStr">
+        <is>
+          <t>Dotyczy faktur wystawianych sponsorom.</t>
         </is>
       </c>
       <c r="D34" s="47" t="n"/>
@@ -1263,7 +1261,11 @@
       <c r="H34" s="47" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="45">
-      <c r="A35" s="47" t="n"/>
+      <c r="A35" s="47" t="inlineStr">
+        <is>
+          <t>Podatek od nagród (ryczałt)</t>
+        </is>
+      </c>
       <c r="D35" s="47" t="n"/>
       <c r="E35" s="47" t="n"/>
       <c r="F35" s="47" t="n"/>
@@ -1271,11 +1273,7 @@
       <c r="H35" s="47" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="45">
-      <c r="A36" s="49" t="inlineStr">
-        <is>
-          <t>CZEGO JESZCZE NIE MA</t>
-        </is>
-      </c>
+      <c r="A36" s="47" t="n"/>
       <c r="D36" s="47" t="n"/>
       <c r="E36" s="47" t="n"/>
       <c r="F36" s="47" t="n"/>
@@ -1283,9 +1281,9 @@
       <c r="H36" s="47" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="45">
-      <c r="A37" s="50" t="inlineStr">
-        <is>
-          <t>Honoraria jury we wszystkich plebiscytach - osobno za ocenę zgłoszeń i za etap przygotowania karty oceny</t>
+      <c r="A37" s="49" t="inlineStr">
+        <is>
+          <t>CZEGO JESZCZE NIE MA</t>
         </is>
       </c>
       <c r="D37" s="47" t="n"/>
@@ -1297,7 +1295,7 @@
     <row r="38" ht="15" customHeight="1" s="45">
       <c r="A38" s="50" t="inlineStr">
         <is>
-          <t>Realizacja części artystycznej gali</t>
+          <t>Honoraria jury we wszystkich plebiscytach - osobno za ocenę zgłoszeń i za etap przygotowania karty oceny</t>
         </is>
       </c>
       <c r="D38" s="47" t="n"/>
@@ -1307,9 +1305,9 @@
       <c r="H38" s="47" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="45">
-      <c r="A39" s="48" t="inlineStr">
-        <is>
-          <t>Po wpisaniu tych kwot rosną Budżet Plebiscytu, Budżet Plakatu i Budżet Filmu. W Budżecie Plakatu czekają na wycenę cztery pozycje, w Budżecie Filmu pięć - wszystkie opisane w kolumnie Uwagi.</t>
+      <c r="A39" s="50" t="inlineStr">
+        <is>
+          <t>Realizacja części artystycznej gali</t>
         </is>
       </c>
       <c r="D39" s="47" t="n"/>
@@ -1319,7 +1317,11 @@
       <c r="H39" s="47" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="45">
-      <c r="A40" s="47" t="n"/>
+      <c r="A40" s="48" t="inlineStr">
+        <is>
+          <t>Po wpisaniu tych kwot rosną Budżet Plebiscytu, Budżet Plakatu i Budżet Filmu. W Budżecie Plakatu czekają na wycenę cztery pozycje, w Budżecie Filmu pięć - wszystkie opisane w kolumnie Uwagi.</t>
+        </is>
+      </c>
       <c r="D40" s="47" t="n"/>
       <c r="E40" s="47" t="n"/>
       <c r="F40" s="47" t="n"/>
@@ -1327,11 +1329,7 @@
       <c r="H40" s="47" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="45">
-      <c r="A41" s="49" t="inlineStr">
-        <is>
-          <t>JAK CZYTAĆ BUDŻETY</t>
-        </is>
-      </c>
+      <c r="A41" s="47" t="n"/>
       <c r="D41" s="47" t="n"/>
       <c r="E41" s="47" t="n"/>
       <c r="F41" s="47" t="n"/>
@@ -1339,9 +1337,9 @@
       <c r="H41" s="47" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="45">
-      <c r="A42" s="48" t="inlineStr">
-        <is>
-          <t>Każda z zakładek budżetowych ma ten sam układ: praca organizatora, koszty twarde, podsumowanie.</t>
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>JAK CZYTAĆ BUDŻETY</t>
         </is>
       </c>
       <c r="D42" s="47" t="n"/>
@@ -1353,7 +1351,7 @@
     <row r="43" ht="15" customHeight="1" s="45">
       <c r="A43" s="48" t="inlineStr">
         <is>
-          <t>W podsumowaniu jest kwota netto, VAT i kwota brutto, którą sponsor widzi na fakturze.</t>
+          <t>Każda z zakładek budżetowych ma ten sam układ: praca organizatora, koszty twarde, podsumowanie.</t>
         </is>
       </c>
       <c r="D43" s="47" t="n"/>
@@ -1363,451 +1361,462 @@
       <c r="H43" s="47" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="45">
-      <c r="A44" s="47" t="inlineStr">
+      <c r="A44" s="48" t="inlineStr">
+        <is>
+          <t>W podsumowaniu jest kwota netto, VAT i kwota brutto, którą sponsor widzi na fakturze.</t>
+        </is>
+      </c>
+      <c r="D44" s="47" t="n"/>
+      <c r="E44" s="47" t="n"/>
+      <c r="F44" s="47" t="n"/>
+      <c r="G44" s="47" t="n"/>
+      <c r="H44" s="47" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="45">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>Kolumna "Rok kosztu" w każdej zakładce mówi, na który rok edycji przypada dana pozycja: 2027 to rok naboru, 2028 to ocena jury, nagrody, produkcja antologii, gala i wystawy. Rezerwa i marża dzielą się proporcjonalnie do kosztów danego roku. Podział w tym układzie pokazuje załącznik "Zestawienie zadania".</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="45">
-      <c r="A45" s="59" t="inlineStr">
+    <row r="46" ht="15" customHeight="1" s="45">
+      <c r="A46" s="59" t="inlineStr">
         <is>
           <t>AKADEMIA - PARAMETRY SKALOWANIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="45">
-      <c r="A46" s="47" t="inlineStr">
-        <is>
-          <t>Odczytów na jedno zgłoszenie w rundzie pierwszej</t>
-        </is>
-      </c>
-      <c r="B46" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="C46" s="47" t="inlineStr">
-        <is>
-          <t>Regulamin § 8: co najmniej dwóch czytelników przy 21-60 zgłoszeniach; powyżej 200 przesiew jednoosobowy z drugim odczytem poniżej progu.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="45">
       <c r="A47" s="47" t="inlineStr">
         <is>
-          <t>Voucher za każde 100 ocenionych rozmów (netto)</t>
-        </is>
-      </c>
-      <c r="B47" s="60" t="n">
-        <v>500</v>
+          <t>Odczytów na jedno zgłoszenie w rundzie pierwszej</t>
+        </is>
+      </c>
+      <c r="B47" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="C47" s="47" t="inlineStr">
         <is>
-          <t>Świadczenie rzeczowe sponsora Akademii. Do ustalenia ze sponsorem.</t>
+          <t>Regulamin § 8: co najmniej dwóch czytelników przy 21-60 zgłoszeniach; powyżej 200 przesiew jednoosobowy z drugim odczytem poniżej progu.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="45">
       <c r="A48" s="47" t="inlineStr">
         <is>
-          <t>Honorarium podstawowe czytelnika (netto)</t>
+          <t>Voucher za każde 100 ocenionych rozmów (netto)</t>
         </is>
       </c>
       <c r="B48" s="60" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="C48" s="47" t="inlineStr">
         <is>
-          <t>Przeniesione z Budżetu Nagrody. Voucher jest dodatkiem, nie zamiennikiem.</t>
+          <t>Świadczenie rzeczowe sponsora Akademii. Do ustalenia ze sponsorem.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="45">
       <c r="A49" s="47" t="inlineStr">
         <is>
-          <t>Liczba czytelników w pierwszej edycji</t>
-        </is>
-      </c>
-      <c r="B49" s="56" t="n">
-        <v>15</v>
+          <t>Honorarium podstawowe czytelnika (netto)</t>
+        </is>
+      </c>
+      <c r="B49" s="60" t="n">
+        <v>2500</v>
       </c>
       <c r="C49" s="47" t="inlineStr">
         <is>
-          <t>Maksymalnie 20 zgłoszeń na czytelnika (regulamin § 8).</t>
+          <t>Przeniesione z Budżetu Nagrody. Voucher jest dodatkiem, nie zamiennikiem.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="45">
       <c r="A50" s="47" t="inlineStr">
         <is>
+          <t>Liczba czytelników w pierwszej edycji</t>
+        </is>
+      </c>
+      <c r="B50" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="C50" s="47" t="inlineStr">
+        <is>
+          <t>Maksymalnie 20 zgłoszeń na czytelnika (regulamin § 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="45">
+      <c r="A51" s="47" t="inlineStr">
+        <is>
           <t>Czas na jeden odczyt rozmowy wraz z kartą oceny (minut)</t>
         </is>
       </c>
-      <c r="B50" s="61" t="n">
+      <c r="B51" s="61" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="45"/>
-    <row r="52" ht="15" customHeight="1" s="45">
-      <c r="A52" s="62" t="inlineStr">
+    <row r="52" ht="15" customHeight="1" s="45"/>
+    <row r="53" ht="15" customHeight="1" s="45">
+      <c r="A53" s="62" t="inlineStr">
         <is>
           <t>PLAKAT - PARAMETRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="45">
-      <c r="A53" s="44" t="inlineStr">
-        <is>
-          <t>Liczba zgłoszeń plakatów</t>
-        </is>
-      </c>
-      <c r="B53" s="63" t="n">
-        <v>150</v>
-      </c>
-      <c r="C53" s="44" t="inlineStr">
-        <is>
-          <t>Wpływa na koszt kontroli formalnej.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="45">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>Nagrody plakatu łącznie (brutto)</t>
-        </is>
-      </c>
-      <c r="B54" s="60" t="n">
-        <v>90000</v>
+          <t>Liczba zgłoszeń plakatów</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="n">
+        <v>150</v>
       </c>
       <c r="C54" s="44" t="inlineStr">
         <is>
-          <t>50 tys. + 25 tys. + 15 tys. dla czołowej trójki.</t>
+          <t>Wpływa na koszt kontroli formalnej.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="45">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>Nagrody publiczności plakatu łącznie (brutto)</t>
+          <t>Nagrody plakatu łącznie (brutto)</t>
         </is>
       </c>
       <c r="B55" s="60" t="n">
-        <v>12000</v>
+        <v>90000</v>
       </c>
       <c r="C55" s="44" t="inlineStr">
         <is>
-          <t>3 000 zł dla pracy z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych plakatów (§ 12 ust. 6).</t>
+          <t>50 tys. + 25 tys. + 15 tys. dla czołowej trójki.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="45">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>Medal zwycięzcy i dyplomy plakatu (netto)</t>
+          <t>Nagrody publiczności plakatu łącznie (brutto)</t>
         </is>
       </c>
       <c r="B56" s="60" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
       <c r="C56" s="44" t="inlineStr">
         <is>
-          <t>Ten sam medal co w plebiscycie na rozmowę, cena jak w Budżecie Nagrody.</t>
+          <t>3 000 zł dla pracy z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych plakatów (§ 12 ust. 6).</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="45">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>Liczba jurorów plakatu</t>
-        </is>
-      </c>
-      <c r="B57" s="63" t="n">
-        <v>5</v>
+          <t>Medal zwycięzcy i dyplomy plakatu (netto)</t>
+        </is>
+      </c>
+      <c r="B57" s="60" t="n">
+        <v>1200</v>
       </c>
       <c r="C57" s="44" t="inlineStr">
         <is>
-          <t>Kotwica, nie decyzja: pozycja honorariów w Budżecie Plakatu stoi na zerze jako DO USTALENIA, do rozmowy z przewodniczącym jury.</t>
+          <t>Ten sam medal co w plebiscycie na rozmowę, cena jak w Budżecie Nagrody.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="45">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>Godzin oceny na jurora</t>
+          <t>Liczba jurorów plakatu</t>
         </is>
       </c>
       <c r="B58" s="63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C58" s="44" t="inlineStr">
         <is>
-          <t>Oglądanie reprodukcji jest szybsze niż odsłuch utworów; przy jury przyjęto 15 h.</t>
+          <t>Kotwica, nie decyzja: pozycja honorariów w Budżecie Plakatu stoi na zerze jako DO USTALENIA, do rozmowy z przewodniczącym jury.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="45">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>Stawka jury plakatu za godzinę (netto)</t>
-        </is>
-      </c>
-      <c r="B59" s="60" t="n">
-        <v>290</v>
+          <t>Godzin oceny na jurora</t>
+        </is>
+      </c>
+      <c r="B59" s="63" t="n">
+        <v>10</v>
       </c>
       <c r="C59" s="44" t="inlineStr">
         <is>
-          <t>Stawka przyjęta dla jury oceniającej rozmowy.</t>
+          <t>Oglądanie reprodukcji jest szybsze niż odsłuch utworów; przy jury przyjęto 15 h.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="45">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>Liczba prac finałowych</t>
-        </is>
-      </c>
-      <c r="B60" s="63" t="n">
-        <v>10</v>
+          <t>Stawka jury plakatu za godzinę (netto)</t>
+        </is>
+      </c>
+      <c r="B60" s="60" t="n">
+        <v>290</v>
       </c>
       <c r="C60" s="44" t="inlineStr">
         <is>
-          <t>Dziesiątka, której oryginały jadą na wystawę.</t>
+          <t>Stawka przyjęta dla jury oceniającej rozmowy.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="45">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>Transport jednej pracy w jedną stronę (netto)</t>
-        </is>
-      </c>
-      <c r="B61" s="60" t="n">
-        <v>400</v>
+          <t>Liczba prac finałowych</t>
+        </is>
+      </c>
+      <c r="B61" s="63" t="n">
+        <v>10</v>
       </c>
       <c r="C61" s="44" t="inlineStr">
         <is>
-          <t>Szacunek, nie oferta. Format do 150 cm przekracza limity standardowych przesyłek.</t>
+          <t>Dziesiątka, której oryginały jadą na wystawę.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="45">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>Ubezpieczenie prac na czas wystawy (netto)</t>
+          <t>Transport jednej pracy w jedną stronę (netto)</t>
         </is>
       </c>
       <c r="B62" s="60" t="n">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="C62" s="44" t="inlineStr">
         <is>
-          <t>Szacunek przy sumie deklarowanej rzędu 100 tys. zł dla całej dziesiątki.</t>
+          <t>Szacunek, nie oferta. Format do 150 cm przekracza limity standardowych przesyłek.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="45">
       <c r="A63" s="44" t="inlineStr">
         <is>
+          <t>Ubezpieczenie prac na czas wystawy (netto)</t>
+        </is>
+      </c>
+      <c r="B63" s="60" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C63" s="44" t="inlineStr">
+        <is>
+          <t>Szacunek przy sumie deklarowanej rzędu 100 tys. zł dla całej dziesiątki.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="45">
+      <c r="A64" s="44" t="inlineStr">
+        <is>
           <t>Rezerwa w Budżecie Plakatu</t>
         </is>
       </c>
-      <c r="B63" s="60" t="n">
+      <c r="B64" s="60" t="n">
         <v>0.12</v>
       </c>
-      <c r="C63" s="44" t="inlineStr">
+      <c r="C64" s="44" t="inlineStr">
         <is>
           <t>Narzut na nieprzewidziane.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1" s="45"/>
-    <row r="65" ht="15" customHeight="1" s="45">
-      <c r="A65" s="62" t="inlineStr">
+    <row r="65" ht="15" customHeight="1" s="45"/>
+    <row r="66" ht="15" customHeight="1" s="45">
+      <c r="A66" s="62" t="inlineStr">
         <is>
           <t>FILM - PARAMETRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="45">
-      <c r="A66" s="44" t="inlineStr">
-        <is>
-          <t>Liczba zgłoszeń filmów</t>
-        </is>
-      </c>
-      <c r="B66" s="56" t="n">
-        <v>150</v>
-      </c>
-      <c r="C66" s="44" t="inlineStr">
-        <is>
-          <t>Wpływa na koszt kontroli formalnej i na wielkość Akademii filmu.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="45">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>Nagrody filmu łącznie (brutto)</t>
+          <t>Liczba zgłoszeń filmów</t>
         </is>
       </c>
       <c r="B67" s="56" t="n">
-        <v>180000</v>
+        <v>150</v>
       </c>
       <c r="C67" s="44" t="inlineStr">
         <is>
-          <t>100 tys. + 50 tys. + 30 tys. dla czołowej trójki. Siedem wyróżnień nie jest pieniężnych.</t>
+          <t>Wpływa na koszt kontroli formalnej i na wielkość Akademii filmu.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="45">
       <c r="A68" s="44" t="inlineStr">
         <is>
-          <t>Nagrody publiczności filmu łącznie (brutto)</t>
+          <t>Nagrody filmu łącznie (brutto)</t>
         </is>
       </c>
       <c r="B68" s="56" t="n">
-        <v>12000</v>
+        <v>180000</v>
       </c>
       <c r="C68" s="44" t="inlineStr">
         <is>
-          <t>3 000 zł dla filmu z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych filmów (§ 11a ust. 5).</t>
+          <t>100 tys. + 50 tys. + 30 tys. dla czołowej trójki. Siedem wyróżnień nie jest pieniężnych.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="45">
       <c r="A69" s="44" t="inlineStr">
         <is>
-          <t>Medal zwycięzcy i dyplomy filmu (netto)</t>
+          <t>Nagrody publiczności filmu łącznie (brutto)</t>
         </is>
       </c>
       <c r="B69" s="56" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
       <c r="C69" s="44" t="inlineStr">
         <is>
-          <t>Ten sam medal co w pozostałych plebiscytach; dyplomy dla dziesięciu finalistów.</t>
+          <t>3 000 zł dla filmu z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych filmów (§ 11a ust. 5).</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="45">
       <c r="A70" s="44" t="inlineStr">
         <is>
-          <t>Liczba filmów finałowych</t>
+          <t>Medal zwycięzcy i dyplomy filmu (netto)</t>
         </is>
       </c>
       <c r="B70" s="56" t="n">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="C70" s="44" t="inlineStr">
         <is>
-          <t>Dziesięciu finalistów: trójka z nagrodami pieniężnymi i siedem wyróżnień. Minutowe skróty na gali dostaje pięć najwyżej ocenionych.</t>
+          <t>Ten sam medal co w pozostałych plebiscytach; dyplomy dla dziesięciu finalistów.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="45">
       <c r="A71" s="44" t="inlineStr">
         <is>
-          <t>Liczba jurorów filmu</t>
+          <t>Liczba filmów finałowych</t>
         </is>
       </c>
       <c r="B71" s="56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C71" s="44" t="inlineStr">
         <is>
-          <t>Kotwica, nie decyzja: pozycja honorariów w Budżecie Filmu stoi na zerze jako DO USTALENIA.</t>
+          <t>Dziesięciu finalistów: trójka z nagrodami pieniężnymi i siedem wyróżnień. Minutowe skróty na gali dostaje pięć najwyżej ocenionych.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="45">
       <c r="A72" s="44" t="inlineStr">
         <is>
-          <t>Godzin oceny na jurora filmu</t>
+          <t>Liczba jurorów filmu</t>
         </is>
       </c>
       <c r="B72" s="56" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="C72" s="44" t="inlineStr">
         <is>
-          <t>Akademia przekazuje jury nie więcej niż dwadzieścia filmów (§ 8 ust. 5a); dwadzieścia filmów po najwyżej 90 minut to 30 godzin samego oglądania, reszta na karty oceny, obrady i werdykt.</t>
+          <t>Kotwica, nie decyzja: pozycja honorariów w Budżecie Filmu stoi na zerze jako DO USTALENIA.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="45">
       <c r="A73" s="44" t="inlineStr">
         <is>
-          <t>Stawka jury filmu za godzinę (netto)</t>
+          <t>Godzin oceny na jurora filmu</t>
         </is>
       </c>
       <c r="B73" s="56" t="n">
-        <v>290</v>
+        <v>40</v>
       </c>
       <c r="C73" s="44" t="inlineStr">
         <is>
-          <t>Stawka przyjęta dla jury oceniającej rozmowy.</t>
+          <t>Akademia przekazuje jury nie więcej niż dwadzieścia filmów (§ 8 ust. 5a); dwadzieścia filmów po najwyżej 90 minut to 30 godzin samego oglądania, reszta na karty oceny, obrady i werdykt.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="45">
       <c r="A74" s="44" t="inlineStr">
         <is>
-          <t>Rezerwa w Budżecie Filmu</t>
+          <t>Stawka jury filmu za godzinę (netto)</t>
         </is>
       </c>
       <c r="B74" s="56" t="n">
-        <v>0.12</v>
+        <v>290</v>
       </c>
       <c r="C74" s="44" t="inlineStr">
         <is>
-          <t>Narzut na nieprzewidziane, jak w pozostałych budżetach.</t>
+          <t>Stawka przyjęta dla jury oceniającej rozmowy.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="45">
       <c r="A75" s="44" t="inlineStr">
         <is>
-          <t>Obejrzeń jednego filmu w Akademii</t>
+          <t>Rezerwa w Budżecie Filmu</t>
         </is>
       </c>
       <c r="B75" s="56" t="n">
-        <v>2</v>
+        <v>0.12</v>
       </c>
       <c r="C75" s="44" t="inlineStr">
         <is>
-          <t>Dwa niezależne obejrzenia, analogicznie do dwóch odczytów rozmowy.</t>
+          <t>Narzut na nieprzewidziane, jak w pozostałych budżetach.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="45">
       <c r="A76" s="44" t="inlineStr">
         <is>
-          <t>Honorarium za obejrzenie jednego filmu (netto)</t>
+          <t>Obejrzeń jednego filmu w Akademii</t>
         </is>
       </c>
       <c r="B76" s="56" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="C76" s="44" t="inlineStr">
         <is>
-          <t>Film do 90 minut plus karta oceny to około 2 godzin pracy. Ustalenie z 26.10.2026.</t>
+          <t>Dwa niezależne obejrzenia, analogicznie do dwóch odczytów rozmowy.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="45">
       <c r="A77" s="44" t="inlineStr">
         <is>
+          <t>Honorarium za obejrzenie jednego filmu (netto)</t>
+        </is>
+      </c>
+      <c r="B77" s="56" t="n">
+        <v>300</v>
+      </c>
+      <c r="C77" s="44" t="inlineStr">
+        <is>
+          <t>Film do 90 minut plus karta oceny to około 2 godzin pracy. Ustalenie z 26.10.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" s="45">
+      <c r="A78" s="44" t="inlineStr">
+        <is>
           <t>Maksimum filmów na jednego oceniającego</t>
         </is>
       </c>
-      <c r="B77" s="56" t="n">
+      <c r="B78" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="C77" s="44" t="inlineStr">
+      <c r="C78" s="44" t="inlineStr">
         <is>
           <t>Dziesięć filmów to około 20 godzin oglądania. Wyznacza, ilu ludzi trzeba przy danym wolumenie.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="45"/>
     <row r="79" ht="15" customHeight="1" s="45"/>
     <row r="80" ht="15" customHeight="1" s="45"/>
     <row r="81" ht="15" customHeight="1" s="45"/>
@@ -2484,8 +2493,9 @@
           <t>Nagrody publiczności (brutto)</t>
         </is>
       </c>
-      <c r="B27" s="70" t="n">
-        <v>12000</v>
+      <c r="B27" s="70">
+        <f>Wyjaśnienia!$B$26</f>
+        <v/>
       </c>
       <c r="C27" s="65" t="n">
         <v>1</v>
@@ -2496,7 +2506,7 @@
       </c>
       <c r="E27" s="57" t="inlineStr">
         <is>
-          <t>10 000 zł dla zgłoszenia z największą liczbą głosów oraz 2 000 zł za najlepsze uzasadnienie oddanego głosu; kwotę ustawia się tutaj, w pozostałych plebiscytach w zakładce Wyjaśnienia</t>
+          <t>10 000 zł dla zgłoszenia z największą liczbą głosów oraz 2 000 zł za najlepsze uzasadnienie oddanego głosu</t>
         </is>
       </c>
       <c r="F27" s="47" t="n"/>
@@ -2640,7 +2650,7 @@
         </is>
       </c>
       <c r="D36" s="47">
-        <f>(D34+D35-D27-D29)*Wyjaśnienia!$B$30</f>
+        <f>(D34+D35-D27-D29)*Wyjaśnienia!$B$31</f>
         <v/>
       </c>
       <c r="E36" s="44" t="inlineStr">
@@ -2675,7 +2685,7 @@
       <c r="B38" s="47" t="n"/>
       <c r="C38" s="47" t="n"/>
       <c r="D38" s="52">
-        <f>D37*Wyjaśnienia!$B$33</f>
+        <f>D37*Wyjaśnienia!$B$34</f>
         <v/>
       </c>
       <c r="E38" s="47" t="n"/>
@@ -3602,7 +3612,7 @@
       <c r="B37" s="47" t="n"/>
       <c r="C37" s="47" t="n"/>
       <c r="D37" s="52">
-        <f>(D35+D36)*Wyjaśnienia!$B$31</f>
+        <f>(D35+D36)*Wyjaśnienia!$B$32</f>
         <v/>
       </c>
       <c r="E37" s="47" t="n"/>
@@ -3634,7 +3644,7 @@
       <c r="B39" s="47" t="n"/>
       <c r="C39" s="47" t="n"/>
       <c r="D39" s="52">
-        <f>D38*Wyjaśnienia!$B$33</f>
+        <f>D38*Wyjaśnienia!$B$34</f>
         <v/>
       </c>
       <c r="E39" s="47" t="n"/>
@@ -4114,11 +4124,11 @@
         </is>
       </c>
       <c r="B18" s="67">
-        <f>Wyjaśnienia!$B$26</f>
+        <f>Wyjaśnienia!$B$27</f>
         <v/>
       </c>
       <c r="C18" s="66">
-        <f>Wyjaśnienia!$B$27</f>
+        <f>Wyjaśnienia!$B$28</f>
         <v/>
       </c>
       <c r="D18" s="67">
@@ -4143,7 +4153,7 @@
         </is>
       </c>
       <c r="B19" s="67">
-        <f>Wyjaśnienia!$B$28</f>
+        <f>Wyjaśnienia!$B$29</f>
         <v/>
       </c>
       <c r="C19" s="65" t="n">
@@ -4171,7 +4181,7 @@
         </is>
       </c>
       <c r="B20" s="67">
-        <f>Wyjaśnienia!$B$29</f>
+        <f>Wyjaśnienia!$B$30</f>
         <v/>
       </c>
       <c r="C20" s="65" t="n">
@@ -4409,7 +4419,7 @@
       <c r="B32" s="47" t="n"/>
       <c r="C32" s="47" t="n"/>
       <c r="D32" s="52">
-        <f>(D30+D31)*Wyjaśnienia!$B$32</f>
+        <f>(D30+D31)*Wyjaśnienia!$B$33</f>
         <v/>
       </c>
       <c r="E32" s="47" t="n"/>
@@ -4441,7 +4451,7 @@
       <c r="B34" s="47" t="n"/>
       <c r="C34" s="47" t="n"/>
       <c r="D34" s="52">
-        <f>D33*Wyjaśnienia!$B$33</f>
+        <f>D33*Wyjaśnienia!$B$34</f>
         <v/>
       </c>
       <c r="E34" s="47" t="n"/>
@@ -4646,7 +4656,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="68">
-        <f>B7+C7*Wyjaśnienia!$B$53/60</f>
+        <f>B7+C7*Wyjaśnienia!$B$54/60</f>
         <v/>
       </c>
       <c r="E7" s="52">
@@ -4673,7 +4683,7 @@
       </c>
       <c r="C8" s="68" t="n"/>
       <c r="D8" s="68">
-        <f>B8+C8*Wyjaśnienia!$B$53/60</f>
+        <f>B8+C8*Wyjaśnienia!$B$54/60</f>
         <v/>
       </c>
       <c r="E8" s="52">
@@ -4700,7 +4710,7 @@
       </c>
       <c r="C9" s="68" t="n"/>
       <c r="D9" s="68">
-        <f>B9+C9*Wyjaśnienia!$B$53/60</f>
+        <f>B9+C9*Wyjaśnienia!$B$54/60</f>
         <v/>
       </c>
       <c r="E9" s="52">
@@ -4727,7 +4737,7 @@
       </c>
       <c r="C10" s="68" t="n"/>
       <c r="D10" s="68">
-        <f>B10+C10*Wyjaśnienia!$B$53/60</f>
+        <f>B10+C10*Wyjaśnienia!$B$54/60</f>
         <v/>
       </c>
       <c r="E10" s="52">
@@ -4754,7 +4764,7 @@
       </c>
       <c r="C11" s="68" t="n"/>
       <c r="D11" s="68">
-        <f>B11+C11*Wyjaśnienia!$B$53/60</f>
+        <f>B11+C11*Wyjaśnienia!$B$54/60</f>
         <v/>
       </c>
       <c r="E11" s="52">
@@ -4781,7 +4791,7 @@
       </c>
       <c r="C12" s="68" t="n"/>
       <c r="D12" s="68">
-        <f>B12+C12*Wyjaśnienia!$B$53/60</f>
+        <f>B12+C12*Wyjaśnienia!$B$54/60</f>
         <v/>
       </c>
       <c r="E12" s="52">
@@ -4808,7 +4818,7 @@
       </c>
       <c r="C13" s="68" t="n"/>
       <c r="D13" s="68">
-        <f>B13+C13*Wyjaśnienia!$B$53/60</f>
+        <f>B13+C13*Wyjaśnienia!$B$54/60</f>
         <v/>
       </c>
       <c r="E13" s="52">
@@ -4890,7 +4900,7 @@
         </is>
       </c>
       <c r="B18" s="52">
-        <f>Wyjaśnienia!$B$54</f>
+        <f>Wyjaśnienia!$B$55</f>
         <v/>
       </c>
       <c r="C18" s="68" t="n">
@@ -4916,7 +4926,7 @@
         </is>
       </c>
       <c r="B19" s="52">
-        <f>Wyjaśnienia!$B$55</f>
+        <f>Wyjaśnienia!$B$56</f>
         <v/>
       </c>
       <c r="C19" s="68" t="n">
@@ -4942,7 +4952,7 @@
         </is>
       </c>
       <c r="B20" s="52">
-        <f>Wyjaśnienia!$B$56</f>
+        <f>Wyjaśnienia!$B$57</f>
         <v/>
       </c>
       <c r="C20" s="68" t="n">
@@ -5018,11 +5028,11 @@
         </is>
       </c>
       <c r="B23" s="52">
-        <f>Wyjaśnienia!$B$61*2</f>
+        <f>Wyjaśnienia!$B$62*2</f>
         <v/>
       </c>
       <c r="C23" s="68">
-        <f>Wyjaśnienia!$B$60</f>
+        <f>Wyjaśnienia!$B$61</f>
         <v/>
       </c>
       <c r="D23" s="52">
@@ -5045,7 +5055,7 @@
         </is>
       </c>
       <c r="B24" s="52">
-        <f>Wyjaśnienia!$B$62</f>
+        <f>Wyjaśnienia!$B$63</f>
         <v/>
       </c>
       <c r="C24" s="68" t="n">
@@ -5192,7 +5202,7 @@
         </is>
       </c>
       <c r="D32" s="52">
-        <f>Wyjaśnienia!$B$54+Wyjaśnienia!$B$55</f>
+        <f>Wyjaśnienia!$B$55+Wyjaśnienia!$B$56</f>
         <v/>
       </c>
     </row>
@@ -5225,7 +5235,7 @@
         </is>
       </c>
       <c r="D35" s="52">
-        <f>(D33+D34)*Wyjaśnienia!$B$63</f>
+        <f>(D33+D34)*Wyjaśnienia!$B$64</f>
         <v/>
       </c>
     </row>
@@ -5247,7 +5257,7 @@
         </is>
       </c>
       <c r="D37" s="52">
-        <f>D36*Wyjaśnienia!$B$33</f>
+        <f>D36*Wyjaśnienia!$B$34</f>
         <v/>
       </c>
     </row>
@@ -5454,7 +5464,7 @@
         </is>
       </c>
       <c r="B8" s="78">
-        <f>Wyjaśnienia!$B$46</f>
+        <f>Wyjaśnienia!$B$47</f>
         <v/>
       </c>
       <c r="F8" s="72" t="inlineStr">
@@ -5486,7 +5496,7 @@
         </is>
       </c>
       <c r="B10" s="78">
-        <f>Wyjaśnienia!$B$66</f>
+        <f>Wyjaśnienia!$B$67</f>
         <v/>
       </c>
       <c r="F10" s="72" t="inlineStr">
@@ -5502,7 +5512,7 @@
         </is>
       </c>
       <c r="B11" s="78">
-        <f>Wyjaśnienia!$B$75</f>
+        <f>Wyjaśnienia!$B$76</f>
         <v/>
       </c>
       <c r="F11" s="72" t="inlineStr">
@@ -5573,11 +5583,11 @@
         </is>
       </c>
       <c r="B16" s="80">
-        <f>Wyjaśnienia!$B$48</f>
+        <f>Wyjaśnienia!$B$49</f>
         <v/>
       </c>
       <c r="C16" s="78">
-        <f>Wyjaśnienia!$B$49</f>
+        <f>Wyjaśnienia!$B$50</f>
         <v/>
       </c>
       <c r="D16" s="80">
@@ -5600,7 +5610,7 @@
         </is>
       </c>
       <c r="B17" s="80">
-        <f>Wyjaśnienia!$B$47</f>
+        <f>Wyjaśnienia!$B$48</f>
         <v/>
       </c>
       <c r="C17" s="78">
@@ -5627,7 +5637,7 @@
         </is>
       </c>
       <c r="B18" s="80">
-        <f>Wyjaśnienia!$B$76</f>
+        <f>Wyjaśnienia!$B$77</f>
         <v/>
       </c>
       <c r="C18" s="78">
@@ -5844,7 +5854,7 @@
         </is>
       </c>
       <c r="D32" s="80">
-        <f>(D30+D31)*Wyjaśnienia!$B$30</f>
+        <f>(D30+D31)*Wyjaśnienia!$B$31</f>
         <v/>
       </c>
     </row>
@@ -5866,7 +5876,7 @@
         </is>
       </c>
       <c r="D34" s="80">
-        <f>D33*Wyjaśnienia!$B$33</f>
+        <f>D33*Wyjaśnienia!$B$34</f>
         <v/>
       </c>
     </row>
@@ -5927,7 +5937,7 @@
         <v>150</v>
       </c>
       <c r="B40" s="78">
-        <f>A40*Wyjaśnienia!$B$46</f>
+        <f>A40*Wyjaśnienia!$B$47</f>
         <v/>
       </c>
       <c r="C40" s="78">
@@ -5935,11 +5945,11 @@
         <v/>
       </c>
       <c r="D40" s="80">
-        <f>C40*Wyjaśnienia!$B$47</f>
+        <f>C40*Wyjaśnienia!$B$48</f>
         <v/>
       </c>
       <c r="E40" s="78">
-        <f>ROUNDUP(B40*Wyjaśnienia!$B$50/60,0)</f>
+        <f>ROUNDUP(B40*Wyjaśnienia!$B$51/60,0)</f>
         <v/>
       </c>
     </row>
@@ -5948,7 +5958,7 @@
         <v>1000</v>
       </c>
       <c r="B41" s="78">
-        <f>A41*Wyjaśnienia!$B$46</f>
+        <f>A41*Wyjaśnienia!$B$47</f>
         <v/>
       </c>
       <c r="C41" s="78">
@@ -5956,11 +5966,11 @@
         <v/>
       </c>
       <c r="D41" s="80">
-        <f>C41*Wyjaśnienia!$B$47</f>
+        <f>C41*Wyjaśnienia!$B$48</f>
         <v/>
       </c>
       <c r="E41" s="78">
-        <f>ROUNDUP(B41*Wyjaśnienia!$B$50/60,0)</f>
+        <f>ROUNDUP(B41*Wyjaśnienia!$B$51/60,0)</f>
         <v/>
       </c>
     </row>
@@ -5969,7 +5979,7 @@
         <v>10000</v>
       </c>
       <c r="B42" s="78">
-        <f>A42*Wyjaśnienia!$B$46</f>
+        <f>A42*Wyjaśnienia!$B$47</f>
         <v/>
       </c>
       <c r="C42" s="78">
@@ -5977,11 +5987,11 @@
         <v/>
       </c>
       <c r="D42" s="80">
-        <f>C42*Wyjaśnienia!$B$47</f>
+        <f>C42*Wyjaśnienia!$B$48</f>
         <v/>
       </c>
       <c r="E42" s="78">
-        <f>ROUNDUP(B42*Wyjaśnienia!$B$50/60,0)</f>
+        <f>ROUNDUP(B42*Wyjaśnienia!$B$51/60,0)</f>
         <v/>
       </c>
     </row>
@@ -5990,7 +6000,7 @@
         <v>100000</v>
       </c>
       <c r="B43" s="78">
-        <f>A43*Wyjaśnienia!$B$46</f>
+        <f>A43*Wyjaśnienia!$B$47</f>
         <v/>
       </c>
       <c r="C43" s="78">
@@ -5998,11 +6008,11 @@
         <v/>
       </c>
       <c r="D43" s="80">
-        <f>C43*Wyjaśnienia!$B$47</f>
+        <f>C43*Wyjaśnienia!$B$48</f>
         <v/>
       </c>
       <c r="E43" s="78">
-        <f>ROUNDUP(B43*Wyjaśnienia!$B$50/60,0)</f>
+        <f>ROUNDUP(B43*Wyjaśnienia!$B$51/60,0)</f>
         <v/>
       </c>
     </row>
@@ -6011,7 +6021,7 @@
         <v>1000000</v>
       </c>
       <c r="B44" s="78">
-        <f>A44*Wyjaśnienia!$B$46</f>
+        <f>A44*Wyjaśnienia!$B$47</f>
         <v/>
       </c>
       <c r="C44" s="78">
@@ -6019,11 +6029,11 @@
         <v/>
       </c>
       <c r="D44" s="80">
-        <f>C44*Wyjaśnienia!$B$47</f>
+        <f>C44*Wyjaśnienia!$B$48</f>
         <v/>
       </c>
       <c r="E44" s="78">
-        <f>ROUNDUP(B44*Wyjaśnienia!$B$50/60,0)</f>
+        <f>ROUNDUP(B44*Wyjaśnienia!$B$51/60,0)</f>
         <v/>
       </c>
     </row>
@@ -6059,11 +6069,11 @@
         <v>30</v>
       </c>
       <c r="B47" s="78">
-        <f>A47*Wyjaśnienia!$B$75</f>
+        <f>A47*Wyjaśnienia!$B$76</f>
         <v/>
       </c>
       <c r="C47" s="80">
-        <f>B47*Wyjaśnienia!$B$76</f>
+        <f>B47*Wyjaśnienia!$B$77</f>
         <v/>
       </c>
       <c r="D47" s="78">
@@ -6071,7 +6081,7 @@
         <v/>
       </c>
       <c r="E47" s="78">
-        <f>ROUNDUP(B47/Wyjaśnienia!$B$77,0)</f>
+        <f>ROUNDUP(B47/Wyjaśnienia!$B$78,0)</f>
         <v/>
       </c>
     </row>
@@ -6080,11 +6090,11 @@
         <v>150</v>
       </c>
       <c r="B48" s="78">
-        <f>A48*Wyjaśnienia!$B$75</f>
+        <f>A48*Wyjaśnienia!$B$76</f>
         <v/>
       </c>
       <c r="C48" s="80">
-        <f>B48*Wyjaśnienia!$B$76</f>
+        <f>B48*Wyjaśnienia!$B$77</f>
         <v/>
       </c>
       <c r="D48" s="78">
@@ -6092,7 +6102,7 @@
         <v/>
       </c>
       <c r="E48" s="78">
-        <f>ROUNDUP(B48/Wyjaśnienia!$B$77,0)</f>
+        <f>ROUNDUP(B48/Wyjaśnienia!$B$78,0)</f>
         <v/>
       </c>
     </row>
@@ -6101,11 +6111,11 @@
         <v>500</v>
       </c>
       <c r="B49" s="78">
-        <f>A49*Wyjaśnienia!$B$75</f>
+        <f>A49*Wyjaśnienia!$B$76</f>
         <v/>
       </c>
       <c r="C49" s="80">
-        <f>B49*Wyjaśnienia!$B$76</f>
+        <f>B49*Wyjaśnienia!$B$77</f>
         <v/>
       </c>
       <c r="D49" s="78">
@@ -6113,7 +6123,7 @@
         <v/>
       </c>
       <c r="E49" s="78">
-        <f>ROUNDUP(B49/Wyjaśnienia!$B$77,0)</f>
+        <f>ROUNDUP(B49/Wyjaśnienia!$B$78,0)</f>
         <v/>
       </c>
     </row>
@@ -6122,11 +6132,11 @@
         <v>2000</v>
       </c>
       <c r="B50" s="78">
-        <f>A50*Wyjaśnienia!$B$75</f>
+        <f>A50*Wyjaśnienia!$B$76</f>
         <v/>
       </c>
       <c r="C50" s="80">
-        <f>B50*Wyjaśnienia!$B$76</f>
+        <f>B50*Wyjaśnienia!$B$77</f>
         <v/>
       </c>
       <c r="D50" s="78">
@@ -6134,7 +6144,7 @@
         <v/>
       </c>
       <c r="E50" s="78">
-        <f>ROUNDUP(B50/Wyjaśnienia!$B$77,0)</f>
+        <f>ROUNDUP(B50/Wyjaśnienia!$B$78,0)</f>
         <v/>
       </c>
     </row>
@@ -6143,11 +6153,11 @@
         <v>10000</v>
       </c>
       <c r="B51" s="78">
-        <f>A51*Wyjaśnienia!$B$75</f>
+        <f>A51*Wyjaśnienia!$B$76</f>
         <v/>
       </c>
       <c r="C51" s="80">
-        <f>B51*Wyjaśnienia!$B$76</f>
+        <f>B51*Wyjaśnienia!$B$77</f>
         <v/>
       </c>
       <c r="D51" s="78">
@@ -6155,7 +6165,7 @@
         <v/>
       </c>
       <c r="E51" s="78">
-        <f>ROUNDUP(B51/Wyjaśnienia!$B$77,0)</f>
+        <f>ROUNDUP(B51/Wyjaśnienia!$B$78,0)</f>
         <v/>
       </c>
     </row>
@@ -6248,7 +6258,7 @@
         <v>0</v>
       </c>
       <c r="C59" s="78">
-        <f>Wyjaśnienia!$B$53*2</f>
+        <f>Wyjaśnienia!$B$54*2</f>
         <v/>
       </c>
       <c r="D59" s="80">
@@ -6444,7 +6454,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="68">
-        <f>B7+C7*Wyjaśnienia!$B$66/60</f>
+        <f>B7+C7*Wyjaśnienia!$B$67/60</f>
         <v/>
       </c>
       <c r="E7" s="52">
@@ -6471,7 +6481,7 @@
       </c>
       <c r="C8" s="63" t="n"/>
       <c r="D8" s="68">
-        <f>B8+C8*Wyjaśnienia!$B$66/60</f>
+        <f>B8+C8*Wyjaśnienia!$B$67/60</f>
         <v/>
       </c>
       <c r="E8" s="52">
@@ -6498,7 +6508,7 @@
       </c>
       <c r="C9" s="63" t="n"/>
       <c r="D9" s="68">
-        <f>B9+C9*Wyjaśnienia!$B$66/60</f>
+        <f>B9+C9*Wyjaśnienia!$B$67/60</f>
         <v/>
       </c>
       <c r="E9" s="52">
@@ -6525,7 +6535,7 @@
       </c>
       <c r="C10" s="63" t="n"/>
       <c r="D10" s="68">
-        <f>B10+C10*Wyjaśnienia!$B$66/60</f>
+        <f>B10+C10*Wyjaśnienia!$B$67/60</f>
         <v/>
       </c>
       <c r="E10" s="52">
@@ -6552,7 +6562,7 @@
       </c>
       <c r="C11" s="63" t="n"/>
       <c r="D11" s="68">
-        <f>B11+C11*Wyjaśnienia!$B$66/60</f>
+        <f>B11+C11*Wyjaśnienia!$B$67/60</f>
         <v/>
       </c>
       <c r="E11" s="52">
@@ -6579,7 +6589,7 @@
       </c>
       <c r="C12" s="63" t="n"/>
       <c r="D12" s="68">
-        <f>B12+C12*Wyjaśnienia!$B$66/60</f>
+        <f>B12+C12*Wyjaśnienia!$B$67/60</f>
         <v/>
       </c>
       <c r="E12" s="52">
@@ -6606,7 +6616,7 @@
       </c>
       <c r="C13" s="63" t="n"/>
       <c r="D13" s="68">
-        <f>B13+C13*Wyjaśnienia!$B$66/60</f>
+        <f>B13+C13*Wyjaśnienia!$B$67/60</f>
         <v/>
       </c>
       <c r="E13" s="52">
@@ -6633,7 +6643,7 @@
       </c>
       <c r="C14" s="63" t="n"/>
       <c r="D14" s="68">
-        <f>B14+C14*Wyjaśnienia!$B$66/60</f>
+        <f>B14+C14*Wyjaśnienia!$B$67/60</f>
         <v/>
       </c>
       <c r="E14" s="52">
@@ -6717,7 +6727,7 @@
         </is>
       </c>
       <c r="B19" s="52">
-        <f>Wyjaśnienia!$B$67</f>
+        <f>Wyjaśnienia!$B$68</f>
         <v/>
       </c>
       <c r="C19" s="68" t="n">
@@ -6743,7 +6753,7 @@
         </is>
       </c>
       <c r="B20" s="52">
-        <f>Wyjaśnienia!$B$68</f>
+        <f>Wyjaśnienia!$B$69</f>
         <v/>
       </c>
       <c r="C20" s="68" t="n">
@@ -6769,7 +6779,7 @@
         </is>
       </c>
       <c r="B21" s="52">
-        <f>Wyjaśnienia!$B$69</f>
+        <f>Wyjaśnienia!$B$70</f>
         <v/>
       </c>
       <c r="C21" s="68" t="n">
@@ -6966,7 +6976,7 @@
         </is>
       </c>
       <c r="D31" s="52">
-        <f>Wyjaśnienia!$B$67+Wyjaśnienia!$B$68</f>
+        <f>Wyjaśnienia!$B$68+Wyjaśnienia!$B$69</f>
         <v/>
       </c>
     </row>
@@ -6999,7 +7009,7 @@
         </is>
       </c>
       <c r="D34" s="52">
-        <f>(D32+D33)*Wyjaśnienia!$B$74</f>
+        <f>(D32+D33)*Wyjaśnienia!$B$75</f>
         <v/>
       </c>
     </row>
@@ -7021,7 +7031,7 @@
         </is>
       </c>
       <c r="D36" s="52">
-        <f>D35*Wyjaśnienia!$B$33</f>
+        <f>D35*Wyjaśnienia!$B$34</f>
         <v/>
       </c>
     </row>
@@ -7521,7 +7531,7 @@
       <c r="B25" s="47" t="n"/>
       <c r="C25" s="47" t="n"/>
       <c r="D25" s="52">
-        <f>(D23+D24)*Wyjaśnienia!$B$30</f>
+        <f>(D23+D24)*Wyjaśnienia!$B$31</f>
         <v/>
       </c>
       <c r="E25" s="47" t="n"/>
@@ -7553,7 +7563,7 @@
       <c r="B27" s="47" t="n"/>
       <c r="C27" s="47" t="n"/>
       <c r="D27" s="52">
-        <f>D26*Wyjaśnienia!$B$33</f>
+        <f>D26*Wyjaśnienia!$B$34</f>
         <v/>
       </c>
       <c r="E27" s="47" t="n"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -1203,7 +1203,7 @@
     <row r="32" ht="15" customHeight="1" s="45">
       <c r="A32" s="47" t="inlineStr">
         <is>
-          <t>Marża w Budżecie Antologii</t>
+          <t>Wynagrodzenie wykonawcy i rezerwa w Budżecie Antologii</t>
         </is>
       </c>
       <c r="B32" s="58" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="C32" s="57" t="inlineStr">
         <is>
-          <t>Narzut wynagrodzenia podmiotu, który wykona tę część, liczony od pracy i kosztów twardych. Nie są to środki pozostające u Organizatora ani rezerwa. W kosztorysie dotacyjnym pozycja ta nie wystąpi.</t>
+          <t>Dwadzieścia procent to wynagrodzenie podmiotu, który wykona tę część; dziesięć procent to rezerwa na przekroczenia. Rezerwa niewykorzystana oraz pozycje nieponiesione wracają do Mecenasa albo, na jego pisemny wybór, przechodzą na antologię kolejnej edycji - nigdy na pulę nagród.</t>
         </is>
       </c>
       <c r="D32" s="47" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="E29" s="57" t="inlineStr">
         <is>
-          <t>Dostęp do narzędzi AI, bez których 937 godzin pracy organizatora nie jest wykonalne; rzędu 2,5 tys. zł miesięcznie</t>
+          <t>Dostęp do narzędzi AI, bez których 1469 godzin pracy organizatora nie jest wykonalne; rzędu 2,5 tys. zł miesięcznie</t>
         </is>
       </c>
       <c r="F29" s="47" t="n"/>
@@ -3606,7 +3606,7 @@
     <row r="37" ht="15" customHeight="1" s="45">
       <c r="A37" s="64" t="inlineStr">
         <is>
-          <t>Marża (od pracy i kosztów, bez nagród)</t>
+          <t>Wynagrodzenie wykonawcy i rezerwa (od pracy i kosztów)</t>
         </is>
       </c>
       <c r="B37" s="47" t="n"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="C7" s="52">
-        <f>'Budżet Antologii'!$D$38</f>
+        <f>'Budżet Antologii'!$D$39</f>
         <v/>
       </c>
       <c r="D7" s="47" t="n"/>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="C13" s="55">
-        <f>'Budżet Nagrody'!$D$37+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$38+'Budżet Plebiscytu'!$D$33+'Budżet Plakatu'!$D$36+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$35</f>
+        <f>'Budżet Nagrody'!$D$37+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$39+'Budżet Plebiscytu'!$D$33+'Budżet Plakatu'!$D$36+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$35</f>
         <v/>
       </c>
       <c r="D13" s="47" t="n"/>
@@ -2795,7 +2795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="54" customWidth="1" style="44" min="1" max="1"/>
@@ -3544,59 +3544,61 @@
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="45">
-      <c r="A32" s="50" t="inlineStr">
+      <c r="A32" s="72" t="inlineStr">
+        <is>
+          <t>Produkcja audiobooka antologii (trzy głosy)</t>
+        </is>
+      </c>
+      <c r="B32" s="60" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C32" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="52">
+        <f>B32*C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="44" t="inlineStr">
+        <is>
+          <t>około 10 godzin gotowego nagrania; trzej lektorzy - uczestnik, sztuczna inteligencja i komentarze jury - studio, montaż dialogowy i mastering</t>
+        </is>
+      </c>
+      <c r="F32" s="72" t="n"/>
+      <c r="G32" s="68" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="45">
+      <c r="A33" s="50" t="inlineStr">
         <is>
           <t>Razem koszty twarde</t>
         </is>
       </c>
-      <c r="B32" s="47" t="n"/>
-      <c r="C32" s="47" t="n"/>
-      <c r="D32" s="53">
-        <f>SUM(D19:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="47" t="n"/>
-      <c r="F32" s="47" t="n"/>
-      <c r="H32" s="47" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="45">
-      <c r="A33" s="47" t="n"/>
       <c r="H33" s="47" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="45">
-      <c r="A34" s="49" t="inlineStr">
+      <c r="A34" s="47" t="n"/>
+      <c r="H34" s="47" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="45">
+      <c r="A35" s="49" t="inlineStr">
         <is>
           <t>PODSUMOWANIE</t>
         </is>
       </c>
-      <c r="H34" s="47" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="45">
-      <c r="A35" s="64" t="inlineStr">
-        <is>
-          <t>Praca organizatora</t>
-        </is>
-      </c>
-      <c r="B35" s="47" t="n"/>
-      <c r="C35" s="47" t="n"/>
-      <c r="D35" s="52">
-        <f>E15</f>
-        <v/>
-      </c>
-      <c r="E35" s="47" t="n"/>
-      <c r="F35" s="47" t="n"/>
       <c r="H35" s="47" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="45">
       <c r="A36" s="64" t="inlineStr">
         <is>
-          <t>Koszty twarde</t>
+          <t>Praca organizatora</t>
         </is>
       </c>
       <c r="B36" s="47" t="n"/>
       <c r="C36" s="47" t="n"/>
       <c r="D36" s="52">
-        <f>D32</f>
+        <f>E15</f>
         <v/>
       </c>
       <c r="E36" s="47" t="n"/>
@@ -3606,13 +3608,13 @@
     <row r="37" ht="15" customHeight="1" s="45">
       <c r="A37" s="64" t="inlineStr">
         <is>
-          <t>Wynagrodzenie wykonawcy i rezerwa (od pracy i kosztów)</t>
+          <t>Koszty twarde</t>
         </is>
       </c>
       <c r="B37" s="47" t="n"/>
       <c r="C37" s="47" t="n"/>
       <c r="D37" s="52">
-        <f>(D35+D36)*Wyjaśnienia!$B$32</f>
+        <f>SUM(D19:D32)</f>
         <v/>
       </c>
       <c r="E37" s="47" t="n"/>
@@ -3620,15 +3622,15 @@
       <c r="H37" s="47" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="45">
-      <c r="A38" s="50" t="inlineStr">
-        <is>
-          <t>RAZEM NETTO</t>
+      <c r="A38" s="64" t="inlineStr">
+        <is>
+          <t>Wynagrodzenie wykonawcy i rezerwa (od pracy i kosztów)</t>
         </is>
       </c>
       <c r="B38" s="47" t="n"/>
       <c r="C38" s="47" t="n"/>
-      <c r="D38" s="53">
-        <f>SUM(D35:D37)</f>
+      <c r="D38" s="52">
+        <f>(D36+D37)*Wyjaśnienia!$B$32</f>
         <v/>
       </c>
       <c r="E38" s="47" t="n"/>
@@ -3636,15 +3638,15 @@
       <c r="H38" s="47" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="45">
-      <c r="A39" s="64" t="inlineStr">
-        <is>
-          <t>VAT</t>
+      <c r="A39" s="50" t="inlineStr">
+        <is>
+          <t>RAZEM NETTO</t>
         </is>
       </c>
       <c r="B39" s="47" t="n"/>
       <c r="C39" s="47" t="n"/>
-      <c r="D39" s="52">
-        <f>D38*Wyjaśnienia!$B$34</f>
+      <c r="D39" s="53">
+        <f>SUM(D36:D38)</f>
         <v/>
       </c>
       <c r="E39" s="47" t="n"/>
@@ -3652,22 +3654,37 @@
       <c r="H39" s="47" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="45">
-      <c r="A40" s="50" t="inlineStr">
-        <is>
-          <t>DO ZAPŁATY BRUTTO - ta liczba trafia na fakturę</t>
+      <c r="A40" s="64" t="inlineStr">
+        <is>
+          <t>VAT</t>
         </is>
       </c>
       <c r="B40" s="47" t="n"/>
       <c r="C40" s="47" t="n"/>
-      <c r="D40" s="71">
-        <f>D38+D39</f>
+      <c r="D40" s="52">
+        <f>D39*Wyjaśnienia!$B$34</f>
         <v/>
       </c>
       <c r="E40" s="47" t="n"/>
       <c r="F40" s="47" t="n"/>
       <c r="H40" s="47" t="n"/>
     </row>
-    <row r="41" ht="15" customHeight="1" s="45"/>
+    <row r="41" ht="15" customHeight="1" s="45">
+      <c r="A41" s="50" t="inlineStr">
+        <is>
+          <t>DO ZAPŁATY BRUTTO - ta liczba trafia na fakturę</t>
+        </is>
+      </c>
+      <c r="B41" s="47" t="n"/>
+      <c r="C41" s="47" t="n"/>
+      <c r="D41" s="71">
+        <f>D39+D40</f>
+        <v/>
+      </c>
+      <c r="E41" s="47" t="n"/>
+      <c r="F41" s="47" t="n"/>
+      <c r="H41" s="47" t="n"/>
+    </row>
     <row r="42" ht="15" customHeight="1" s="45"/>
     <row r="43" ht="15" customHeight="1" s="45"/>
     <row r="44" ht="15" customHeight="1" s="45"/>

--- a/budzet-edycji-pierwszej.xlsx
+++ b/budzet-edycji-pierwszej.xlsx
@@ -10,11 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wyjaśnienia" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Nagrody" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Antologii" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Plebiscytu" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Plakatu" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Akademii" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Filmu" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Gali" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Uruchomienia" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Plebiscytu" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Plakatu" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Akademii" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Filmu" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budżet Gali" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -652,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.68359375" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="45.4" customWidth="1" style="44" min="1" max="1"/>
@@ -861,26 +862,30 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="45">
-      <c r="A13" s="54" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
+        <is>
+          <t>Budżet Uruchomienia - fundacja, znak, strona i narzędzia</t>
+        </is>
+      </c>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>Mecenas Założycielski</t>
+        </is>
+      </c>
+      <c r="C13" s="53">
+        <f>'Budżet Uruchomienia'!$D$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="45">
+      <c r="A14" s="54" t="inlineStr">
         <is>
           <t>RAZEM</t>
         </is>
       </c>
-      <c r="C13" s="55">
-        <f>'Budżet Nagrody'!$D$37+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$39+'Budżet Plebiscytu'!$D$33+'Budżet Plakatu'!$D$36+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$35</f>
-        <v/>
-      </c>
-      <c r="D13" s="47" t="n"/>
-      <c r="E13" s="47" t="n"/>
-      <c r="F13" s="47" t="n"/>
-      <c r="G13" s="47" t="n"/>
-      <c r="H13" s="47" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="45">
-      <c r="A14" s="49" t="inlineStr">
-        <is>
-          <t>LICZBY, KTÓRE USTAWIASZ</t>
-        </is>
+      <c r="C14" s="55">
+        <f>'Budżet Nagrody'!$D$37+'Budżet Gali'!$D$26+'Budżet Antologii'!$D$39+'Budżet Uruchomienia'!$D$27+'Budżet Plebiscytu'!$D$33+'Budżet Plakatu'!$D$36+'Budżet Akademii'!$D$33+'Budżet Filmu'!$D$35</f>
+        <v/>
       </c>
       <c r="D14" s="47" t="n"/>
       <c r="E14" s="47" t="n"/>
@@ -889,9 +894,9 @@
       <c r="H14" s="47" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="45">
-      <c r="A15" s="48" t="inlineStr">
-        <is>
-          <t>Zmieniasz wyłącznie żółte pola poniżej. Wszystkie budżety przeliczą się same.</t>
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>LICZBY, KTÓRE USTAWIASZ</t>
         </is>
       </c>
       <c r="D15" s="47" t="n"/>
@@ -901,17 +906,9 @@
       <c r="H15" s="47" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="45">
-      <c r="A16" s="47" t="inlineStr">
-        <is>
-          <t>Stawka godzinowa organizatora (netto)</t>
-        </is>
-      </c>
-      <c r="B16" s="56" t="n">
-        <v>220</v>
-      </c>
-      <c r="C16" s="57" t="inlineStr">
-        <is>
-          <t>Podstawa wyceny Twojej pracy we wszystkich budżetach.</t>
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>Zmieniasz wyłącznie żółte pola poniżej. Wszystkie budżety przeliczą się same.</t>
         </is>
       </c>
       <c r="D16" s="47" t="n"/>
@@ -923,15 +920,15 @@
     <row r="17" ht="15" customHeight="1" s="45">
       <c r="A17" s="47" t="inlineStr">
         <is>
-          <t>Liczba zgłoszeń do Nagrody</t>
+          <t>Stawka godzinowa organizatora (netto)</t>
         </is>
       </c>
       <c r="B17" s="56" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="C17" s="57" t="inlineStr">
         <is>
-          <t>Wpływa na godziny oceny formalnej i korespondencji.</t>
+          <t>Podstawa wyceny Twojej pracy we wszystkich budżetach.</t>
         </is>
       </c>
       <c r="D17" s="47" t="n"/>
@@ -943,15 +940,15 @@
     <row r="18" ht="15" customHeight="1" s="45">
       <c r="A18" s="47" t="inlineStr">
         <is>
-          <t>Nagroda główna (brutto)</t>
+          <t>Liczba zgłoszeń do Nagrody</t>
         </is>
       </c>
       <c r="B18" s="56" t="n">
-        <v>300000</v>
+        <v>150</v>
       </c>
       <c r="C18" s="57" t="inlineStr">
         <is>
-          <t>Największa pojedyncza pozycja całości.</t>
+          <t>Wpływa na godziny oceny formalnej i korespondencji.</t>
         </is>
       </c>
       <c r="D18" s="47" t="n"/>
@@ -963,15 +960,15 @@
     <row r="19" ht="15" customHeight="1" s="45">
       <c r="A19" s="47" t="inlineStr">
         <is>
-          <t>Wyróżnienie dla finalisty (brutto)</t>
+          <t>Nagroda główna (brutto)</t>
         </is>
       </c>
       <c r="B19" s="56" t="n">
-        <v>3000</v>
+        <v>300000</v>
       </c>
       <c r="C19" s="57" t="inlineStr">
         <is>
-          <t>Siedem osób z dziesiątki antologii, poza podium.</t>
+          <t>Największa pojedyncza pozycja całości.</t>
         </is>
       </c>
       <c r="D19" s="47" t="n"/>
@@ -983,15 +980,15 @@
     <row r="20" ht="15" customHeight="1" s="45">
       <c r="A20" s="47" t="inlineStr">
         <is>
-          <t>Liczba wyróżnień</t>
+          <t>Wyróżnienie dla finalisty (brutto)</t>
         </is>
       </c>
       <c r="B20" s="56" t="n">
-        <v>7</v>
+        <v>3000</v>
       </c>
       <c r="C20" s="57" t="inlineStr">
         <is>
-          <t>Dziesiątka minus laureat, drugie i trzecie miejsce.</t>
+          <t>Siedem osób z dziesiątki antologii, poza podium.</t>
         </is>
       </c>
       <c r="D20" s="47" t="n"/>
@@ -1003,65 +1000,65 @@
     <row r="21" ht="15" customHeight="1" s="45">
       <c r="A21" s="47" t="inlineStr">
         <is>
-          <t>Nagroda za drugie miejsce (brutto)</t>
+          <t>Liczba wyróżnień</t>
         </is>
       </c>
       <c r="B21" s="56" t="n">
-        <v>40000</v>
+        <v>7</v>
       </c>
       <c r="C21" s="57" t="inlineStr">
         <is>
-          <t>Druga rozmowa z werdyktu jury.</t>
-        </is>
-      </c>
+          <t>Dziesiątka minus laureat, drugie i trzecie miejsce.</t>
+        </is>
+      </c>
+      <c r="D21" s="47" t="n"/>
+      <c r="E21" s="47" t="n"/>
+      <c r="F21" s="47" t="n"/>
+      <c r="G21" s="47" t="n"/>
+      <c r="H21" s="47" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="45">
       <c r="A22" s="47" t="inlineStr">
         <is>
-          <t>Nagroda za trzecie miejsce (brutto)</t>
+          <t>Nagroda za drugie miejsce (brutto)</t>
         </is>
       </c>
       <c r="B22" s="56" t="n">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="C22" s="57" t="inlineStr">
         <is>
-          <t>Trzecia rozmowa z werdyktu jury.</t>
+          <t>Druga rozmowa z werdyktu jury.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="45">
       <c r="A23" s="47" t="inlineStr">
         <is>
-          <t>Liczba zgłoszeń do plebiscytu</t>
+          <t>Nagroda za trzecie miejsce (brutto)</t>
         </is>
       </c>
       <c r="B23" s="56" t="n">
-        <v>150</v>
+        <v>10000</v>
       </c>
       <c r="C23" s="57" t="inlineStr">
         <is>
-          <t>Wpływa na koszt kontroli zgłoszeń.</t>
-        </is>
-      </c>
-      <c r="D23" s="47" t="n"/>
-      <c r="E23" s="47" t="n"/>
-      <c r="F23" s="47" t="n"/>
-      <c r="G23" s="47" t="n"/>
-      <c r="H23" s="47" t="n"/>
+          <t>Trzecia rozmowa z werdyktu jury.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="45">
       <c r="A24" s="47" t="inlineStr">
         <is>
-          <t>Nagrody plebiscytu łącznie (brutto)</t>
+          <t>Liczba zgłoszeń do plebiscytu</t>
         </is>
       </c>
       <c r="B24" s="56" t="n">
-        <v>35000</v>
+        <v>150</v>
       </c>
       <c r="C24" s="57" t="inlineStr">
         <is>
-          <t>20 tys. + 10 tys. + 5 tys. dla czołowej trójki.</t>
+          <t>Wpływa na koszt kontroli zgłoszeń.</t>
         </is>
       </c>
       <c r="D24" s="47" t="n"/>
@@ -1073,15 +1070,15 @@
     <row r="25" ht="15" customHeight="1" s="45">
       <c r="A25" s="47" t="inlineStr">
         <is>
-          <t>Nagrody publiczności piosenki łącznie (brutto)</t>
+          <t>Nagrody plebiscytu łącznie (brutto)</t>
         </is>
       </c>
       <c r="B25" s="56" t="n">
-        <v>12000</v>
+        <v>35000</v>
       </c>
       <c r="C25" s="57" t="inlineStr">
         <is>
-          <t>3 000 zł dla wykonawcy oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych piosenek. Uzasadnienie jest obowiązkowe przy każdym głosie, od 200 do 1500 znaków (§ 11 ust. 2 regulaminu).</t>
+          <t>20 tys. + 10 tys. + 5 tys. dla czołowej trójki.</t>
         </is>
       </c>
       <c r="D25" s="47" t="n"/>
@@ -1093,45 +1090,45 @@
     <row r="26" ht="15" customHeight="1" s="45">
       <c r="A26" s="47" t="inlineStr">
         <is>
-          <t>Nagrody publiczności rozmowy łącznie (brutto)</t>
+          <t>Nagrody publiczności piosenki łącznie (brutto)</t>
         </is>
       </c>
       <c r="B26" s="56" t="n">
         <v>12000</v>
       </c>
+      <c r="C26" s="57" t="inlineStr">
+        <is>
+          <t>3 000 zł dla wykonawcy oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych piosenek. Uzasadnienie jest obowiązkowe przy każdym głosie, od 200 do 1500 znaków (§ 11 ust. 2 regulaminu).</t>
+        </is>
+      </c>
+      <c r="D26" s="47" t="n"/>
+      <c r="E26" s="47" t="n"/>
+      <c r="F26" s="47" t="n"/>
+      <c r="G26" s="47" t="n"/>
+      <c r="H26" s="47" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="45">
       <c r="A27" s="47" t="inlineStr">
         <is>
-          <t>Nagranie studyjne - koszt za utwór (netto)</t>
+          <t>Nagrody publiczności rozmowy łącznie (brutto)</t>
         </is>
       </c>
       <c r="B27" s="56" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C27" s="57" t="inlineStr">
-        <is>
-          <t>Środek widełek 5-10 tys. Do wyceny przez Michała Sołtana.</t>
-        </is>
-      </c>
-      <c r="D27" s="47" t="n"/>
-      <c r="E27" s="47" t="n"/>
-      <c r="F27" s="47" t="n"/>
-      <c r="G27" s="47" t="n"/>
-      <c r="H27" s="47" t="n"/>
+        <v>12000</v>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="45">
       <c r="A28" s="47" t="inlineStr">
         <is>
-          <t>Liczba nagrań studyjnych</t>
+          <t>Nagranie studyjne - koszt za utwór (netto)</t>
         </is>
       </c>
       <c r="B28" s="56" t="n">
-        <v>10</v>
+        <v>7500</v>
       </c>
       <c r="C28" s="57" t="inlineStr">
         <is>
-          <t>Dziesięciu finalistów; te nagrania trafiają na płytę.</t>
+          <t>Środek widełek 5-10 tys. Do wyceny przez Michała Sołtana.</t>
         </is>
       </c>
       <c r="D28" s="47" t="n"/>
@@ -1143,15 +1140,15 @@
     <row r="29" ht="15" customHeight="1" s="45">
       <c r="A29" s="47" t="inlineStr">
         <is>
-          <t>Hymn z teledyskiem (netto)</t>
+          <t>Liczba nagrań studyjnych</t>
         </is>
       </c>
       <c r="B29" s="56" t="n">
-        <v>80000</v>
+        <v>10</v>
       </c>
       <c r="C29" s="57" t="inlineStr">
         <is>
-          <t>Środek widełek 60-100 tys. Górny koniec przy szerszym składzie.</t>
+          <t>Dziesięciu finalistów; te nagrania trafiają na płytę.</t>
         </is>
       </c>
       <c r="D29" s="47" t="n"/>
@@ -1163,15 +1160,15 @@
     <row r="30" ht="15" customHeight="1" s="45">
       <c r="A30" s="47" t="inlineStr">
         <is>
-          <t>Medal zwycięzcy i dyplomy piosenki (netto)</t>
+          <t>Hymn z teledyskiem (netto)</t>
         </is>
       </c>
       <c r="B30" s="56" t="n">
-        <v>1200</v>
+        <v>80000</v>
       </c>
       <c r="C30" s="57" t="inlineStr">
         <is>
-          <t>Ten sam medal co w plebiscycie na rozmowę, cena jak w Budżecie Nagrody.</t>
+          <t>Środek widełek 60-100 tys. Górny koniec przy szerszym składzie.</t>
         </is>
       </c>
       <c r="D30" s="47" t="n"/>
@@ -1183,15 +1180,15 @@
     <row r="31" ht="15" customHeight="1" s="45">
       <c r="A31" s="47" t="inlineStr">
         <is>
-          <t>Rezerwa w Budżecie Nagrody</t>
-        </is>
-      </c>
-      <c r="B31" s="58" t="n">
-        <v>0.12</v>
+          <t>Medal zwycięzcy i dyplomy piosenki (netto)</t>
+        </is>
+      </c>
+      <c r="B31" s="56" t="n">
+        <v>1200</v>
       </c>
       <c r="C31" s="57" t="inlineStr">
         <is>
-          <t>Narzut na nieprzewidziane.</t>
+          <t>Ten sam medal co w plebiscycie na rozmowę, cena jak w Budżecie Nagrody.</t>
         </is>
       </c>
       <c r="D31" s="47" t="n"/>
@@ -1203,15 +1200,15 @@
     <row r="32" ht="15" customHeight="1" s="45">
       <c r="A32" s="47" t="inlineStr">
         <is>
-          <t>Wynagrodzenie wykonawcy i rezerwa w Budżecie Antologii</t>
+          <t>Rezerwa w Budżecie Nagrody</t>
         </is>
       </c>
       <c r="B32" s="58" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="C32" s="57" t="inlineStr">
         <is>
-          <t>Dwadzieścia procent to wynagrodzenie podmiotu, który wykona tę część; dziesięć procent to rezerwa na przekroczenia. Rezerwa niewykorzystana oraz pozycje nieponiesione wracają do Mecenasa albo, na jego pisemny wybór, przechodzą na antologię kolejnej edycji - nigdy na pulę nagród.</t>
+          <t>Narzut na nieprzewidziane.</t>
         </is>
       </c>
       <c r="D32" s="47" t="n"/>
@@ -1223,15 +1220,15 @@
     <row r="33" ht="15" customHeight="1" s="45">
       <c r="A33" s="47" t="inlineStr">
         <is>
-          <t>Rezerwa w Budżecie Plebiscytu</t>
+          <t>Wynagrodzenie wykonawcy i rezerwa w Budżecie Antologii</t>
         </is>
       </c>
       <c r="B33" s="58" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="C33" s="57" t="inlineStr">
         <is>
-          <t>Narzut na nieprzewidziane.</t>
+          <t>Dwadzieścia procent to wynagrodzenie podmiotu, który wykona tę część; dziesięć procent to rezerwa na przekroczenia. Rezerwa niewykorzystana oraz pozycje nieponiesione wracają do Mecenasa albo, na jego pisemny wybór, przechodzą na antologię kolejnej edycji - nigdy na pulę nagród.</t>
         </is>
       </c>
       <c r="D33" s="47" t="n"/>
@@ -1243,15 +1240,15 @@
     <row r="34" ht="15" customHeight="1" s="45">
       <c r="A34" s="47" t="inlineStr">
         <is>
-          <t>Stawka VAT</t>
+          <t>Rezerwa w Budżecie Plebiscytu</t>
         </is>
       </c>
       <c r="B34" s="58" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="C34" s="57" t="inlineStr">
         <is>
-          <t>Dotyczy faktur wystawianych sponsorom.</t>
+          <t>Narzut na nieprzewidziane.</t>
         </is>
       </c>
       <c r="D34" s="47" t="n"/>
@@ -1263,7 +1260,15 @@
     <row r="35" ht="15" customHeight="1" s="45">
       <c r="A35" s="47" t="inlineStr">
         <is>
-          <t>Podatek od nagród (ryczałt)</t>
+          <t>Stawka VAT</t>
+        </is>
+      </c>
+      <c r="B35" s="58" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C35" s="57" t="inlineStr">
+        <is>
+          <t>Dotyczy faktur wystawianych sponsorom.</t>
         </is>
       </c>
       <c r="D35" s="47" t="n"/>
@@ -1273,7 +1278,11 @@
       <c r="H35" s="47" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="45">
-      <c r="A36" s="47" t="n"/>
+      <c r="A36" s="47" t="inlineStr">
+        <is>
+          <t>Podatek od nagród (ryczałt)</t>
+        </is>
+      </c>
       <c r="D36" s="47" t="n"/>
       <c r="E36" s="47" t="n"/>
       <c r="F36" s="47" t="n"/>
@@ -1281,11 +1290,7 @@
       <c r="H36" s="47" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="45">
-      <c r="A37" s="49" t="inlineStr">
-        <is>
-          <t>CZEGO JESZCZE NIE MA</t>
-        </is>
-      </c>
+      <c r="A37" s="47" t="n"/>
       <c r="D37" s="47" t="n"/>
       <c r="E37" s="47" t="n"/>
       <c r="F37" s="47" t="n"/>
@@ -1293,9 +1298,9 @@
       <c r="H37" s="47" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="45">
-      <c r="A38" s="50" t="inlineStr">
-        <is>
-          <t>Honoraria jury we wszystkich plebiscytach - osobno za ocenę zgłoszeń i za etap przygotowania karty oceny</t>
+      <c r="A38" s="49" t="inlineStr">
+        <is>
+          <t>CZEGO JESZCZE NIE MA</t>
         </is>
       </c>
       <c r="D38" s="47" t="n"/>
@@ -1307,7 +1312,7 @@
     <row r="39" ht="15" customHeight="1" s="45">
       <c r="A39" s="50" t="inlineStr">
         <is>
-          <t>Realizacja części artystycznej gali</t>
+          <t>Honoraria jury we wszystkich plebiscytach - osobno za ocenę zgłoszeń i za etap przygotowania karty oceny</t>
         </is>
       </c>
       <c r="D39" s="47" t="n"/>
@@ -1317,9 +1322,9 @@
       <c r="H39" s="47" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="45">
-      <c r="A40" s="48" t="inlineStr">
-        <is>
-          <t>Po wpisaniu tych kwot rosną Budżet Plebiscytu, Budżet Plakatu i Budżet Filmu. W Budżecie Plakatu czekają na wycenę cztery pozycje, w Budżecie Filmu pięć - wszystkie opisane w kolumnie Uwagi.</t>
+      <c r="A40" s="50" t="inlineStr">
+        <is>
+          <t>Realizacja części artystycznej gali</t>
         </is>
       </c>
       <c r="D40" s="47" t="n"/>
@@ -1329,7 +1334,11 @@
       <c r="H40" s="47" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="45">
-      <c r="A41" s="47" t="n"/>
+      <c r="A41" s="48" t="inlineStr">
+        <is>
+          <t>Po wpisaniu tych kwot rosną Budżet Plebiscytu, Budżet Plakatu i Budżet Filmu. W Budżecie Plakatu czekają na wycenę cztery pozycje, w Budżecie Filmu pięć - wszystkie opisane w kolumnie Uwagi.</t>
+        </is>
+      </c>
       <c r="D41" s="47" t="n"/>
       <c r="E41" s="47" t="n"/>
       <c r="F41" s="47" t="n"/>
@@ -1337,11 +1346,7 @@
       <c r="H41" s="47" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="45">
-      <c r="A42" s="49" t="inlineStr">
-        <is>
-          <t>JAK CZYTAĆ BUDŻETY</t>
-        </is>
-      </c>
+      <c r="A42" s="47" t="n"/>
       <c r="D42" s="47" t="n"/>
       <c r="E42" s="47" t="n"/>
       <c r="F42" s="47" t="n"/>
@@ -1349,9 +1354,9 @@
       <c r="H42" s="47" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="45">
-      <c r="A43" s="48" t="inlineStr">
-        <is>
-          <t>Każda z zakładek budżetowych ma ten sam układ: praca organizatora, koszty twarde, podsumowanie.</t>
+      <c r="A43" s="49" t="inlineStr">
+        <is>
+          <t>JAK CZYTAĆ BUDŻETY</t>
         </is>
       </c>
       <c r="D43" s="47" t="n"/>
@@ -1363,7 +1368,7 @@
     <row r="44" ht="15" customHeight="1" s="45">
       <c r="A44" s="48" t="inlineStr">
         <is>
-          <t>W podsumowaniu jest kwota netto, VAT i kwota brutto, którą sponsor widzi na fakturze.</t>
+          <t>Każda z zakładek budżetowych ma ten sam układ: praca organizatora, koszty twarde, podsumowanie.</t>
         </is>
       </c>
       <c r="D44" s="47" t="n"/>
@@ -1373,451 +1378,462 @@
       <c r="H44" s="47" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="45">
-      <c r="A45" s="47" t="inlineStr">
+      <c r="A45" s="48" t="inlineStr">
+        <is>
+          <t>W podsumowaniu jest kwota netto, VAT i kwota brutto, którą sponsor widzi na fakturze.</t>
+        </is>
+      </c>
+      <c r="D45" s="47" t="n"/>
+      <c r="E45" s="47" t="n"/>
+      <c r="F45" s="47" t="n"/>
+      <c r="G45" s="47" t="n"/>
+      <c r="H45" s="47" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="45">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>Kolumna "Rok kosztu" w każdej zakładce mówi, na który rok edycji przypada dana pozycja: 2027 to rok naboru, 2028 to ocena jury, nagrody, produkcja antologii, gala i wystawy. Rezerwa i marża dzielą się proporcjonalnie do kosztów danego roku. Podział w tym układzie pokazuje załącznik "Zestawienie zadania".</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="45">
-      <c r="A46" s="59" t="inlineStr">
+    <row r="47" ht="15" customHeight="1" s="45">
+      <c r="A47" s="59" t="inlineStr">
         <is>
           <t>AKADEMIA - PARAMETRY SKALOWANIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="45">
-      <c r="A47" s="47" t="inlineStr">
-        <is>
-          <t>Odczytów na jedno zgłoszenie w rundzie pierwszej</t>
-        </is>
-      </c>
-      <c r="B47" s="56" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" s="47" t="inlineStr">
-        <is>
-          <t>Regulamin § 8: co najmniej dwóch czytelników przy 21-60 zgłoszeniach; powyżej 200 przesiew jednoosobowy z drugim odczytem poniżej progu.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="45">
       <c r="A48" s="47" t="inlineStr">
         <is>
-          <t>Voucher za każde 100 ocenionych rozmów (netto)</t>
-        </is>
-      </c>
-      <c r="B48" s="60" t="n">
-        <v>500</v>
+          <t>Odczytów na jedno zgłoszenie w rundzie pierwszej</t>
+        </is>
+      </c>
+      <c r="B48" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="C48" s="47" t="inlineStr">
         <is>
-          <t>Świadczenie rzeczowe sponsora Akademii. Do ustalenia ze sponsorem.</t>
+          <t>Regulamin § 8: co najmniej dwóch czytelników przy 21-60 zgłoszeniach; powyżej 200 przesiew jednoosobowy z drugim odczytem poniżej progu.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="45">
       <c r="A49" s="47" t="inlineStr">
         <is>
-          <t>Honorarium podstawowe czytelnika (netto)</t>
+          <t>Voucher za każde 100 ocenionych rozmów (netto)</t>
         </is>
       </c>
       <c r="B49" s="60" t="n">
-        <v>2500</v>
+        <v>500</v>
       </c>
       <c r="C49" s="47" t="inlineStr">
         <is>
-          <t>Przeniesione z Budżetu Nagrody. Voucher jest dodatkiem, nie zamiennikiem.</t>
+          <t>Świadczenie rzeczowe sponsora Akademii. Do ustalenia ze sponsorem.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="45">
       <c r="A50" s="47" t="inlineStr">
         <is>
-          <t>Liczba czytelników w pierwszej edycji</t>
-        </is>
-      </c>
-      <c r="B50" s="56" t="n">
-        <v>15</v>
+          <t>Honorarium podstawowe czytelnika (netto)</t>
+        </is>
+      </c>
+      <c r="B50" s="60" t="n">
+        <v>2500</v>
       </c>
       <c r="C50" s="47" t="inlineStr">
         <is>
-          <t>Maksymalnie 20 zgłoszeń na czytelnika (regulamin § 8).</t>
+          <t>Przeniesione z Budżetu Nagrody. Voucher jest dodatkiem, nie zamiennikiem.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="45">
       <c r="A51" s="47" t="inlineStr">
         <is>
+          <t>Liczba czytelników w pierwszej edycji</t>
+        </is>
+      </c>
+      <c r="B51" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="C51" s="47" t="inlineStr">
+        <is>
+          <t>Maksymalnie 20 zgłoszeń na czytelnika (regulamin § 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="45">
+      <c r="A52" s="47" t="inlineStr">
+        <is>
           <t>Czas na jeden odczyt rozmowy wraz z kartą oceny (minut)</t>
         </is>
       </c>
-      <c r="B51" s="61" t="n">
+      <c r="B52" s="61" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="45"/>
-    <row r="53" ht="15" customHeight="1" s="45">
-      <c r="A53" s="62" t="inlineStr">
+    <row r="53" ht="15" customHeight="1" s="45"/>
+    <row r="54" ht="15" customHeight="1" s="45">
+      <c r="A54" s="62" t="inlineStr">
         <is>
           <t>PLAKAT - PARAMETRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="45">
-      <c r="A54" s="44" t="inlineStr">
-        <is>
-          <t>Liczba zgłoszeń plakatów</t>
-        </is>
-      </c>
-      <c r="B54" s="63" t="n">
-        <v>150</v>
-      </c>
-      <c r="C54" s="44" t="inlineStr">
-        <is>
-          <t>Wpływa na koszt kontroli formalnej.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="45">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>Nagrody plakatu łącznie (brutto)</t>
-        </is>
-      </c>
-      <c r="B55" s="60" t="n">
-        <v>90000</v>
+          <t>Liczba zgłoszeń plakatów</t>
+        </is>
+      </c>
+      <c r="B55" s="63" t="n">
+        <v>150</v>
       </c>
       <c r="C55" s="44" t="inlineStr">
         <is>
-          <t>50 tys. + 25 tys. + 15 tys. dla czołowej trójki.</t>
+          <t>Wpływa na koszt kontroli formalnej.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="45">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>Nagrody publiczności plakatu łącznie (brutto)</t>
+          <t>Nagrody plakatu łącznie (brutto)</t>
         </is>
       </c>
       <c r="B56" s="60" t="n">
-        <v>12000</v>
+        <v>90000</v>
       </c>
       <c r="C56" s="44" t="inlineStr">
         <is>
-          <t>3 000 zł dla pracy z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych plakatów (§ 12 ust. 6).</t>
+          <t>50 tys. + 25 tys. + 15 tys. dla czołowej trójki.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="45">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>Medal zwycięzcy i dyplomy plakatu (netto)</t>
+          <t>Nagrody publiczności plakatu łącznie (brutto)</t>
         </is>
       </c>
       <c r="B57" s="60" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
       <c r="C57" s="44" t="inlineStr">
         <is>
-          <t>Ten sam medal co w plebiscycie na rozmowę, cena jak w Budżecie Nagrody.</t>
+          <t>3 000 zł dla pracy z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych plakatów (§ 12 ust. 6).</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="45">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>Liczba jurorów plakatu</t>
-        </is>
-      </c>
-      <c r="B58" s="63" t="n">
-        <v>5</v>
+          <t>Medal zwycięzcy i dyplomy plakatu (netto)</t>
+        </is>
+      </c>
+      <c r="B58" s="60" t="n">
+        <v>1200</v>
       </c>
       <c r="C58" s="44" t="inlineStr">
         <is>
-          <t>Kotwica, nie decyzja: pozycja honorariów w Budżecie Plakatu stoi na zerze jako DO USTALENIA, do rozmowy z przewodniczącym jury.</t>
+          <t>Ten sam medal co w plebiscycie na rozmowę, cena jak w Budżecie Nagrody.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="45">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>Godzin oceny na jurora</t>
+          <t>Liczba jurorów plakatu</t>
         </is>
       </c>
       <c r="B59" s="63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C59" s="44" t="inlineStr">
         <is>
-          <t>Oglądanie reprodukcji jest szybsze niż odsłuch utworów; przy jury przyjęto 15 h.</t>
+          <t>Kotwica, nie decyzja: pozycja honorariów w Budżecie Plakatu stoi na zerze jako DO USTALENIA, do rozmowy z przewodniczącym jury.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="45">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>Stawka jury plakatu za godzinę (netto)</t>
-        </is>
-      </c>
-      <c r="B60" s="60" t="n">
-        <v>290</v>
+          <t>Godzin oceny na jurora</t>
+        </is>
+      </c>
+      <c r="B60" s="63" t="n">
+        <v>10</v>
       </c>
       <c r="C60" s="44" t="inlineStr">
         <is>
-          <t>Stawka przyjęta dla jury oceniającej rozmowy.</t>
+          <t>Oglądanie reprodukcji jest szybsze niż odsłuch utworów; przy jury przyjęto 15 h.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="45">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>Liczba prac finałowych</t>
-        </is>
-      </c>
-      <c r="B61" s="63" t="n">
-        <v>10</v>
+          <t>Stawka jury plakatu za godzinę (netto)</t>
+        </is>
+      </c>
+      <c r="B61" s="60" t="n">
+        <v>290</v>
       </c>
       <c r="C61" s="44" t="inlineStr">
         <is>
-          <t>Dziesiątka, której oryginały jadą na wystawę.</t>
+          <t>Stawka przyjęta dla jury oceniającej rozmowy.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="45">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>Transport jednej pracy w jedną stronę (netto)</t>
-        </is>
-      </c>
-      <c r="B62" s="60" t="n">
-        <v>400</v>
+          <t>Liczba prac finałowych</t>
+        </is>
+      </c>
+      <c r="B62" s="63" t="n">
+        <v>10</v>
       </c>
       <c r="C62" s="44" t="inlineStr">
         <is>
-          <t>Szacunek, nie oferta. Format do 150 cm przekracza limity standardowych przesyłek.</t>
+          <t>Dziesiątka, której oryginały jadą na wystawę.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="45">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>Ubezpieczenie prac na czas wystawy (netto)</t>
+          <t>Transport jednej pracy w jedną stronę (netto)</t>
         </is>
       </c>
       <c r="B63" s="60" t="n">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="C63" s="44" t="inlineStr">
         <is>
-          <t>Szacunek przy sumie deklarowanej rzędu 100 tys. zł dla całej dziesiątki.</t>
+          <t>Szacunek, nie oferta. Format do 150 cm przekracza limity standardowych przesyłek.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="45">
       <c r="A64" s="44" t="inlineStr">
         <is>
+          <t>Ubezpieczenie prac na czas wystawy (netto)</t>
+        </is>
+      </c>
+      <c r="B64" s="60" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C64" s="44" t="inlineStr">
+        <is>
+          <t>Szacunek przy sumie deklarowanej rzędu 100 tys. zł dla całej dziesiątki.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="45">
+      <c r="A65" s="44" t="inlineStr">
+        <is>
           <t>Rezerwa w Budżecie Plakatu</t>
         </is>
       </c>
-      <c r="B64" s="60" t="n">
+      <c r="B65" s="60" t="n">
         <v>0.12</v>
       </c>
-      <c r="C64" s="44" t="inlineStr">
+      <c r="C65" s="44" t="inlineStr">
         <is>
           <t>Narzut na nieprzewidziane.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1" s="45"/>
-    <row r="66" ht="15" customHeight="1" s="45">
-      <c r="A66" s="62" t="inlineStr">
+    <row r="66" ht="15" customHeight="1" s="45"/>
+    <row r="67" ht="15" customHeight="1" s="45">
+      <c r="A67" s="62" t="inlineStr">
         <is>
           <t>FILM - PARAMETRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="45">
-      <c r="A67" s="44" t="inlineStr">
-        <is>
-          <t>Liczba zgłoszeń filmów</t>
-        </is>
-      </c>
-      <c r="B67" s="56" t="n">
-        <v>150</v>
-      </c>
-      <c r="C67" s="44" t="inlineStr">
-        <is>
-          <t>Wpływa na koszt kontroli formalnej i na wielkość Akademii filmu.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="45">
       <c r="A68" s="44" t="inlineStr">
         <is>
-          <t>Nagrody filmu łącznie (brutto)</t>
+          <t>Liczba zgłoszeń filmów</t>
         </is>
       </c>
       <c r="B68" s="56" t="n">
-        <v>180000</v>
+        <v>150</v>
       </c>
       <c r="C68" s="44" t="inlineStr">
         <is>
-          <t>100 tys. + 50 tys. + 30 tys. dla czołowej trójki. Siedem wyróżnień nie jest pieniężnych.</t>
+          <t>Wpływa na koszt kontroli formalnej i na wielkość Akademii filmu.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="45">
       <c r="A69" s="44" t="inlineStr">
         <is>
-          <t>Nagrody publiczności filmu łącznie (brutto)</t>
+          <t>Nagrody filmu łącznie (brutto)</t>
         </is>
       </c>
       <c r="B69" s="56" t="n">
-        <v>12000</v>
+        <v>180000</v>
       </c>
       <c r="C69" s="44" t="inlineStr">
         <is>
-          <t>3 000 zł dla filmu z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych filmów (§ 11a ust. 5).</t>
+          <t>100 tys. + 50 tys. + 30 tys. dla czołowej trójki. Siedem wyróżnień nie jest pieniężnych.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="45">
       <c r="A70" s="44" t="inlineStr">
         <is>
-          <t>Medal zwycięzcy i dyplomy filmu (netto)</t>
+          <t>Nagrody publiczności filmu łącznie (brutto)</t>
         </is>
       </c>
       <c r="B70" s="56" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
       <c r="C70" s="44" t="inlineStr">
         <is>
-          <t>Ten sam medal co w pozostałych plebiscytach; dyplomy dla dziesięciu finalistów.</t>
+          <t>3 000 zł dla filmu z największą liczbą głosów oraz 1 000 zł jako Nagroda dla publicznych ocen zgłoszonych filmów (§ 11a ust. 5).</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="45">
       <c r="A71" s="44" t="inlineStr">
         <is>
-          <t>Liczba filmów finałowych</t>
+          <t>Medal zwycięzcy i dyplomy filmu (netto)</t>
         </is>
       </c>
       <c r="B71" s="56" t="n">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="C71" s="44" t="inlineStr">
         <is>
-          <t>Dziesięciu finalistów: trójka z nagrodami pieniężnymi i siedem wyróżnień. Minutowe skróty na gali dostaje pięć najwyżej ocenionych.</t>
+          <t>Ten sam medal co w pozostałych plebiscytach; dyplomy dla dziesięciu finalistów.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="45">
       <c r="A72" s="44" t="inlineStr">
         <is>
-          <t>Liczba jurorów filmu</t>
+          <t>Liczba filmów finałowych</t>
         </is>
       </c>
       <c r="B72" s="56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C72" s="44" t="inlineStr">
         <is>
-          <t>Kotwica, nie decyzja: pozycja honorariów w Budżecie Filmu stoi na zerze jako DO USTALENIA.</t>
+          <t>Dziesięciu finalistów: trójka z nagrodami pieniężnymi i siedem wyróżnień. Minutowe skróty na gali dostaje pięć najwyżej ocenionych.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="45">
       <c r="A73" s="44" t="inlineStr">
         <is>
-          <t>Godzin oceny na jurora filmu</t>
+          <t>Liczba jurorów filmu</t>
         </is>
       </c>
       <c r="B73" s="56" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="C73" s="44" t="inlineStr">
         <is>
-          <t>Akademia przekazuje jury nie więcej niż dwadzieścia filmów (§ 8 ust. 5a); dwadzieścia filmów po najwyżej 90 minut to 30 godzin samego oglądania, reszta na karty oceny, obrady i werdykt.</t>
+          <t>Kotwica, nie decyzja: pozycja honorariów w Budżecie Filmu stoi na zerze jako DO USTALENIA.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="45">
       <c r="A74" s="44" t="inlineStr">
         <is>
-          <t>Stawka jury filmu za godzinę (netto)</t>
+          <t>Godzin oceny na jurora filmu</t>
         </is>
       </c>
       <c r="B74" s="56" t="n">
-        <v>290</v>
+        <v>40</v>
       </c>
       <c r="C74" s="44" t="inlineStr">
         <is>
-          <t>Stawka przyjęta dla jury oceniającej rozmowy.</t>
+          <t>Akademia przekazuje jury nie więcej niż dwadzieścia filmów (§ 8 ust. 5a); dwadzieścia filmów po najwyżej 90 minut to 30 godzin samego oglądania, reszta na karty oceny, obrady i werdykt.</t>
         </is>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="45">
       <c r="A75" s="44" t="inlineStr">
         <is>
-          <t>Rezerwa w Budżecie Filmu</t>
+          <t>Stawka jury filmu za godzinę (netto)</t>
         </is>
       </c>
       <c r="B75" s="56" t="n">
-        <v>0.12</v>
+        <v>290</v>
       </c>
       <c r="C75" s="44" t="inlineStr">
         <is>
-          <t>Narzut na nieprzewidziane, jak w pozostałych budżetach.</t>
+          <t>Stawka przyjęta dla jury oceniającej rozmowy.</t>
         </is>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="45">
       <c r="A76" s="44" t="inlineStr">
         <is>
-          <t>Obejrzeń jednego filmu w Akademii</t>
+          <t>Rezerwa w Budżecie Filmu</t>
         </is>
       </c>
       <c r="B76" s="56" t="n">
-        <v>2</v>
+        <v>0.12</v>
       </c>
       <c r="C76" s="44" t="inlineStr">
         <is>
-          <t>Dwa niezależne obejrzenia, analogicznie do dwóch odczytów rozmowy.</t>
+          <t>Narzut na nieprzewidziane, jak w pozostałych budżetach.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="45">
       <c r="A77" s="44" t="inlineStr">
         <is>
-          <t>Honorarium za obejrzenie jednego filmu (netto)</t>
+          <t>Obejrzeń jednego filmu w Akademii</t>
         </is>
       </c>
       <c r="B77" s="56" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="C77" s="44" t="inlineStr">
         <is>
-          <t>Film do 90 minut plus karta oceny to około 2 godzin pracy. Ustalenie z 26.10.2026.</t>
+          <t>Dwa niezależne obejrzenia, analogicznie do dwóch odczytów rozmowy.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="45">
       <c r="A78" s="44" t="inlineStr">
         <is>
+          <t>Honorarium za obejrzenie jednego filmu (netto)</t>
+        </is>
+      </c>
+      <c r="B78" s="56" t="n">
+        <v>300</v>
+      </c>
+      <c r="C78" s="44" t="inlineStr">
+        <is>
+          <t>Film do 90 minut plus karta oceny to około 2 godzin pracy. Ustalenie z 26.10.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="45">
+      <c r="A79" s="44" t="inlineStr">
+        <is>
           <t>Maksimum filmów na jednego oceniającego</t>
         </is>
       </c>
-      <c r="B78" s="56" t="n">
+      <c r="B79" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="C78" s="44" t="inlineStr">
+      <c r="C79" s="44" t="inlineStr">
         <is>
           <t>Dziesięć filmów to około 20 godzin oglądania. Wyznacza, ilu ludzi trzeba przy danym wolumenie.</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="45"/>
     <row r="80" ht="15" customHeight="1" s="45"/>
     <row r="81" ht="15" customHeight="1" s="45"/>
     <row r="82" ht="15" customHeight="1" s="45"/>
@@ -1966,11 +1982,11 @@
         <v>0</v>
       </c>
       <c r="D7" s="66">
-        <f>B7+C7*Wyjaśnienia!$B$17/60</f>
+        <f>B7+C7*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E7" s="67">
-        <f>D7*Wyjaśnienia!$B$16</f>
+        <f>D7*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F7" s="57" t="inlineStr">
@@ -1996,11 +2012,11 @@
         <v>0</v>
       </c>
       <c r="D8" s="66">
-        <f>B8+C8*Wyjaśnienia!$B$17/60</f>
+        <f>B8+C8*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E8" s="67">
-        <f>D8*Wyjaśnienia!$B$16</f>
+        <f>D8*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F8" s="57" t="inlineStr">
@@ -2026,11 +2042,11 @@
         <v>0</v>
       </c>
       <c r="D9" s="66">
-        <f>B9+C9*Wyjaśnienia!$B$17/60</f>
+        <f>B9+C9*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E9" s="67">
-        <f>D9*Wyjaśnienia!$B$16</f>
+        <f>D9*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F9" s="57" t="inlineStr">
@@ -2056,11 +2072,11 @@
         <v>6</v>
       </c>
       <c r="D10" s="66">
-        <f>B10+C10*Wyjaśnienia!$B$17/60</f>
+        <f>B10+C10*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E10" s="67">
-        <f>D10*Wyjaśnienia!$B$16</f>
+        <f>D10*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F10" s="57" t="inlineStr">
@@ -2086,11 +2102,11 @@
         <v>4</v>
       </c>
       <c r="D11" s="66">
-        <f>B11+C11*Wyjaśnienia!$B$17/60</f>
+        <f>B11+C11*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E11" s="67">
-        <f>D11*Wyjaśnienia!$B$16</f>
+        <f>D11*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F11" s="57" t="inlineStr">
@@ -2116,11 +2132,11 @@
         <v>0</v>
       </c>
       <c r="D12" s="66">
-        <f>B12+C12*Wyjaśnienia!$B$17/60</f>
+        <f>B12+C12*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E12" s="67">
-        <f>D12*Wyjaśnienia!$B$16</f>
+        <f>D12*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F12" s="57" t="inlineStr">
@@ -2146,11 +2162,11 @@
         <v>0</v>
       </c>
       <c r="D13" s="66">
-        <f>B13+C13*Wyjaśnienia!$B$17/60</f>
+        <f>B13+C13*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E13" s="67">
-        <f>D13*Wyjaśnienia!$B$16</f>
+        <f>D13*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F13" s="57" t="inlineStr">
@@ -2176,11 +2192,11 @@
         <v>0</v>
       </c>
       <c r="D14" s="66">
-        <f>B14+C14*Wyjaśnienia!$B$17/60</f>
+        <f>B14+C14*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E14" s="67">
-        <f>D14*Wyjaśnienia!$B$16</f>
+        <f>D14*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F14" s="57" t="inlineStr">
@@ -2206,11 +2222,11 @@
         <v>0</v>
       </c>
       <c r="D15" s="66">
-        <f>B15+C15*Wyjaśnienia!$B$17/60</f>
+        <f>B15+C15*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E15" s="67">
-        <f>D15*Wyjaśnienia!$B$16</f>
+        <f>D15*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F15" s="57" t="inlineStr">
@@ -2236,11 +2252,11 @@
         <v>0</v>
       </c>
       <c r="D16" s="66">
-        <f>B16+C16*Wyjaśnienia!$B$17/60</f>
+        <f>B16+C16*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E16" s="67">
-        <f>D16*Wyjaśnienia!$B$16</f>
+        <f>D16*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F16" s="57" t="inlineStr">
@@ -2494,7 +2510,7 @@
         </is>
       </c>
       <c r="B27" s="70">
-        <f>Wyjaśnienia!$B$26</f>
+        <f>Wyjaśnienia!$B$27</f>
         <v/>
       </c>
       <c r="C27" s="65" t="n">
@@ -2604,7 +2620,7 @@
       <c r="B33" s="47" t="n"/>
       <c r="C33" s="47" t="n"/>
       <c r="D33" s="67">
-        <f>Wyjaśnienia!$B$18+Wyjaśnienia!$B$21+Wyjaśnienia!$B$22+Wyjaśnienia!$B$19*Wyjaśnienia!$B$20</f>
+        <f>Wyjaśnienia!$B$19+Wyjaśnienia!$B$22+Wyjaśnienia!$B$23+Wyjaśnienia!$B$20*Wyjaśnienia!$B$21</f>
         <v/>
       </c>
       <c r="E33" s="47" t="n"/>
@@ -2650,7 +2666,7 @@
         </is>
       </c>
       <c r="D36" s="47">
-        <f>(D34+D35-D27-D29)*Wyjaśnienia!$B$31</f>
+        <f>(D34+D35-D27-D29)*Wyjaśnienia!$B$32</f>
         <v/>
       </c>
       <c r="E36" s="44" t="inlineStr">
@@ -2685,7 +2701,7 @@
       <c r="B38" s="47" t="n"/>
       <c r="C38" s="47" t="n"/>
       <c r="D38" s="52">
-        <f>D37*Wyjaśnienia!$B$34</f>
+        <f>D37*Wyjaśnienia!$B$35</f>
         <v/>
       </c>
       <c r="E38" s="47" t="n"/>
@@ -2899,11 +2915,11 @@
         <v>0</v>
       </c>
       <c r="D7" s="66">
-        <f>B7+C7*Wyjaśnienia!$B$17/60</f>
+        <f>B7+C7*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E7" s="67">
-        <f>D7*Wyjaśnienia!$B$16</f>
+        <f>D7*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F7" s="57" t="inlineStr">
@@ -2929,11 +2945,11 @@
         <v>0</v>
       </c>
       <c r="D8" s="66">
-        <f>B8+C8*Wyjaśnienia!$B$17/60</f>
+        <f>B8+C8*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E8" s="67">
-        <f>D8*Wyjaśnienia!$B$16</f>
+        <f>D8*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F8" s="57" t="inlineStr">
@@ -2959,11 +2975,11 @@
         <v>4</v>
       </c>
       <c r="D9" s="66">
-        <f>B9+C9*Wyjaśnienia!$B$17/60</f>
+        <f>B9+C9*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E9" s="67">
-        <f>D9*Wyjaśnienia!$B$16</f>
+        <f>D9*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F9" s="57" t="inlineStr">
@@ -2977,93 +2993,33 @@
       <c r="H9" s="47" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="45">
-      <c r="A10" s="64" t="inlineStr">
-        <is>
-          <t>Skraper i kopia archiwalna zgłoszenia</t>
-        </is>
-      </c>
-      <c r="B10" s="65" t="n">
-        <v>50</v>
-      </c>
-      <c r="C10" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="66">
-        <f>B10+C10*Wyjaśnienia!$B$17/60</f>
-        <v/>
-      </c>
-      <c r="E10" s="67">
-        <f>D10*Wyjaśnienia!$B$16</f>
-        <v/>
-      </c>
-      <c r="F10" s="57" t="inlineStr">
-        <is>
-          <t>Playwright: PDF, pełny HTML, zrzut, znacznik czasu, suma kontrolna</t>
-        </is>
-      </c>
-      <c r="G10" s="68" t="n">
-        <v>2027</v>
-      </c>
+      <c r="A10" s="64" t="n"/>
+      <c r="B10" s="65" t="n"/>
+      <c r="C10" s="65" t="n"/>
+      <c r="D10" s="66" t="n"/>
+      <c r="E10" s="67" t="n"/>
+      <c r="F10" s="57" t="n"/>
+      <c r="G10" s="68" t="n"/>
       <c r="H10" s="47" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="45">
-      <c r="A11" s="64" t="inlineStr">
-        <is>
-          <t>Narzędzie do oceny formalnej</t>
-        </is>
-      </c>
-      <c r="B11" s="65" t="n">
-        <v>25</v>
-      </c>
-      <c r="C11" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="66">
-        <f>B11+C11*Wyjaśnienia!$B$17/60</f>
-        <v/>
-      </c>
-      <c r="E11" s="67">
-        <f>D11*Wyjaśnienia!$B$16</f>
-        <v/>
-      </c>
-      <c r="F11" s="57" t="inlineStr">
-        <is>
-          <t>liczenie słów i wypowiedzi, wykluczanie kodu, język, ciągłość wątku</t>
-        </is>
-      </c>
-      <c r="G11" s="68" t="n">
-        <v>2027</v>
-      </c>
+      <c r="A11" s="64" t="n"/>
+      <c r="B11" s="65" t="n"/>
+      <c r="C11" s="65" t="n"/>
+      <c r="D11" s="66" t="n"/>
+      <c r="E11" s="67" t="n"/>
+      <c r="F11" s="57" t="n"/>
+      <c r="G11" s="68" t="n"/>
       <c r="H11" s="47" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="45">
-      <c r="A12" s="64" t="inlineStr">
-        <is>
-          <t>Panel oceny dla Akademii i jury</t>
-        </is>
-      </c>
-      <c r="B12" s="65" t="n">
-        <v>160</v>
-      </c>
-      <c r="C12" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="66">
-        <f>B12+C12*Wyjaśnienia!$B$17/60</f>
-        <v/>
-      </c>
-      <c r="E12" s="67">
-        <f>D12*Wyjaśnienia!$B$16</f>
-        <v/>
-      </c>
-      <c r="F12" s="57" t="inlineStr">
-        <is>
-          <t>konta, przydziały, karta oceny, rozbieżności, trzeci odczyt, ślad audytowy</t>
-        </is>
-      </c>
-      <c r="G12" s="68" t="n">
-        <v>2027</v>
-      </c>
+      <c r="A12" s="64" t="n"/>
+      <c r="B12" s="65" t="n"/>
+      <c r="C12" s="65" t="n"/>
+      <c r="D12" s="66" t="n"/>
+      <c r="E12" s="67" t="n"/>
+      <c r="F12" s="57" t="n"/>
+      <c r="G12" s="68" t="n"/>
       <c r="H12" s="47" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="45">
@@ -3079,11 +3035,11 @@
         <v>0</v>
       </c>
       <c r="D13" s="66">
-        <f>B13+C13*Wyjaśnienia!$B$17/60</f>
+        <f>B13+C13*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E13" s="67">
-        <f>D13*Wyjaśnienia!$B$16</f>
+        <f>D13*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F13" s="57" t="inlineStr">
@@ -3109,11 +3065,11 @@
         <v>0</v>
       </c>
       <c r="D14" s="66">
-        <f>B14+C14*Wyjaśnienia!$B$17/60</f>
+        <f>B14+C14*Wyjaśnienia!$B$18/60</f>
         <v/>
       </c>
       <c r="E14" s="67">
-        <f>D14*Wyjaśnienia!$B$16</f>
+        <f>D14*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F14" s="57" t="n"/>
@@ -3192,88 +3148,33 @@
       <c r="H18" s="47" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="45">
-      <c r="A19" s="64" t="inlineStr">
-        <is>
-          <t>Powołanie fundacji-organizatora</t>
-        </is>
-      </c>
-      <c r="B19" s="70" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C19" s="65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="67">
-        <f>B19*C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="57" t="inlineStr">
-        <is>
-          <t>notariusz, statut, wpis do KRS, fundusz założycielski</t>
-        </is>
-      </c>
+      <c r="A19" s="64" t="n"/>
+      <c r="B19" s="70" t="n"/>
+      <c r="C19" s="65" t="n"/>
+      <c r="D19" s="67" t="n"/>
+      <c r="E19" s="57" t="n"/>
       <c r="F19" s="47" t="n"/>
-      <c r="G19" s="68" t="n">
-        <v>2027</v>
-      </c>
+      <c r="G19" s="68" t="n"/>
       <c r="H19" s="47" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="45">
-      <c r="A20" s="64" t="inlineStr">
-        <is>
-          <t>Konsultacja prawna przed otwarciem naboru</t>
-        </is>
-      </c>
-      <c r="B20" s="70" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C20" s="65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="67">
-        <f>B20*C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="57" t="inlineStr">
-        <is>
-          <t>sześć obszarów, w tym licencja i archiwum; obowiązkowa przed naborem</t>
-        </is>
-      </c>
-      <c r="F20" s="47" t="inlineStr">
-        <is>
-          <t>sześć obszarów, w tym licencja i archiwum; kwota z zapasem wobec ofert kancelarii</t>
-        </is>
-      </c>
-      <c r="G20" s="68" t="n">
-        <v>2027</v>
-      </c>
+      <c r="A20" s="64" t="n"/>
+      <c r="B20" s="70" t="n"/>
+      <c r="C20" s="65" t="n"/>
+      <c r="D20" s="67" t="n"/>
+      <c r="E20" s="57" t="n"/>
+      <c r="F20" s="47" t="n"/>
+      <c r="G20" s="68" t="n"/>
       <c r="H20" s="47" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="45">
-      <c r="A21" s="64" t="inlineStr">
-        <is>
-          <t>Domeny, poczta, hosting, magazyn kopii archiwalnych</t>
-        </is>
-      </c>
-      <c r="B21" s="70" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C21" s="65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="67">
-        <f>B21*C21</f>
-        <v/>
-      </c>
-      <c r="E21" s="57" t="inlineStr">
-        <is>
-          <t>magazyn obiektowy w UE z kopią zapasową, retencja min. 5 lat, PDF/HTML/zrzuty/EPUB; w tym skrzynka pocztowa w domenie wraz z aliasami (kontakt@, imienny) - rzędu 150-450 zł rocznie, aliasy bez dopłaty; przejście na własną skrzynkę przenosi MX i wyłącza Cloudflare Email Routing</t>
-        </is>
-      </c>
+      <c r="A21" s="64" t="n"/>
+      <c r="B21" s="70" t="n"/>
+      <c r="C21" s="65" t="n"/>
+      <c r="D21" s="67" t="n"/>
+      <c r="E21" s="57" t="n"/>
       <c r="F21" s="47" t="n"/>
-      <c r="G21" s="68" t="n">
-        <v>2027</v>
-      </c>
+      <c r="G21" s="68" t="n"/>
       <c r="H21" s="47" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="45">
@@ -3412,110 +3313,42 @@
       <c r="H26" s="47" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="45">
-      <c r="A27" s="64" t="inlineStr">
-        <is>
-          <t>Przebudowa strony: UI/UX i teksty (agencja)</t>
-        </is>
-      </c>
-      <c r="B27" s="70" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C27" s="65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="67">
-        <f>B27*C27</f>
-        <v/>
-      </c>
-      <c r="E27" s="57" t="inlineStr">
-        <is>
-          <t>projekt i wdrożenie strony Nagrody wraz z copywritingiem</t>
-        </is>
-      </c>
+      <c r="A27" s="64" t="n"/>
+      <c r="B27" s="70" t="n"/>
+      <c r="C27" s="65" t="n"/>
+      <c r="D27" s="67" t="n"/>
+      <c r="E27" s="57" t="n"/>
       <c r="F27" s="47" t="n"/>
-      <c r="G27" s="68" t="n">
-        <v>2027</v>
-      </c>
+      <c r="G27" s="68" t="n"/>
       <c r="H27" s="47" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="45">
-      <c r="A28" s="64" t="inlineStr">
-        <is>
-          <t>Obsługa fundacji za pierwszy rok</t>
-        </is>
-      </c>
-      <c r="B28" s="70" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C28" s="65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="67">
-        <f>B28*C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="57" t="inlineStr">
-        <is>
-          <t>księgowość, sprawozdanie finansowe i sprawozdanie dla ministra nadzorującego</t>
-        </is>
-      </c>
+      <c r="A28" s="64" t="n"/>
+      <c r="B28" s="70" t="n"/>
+      <c r="C28" s="65" t="n"/>
+      <c r="D28" s="67" t="n"/>
+      <c r="E28" s="57" t="n"/>
       <c r="F28" s="47" t="n"/>
-      <c r="G28" s="68" t="n">
-        <v>2027</v>
-      </c>
+      <c r="G28" s="68" t="n"/>
       <c r="H28" s="47" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="45">
-      <c r="A29" s="64" t="inlineStr">
-        <is>
-          <t>Narzędzia AI i licencje oprogramowania (rok)</t>
-        </is>
-      </c>
-      <c r="B29" s="70" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C29" s="65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="67">
-        <f>B29*C29</f>
-        <v/>
-      </c>
-      <c r="E29" s="57" t="inlineStr">
-        <is>
-          <t>Dostęp do narzędzi AI, bez których 1469 godzin pracy organizatora nie jest wykonalne; rzędu 2,5 tys. zł miesięcznie</t>
-        </is>
-      </c>
+      <c r="A29" s="64" t="n"/>
+      <c r="B29" s="70" t="n"/>
+      <c r="C29" s="65" t="n"/>
+      <c r="D29" s="67" t="n"/>
+      <c r="E29" s="57" t="n"/>
       <c r="F29" s="47" t="n"/>
-      <c r="G29" s="68" t="n">
-        <v>2027</v>
-      </c>
+      <c r="G29" s="68" t="n"/>
       <c r="H29" s="47" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="45">
-      <c r="A30" s="72" t="inlineStr">
-        <is>
-          <t>Rejestracja znaku towarowego Konstela w EUIPO</t>
-        </is>
-      </c>
-      <c r="B30" s="60" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C30" s="73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="52">
-        <f>B30*C30</f>
-        <v/>
-      </c>
-      <c r="F30" s="72" t="inlineStr">
-        <is>
-          <t>jedna klasa, ochrona w całej Unii; opłaty urzędowe około 850 euro</t>
-        </is>
-      </c>
-      <c r="G30" s="68" t="n">
-        <v>2027</v>
-      </c>
+      <c r="A30" s="72" t="n"/>
+      <c r="B30" s="60" t="n"/>
+      <c r="C30" s="73" t="n"/>
+      <c r="D30" s="52" t="n"/>
+      <c r="F30" s="72" t="n"/>
+      <c r="G30" s="68" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="45">
       <c r="A31" s="72" t="inlineStr">
@@ -3630,7 +3463,7 @@
       <c r="B38" s="47" t="n"/>
       <c r="C38" s="47" t="n"/>
       <c r="D38" s="52">
-        <f>(D36+D37)*Wyjaśnienia!$B$32</f>
+        <f>(D36+D37)*Wyjaśnienia!$B$33</f>
         <v/>
       </c>
       <c r="E38" s="47" t="n"/>
@@ -3662,7 +3495,7 @@
       <c r="B40" s="47" t="n"/>
       <c r="C40" s="47" t="n"/>
       <c r="D40" s="52">
-        <f>D39*Wyjaśnienia!$B$34</f>
+        <f>D39*Wyjaśnienia!$B$35</f>
         <v/>
       </c>
       <c r="E40" s="47" t="n"/>
@@ -3767,6 +3600,460 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" style="45" min="1" max="1"/>
+    <col width="16" customWidth="1" style="45" min="2" max="2"/>
+    <col width="14" customWidth="1" style="45" min="3" max="3"/>
+    <col width="14" customWidth="1" style="45" min="4" max="4"/>
+    <col width="70" customWidth="1" style="45" min="5" max="5"/>
+    <col width="30" customWidth="1" style="45" min="6" max="6"/>
+    <col width="11" customWidth="1" style="45" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Budżet Uruchomienia - fundacja, znak towarowy, strona i narzędzia</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Finansuje: Mecenas Założycielski. Kwoty netto, chyba że napisano inaczej.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Pozycje wspólne całego przedsięwzięcia, wydzielone z Budżetu Antologii 30.10.2026. Służą czterem plebiscytom, akademii, gali i wystawie, a powstają raz i działają w kolejnych edycjach. Wydzielenie bierze się stąd, że obciążanie nimi jednego partnera czyniło jego ofertę nie do obrony.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PRACA ORGANIZATORA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pozycja</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Godziny</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Razem godzin</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Kwota</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Skraper i kopia archiwalna zgłoszenia</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>D7*Wyjaśnienia!$B$17</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>D10*Wyjaśnienia!$B$17</f>
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Narzędzie do oceny formalnej</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <f>B8</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>D8*Wyjaśnienia!$B$17</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>D11*Wyjaśnienia!$B$17</f>
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Panel oceny dla Akademii i jury</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>160</v>
+      </c>
+      <c r="D9">
+        <f>B9</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>D9*Wyjaśnienia!$B$17</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>D12*Wyjaśnienia!$B$17</f>
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Razem praca</t>
+        </is>
+      </c>
+      <c r="D10">
+        <f>SUM(D7:D9)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>SUM(E7:E9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KOSZTY TWARDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Pozycja</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cena jednostkowa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ilość</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Kwota</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Uwagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Powołanie fundacji-organizatora</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <f>B14*C14</f>
+        <v/>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>notariusz, statut, wpis do KRS, fundusz założycielski</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Konsultacja prawna przed otwarciem naboru</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <f>B15*C15</f>
+        <v/>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sześć obszarów, w tym licencja i archiwum; obowiązkowa przed naborem</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Domeny, poczta, hosting, magazyn kopii archiwalnych</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <f>B16*C16</f>
+        <v/>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>magazyn obiektowy w UE z kopią zapasową, retencja min. 5 lat, PDF/HTML/zrzuty/EPUB; w tym skrzynka pocztowa w domenie wraz z aliasami (kontakt@, imienny) - rzędu 150-450 zł rocznie, aliasy bez dopłaty; przejście na własną skrzynkę przenosi MX i wyłącza Cloudflare Email Routing</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Przebudowa strony: UI/UX i teksty (agencja)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <f>B17*C17</f>
+        <v/>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>projekt i wdrożenie strony Nagrody wraz z copywritingiem</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Obsługa fundacji za pierwszy rok</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <f>B18*C18</f>
+        <v/>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>księgowość, sprawozdanie finansowe i sprawozdanie dla ministra nadzorującego</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Narzędzia AI i licencje oprogramowania (rok)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <f>B19*C19</f>
+        <v/>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Dostęp do narzędzi AI, bez których 1469 godzin pracy organizatora nie jest wykonalne; rzędu 2,5 tys. zł miesięcznie</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Rejestracja znaku towarowego Konstela w EUIPO</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Razem koszty twarde</t>
+        </is>
+      </c>
+      <c r="D21">
+        <f>SUM(D14:D20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PODSUMOWANIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Praca organizatora</t>
+        </is>
+      </c>
+      <c r="D24">
+        <f>E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Koszty twarde</t>
+        </is>
+      </c>
+      <c r="D25">
+        <f>D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wynagrodzenie wykonawcy i rezerwa (od pracy i kosztów)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <f>(D24+D25)*Wyjaśnienia!$B$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RAZEM NETTO</t>
+        </is>
+      </c>
+      <c r="D27">
+        <f>SUM(D24:D26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D28">
+        <f>D27*Wyjaśnienia!$B$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DO ZAPŁATY BRUTTO - ta liczba trafia na fakturę</t>
+        </is>
+      </c>
+      <c r="D29">
+        <f>D27+D28</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -3875,11 +4162,11 @@
         <v>10</v>
       </c>
       <c r="D7" s="66">
-        <f>B7+C7*Wyjaśnienia!$B$23/60</f>
+        <f>B7+C7*Wyjaśnienia!$B$24/60</f>
         <v/>
       </c>
       <c r="E7" s="67">
-        <f>D7*Wyjaśnienia!$B$16</f>
+        <f>D7*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F7" s="57" t="inlineStr">
@@ -3903,11 +4190,11 @@
       </c>
       <c r="C8" s="66" t="n"/>
       <c r="D8" s="66">
-        <f>B8+C8*Wyjaśnienia!$B$23/60</f>
+        <f>B8+C8*Wyjaśnienia!$B$24/60</f>
         <v/>
       </c>
       <c r="E8" s="67">
-        <f>D8*Wyjaśnienia!$B$16</f>
+        <f>D8*Wyjaśnienia!$B$17</f>
         <v/>
       </c>
       <c r="F8" s="57" t="inlineStr">
@@ -3931,11 +4218,11 @@
       </c>
       <c r="C9" s="66" t="n"/>
       <c r="D9" s="66">
-        <f>B9+C9*Wyjaśnienia!$B$23/60</f>
+        <f>B9+C9*Wyjaśnienia!$B$24/60</f>
         <v/>
       </c>
       <c r="E9" s="67">
-        <f>D9*Wyjaśnienia!$B$16</f>
+        <f>D9*Wyjaśn